--- a/카드_아키타입/02_젤.xlsx
+++ b/카드_아키타입/02_젤.xlsx
@@ -481,7 +481,7 @@
       <row>27</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -1406,7 +1406,7 @@
       <row>128</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="49" name="Image 49" descr="Picture"/>

--- a/카드_아키타입/02_젤.xlsx
+++ b/카드_아키타입/02_젤.xlsx
@@ -203,7 +203,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -228,7 +228,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="933450"/>
@@ -253,7 +253,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="333375"/>
@@ -278,7 +278,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="438150"/>
@@ -303,7 +303,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>11</row>
+      <row>12</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -328,8 +328,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
-      <rowOff>1085850</rowOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -353,8 +353,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>11</row>
-      <rowOff>1085850</rowOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -378,8 +378,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>11</row>
-      <rowOff>1085850</rowOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -403,8 +403,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>11</row>
-      <rowOff>1085850</rowOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -428,8 +428,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>11</row>
-      <rowOff>1085850</rowOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -453,7 +453,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -478,7 +478,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>27</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="781050"/>
@@ -503,7 +503,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>27</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="495300"/>
@@ -528,7 +528,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>27</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -553,7 +553,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>27</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -578,8 +578,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>1085850</rowOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -603,7 +603,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -628,7 +628,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>44</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="857250"/>
@@ -653,7 +653,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>44</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="333375"/>
@@ -678,7 +678,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>44</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -703,7 +703,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>44</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -728,8 +728,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
-      <rowOff>1085850</rowOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -753,8 +753,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>44</row>
-      <rowOff>1085850</rowOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -778,8 +778,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>44</row>
-      <rowOff>1085850</rowOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -803,8 +803,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>44</row>
-      <rowOff>1085850</rowOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -828,7 +828,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>58</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -853,7 +853,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>58</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -878,7 +878,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>58</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -903,7 +903,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>58</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -928,7 +928,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>58</row>
+      <row>62</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -953,7 +953,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="781050" cy="1047750"/>
@@ -978,7 +978,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>72</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1003,7 +1003,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>72</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1028,7 +1028,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>72</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1053,7 +1053,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1078,7 +1078,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>86</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1103,7 +1103,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>86</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1128,7 +1128,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>86</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1153,7 +1153,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
@@ -1178,7 +1178,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>99</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="438150"/>
@@ -1203,7 +1203,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>99</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1228,7 +1228,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>99</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1253,7 +1253,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>99</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1278,7 +1278,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>113</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1303,7 +1303,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>113</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="438150"/>
@@ -1328,7 +1328,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>113</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1353,7 +1353,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>113</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1378,7 +1378,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>113</row>
+      <row>118</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1403,7 +1403,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>128</row>
+      <row>133</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="781050"/>
@@ -1428,7 +1428,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>128</row>
+      <row>133</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="819150"/>
@@ -1453,7 +1453,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>142</row>
+      <row>147</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="647700" cy="1047750"/>
@@ -1478,7 +1478,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>155</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -1503,7 +1503,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>155</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1528,7 +1528,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>155</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="285750"/>
@@ -1553,7 +1553,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>155</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="552450" cy="1047750"/>
@@ -1578,7 +1578,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>155</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
@@ -1603,8 +1603,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>155</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1628,8 +1628,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>155</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1653,8 +1653,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>155</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1678,8 +1678,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>155</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1703,8 +1703,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>155</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1728,8 +1728,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>155</row>
-      <rowOff>2171700</rowOff>
+      <row>162</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1753,8 +1753,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>155</row>
-      <rowOff>2171700</rowOff>
+      <row>162</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1778,8 +1778,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>155</row>
-      <rowOff>2171700</rowOff>
+      <row>162</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1803,8 +1803,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>155</row>
-      <rowOff>2171700</rowOff>
+      <row>162</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1828,8 +1828,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>155</row>
-      <rowOff>2171700</rowOff>
+      <row>162</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1853,8 +1853,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>155</row>
-      <rowOff>3257550</rowOff>
+      <row>163</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1878,8 +1878,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>155</row>
-      <rowOff>3257550</rowOff>
+      <row>163</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1903,8 +1903,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>155</row>
-      <rowOff>3257550</rowOff>
+      <row>163</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1928,8 +1928,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>155</row>
-      <rowOff>3257550</rowOff>
+      <row>163</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1953,7 +1953,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>171</row>
+      <row>179</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="647700" cy="1047750"/>
@@ -1978,7 +1978,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>189</row>
+      <row>198</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -2003,7 +2003,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>189</row>
+      <row>198</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2028,7 +2028,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>189</row>
+      <row>198</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2053,7 +2053,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>189</row>
+      <row>198</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2078,7 +2078,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>189</row>
+      <row>198</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2103,8 +2103,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>189</row>
-      <rowOff>1085850</rowOff>
+      <row>199</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2128,8 +2128,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>189</row>
-      <rowOff>1085850</rowOff>
+      <row>199</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2153,7 +2153,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>200</row>
+      <row>210</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -2178,7 +2178,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>200</row>
+      <row>210</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2203,7 +2203,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>200</row>
+      <row>210</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2228,7 +2228,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>200</row>
+      <row>210</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2253,7 +2253,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>200</row>
+      <row>210</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2278,8 +2278,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>200</row>
-      <rowOff>1085850</rowOff>
+      <row>211</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2303,8 +2303,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>200</row>
-      <rowOff>1085850</rowOff>
+      <row>211</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2328,8 +2328,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>200</row>
-      <rowOff>1085850</rowOff>
+      <row>211</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2353,8 +2353,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>200</row>
-      <rowOff>1085850</rowOff>
+      <row>211</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2378,8 +2378,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>200</row>
-      <rowOff>1085850</rowOff>
+      <row>211</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2403,7 +2403,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>218</row>
+      <row>230</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2428,7 +2428,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>218</row>
+      <row>230</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2453,7 +2453,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>218</row>
+      <row>230</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2478,7 +2478,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>218</row>
+      <row>230</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2791,7 +2791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2832,7 +2832,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
@@ -2854,7 +2854,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="64" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D4" s="4" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>레몬에센셜오일</t>
@@ -2926,7 +2926,7 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
     </row>
-    <row r="8" ht="600" customHeight="1">
+    <row r="8" ht="384" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>무제 문서
@@ -2952,8 +2952,14 @@
 미니 블랜더를 이용할 경우는 쉽게 고른 점도를 낼 수 있습니당.
 스프레이타입은 모든 재료를 넣고 뚜껑을 야무지게 닫은 후
 흔들어주시면 완성되었습니다.
-공기 정화 방향용으로 아무 곳이나 뿌릴 수 있어서 좋았습니다.
-알콜류의 세균력은....
+공기 정화 방향용으로 아무 곳이나 뿌릴 수 있어서 좋았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="336" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>알콜류의 세균력은....
 세균 막의 지질 복합체를 파괴하고 단백질을 변성ㆍ응고시켜 살균작용을 나타낸답니다.
 그런데 100% 에탄올은 단백질을 응고시키는 능력이 너무 탁월해
 세균 표면의 단백질을 한꺼번에 응고시켜버리기 때문에
@@ -2977,18 +2983,18 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="10" ht="14" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+    </row>
+    <row r="11" ht="96" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>1. 카보머프리젤을 계량해주세요. | 2. 식물성글리세린과 | 3. 에센셜오일을 비롯한 아로마베이스95까지 모든 재료를 계량해주세요.
 |
@@ -2998,216 +3004,217 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="171" customHeight="1"/>
-    <row r="13" ht="6" customHeight="1"/>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="85.5" customHeight="1"/>
+    <row r="14" ht="85.5" customHeight="1"/>
+    <row r="15" ht="6" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>허니 촉촉 바디젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>68g</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>수분, 자체 점증.</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>워터 코포아수</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>천연 레시틴으로 코포아수 버터를 리포좀화.</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>워터 아르간</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>세라마이드 (수용성)</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>세라마이드 리포좀화</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>스쿠알란, / 보르피린</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>꿀 추출물</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>원하는 / 추출물</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>균번식 억제제</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (알로에베라겔의 양을 67g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>스윗 오렌지에센셜오일</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>오렌지 껍질 오일</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>네롤리에센셜오일</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>3방울</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>오렌지꽃오일, / 민감, 모든 피부</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="25" ht="14" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="90" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26" ht="96" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>클레오파트라, 네로의 아내 포파이아 등 전설적인 미인들이 꿀과
 우유로 목욕을 했다는 것은 이미 알려진 사실인데요 그만큼 꿀은 거친
@@ -3217,265 +3224,271 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+    </row>
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>1. 모든 재료를 계량한 후
 2. 골고루 섞어주세요.
 3. 용기에 넣으면 완성.</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>— 이미지 —</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="171" customHeight="1">
-      <c r="A28" s="10" t="n"/>
       <c r="B28" s="10" t="n"/>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="10" t="n"/>
     </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>— 이미지 —</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="85.5" customHeight="1">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="85.5" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>트러블 SSG~필링젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>내추럴 / 셀룰로오즈</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>프랑스산 목화 섬유질로 / 만든 천연 필링제.</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="D35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>티트리워터</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>37g</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>티트리 수증기 / 증류법으로 추출</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>로즈마리, / 편백워터</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. / 남은 재료 활용 팁 : 젤타입스킨으로 사용가능, / 헤어에센스로 사용가능.</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>카보폴프리젤</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>알란토인분말</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>진정, 계량스푼 작은 쪽 깎아서 4개면 0.2g</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>마치현추출물</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>쇠비름, 진정, / 트러블 관리</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>어성초, / 병풀 추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>3.8g</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="45" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (티트리워터의 양을 36g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>레몬EO</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>레몬껍질오일,상큼, 아로마테라피</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>무향 또는 / 원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-    </row>
-    <row r="41" ht="210" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+    </row>
+    <row r="44" ht="224" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>누구에게나 '때'는 있습니다.
 이 '때'관리만 잘 해줘도
@@ -3494,18 +3507,18 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-    </row>
-    <row r="43" ht="90" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+    </row>
+    <row r="46" ht="96" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>1. 알란토인분말 0.2g은 계량스푼 작은 쪽에 깍아서 4개로 해주세요.
 2. 비커에 넣고 내추럴 셀룰로오즈을 비롯 모든 재료를
@@ -3516,168 +3529,169 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-    </row>
-    <row r="45" ht="171" customHeight="1"/>
-    <row r="46" ht="6" customHeight="1"/>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+    </row>
+    <row r="48" ht="85.5" customHeight="1"/>
+    <row r="49" ht="85.5" customHeight="1"/>
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>이데베논 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>로즈 플라워젤</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 젤타입으로. / 에코보습제, 알란토인 함유</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔, / 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>이데베논</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>코엔자임의 10배, / 항산화효과 / 레시피 처방시 500ppm 함유크림 완성.</t>
         </is>
       </c>
-      <c r="D50" s="8" t="n"/>
-    </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="D54" s="8" t="n"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>비타민 펩타이드, 화이트닝</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>4GF, / 씨네이크펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (로즈플라워 겔의 양을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>다중히아루론산</t>
         </is>
       </c>
-      <c r="B53" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>0~5g</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>고분자, 중분자, 저분자로 이루어짐. / 피부 각층별 수분공급</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>판테놀</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-    </row>
-    <row r="55" ht="105" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+    </row>
+    <row r="59" ht="112" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>황금톡스라 불리는 ,이데베논.
 코엔자임Q10의 10배 항산화효과를 가지고 있습니다.
@@ -3688,22 +3702,22 @@
 또 급이 다른 이데베논의 항산화효과로 시간을 되돌리세요.</t>
         </is>
       </c>
-      <c r="B55" s="10" t="n"/>
-      <c r="C55" s="10" t="n"/>
-      <c r="D55" s="10" t="n"/>
-    </row>
-    <row r="56" ht="14" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-    </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n"/>
+      <c r="D60" s="6" t="n"/>
+    </row>
+    <row r="61" ht="64" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>만들기 과정
 1.로즈플라워겔을 계량하고
@@ -3711,181 +3725,181 @@
 3.고른 점도가 나오면 용기에 담아주세요.</t>
         </is>
       </c>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+    </row>
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6" t="n"/>
-    </row>
-    <row r="59" ht="85.5" customHeight="1">
-      <c r="A59" s="10" t="n"/>
-      <c r="B59" s="10" t="n"/>
-      <c r="C59" s="10" t="n"/>
-      <c r="D59" s="10" t="n"/>
-    </row>
-    <row r="60" ht="6" customHeight="1"/>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="1" t="inlineStr">
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+    </row>
+    <row r="63" ht="85.5" customHeight="1">
+      <c r="A63" s="10" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+    </row>
+    <row r="64" ht="6" customHeight="1"/>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t>TX 멜라 토닝 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="67" ht="48" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>로즈 플라워겔</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 듬뿍 담은젤, / 에코보습제, 알란토인 함유</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>알로에베라겔, / 네롤리플라워젤</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="68" ht="48" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>트라넥삼산 / (펩타이드)</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 / 펩타이드 말단에 합성으로 / 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>화이트 펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="69" ht="48" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>4GF</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>EGF, FGF, IGF, TGF / 복합 펩타이드</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>아세틸헥사, / 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="70" ht="48" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>균번식 억제, 식물복합</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>1.2헥산디올2g / (로즈플라워겔을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>브라이트닝 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>네롤리, 일랑일랑, 버가못FCF, / 프랑킨센스 EO 블렌딩오일, 생략 가능</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="14" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6" t="n"/>
-    </row>
-    <row r="69" ht="375" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+    </row>
+    <row r="73" ht="384" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>트레넥삼산(Tranexamic acid, TX)은 원래 지혈제로 사용되고 있습니다.
 산후 , 외상, 월경, 코피 등 과다 출혈에 사용되는 항플라즈민제로 의약 성분입니다.
@@ -3910,23 +3924,29 @@
 로즈 플라워겔을 배합해
 초간단 수면팩을 만들어보세요.
 당신이 잠든 사이
-피부가 맑아지고 밝아지는데
-도움을 줍니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="14" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
+피부가 맑아지고 밝아지는데</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
+        <is>
+          <t>도움을 줍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="6" t="n"/>
-      <c r="D70" s="6" t="n"/>
-    </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+    </row>
+    <row r="76" ht="64" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량하고
@@ -3935,172 +3955,172 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="6" t="n"/>
-    </row>
-    <row r="73" ht="85.5" customHeight="1"/>
-    <row r="74" ht="6" customHeight="1"/>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="B77" s="6" t="n"/>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n"/>
+    </row>
+    <row r="78" ht="85.5" customHeight="1"/>
+    <row r="79" ht="6" customHeight="1"/>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="1" t="inlineStr">
         <is>
           <t>콜라겐 드림 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B75" s="2" t="n"/>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>워터 호호바</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>호호바오일에 천연레시틴을 / 이용하여 리포좀화, / 수상에 쉽게 분산</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>슈퍼 곡물 / 단백질추출물</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="45" customHeight="1">
-      <c r="A78" s="8" t="inlineStr">
+    <row r="83" ht="48" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>콜라겐 펩타이드</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>인체 흡수가 용이한 / 저분자화 순수 단백질 사용, / 18종의 아미노산으로 구성</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>아카시아, / 마린콜라겐</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>비타민 펩타이드, 화이트닝</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>트라넥 / 삼산펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>85g</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>네롤리플라워겔, / 알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="45" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
+    <row r="86" ht="48" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>1,2 헥산디올</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>보습제, 자유수 억제, 균번식억제</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="14" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="6" t="n"/>
-      <c r="D82" s="6" t="n"/>
-    </row>
-    <row r="83" ht="105" customHeight="1">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+    </row>
+    <row r="88" ht="112" customHeight="1">
+      <c r="A88" s="9" t="inlineStr">
         <is>
           <t>25세 이후 콜라겐 합성이 줄어들므로
 피부가 탄력을 잃고 주름이 생기기 시작하며 활기를 잃게 됩니다.
@@ -4111,22 +4131,22 @@
 보습은 물론 탄력관리에 좋고 생기있는 피부를 가꿔줍니다.</t>
         </is>
       </c>
-      <c r="B83" s="10" t="n"/>
-      <c r="C83" s="10" t="n"/>
-      <c r="D83" s="10" t="n"/>
-    </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="10" t="n"/>
+    </row>
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="6" t="n"/>
-      <c r="D84" s="6" t="n"/>
-    </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+    </row>
+    <row r="90" ht="64" customHeight="1">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량합니다.
@@ -4134,155 +4154,155 @@
 3. 점도가 고르게 되면 용기에 옮겨 담으면 완성.</t>
         </is>
       </c>
-      <c r="B85" s="10" t="n"/>
-      <c r="C85" s="10" t="n"/>
-      <c r="D85" s="10" t="n"/>
-    </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="10" t="n"/>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="6" t="n"/>
-      <c r="D86" s="6" t="n"/>
-    </row>
-    <row r="87" ht="85.5" customHeight="1">
-      <c r="A87" s="10" t="n"/>
-      <c r="B87" s="10" t="n"/>
-      <c r="C87" s="10" t="n"/>
-      <c r="D87" s="10" t="n"/>
-    </row>
-    <row r="88" ht="6" customHeight="1"/>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n"/>
+    </row>
+    <row r="92" ht="85.5" customHeight="1">
+      <c r="A92" s="10" t="n"/>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="10" t="n"/>
+    </row>
+    <row r="93" ht="6" customHeight="1"/>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="1" t="inlineStr">
         <is>
           <t>셀프백신 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n"/>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n"/>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="4" t="inlineStr">
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="4" t="inlineStr">
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B92" s="4" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C92" s="4" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 / 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="D92" s="4" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+      <c r="D97" s="4" t="n"/>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D98" s="4" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="45" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
+    <row r="99" ht="48" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>니아울리에센셜오일</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B99" s="4" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C99" s="4" t="inlineStr">
         <is>
           <t>광엽 티트리라 불림. 향과 성분이 / 유칼립투스와 티트리의 부드러운 버전</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>유칼립튜스, 티트리 등</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="14" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B95" s="6" t="n"/>
-      <c r="C95" s="6" t="n"/>
-      <c r="D95" s="6" t="n"/>
-    </row>
-    <row r="96" ht="300" customHeight="1">
-      <c r="A96" s="7" t="inlineStr">
+      <c r="B100" s="6" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="n"/>
+    </row>
+    <row r="101" ht="320" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>무제 문서
 코로나19 예방을 위해 전문가들이
@@ -4307,18 +4327,18 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
-    </row>
-    <row r="98" ht="75" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
+      <c r="B102" s="6" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="6" t="n"/>
+    </row>
+    <row r="103" ht="80" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -4328,168 +4348,168 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="14" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-    </row>
-    <row r="100" ht="85.5" customHeight="1"/>
-    <row r="101" ht="6" customHeight="1"/>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="1" t="inlineStr">
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+    </row>
+    <row r="105" ht="85.5" customHeight="1"/>
+    <row r="106" ht="6" customHeight="1"/>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="1" t="inlineStr">
         <is>
           <t>상큼 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n"/>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="8" t="inlineStr">
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B104" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="D104" s="8" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="8" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B110" s="8" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C110" s="8" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 / 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="D105" s="8" t="n"/>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="D110" s="8" t="n"/>
+    </row>
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="8" t="inlineStr">
         <is>
           <t>알란토인(액상)</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C111" s="8" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="D106" s="8" t="inlineStr">
+      <c r="D111" s="8" t="inlineStr">
         <is>
           <t>프로폴리스추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+    <row r="112" ht="16" customHeight="1">
+      <c r="A112" s="8" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B112" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C112" s="8" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D112" s="8" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="45" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
+    <row r="113" ht="48" customHeight="1">
+      <c r="A113" s="8" t="inlineStr">
         <is>
           <t>레몬쥬스EO</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>20~25방울</t>
         </is>
       </c>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C113" s="8" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드에센셜오일 / 블랜딩오일</t>
         </is>
       </c>
-      <c r="D108" s="8" t="inlineStr">
+      <c r="D113" s="8" t="inlineStr">
         <is>
           <t>레몬, 만다린, 그레이프푸룻, 라임, 오렌지에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="14" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B109" s="6" t="n"/>
-      <c r="C109" s="6" t="n"/>
-      <c r="D109" s="6" t="n"/>
-    </row>
-    <row r="110" ht="195" customHeight="1">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="B114" s="6" t="n"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="6" t="n"/>
+    </row>
+    <row r="115" ht="208" customHeight="1">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>무제 문서
 그 어느 때보다 손 청결이 중요한 때입니다.
@@ -4506,22 +4526,22 @@
 '상큼 손소독제 만들기'를 안내해드립니다.</t>
         </is>
       </c>
-      <c r="B110" s="10" t="n"/>
-      <c r="C110" s="10" t="n"/>
-      <c r="D110" s="10" t="n"/>
-    </row>
-    <row r="111" ht="14" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
+      <c r="B115" s="10" t="n"/>
+      <c r="C115" s="10" t="n"/>
+      <c r="D115" s="10" t="n"/>
+    </row>
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B111" s="6" t="n"/>
-      <c r="C111" s="6" t="n"/>
-      <c r="D111" s="6" t="n"/>
-    </row>
-    <row r="112" ht="75" customHeight="1">
-      <c r="A112" s="9" t="inlineStr">
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="6" t="n"/>
+    </row>
+    <row r="117" ht="80" customHeight="1">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -4530,221 +4550,221 @@
 언제나 어디서나 사용하세요.</t>
         </is>
       </c>
-      <c r="B112" s="10" t="n"/>
-      <c r="C112" s="10" t="n"/>
-      <c r="D112" s="10" t="n"/>
-    </row>
-    <row r="113" ht="14" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="B117" s="10" t="n"/>
+      <c r="C117" s="10" t="n"/>
+      <c r="D117" s="10" t="n"/>
+    </row>
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B113" s="6" t="n"/>
-      <c r="C113" s="6" t="n"/>
-      <c r="D113" s="6" t="n"/>
-    </row>
-    <row r="114" ht="85.5" customHeight="1">
-      <c r="A114" s="10" t="n"/>
-      <c r="B114" s="10" t="n"/>
-      <c r="C114" s="10" t="n"/>
-      <c r="D114" s="10" t="n"/>
-    </row>
-    <row r="115" ht="6" customHeight="1"/>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="1" t="inlineStr">
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="6" t="n"/>
+    </row>
+    <row r="119" ht="85.5" customHeight="1">
+      <c r="A119" s="10" t="n"/>
+      <c r="B119" s="10" t="n"/>
+      <c r="C119" s="10" t="n"/>
+      <c r="D119" s="10" t="n"/>
+    </row>
+    <row r="120" ht="6" customHeight="1"/>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="1" t="inlineStr">
         <is>
           <t>트러블 잠잠 스팟젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B116" s="2" t="n"/>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n"/>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="4" t="inlineStr">
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B123" s="4" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C123" s="4" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="D123" s="4" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="30" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B124" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C124" s="4" t="inlineStr">
         <is>
           <t>가용화제. / 물과요일이 분리되지않도록 하는 역할</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D124" s="4" t="inlineStr">
         <is>
           <t>솔루벌라이저</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>라벤더워터</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C125" s="4" t="inlineStr">
         <is>
           <t>진정,재생</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D125" s="4" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="30" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
+    <row r="126" ht="32" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B126" s="4" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C126" s="4" t="inlineStr">
         <is>
           <t>겔타입, 수분공급</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D126" s="4" t="inlineStr">
         <is>
           <t>로즈플라워겔, / 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
+    <row r="127" ht="16" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>항균,진정</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="D127" s="4" t="inlineStr">
         <is>
           <t>카렌듈라추출물</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t>한방보존제</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C128" s="4" t="inlineStr">
         <is>
           <t>복합한방추출물, 균번식억제</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="D128" s="4" t="inlineStr">
         <is>
           <t>수용성보존제</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="14" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
+    <row r="129" ht="14" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B124" s="6" t="n"/>
-      <c r="C124" s="6" t="n"/>
-      <c r="D124" s="6" t="n"/>
-    </row>
-    <row r="125" ht="60" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
+      <c r="B129" s="6" t="n"/>
+      <c r="C129" s="6" t="n"/>
+      <c r="D129" s="6" t="n"/>
+    </row>
+    <row r="130" ht="64" customHeight="1">
+      <c r="A130" s="7" t="inlineStr">
         <is>
           <t>[ 사용법 ]
 티트리에센셜오일은 국소부위에 원액을 발라도 되는 에센셜오일입니다. 스팟젤은 티트리에센셜오일을 전체의 2%를 정도로 희석한 순한 젤타입에센스입니다. 소량을 여드름이 난 부분에 발라주세요.</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B126" s="6" t="n"/>
-      <c r="C126" s="6" t="n"/>
-      <c r="D126" s="6" t="n"/>
-    </row>
-    <row r="127" ht="105" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
+      <c r="B131" s="6" t="n"/>
+      <c r="C131" s="6" t="n"/>
+      <c r="D131" s="6" t="n"/>
+    </row>
+    <row r="132" ht="112" customHeight="1">
+      <c r="A132" s="7" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 티트리, 올리브리퀴드를 계량합니다.
@@ -4756,172 +4776,172 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B128" s="6" t="n"/>
-      <c r="C128" s="6" t="n"/>
-      <c r="D128" s="6" t="n"/>
-    </row>
-    <row r="129" ht="85.5" customHeight="1"/>
-    <row r="130" ht="6" customHeight="1"/>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="1" t="inlineStr">
+      <c r="B133" s="6" t="n"/>
+      <c r="C133" s="6" t="n"/>
+      <c r="D133" s="6" t="n"/>
+    </row>
+    <row r="134" ht="85.5" customHeight="1"/>
+    <row r="135" ht="6" customHeight="1"/>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="1" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 바디팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B131" s="2" t="n"/>
-      <c r="C131" s="2" t="n"/>
-      <c r="D131" s="2" t="n"/>
-    </row>
-    <row r="132" ht="15" customHeight="1">
-      <c r="A132" s="3" t="inlineStr">
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n"/>
+    </row>
+    <row r="137" ht="15" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="8" t="inlineStr">
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>그린 클레이</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>54.35%</t>
         </is>
       </c>
-      <c r="C133" s="8" t="inlineStr">
+      <c r="C138" s="8" t="inlineStr">
         <is>
           <t>녹색 점토, 피지·노폐물 흡착</t>
         </is>
       </c>
-      <c r="D133" s="8" t="inlineStr">
+      <c r="D138" s="8" t="inlineStr">
         <is>
           <t>핑크클레이, 카올린</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="45" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+    <row r="139" ht="48" customHeight="1">
+      <c r="A139" s="8" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>43.48%</t>
         </is>
       </c>
-      <c r="C134" s="8" t="inlineStr">
+      <c r="C139" s="8" t="inlineStr">
         <is>
           <t>순수한 물 , / 완성품의 색을 고르게.</t>
         </is>
       </c>
-      <c r="D134" s="8" t="inlineStr">
+      <c r="D139" s="8" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+    <row r="140" ht="32" customHeight="1">
+      <c r="A140" s="8" t="inlineStr">
         <is>
           <t>그레이프프룻EO</t>
         </is>
       </c>
-      <c r="B135" s="8" t="inlineStr">
+      <c r="B140" s="8" t="inlineStr">
         <is>
           <t>1.09%</t>
         </is>
       </c>
-      <c r="C135" s="8" t="inlineStr">
+      <c r="C140" s="8" t="inlineStr">
         <is>
           <t>자몽 에센셜오일, 상쾌·수렴</t>
         </is>
       </c>
-      <c r="D135" s="8" t="inlineStr">
+      <c r="D140" s="8" t="inlineStr">
         <is>
           <t>오렌지, 레몬에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="60" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
+    <row r="141" ht="64" customHeight="1">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C136" s="8" t="inlineStr">
+      <c r="C141" s="8" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="D136" s="8" t="inlineStr">
+      <c r="D141" s="8" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="30" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+    <row r="142" ht="32" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>싸이프러스</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B142" s="8" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C137" s="8" t="inlineStr">
+      <c r="C142" s="8" t="inlineStr">
         <is>
           <t>상록 침엽수로 / 스팀 증류법 추출, 숲향</t>
         </is>
       </c>
-      <c r="D137" s="8" t="inlineStr">
+      <c r="D142" s="8" t="inlineStr">
         <is>
           <t>편백</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="14" customHeight="1">
-      <c r="A138" s="5" t="inlineStr">
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B138" s="6" t="n"/>
-      <c r="C138" s="6" t="n"/>
-      <c r="D138" s="6" t="n"/>
-    </row>
-    <row r="139" ht="195" customHeight="1">
-      <c r="A139" s="9" t="inlineStr">
+      <c r="B143" s="6" t="n"/>
+      <c r="C143" s="6" t="n"/>
+      <c r="D143" s="6" t="n"/>
+    </row>
+    <row r="144" ht="208" customHeight="1">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>그린클레이 - 프랑스 아질레지방에서 채취하는 클레이(흙). 미세한 클레이가 피부 깊숙이 침투 모공속 노폐물 배출, 흡착, 풍부한 미네랄 성분 해독 효과를 줍니다. 셀룰라이트관리, 여드름지성 피부에 사용.
 그레이프프룻(자몽껍질오일), 제라늄, 싸이프러스, 쥬니퍼베리, 레몬, 펜넬에센셜오일이 다이어트에 효과적인 오일이다. 림프자극, 독소배출, 호르몬균형, 해독 등의 효과를 준다.
@@ -4932,181 +4952,181 @@
 4. 이런 오일로 비누, 마사지오일, 젤, 로션/크림류 제품을 만들어 병행하면 좋다.</t>
         </is>
       </c>
-      <c r="B139" s="10" t="n"/>
-      <c r="C139" s="10" t="n"/>
-      <c r="D139" s="10" t="n"/>
-    </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="A140" s="5" t="inlineStr">
+      <c r="B144" s="10" t="n"/>
+      <c r="C144" s="10" t="n"/>
+      <c r="D144" s="10" t="n"/>
+    </row>
+    <row r="145" ht="14" customHeight="1">
+      <c r="A145" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B140" s="6" t="n"/>
-      <c r="C140" s="6" t="n"/>
-      <c r="D140" s="6" t="n"/>
-    </row>
-    <row r="141" ht="45" customHeight="1">
-      <c r="A141" s="9" t="inlineStr">
+      <c r="B145" s="6" t="n"/>
+      <c r="C145" s="6" t="n"/>
+      <c r="D145" s="6" t="n"/>
+    </row>
+    <row r="146" ht="48" customHeight="1">
+      <c r="A146" s="9" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 그린클레이, 물, 에센셜오일을 다 넣고
 2. 잘 섞어줍니다.</t>
         </is>
       </c>
-      <c r="B141" s="10" t="n"/>
-      <c r="C141" s="10" t="n"/>
-      <c r="D141" s="10" t="n"/>
-    </row>
-    <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="B146" s="10" t="n"/>
+      <c r="C146" s="10" t="n"/>
+      <c r="D146" s="10" t="n"/>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B142" s="6" t="n"/>
-      <c r="C142" s="6" t="n"/>
-      <c r="D142" s="6" t="n"/>
-    </row>
-    <row r="143" ht="85.5" customHeight="1">
-      <c r="A143" s="10" t="n"/>
-      <c r="B143" s="10" t="n"/>
-      <c r="C143" s="10" t="n"/>
-      <c r="D143" s="10" t="n"/>
-    </row>
-    <row r="144" ht="6" customHeight="1"/>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="1" t="inlineStr">
+      <c r="B147" s="6" t="n"/>
+      <c r="C147" s="6" t="n"/>
+      <c r="D147" s="6" t="n"/>
+    </row>
+    <row r="148" ht="85.5" customHeight="1">
+      <c r="A148" s="10" t="n"/>
+      <c r="B148" s="10" t="n"/>
+      <c r="C148" s="10" t="n"/>
+      <c r="D148" s="10" t="n"/>
+    </row>
+    <row r="149" ht="6" customHeight="1"/>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="1" t="inlineStr">
         <is>
           <t>레몬 손소독제(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B145" s="2" t="n"/>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n"/>
-    </row>
-    <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="3" t="inlineStr">
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n"/>
+    </row>
+    <row r="151" ht="15" customHeight="1">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B146" s="3" t="inlineStr">
+      <c r="B151" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="45" customHeight="1">
-      <c r="A147" s="4" t="inlineStr">
+    <row r="152" ht="48" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>28g</t>
         </is>
       </c>
-      <c r="C147" s="4" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>5중 필터링 정제된 물.</t>
         </is>
       </c>
-      <c r="D147" s="4" t="inlineStr">
+      <c r="D152" s="4" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="30" customHeight="1">
-      <c r="A148" s="4" t="inlineStr">
+    <row r="153" ht="32" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C148" s="4" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr">
         <is>
           <t>보습제, 향이 오랫동안 머물 수 / 있도록 고착제 역할을 함.</t>
         </is>
       </c>
-      <c r="D148" s="4" t="inlineStr">
+      <c r="D153" s="4" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="30" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
+    <row r="154" ht="32" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C154" s="4" t="inlineStr">
         <is>
           <t>에센셜오일 분산, 방향용으로 사용시 / 공기정화, 소독효과</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="D154" s="4" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="30" customHeight="1">
-      <c r="A150" s="4" t="inlineStr">
+    <row r="155" ht="32" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B150" s="4" t="inlineStr">
+      <c r="B155" s="4" t="inlineStr">
         <is>
           <t>15~20방울</t>
         </is>
       </c>
-      <c r="C150" s="4" t="inlineStr">
+      <c r="C155" s="4" t="inlineStr">
         <is>
           <t>레몬껍질에서 추출한 100%천연오일. / 상큼한 향.</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr">
+      <c r="D155" s="4" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 편백 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="14" customHeight="1">
-      <c r="A151" s="5" t="inlineStr">
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B151" s="6" t="n"/>
-      <c r="C151" s="6" t="n"/>
-      <c r="D151" s="6" t="n"/>
-    </row>
-    <row r="152" ht="285" customHeight="1">
-      <c r="A152" s="7" t="inlineStr">
+      <c r="B156" s="6" t="n"/>
+      <c r="C156" s="6" t="n"/>
+      <c r="D156" s="6" t="n"/>
+    </row>
+    <row r="157" ht="304" customHeight="1">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t>2009년 젤타입 손소독제 만들기를 위해
 하이셀을 이용해 만든 젤타입 손소독제입니다.
@@ -5130,18 +5150,18 @@
         </is>
       </c>
     </row>
-    <row r="153" ht="14" customHeight="1">
-      <c r="A153" s="5" t="inlineStr">
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B153" s="6" t="n"/>
-      <c r="C153" s="6" t="n"/>
-      <c r="D153" s="6" t="n"/>
-    </row>
-    <row r="154" ht="285" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
+      <c r="B158" s="6" t="n"/>
+      <c r="C158" s="6" t="n"/>
+      <c r="D158" s="6" t="n"/>
+    </row>
+    <row r="159" ht="304" customHeight="1">
+      <c r="A159" s="7" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 [하이셀 계량하기]
@@ -5164,212 +5184,215 @@
         </is>
       </c>
     </row>
-    <row r="155" ht="14" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B155" s="6" t="n"/>
-      <c r="C155" s="6" t="n"/>
-      <c r="D155" s="6" t="n"/>
-    </row>
-    <row r="156" ht="342" customHeight="1"/>
-    <row r="157" ht="6" customHeight="1"/>
-    <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="1" t="inlineStr">
+      <c r="B160" s="6" t="n"/>
+      <c r="C160" s="6" t="n"/>
+      <c r="D160" s="6" t="n"/>
+    </row>
+    <row r="161" ht="85.5" customHeight="1"/>
+    <row r="162" ht="85.5" customHeight="1"/>
+    <row r="163" ht="85.5" customHeight="1"/>
+    <row r="164" ht="85.5" customHeight="1"/>
+    <row r="165" ht="6" customHeight="1"/>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="1" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B158" s="2" t="n"/>
-      <c r="C158" s="2" t="n"/>
-      <c r="D158" s="2" t="n"/>
-    </row>
-    <row r="159" ht="15" customHeight="1">
-      <c r="A159" s="3" t="inlineStr">
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n"/>
+    </row>
+    <row r="167" ht="15" customHeight="1">
+      <c r="A167" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B159" s="3" t="inlineStr">
+      <c r="B167" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C167" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="D167" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="45" customHeight="1">
-      <c r="A160" s="8" t="inlineStr">
+    <row r="168" ht="48" customHeight="1">
+      <c r="A168" s="8" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B160" s="8" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>92.17%</t>
         </is>
       </c>
-      <c r="C160" s="8" t="inlineStr">
+      <c r="C168" s="8" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="D160" s="8" t="inlineStr">
+      <c r="D168" s="8" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="8" t="inlineStr">
+    <row r="169" ht="16" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B161" s="8" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C161" s="8" t="inlineStr">
+      <c r="C169" s="8" t="inlineStr">
         <is>
           <t>점증제총량의 1%이하</t>
         </is>
       </c>
-      <c r="D161" s="8" t="n"/>
-    </row>
-    <row r="162" ht="60" customHeight="1">
-      <c r="A162" s="8" t="inlineStr">
+      <c r="D169" s="8" t="n"/>
+    </row>
+    <row r="170" ht="64" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B162" s="8" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>4.61%</t>
         </is>
       </c>
-      <c r="C162" s="8" t="inlineStr">
+      <c r="C170" s="8" t="inlineStr">
         <is>
           <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
-      <c r="D162" s="8" t="inlineStr">
+      <c r="D170" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="8" t="inlineStr">
+    <row r="171" ht="32" customHeight="1">
+      <c r="A171" s="8" t="inlineStr">
         <is>
           <t>그레이프프룻EO</t>
         </is>
       </c>
-      <c r="B163" s="8" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C163" s="8" t="inlineStr">
+      <c r="C171" s="8" t="inlineStr">
         <is>
           <t>자몽 에센셜오일, 상쾌·수렴</t>
         </is>
       </c>
-      <c r="D163" s="8" t="inlineStr">
+      <c r="D171" s="8" t="inlineStr">
         <is>
           <t>오렌지, 레몬에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="30" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
+    <row r="172" ht="32" customHeight="1">
+      <c r="A172" s="8" t="inlineStr">
         <is>
           <t>페퍼민트오일</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>0.23%</t>
         </is>
       </c>
-      <c r="C164" s="8" t="inlineStr">
+      <c r="C172" s="8" t="inlineStr">
         <is>
           <t>허브의 고농축오일, / 시원, 커피와 시너지효과</t>
         </is>
       </c>
-      <c r="D164" s="8" t="inlineStr">
+      <c r="D172" s="8" t="inlineStr">
         <is>
           <t>티트리(항균), / 스피아민트 등</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="8" t="inlineStr">
+    <row r="173" ht="16" customHeight="1">
+      <c r="A173" s="8" t="inlineStr">
         <is>
           <t>주니퍼베리EO</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>0.69%</t>
         </is>
       </c>
-      <c r="C165" s="8" t="inlineStr">
+      <c r="C173" s="8" t="inlineStr">
         <is>
           <t>주니퍼베리 에센셜오일, 수렴·정화</t>
         </is>
       </c>
-      <c r="D165" s="8" t="inlineStr">
+      <c r="D173" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="60" customHeight="1">
-      <c r="A166" s="8" t="inlineStr">
+    <row r="174" ht="64" customHeight="1">
+      <c r="A174" s="8" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>0.46%</t>
         </is>
       </c>
-      <c r="C166" s="8" t="inlineStr">
+      <c r="C174" s="8" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="D166" s="8" t="inlineStr">
+      <c r="D174" s="8" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="14" customHeight="1">
-      <c r="A167" s="5" t="inlineStr">
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B167" s="6" t="n"/>
-      <c r="C167" s="6" t="n"/>
-      <c r="D167" s="6" t="n"/>
-    </row>
-    <row r="168" ht="105" customHeight="1">
-      <c r="A168" s="9" t="inlineStr">
+      <c r="B175" s="6" t="n"/>
+      <c r="C175" s="6" t="n"/>
+      <c r="D175" s="6" t="n"/>
+    </row>
+    <row r="176" ht="112" customHeight="1">
+      <c r="A176" s="9" t="inlineStr">
         <is>
           <t>*끈적임없이 흡수되는 다이어트젤
 다이어트에 좋은 에센셜오일 6종: 그레이프프룻, 팬넬, 쥬니퍼베리, 싸이프러스, 레몬, 제라늄
@@ -5379,22 +5402,22 @@
 제라늄 - 호로몬 균형, 피지균형</t>
         </is>
       </c>
-      <c r="B168" s="10" t="n"/>
-      <c r="C168" s="10" t="n"/>
-      <c r="D168" s="10" t="n"/>
-    </row>
-    <row r="169" ht="14" customHeight="1">
-      <c r="A169" s="5" t="inlineStr">
+      <c r="B176" s="10" t="n"/>
+      <c r="C176" s="10" t="n"/>
+      <c r="D176" s="10" t="n"/>
+    </row>
+    <row r="177" ht="14" customHeight="1">
+      <c r="A177" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B169" s="6" t="n"/>
-      <c r="C169" s="6" t="n"/>
-      <c r="D169" s="6" t="n"/>
-    </row>
-    <row r="170" ht="90" customHeight="1">
-      <c r="A170" s="9" t="inlineStr">
+      <c r="B177" s="6" t="n"/>
+      <c r="C177" s="6" t="n"/>
+      <c r="D177" s="6" t="n"/>
+    </row>
+    <row r="178" ht="96" customHeight="1">
+      <c r="A178" s="9" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 로즈워터를 계량한다.
@@ -5404,265 +5427,265 @@
 6~7. 손으로 저어서 마무리해주면 끝!</t>
         </is>
       </c>
-      <c r="B170" s="10" t="n"/>
-      <c r="C170" s="10" t="n"/>
-      <c r="D170" s="10" t="n"/>
-    </row>
-    <row r="171" ht="14" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="B178" s="10" t="n"/>
+      <c r="C178" s="10" t="n"/>
+      <c r="D178" s="10" t="n"/>
+    </row>
+    <row r="179" ht="14" customHeight="1">
+      <c r="A179" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B171" s="6" t="n"/>
-      <c r="C171" s="6" t="n"/>
-      <c r="D171" s="6" t="n"/>
-    </row>
-    <row r="172" ht="85.5" customHeight="1">
-      <c r="A172" s="10" t="n"/>
-      <c r="B172" s="10" t="n"/>
-      <c r="C172" s="10" t="n"/>
-      <c r="D172" s="10" t="n"/>
-    </row>
-    <row r="173" ht="6" customHeight="1"/>
-    <row r="174" ht="22" customHeight="1">
-      <c r="A174" s="1" t="inlineStr">
+      <c r="B179" s="6" t="n"/>
+      <c r="C179" s="6" t="n"/>
+      <c r="D179" s="6" t="n"/>
+    </row>
+    <row r="180" ht="85.5" customHeight="1">
+      <c r="A180" s="10" t="n"/>
+      <c r="B180" s="10" t="n"/>
+      <c r="C180" s="10" t="n"/>
+      <c r="D180" s="10" t="n"/>
+    </row>
+    <row r="181" ht="6" customHeight="1"/>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="1" t="inlineStr">
         <is>
           <t>뱀독 볼륨 에센스(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B174" s="2" t="n"/>
-      <c r="C174" s="2" t="n"/>
-      <c r="D174" s="2" t="n"/>
-    </row>
-    <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="3" t="inlineStr">
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n"/>
+    </row>
+    <row r="183" ht="15" customHeight="1">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr">
+      <c r="B183" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C175" s="3" t="inlineStr">
+      <c r="C183" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D175" s="3" t="inlineStr">
+      <c r="D183" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="30" customHeight="1">
-      <c r="A176" s="4" t="inlineStr">
+    <row r="184" ht="32" customHeight="1">
+      <c r="A184" s="4" t="inlineStr">
         <is>
           <t>(제주산) / 비정제동백오일</t>
         </is>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B184" s="4" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C184" s="4" t="inlineStr">
         <is>
           <t>올레인산 풍부 고보습, / 청정 섬 국내 제주산 야생동백씨 압착.</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="D184" s="4" t="inlineStr">
         <is>
           <t>아르간, 로즈힙, 마카다미아넛오일 등</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="30" customHeight="1">
-      <c r="A177" s="4" t="inlineStr">
+    <row r="185" ht="32" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B185" s="4" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C185" s="4" t="inlineStr">
         <is>
           <t>가용화제, 물에 오일이 분산되도록 도와줌</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="D185" s="4" t="inlineStr">
         <is>
           <t>솔루벌라이저(Polysorbate 80)동량</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="60" customHeight="1">
-      <c r="A178" s="4" t="inlineStr">
+    <row r="186" ht="64" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
         <is>
           <t>오가닉7솔루션</t>
         </is>
       </c>
-      <c r="B178" s="4" t="inlineStr">
+      <c r="B186" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C178" s="4" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr">
         <is>
           <t>비타민류가 다량 함유되어있는 / 유기농 야채(당근, 토마토,브로컬리,현미, 양배추,샐러리, 현미)를 저온 추출.</t>
         </is>
       </c>
-      <c r="D178" s="4" t="inlineStr">
+      <c r="D186" s="4" t="inlineStr">
         <is>
           <t>콜라겐, 석류,토마토,</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="120" customHeight="1">
-      <c r="A179" s="4" t="inlineStr">
+    <row r="187" ht="128" customHeight="1">
+      <c r="A187" s="4" t="inlineStr">
         <is>
           <t>씨네이크(뱀독) / 펩타이드</t>
         </is>
       </c>
-      <c r="B179" s="4" t="inlineStr">
+      <c r="B187" s="4" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C179" s="4" t="inlineStr">
+      <c r="C187" s="4" t="inlineStr">
         <is>
           <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. / 임상시 아세틸헥사펩타이드보다 효과적. / 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. / '바르는 보톡스' 등으로 인기</t>
         </is>
       </c>
-      <c r="D179" s="4" t="n"/>
-    </row>
-    <row r="180" ht="30" customHeight="1">
-      <c r="A180" s="4" t="inlineStr">
+      <c r="D187" s="4" t="n"/>
+    </row>
+    <row r="188" ht="32" customHeight="1">
+      <c r="A188" s="4" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="B188" s="4" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="C188" s="4" t="inlineStr">
         <is>
           <t>녹황색채소에 들어있는 비타민B3. / 식약처 인증 미백원료</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="D188" s="4" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="60" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
+    <row r="189" ht="64" customHeight="1">
+      <c r="A189" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
+      <c r="B189" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C189" s="4" t="inlineStr">
         <is>
           <t>미생물 번식 억제제.</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="D189" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="30" customHeight="1">
-      <c r="A182" s="4" t="inlineStr">
+    <row r="190" ht="32" customHeight="1">
+      <c r="A190" s="4" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="B190" s="4" t="inlineStr">
         <is>
           <t>0~6g</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="C190" s="4" t="inlineStr">
         <is>
           <t>보습제. 원하시면 넣어주세요.</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="D190" s="4" t="inlineStr">
         <is>
           <t>리피듀어, / 식물성글리세린</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="45" customHeight="1">
-      <c r="A183" s="4" t="inlineStr">
+    <row r="191" ht="48" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
         <is>
           <t>로즈우드에센셜오일</t>
         </is>
       </c>
-      <c r="B183" s="4" t="inlineStr">
+      <c r="B191" s="4" t="inlineStr">
         <is>
           <t>4~8방울</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C191" s="4" t="inlineStr">
         <is>
           <t>아로마테라피, / 장미향이 나는 제라늄, 모든 피부</t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="D191" s="4" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈제라늄 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="60" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
+    <row r="192" ht="64" customHeight="1">
+      <c r="A192" s="4" t="inlineStr">
         <is>
           <t>알로에모이스트</t>
         </is>
       </c>
-      <c r="B184" s="4" t="inlineStr">
+      <c r="B192" s="4" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C192" s="4" t="inlineStr">
         <is>
           <t>자체점증, 가용화안정, 수분공급 , 진정</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="D192" s="4" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="14" customHeight="1">
-      <c r="A185" s="5" t="inlineStr">
+    <row r="193" ht="14" customHeight="1">
+      <c r="A193" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B185" s="6" t="n"/>
-      <c r="C185" s="6" t="n"/>
-      <c r="D185" s="6" t="n"/>
-    </row>
-    <row r="186" ht="555" customHeight="1">
-      <c r="A186" s="7" t="inlineStr">
+      <c r="B193" s="6" t="n"/>
+      <c r="C193" s="6" t="n"/>
+      <c r="D193" s="6" t="n"/>
+    </row>
+    <row r="194" ht="384" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t>뱀독 볼륨에센스(젤)은
 바르는 보톡스인 씨네이크펩타이드 최대함량인 4%와
@@ -5687,8 +5710,14 @@
 예를들면
 인도 코브라의 뱀독에서 분리한 포스포리파제A2라는 효소는
 피부세포에 발생하는 암의 한 종류인
-흑색종을 없애는 것이 확인되었고,
-살모사의 뱀독에서 추출한 단백질은
+흑색종을 없애는 것이 확인되었고,</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="208" customHeight="1">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>살모사의 뱀독에서 추출한 단백질은
 유방암 세포의 성장을 70%나 억제하는 것으로 밝혀지기도 했습니다.
 또 독사가 가지고 있는 독들 중 waglerin 1이란 독소를
 모방해 만든 바르는 보톡스 '씨네이크펩타이드'는
@@ -5704,18 +5733,18 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="14" customHeight="1">
-      <c r="A187" s="5" t="inlineStr">
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B187" s="6" t="n"/>
-      <c r="C187" s="6" t="n"/>
-      <c r="D187" s="6" t="n"/>
-    </row>
-    <row r="188" ht="75" customHeight="1">
-      <c r="A188" s="7" t="inlineStr">
+      <c r="B196" s="6" t="n"/>
+      <c r="C196" s="6" t="n"/>
+      <c r="D196" s="6" t="n"/>
+    </row>
+    <row r="197" ht="80" customHeight="1">
+      <c r="A197" s="7" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.동백오일과 올리브리퀴드를 먼저 섞어주세요.
@@ -5724,102 +5753,103 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="14" customHeight="1">
-      <c r="A189" s="5" t="inlineStr">
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B189" s="6" t="n"/>
-      <c r="C189" s="6" t="n"/>
-      <c r="D189" s="6" t="n"/>
-    </row>
-    <row r="190" ht="171" customHeight="1"/>
-    <row r="191" ht="6" customHeight="1"/>
-    <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="1" t="inlineStr">
+      <c r="B198" s="6" t="n"/>
+      <c r="C198" s="6" t="n"/>
+      <c r="D198" s="6" t="n"/>
+    </row>
+    <row r="199" ht="85.5" customHeight="1"/>
+    <row r="200" ht="85.5" customHeight="1"/>
+    <row r="201" ht="6" customHeight="1"/>
+    <row r="202" ht="22" customHeight="1">
+      <c r="A202" s="1" t="inlineStr">
         <is>
           <t>아임레알 제주화산송이팩    [(트러블, 모공이 넓은 피부) / 1회분량]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B192" s="2" t="n"/>
-      <c r="C192" s="2" t="n"/>
-      <c r="D192" s="2" t="n"/>
-    </row>
-    <row r="193" ht="15" customHeight="1">
-      <c r="A193" s="3" t="inlineStr">
+      <c r="B202" s="2" t="n"/>
+      <c r="C202" s="2" t="n"/>
+      <c r="D202" s="2" t="n"/>
+    </row>
+    <row r="203" ht="15" customHeight="1">
+      <c r="A203" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B193" s="3" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C193" s="3" t="inlineStr">
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D193" s="3" t="inlineStr">
+      <c r="D203" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="60" customHeight="1">
-      <c r="A194" s="8" t="inlineStr">
+    <row r="204" ht="64" customHeight="1">
+      <c r="A204" s="8" t="inlineStr">
         <is>
           <t>제주 화산송이분말</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B204" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C194" s="8" t="inlineStr">
+      <c r="C204" s="8" t="inlineStr">
         <is>
           <t>섭씨 2000도의 화산작용이 만든 기능성 미네럴, 제주 화산석 송이 / (먹는 '송이(버섯)' 아니죠^^) / 화산송이 7 : 카오링클레이3</t>
         </is>
       </c>
-      <c r="D194" s="8" t="n"/>
-    </row>
-    <row r="195" ht="45" customHeight="1">
-      <c r="A195" s="8" t="inlineStr">
+      <c r="D204" s="8" t="n"/>
+    </row>
+    <row r="205" ht="48" customHeight="1">
+      <c r="A205" s="8" t="inlineStr">
         <is>
           <t>위치헤이즐워터 / (편백워터)</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B205" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C195" s="8" t="inlineStr">
+      <c r="C205" s="8" t="inlineStr">
         <is>
           <t>제주화산송이 양의 반이하의 양, 정제수도 가능, 위치헤즐은 수렴, 트러블, 모공 넓은 피부적합</t>
         </is>
       </c>
-      <c r="D195" s="8" t="inlineStr">
+      <c r="D205" s="8" t="inlineStr">
         <is>
           <t>정수기 물, 수돗물^^, 녹차우린 물. 어성초우린 물</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="14" customHeight="1">
-      <c r="A196" s="5" t="inlineStr">
+    <row r="206" ht="14" customHeight="1">
+      <c r="A206" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B196" s="6" t="n"/>
-      <c r="C196" s="6" t="n"/>
-      <c r="D196" s="6" t="n"/>
-    </row>
-    <row r="197" ht="345" customHeight="1">
-      <c r="A197" s="9" t="inlineStr">
+      <c r="B206" s="6" t="n"/>
+      <c r="C206" s="6" t="n"/>
+      <c r="D206" s="6" t="n"/>
+    </row>
+    <row r="207" ht="368" customHeight="1">
+      <c r="A207" s="9" t="inlineStr">
         <is>
           <t>제주화산송이,
 먹는 송이가 아니죠^^
@@ -5844,22 +5874,22 @@
 초간단 레알 화산송이팩으로 피부 피지와 노폐물을 관리해보세요.</t>
         </is>
       </c>
-      <c r="B197" s="10" t="n"/>
-      <c r="C197" s="10" t="n"/>
-      <c r="D197" s="10" t="n"/>
-    </row>
-    <row r="198" ht="14" customHeight="1">
-      <c r="A198" s="5" t="inlineStr">
+      <c r="B207" s="10" t="n"/>
+      <c r="C207" s="10" t="n"/>
+      <c r="D207" s="10" t="n"/>
+    </row>
+    <row r="208" ht="14" customHeight="1">
+      <c r="A208" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B198" s="6" t="n"/>
-      <c r="C198" s="6" t="n"/>
-      <c r="D198" s="6" t="n"/>
-    </row>
-    <row r="199" ht="270" customHeight="1">
-      <c r="A199" s="9" t="inlineStr">
+      <c r="B208" s="6" t="n"/>
+      <c r="C208" s="6" t="n"/>
+      <c r="D208" s="6" t="n"/>
+    </row>
+    <row r="209" ht="288" customHeight="1">
+      <c r="A209" s="9" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1. 제주화산송이를 두스푼(약10g)계량하시고
@@ -5879,265 +5909,271 @@
 8.팩을 갤때 사용하셨던 플로럴워터로 피부결을 정돈하세요.</t>
         </is>
       </c>
-      <c r="B199" s="10" t="n"/>
-      <c r="C199" s="10" t="n"/>
-      <c r="D199" s="10" t="n"/>
-    </row>
-    <row r="200" ht="14" customHeight="1">
-      <c r="A200" s="5" t="inlineStr">
+      <c r="B209" s="10" t="n"/>
+      <c r="C209" s="10" t="n"/>
+      <c r="D209" s="10" t="n"/>
+    </row>
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B200" s="6" t="n"/>
-      <c r="C200" s="6" t="n"/>
-      <c r="D200" s="6" t="n"/>
-    </row>
-    <row r="201" ht="171" customHeight="1">
-      <c r="A201" s="10" t="n"/>
-      <c r="B201" s="10" t="n"/>
-      <c r="C201" s="10" t="n"/>
-      <c r="D201" s="10" t="n"/>
-    </row>
-    <row r="202" ht="6" customHeight="1"/>
-    <row r="203" ht="22" customHeight="1">
-      <c r="A203" s="1" t="inlineStr">
+      <c r="B210" s="6" t="n"/>
+      <c r="C210" s="6" t="n"/>
+      <c r="D210" s="6" t="n"/>
+    </row>
+    <row r="211" ht="85.5" customHeight="1">
+      <c r="A211" s="10" t="n"/>
+      <c r="B211" s="10" t="n"/>
+      <c r="C211" s="10" t="n"/>
+      <c r="D211" s="10" t="n"/>
+    </row>
+    <row r="212" ht="85.5" customHeight="1">
+      <c r="A212" s="10" t="n"/>
+      <c r="B212" s="10" t="n"/>
+      <c r="C212" s="10" t="n"/>
+      <c r="D212" s="10" t="n"/>
+    </row>
+    <row r="213" ht="6" customHeight="1"/>
+    <row r="214" ht="22" customHeight="1">
+      <c r="A214" s="1" t="inlineStr">
         <is>
           <t>TX 토닝 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B203" s="2" t="n"/>
-      <c r="C203" s="2" t="n"/>
-      <c r="D203" s="2" t="n"/>
-    </row>
-    <row r="204" ht="15" customHeight="1">
-      <c r="A204" s="3" t="inlineStr">
+      <c r="B214" s="2" t="n"/>
+      <c r="C214" s="2" t="n"/>
+      <c r="D214" s="2" t="n"/>
+    </row>
+    <row r="215" ht="15" customHeight="1">
+      <c r="A215" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B204" s="3" t="inlineStr">
+      <c r="B215" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C204" s="3" t="inlineStr">
+      <c r="C215" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D204" s="3" t="inlineStr">
+      <c r="D215" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="30" customHeight="1">
-      <c r="A205" s="4" t="inlineStr">
+    <row r="216" ht="32" customHeight="1">
+      <c r="A216" s="4" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B205" s="4" t="inlineStr">
+      <c r="B216" s="4" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C205" s="4" t="inlineStr">
+      <c r="C216" s="4" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수 함유 / 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="D205" s="4" t="inlineStr">
+      <c r="D216" s="4" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="30" customHeight="1">
-      <c r="A206" s="4" t="inlineStr">
+    <row r="217" ht="32" customHeight="1">
+      <c r="A217" s="4" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B206" s="4" t="inlineStr">
+      <c r="B217" s="4" t="inlineStr">
         <is>
           <t>22g</t>
         </is>
       </c>
-      <c r="C206" s="4" t="inlineStr">
+      <c r="C217" s="4" t="inlineStr">
         <is>
           <t>불가리아 장미수</t>
         </is>
       </c>
-      <c r="D206" s="4" t="inlineStr">
+      <c r="D217" s="4" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="15" customHeight="1">
-      <c r="A207" s="4" t="inlineStr">
+    <row r="218" ht="16" customHeight="1">
+      <c r="A218" s="4" t="inlineStr">
         <is>
           <t>슈퍼시카4</t>
         </is>
       </c>
-      <c r="B207" s="4" t="inlineStr">
+      <c r="B218" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C207" s="4" t="inlineStr">
+      <c r="C218" s="4" t="inlineStr">
         <is>
           <t>병풀의 핵심성분 4가지 복합물</t>
         </is>
       </c>
-      <c r="D207" s="4" t="inlineStr">
+      <c r="D218" s="4" t="inlineStr">
         <is>
           <t>병풀추출물</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="15" customHeight="1">
-      <c r="A208" s="4" t="inlineStr">
+    <row r="219" ht="16" customHeight="1">
+      <c r="A219" s="4" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B208" s="4" t="inlineStr">
+      <c r="B219" s="4" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C208" s="4" t="inlineStr">
+      <c r="C219" s="4" t="inlineStr">
         <is>
           <t>비타민B3, 식약처 기능성 고시원료</t>
         </is>
       </c>
-      <c r="D208" s="4" t="inlineStr">
+      <c r="D219" s="4" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="45" customHeight="1">
-      <c r="A209" s="4" t="inlineStr">
+    <row r="220" ht="48" customHeight="1">
+      <c r="A220" s="4" t="inlineStr">
         <is>
           <t>프로바이오틱스3</t>
         </is>
       </c>
-      <c r="B209" s="4" t="inlineStr">
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C209" s="4" t="inlineStr">
+      <c r="C220" s="4" t="inlineStr">
         <is>
           <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
         </is>
       </c>
-      <c r="D209" s="4" t="inlineStr">
+      <c r="D220" s="4" t="inlineStr">
         <is>
           <t>사카로, 비피다, 갈락토, 콤부차발효여과물..</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="4" t="inlineStr">
+    <row r="221" ht="16" customHeight="1">
+      <c r="A221" s="4" t="inlineStr">
         <is>
           <t>덱스판테놀</t>
         </is>
       </c>
-      <c r="B210" s="4" t="inlineStr">
+      <c r="B221" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C210" s="4" t="inlineStr">
+      <c r="C221" s="4" t="inlineStr">
         <is>
           <t>비타민B5, 보습 재생</t>
         </is>
       </c>
-      <c r="D210" s="4" t="inlineStr">
+      <c r="D221" s="4" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="45" customHeight="1">
-      <c r="A211" s="4" t="inlineStr">
+    <row r="222" ht="48" customHeight="1">
+      <c r="A222" s="4" t="inlineStr">
         <is>
           <t>트라넥삼산 (펩타이드)</t>
         </is>
       </c>
-      <c r="B211" s="4" t="inlineStr">
+      <c r="B222" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C211" s="4" t="inlineStr">
+      <c r="C222" s="4" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="D211" s="4" t="inlineStr">
+      <c r="D222" s="4" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="15" customHeight="1">
-      <c r="A212" s="4" t="inlineStr">
+    <row r="223" ht="16" customHeight="1">
+      <c r="A223" s="4" t="inlineStr">
         <is>
           <t>글루타치온</t>
         </is>
       </c>
-      <c r="B212" s="4" t="inlineStr">
+      <c r="B223" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C212" s="4" t="inlineStr">
+      <c r="C223" s="4" t="inlineStr">
         <is>
           <t>미백효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="D212" s="4" t="n"/>
-    </row>
-    <row r="213" ht="45" customHeight="1">
-      <c r="A213" s="4" t="inlineStr">
+      <c r="D223" s="4" t="n"/>
+    </row>
+    <row r="224" ht="48" customHeight="1">
+      <c r="A224" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B213" s="4" t="inlineStr">
+      <c r="B224" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C213" s="4" t="inlineStr">
+      <c r="C224" s="4" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="D213" s="4" t="inlineStr">
+      <c r="D224" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="14" customHeight="1">
-      <c r="A214" s="5" t="inlineStr">
+    <row r="225" ht="14" customHeight="1">
+      <c r="A225" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B214" s="6" t="n"/>
-      <c r="C214" s="6" t="n"/>
-      <c r="D214" s="6" t="n"/>
-    </row>
-    <row r="215" ht="435" customHeight="1">
-      <c r="A215" s="7" t="inlineStr">
+      <c r="B225" s="6" t="n"/>
+      <c r="C225" s="6" t="n"/>
+      <c r="D225" s="6" t="n"/>
+    </row>
+    <row r="226" ht="384" customHeight="1">
+      <c r="A226" s="7" t="inlineStr">
         <is>
           <t>기미, 잡티 초기 진압에 TX 토닝 젤 (100g)
 난이도 : 하
@@ -6162,8 +6198,14 @@
 미백에 효과적인 하이드로퀴논 성분은 자극감, 홍조 등 부작용이 있는데
 트라넥삼산은 부작용은 거의 없고 효과는 비슷합니다.
 (트라넥삼산의 효과를 배가 시키기 위해
-펩타이드와 결합시킨 트레넥삼산 펩타이드도 사용 가능합니다.
-현대약품 계열사 특허 성분)
+펩타이드와 결합시킨 트레넥삼산 펩타이드도 사용 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="80" customHeight="1">
+      <c r="A227" s="7" t="inlineStr">
+        <is>
+          <t>현대약품 계열사 특허 성분)
 트라넥삼산과 나이아신아마이드를
 함께 사용하면 화이트닝 효과가 시너지 됩니다.
 TX토닝 젤토너로
@@ -6171,18 +6213,18 @@
         </is>
       </c>
     </row>
-    <row r="216" ht="14" customHeight="1">
-      <c r="A216" s="5" t="inlineStr">
+    <row r="228" ht="14" customHeight="1">
+      <c r="A228" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B216" s="6" t="n"/>
-      <c r="C216" s="6" t="n"/>
-      <c r="D216" s="6" t="n"/>
-    </row>
-    <row r="217" ht="60" customHeight="1">
-      <c r="A217" s="7" t="inlineStr">
+      <c r="B228" s="6" t="n"/>
+      <c r="C228" s="6" t="n"/>
+      <c r="D228" s="6" t="n"/>
+    </row>
+    <row r="229" ht="64" customHeight="1">
+      <c r="A229" s="7" t="inlineStr">
         <is>
           <t>TX 토닝 젤 토너 만들기
 1. 모든 재료를 계량합니다.
@@ -6191,142 +6233,154 @@
         </is>
       </c>
     </row>
-    <row r="218" ht="14" customHeight="1">
-      <c r="A218" s="5" t="inlineStr">
+    <row r="230" ht="14" customHeight="1">
+      <c r="A230" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B218" s="6" t="n"/>
-      <c r="C218" s="6" t="n"/>
-      <c r="D218" s="6" t="n"/>
-    </row>
-    <row r="219" ht="85.5" customHeight="1"/>
-    <row r="220" ht="6" customHeight="1"/>
+      <c r="B230" s="6" t="n"/>
+      <c r="C230" s="6" t="n"/>
+      <c r="D230" s="6" t="n"/>
+    </row>
+    <row r="231" ht="85.5" customHeight="1"/>
+    <row r="232" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="105">
-    <mergeCell ref="A215:D215"/>
-    <mergeCell ref="A97:D97"/>
+  <mergeCells count="117">
+    <mergeCell ref="A150:D150"/>
+    <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A159:D159"/>
     <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A134:D134"/>
     <mergeCell ref="A200:D200"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A152:D152"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="A161:D161"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A176:D176"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A186:D186"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A202:D202"/>
     <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A226:D226"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A178:D178"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A228:D228"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A172:D172"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A212:D212"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A164:D164"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A154:D154"/>
     <mergeCell ref="A214:D214"/>
-    <mergeCell ref="A85:D85"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A188:D188"/>
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A141:D141"/>
-    <mergeCell ref="A125:D125"/>
-    <mergeCell ref="A190:D190"/>
+    <mergeCell ref="A163:D163"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A195:D195"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A206:D206"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A117:D117"/>
     <mergeCell ref="A199:D199"/>
-    <mergeCell ref="A111:D111"/>
+    <mergeCell ref="A230:D230"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A127:D127"/>
-    <mergeCell ref="A167:D167"/>
+    <mergeCell ref="A48:D48"/>
     <mergeCell ref="A30:D30"/>
     <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A142:D142"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A216:D216"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A169:D169"/>
+    <mergeCell ref="A182:D182"/>
+    <mergeCell ref="A225:D225"/>
     <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A153:D153"/>
-    <mergeCell ref="A218:D218"/>
-    <mergeCell ref="A128:D128"/>
-    <mergeCell ref="A217:D217"/>
-    <mergeCell ref="A192:D192"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A162:D162"/>
+    <mergeCell ref="A227:D227"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="A177:D177"/>
+    <mergeCell ref="A208:D208"/>
+    <mergeCell ref="A136:D136"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A105:D105"/>
     <mergeCell ref="A145:D145"/>
     <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A139:D139"/>
-    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A160:D160"/>
+    <mergeCell ref="A210:D210"/>
+    <mergeCell ref="A179:D179"/>
     <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A203:D203"/>
+    <mergeCell ref="A194:D194"/>
+    <mergeCell ref="A76:D76"/>
     <mergeCell ref="A116:D116"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A91:D91"/>
     <mergeCell ref="A131:D131"/>
     <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A140:D140"/>
-    <mergeCell ref="A171:D171"/>
-    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="A231:D231"/>
+    <mergeCell ref="A180:D180"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A155:D155"/>
-    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A115:D115"/>
     <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A83:D83"/>
+    <mergeCell ref="A229:D229"/>
+    <mergeCell ref="A77:D77"/>
     <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A157:D157"/>
+    <mergeCell ref="A166:D166"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A207:D207"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A168:D168"/>
-    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A78:D78"/>
     <mergeCell ref="A87:D87"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A133:D133"/>
+    <mergeCell ref="A193:D193"/>
+    <mergeCell ref="A80:D80"/>
     <mergeCell ref="A89:D89"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A104:D104"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A185:D185"/>
-    <mergeCell ref="A219:D219"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A209:D209"/>
+    <mergeCell ref="A147:D147"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A156:D156"/>
-    <mergeCell ref="A170:D170"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A201:D201"/>
-    <mergeCell ref="A82:D82"/>
-    <mergeCell ref="A138:D138"/>
+    <mergeCell ref="A211:D211"/>
+    <mergeCell ref="A130:D130"/>
+    <mergeCell ref="A148:D148"/>
+    <mergeCell ref="A132:D132"/>
     <mergeCell ref="A197:D197"/>
-    <mergeCell ref="A110:D110"/>
-    <mergeCell ref="A187:D187"/>
+    <mergeCell ref="A146:D146"/>
+    <mergeCell ref="A119:D119"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A196:D196"/>
-    <mergeCell ref="A174:D174"/>
-    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A118:D118"/>
     <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A189:D189"/>
     <mergeCell ref="A158:D158"/>
     <mergeCell ref="A198:D198"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A95:D95"/>
-    <mergeCell ref="A151:D151"/>
     <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A175:D175"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A150" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A182" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A202" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A214" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>

--- a/카드_아키타입/02_젤.xlsx
+++ b/카드_아키타입/02_젤.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1619250"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="13500100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="13500100"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="13500100"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="13500100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="15347950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>12</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="15347950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="19075400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="19075400"/>
     <ext cx="1809750" cy="1485900"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="19075400"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>26</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="19075400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="20923250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>26</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="20923250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>26</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="20923250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>26</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="20923250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>26</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="22771100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="27495500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="27495500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="27495500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>41</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="27495500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="29343350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>53</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="33070800"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>53</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="33070800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>53</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="33070800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>53</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="33070800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>66</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="42710100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>66</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="42710100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>66</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="42710100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>66</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="42710100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="48082200"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="48082200"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="48082200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="48082200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="49930050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="55486300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="55486300"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="55486300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="55486300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="57334150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>101</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="61671200"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>101</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="61671200"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="66433700"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="73025000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="73025000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="73025000"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="73025000"/>
     <ext cx="952500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>126</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="74872850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>126</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="74872850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>126</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="74872850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>126</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="74872850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>126</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="76720700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>126</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="76720700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>126</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="76720700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>126</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="76720700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>126</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="78568550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>126</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="78568550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>126</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="78568550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>126</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="78568550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>126</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="80416400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>126</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="80416400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>126</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="80416400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>137</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="83477100"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="90474800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="90474800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="90474800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="90474800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="92322650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="92322650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="92322650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>168</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="106210100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>168</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="106210100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>168</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="106210100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>168</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="106210100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>168</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="108057950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>168</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="108057950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>168</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="108057950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>168</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="108057950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>168</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="109905800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>168</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="109905800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>177</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="116865400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>177</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="116865400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>177</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="116865400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>177</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="116865400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2498,7 +2038,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/02_젤.xlsx
+++ b/카드_아키타입/02_젤.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1619250"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="1847850"/>
+    <pos x="9239250" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="1847850"/>
+    <pos x="11087100" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="1847850"/>
+    <pos x="12934950" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="3695700"/>
+    <pos x="7391400" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="3695700"/>
+    <pos x="9239250" y="3695700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="13500100"/>
+    <pos x="7391400" y="13500100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="13500100"/>
+    <pos x="9239250" y="13500100"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="13500100"/>
+    <pos x="11087100" y="13500100"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="13500100"/>
+    <pos x="12934950" y="13500100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="15347950"/>
+    <pos x="7391400" y="15347950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="15347950"/>
+    <pos x="9239250" y="15347950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="19075400"/>
+    <pos x="7391400" y="19075400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="19075400"/>
+    <pos x="9239250" y="19075400"/>
     <ext cx="1809750" cy="1485900"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="19075400"/>
+    <pos x="11087100" y="19075400"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="19075400"/>
+    <pos x="12934950" y="19075400"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="20923250"/>
+    <pos x="7391400" y="20923250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="20923250"/>
+    <pos x="9239250" y="20923250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="20923250"/>
+    <pos x="11087100" y="20923250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="20923250"/>
+    <pos x="12934950" y="20923250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="22771100"/>
+    <pos x="7391400" y="22771100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="27495500"/>
+    <pos x="7391400" y="27495500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="27495500"/>
+    <pos x="9239250" y="27495500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="27495500"/>
+    <pos x="11087100" y="27495500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="27495500"/>
+    <pos x="12934950" y="27495500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="29343350"/>
+    <pos x="7391400" y="29343350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="33070800"/>
+    <pos x="7391400" y="33070800"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="33070800"/>
+    <pos x="9239250" y="33070800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="33070800"/>
+    <pos x="11087100" y="33070800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="33070800"/>
+    <pos x="12934950" y="33070800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="42710100"/>
+    <pos x="7391400" y="42710100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="42710100"/>
+    <pos x="9239250" y="42710100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="42710100"/>
+    <pos x="11087100" y="42710100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="42710100"/>
+    <pos x="12934950" y="42710100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="48082200"/>
+    <pos x="7391400" y="48082200"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="48082200"/>
+    <pos x="9239250" y="48082200"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="48082200"/>
+    <pos x="11087100" y="48082200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="48082200"/>
+    <pos x="12934950" y="48082200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="49930050"/>
+    <pos x="7391400" y="49930050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="55486300"/>
+    <pos x="7391400" y="55486300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="55486300"/>
+    <pos x="9239250" y="55486300"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="55486300"/>
+    <pos x="11087100" y="55486300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="55486300"/>
+    <pos x="12934950" y="55486300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="57334150"/>
+    <pos x="7391400" y="57334150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="61671200"/>
+    <pos x="7391400" y="61671200"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="61671200"/>
+    <pos x="9239250" y="61671200"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="66433700"/>
+    <pos x="7391400" y="66433700"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="73025000"/>
+    <pos x="7391400" y="73025000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="73025000"/>
+    <pos x="9239250" y="73025000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="73025000"/>
+    <pos x="11087100" y="73025000"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="73025000"/>
+    <pos x="12934950" y="73025000"/>
     <ext cx="952500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="74872850"/>
+    <pos x="7391400" y="74872850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="74872850"/>
+    <pos x="9239250" y="74872850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="74872850"/>
+    <pos x="11087100" y="74872850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="74872850"/>
+    <pos x="12934950" y="74872850"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="76720700"/>
+    <pos x="7391400" y="76720700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="76720700"/>
+    <pos x="9239250" y="76720700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="76720700"/>
+    <pos x="11087100" y="76720700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="76720700"/>
+    <pos x="12934950" y="76720700"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="78568550"/>
+    <pos x="7391400" y="78568550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="78568550"/>
+    <pos x="9239250" y="78568550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="78568550"/>
+    <pos x="11087100" y="78568550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="78568550"/>
+    <pos x="12934950" y="78568550"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="80416400"/>
+    <pos x="7391400" y="80416400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="80416400"/>
+    <pos x="9239250" y="80416400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="80416400"/>
+    <pos x="11087100" y="80416400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="83477100"/>
+    <pos x="7391400" y="83477100"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="90474800"/>
+    <pos x="7391400" y="90474800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="90474800"/>
+    <pos x="9239250" y="90474800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="90474800"/>
+    <pos x="11087100" y="90474800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="90474800"/>
+    <pos x="12934950" y="90474800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="92322650"/>
+    <pos x="7391400" y="92322650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="92322650"/>
+    <pos x="9239250" y="92322650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="92322650"/>
+    <pos x="11087100" y="92322650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="106210100"/>
+    <pos x="7391400" y="106210100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="106210100"/>
+    <pos x="9239250" y="106210100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="106210100"/>
+    <pos x="11087100" y="106210100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="106210100"/>
+    <pos x="12934950" y="106210100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="108057950"/>
+    <pos x="7391400" y="108057950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="108057950"/>
+    <pos x="9239250" y="108057950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="108057950"/>
+    <pos x="11087100" y="108057950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="108057950"/>
+    <pos x="12934950" y="108057950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="109905800"/>
+    <pos x="7391400" y="109905800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="109905800"/>
+    <pos x="9239250" y="109905800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="116865400"/>
+    <pos x="7391400" y="116865400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="116865400"/>
+    <pos x="9239250" y="116865400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="116865400"/>
+    <pos x="11087100" y="116865400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="116865400"/>
+    <pos x="12934950" y="116865400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2338,7 +2338,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/02_젤.xlsx
+++ b/카드_아키타입/02_젤.xlsx
@@ -17,13 +17,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B5900"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="003A3A3A"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -37,16 +46,31 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002A4A6B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="0055606E"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCEFBE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6DC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -60,7 +84,57 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EAD9F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9F0D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFF3F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBD9E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F7FAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8F5D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5D9C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF0CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,32 +169,77 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -200,7 +319,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7391400" y="0"/>
+    <pos x="7848600" y="1092200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -220,7 +339,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="0"/>
+    <pos x="9696450" y="1092200"/>
     <ext cx="1809750" cy="1619250"/>
     <pic>
       <nvPicPr>
@@ -240,7 +359,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="0"/>
+    <pos x="11544300" y="1092200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -260,7 +379,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="0"/>
+    <pos x="13392150" y="1092200"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -280,7 +399,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="1847850"/>
+    <pos x="7848600" y="2940050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +419,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="1847850"/>
+    <pos x="9696450" y="2940050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +439,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="1847850"/>
+    <pos x="11544300" y="2940050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +459,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="1847850"/>
+    <pos x="13392150" y="2940050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +479,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="3695700"/>
+    <pos x="7848600" y="4787900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +499,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="3695700"/>
+    <pos x="9696450" y="4787900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +519,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="13500100"/>
+    <pos x="7848600" y="14973300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -420,7 +539,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="13500100"/>
+    <pos x="9696450" y="14973300"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -440,7 +559,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="13500100"/>
+    <pos x="11544300" y="14973300"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -460,7 +579,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="13500100"/>
+    <pos x="13392150" y="14973300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -480,7 +599,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="15347950"/>
+    <pos x="7848600" y="16821150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -500,7 +619,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="15347950"/>
+    <pos x="9696450" y="16821150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -520,7 +639,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="19075400"/>
+    <pos x="7848600" y="21539200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -540,7 +659,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="19075400"/>
+    <pos x="9696450" y="21539200"/>
     <ext cx="1809750" cy="1485900"/>
     <pic>
       <nvPicPr>
@@ -560,7 +679,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="19075400"/>
+    <pos x="11544300" y="21539200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -580,7 +699,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="19075400"/>
+    <pos x="13392150" y="21539200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -600,7 +719,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="20923250"/>
+    <pos x="7848600" y="23387050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -620,7 +739,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="20923250"/>
+    <pos x="9696450" y="23387050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -640,7 +759,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="20923250"/>
+    <pos x="11544300" y="23387050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -660,7 +779,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="20923250"/>
+    <pos x="13392150" y="23387050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -680,7 +799,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="22771100"/>
+    <pos x="7848600" y="25234900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -700,7 +819,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="27495500"/>
+    <pos x="7848600" y="31153100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -720,7 +839,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="27495500"/>
+    <pos x="9696450" y="31153100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +859,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="27495500"/>
+    <pos x="11544300" y="31153100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +879,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="27495500"/>
+    <pos x="13392150" y="31153100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +899,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="29343350"/>
+    <pos x="7848600" y="33000950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +919,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="33070800"/>
+    <pos x="7848600" y="37312600"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +939,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="33070800"/>
+    <pos x="9696450" y="37312600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +959,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="33070800"/>
+    <pos x="11544300" y="37312600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +979,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="33070800"/>
+    <pos x="13392150" y="37312600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +999,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="42710100"/>
+    <pos x="7848600" y="47739300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +1019,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="42710100"/>
+    <pos x="9696450" y="47739300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -920,7 +1039,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="42710100"/>
+    <pos x="11544300" y="47739300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -940,7 +1059,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="42710100"/>
+    <pos x="13392150" y="47739300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -960,7 +1079,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="48082200"/>
+    <pos x="7848600" y="53898800"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +1099,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="48082200"/>
+    <pos x="9696450" y="53898800"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1119,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="48082200"/>
+    <pos x="11544300" y="53898800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1139,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="48082200"/>
+    <pos x="13392150" y="53898800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1159,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="49930050"/>
+    <pos x="7848600" y="55746650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1179,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="55486300"/>
+    <pos x="7848600" y="61683900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1199,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="55486300"/>
+    <pos x="9696450" y="61683900"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1219,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="55486300"/>
+    <pos x="11544300" y="61683900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1239,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="55486300"/>
+    <pos x="13392150" y="61683900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1259,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="57334150"/>
+    <pos x="7848600" y="63531750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1279,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="61671200"/>
+    <pos x="7848600" y="68453000"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1299,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="61671200"/>
+    <pos x="9696450" y="68453000"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1319,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="66433700"/>
+    <pos x="7848600" y="73393300"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1339,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="73025000"/>
+    <pos x="7848600" y="80187800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1359,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="73025000"/>
+    <pos x="9696450" y="80187800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1379,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="73025000"/>
+    <pos x="11544300" y="80187800"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1399,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="73025000"/>
+    <pos x="13392150" y="80187800"/>
     <ext cx="952500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1419,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="74872850"/>
+    <pos x="7848600" y="82035650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1439,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="74872850"/>
+    <pos x="9696450" y="82035650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1459,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="74872850"/>
+    <pos x="11544300" y="82035650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1479,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="74872850"/>
+    <pos x="13392150" y="82035650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1499,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="76720700"/>
+    <pos x="7848600" y="83883500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1519,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="76720700"/>
+    <pos x="9696450" y="83883500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1539,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="76720700"/>
+    <pos x="11544300" y="83883500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1559,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="76720700"/>
+    <pos x="13392150" y="83883500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1579,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="78568550"/>
+    <pos x="7848600" y="85731350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1599,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="78568550"/>
+    <pos x="9696450" y="85731350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1619,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="78568550"/>
+    <pos x="11544300" y="85731350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1639,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="78568550"/>
+    <pos x="13392150" y="85731350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1659,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="80416400"/>
+    <pos x="7848600" y="87579200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1679,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="80416400"/>
+    <pos x="9696450" y="87579200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1699,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="80416400"/>
+    <pos x="11544300" y="87579200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1719,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="83477100"/>
+    <pos x="7848600" y="91224100"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1739,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="90474800"/>
+    <pos x="7848600" y="98221800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1759,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="90474800"/>
+    <pos x="9696450" y="98221800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1779,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="90474800"/>
+    <pos x="11544300" y="98221800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1799,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="90474800"/>
+    <pos x="13392150" y="98221800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1819,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="92322650"/>
+    <pos x="7848600" y="100069650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1839,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="92322650"/>
+    <pos x="9696450" y="100069650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1859,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="92322650"/>
+    <pos x="11544300" y="100069650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1879,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="106210100"/>
+    <pos x="7848600" y="115150900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1899,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="106210100"/>
+    <pos x="9696450" y="115150900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1919,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="106210100"/>
+    <pos x="11544300" y="115150900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1939,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="106210100"/>
+    <pos x="13392150" y="115150900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1959,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="108057950"/>
+    <pos x="7848600" y="116998750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1979,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="108057950"/>
+    <pos x="9696450" y="116998750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1999,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="108057950"/>
+    <pos x="11544300" y="116998750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +2019,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="108057950"/>
+    <pos x="13392150" y="116998750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +2039,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="109905800"/>
+    <pos x="7848600" y="118846600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +2059,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="109905800"/>
+    <pos x="9696450" y="118846600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +2079,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="116865400"/>
+    <pos x="7848600" y="126390400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +2099,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="116865400"/>
+    <pos x="9696450" y="126390400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2119,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="116865400"/>
+    <pos x="11544300" y="126390400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2139,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="116865400"/>
+    <pos x="13392150" y="126390400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2331,144 +2450,249 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D193"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>아로마 손소독제젤타입    ↗ 원본</t>
+          <t>━  젤 골격 치트시트  (이 파일 15종 기준)  ━</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>전형 구성(%):  수상 22~28% · 유화 2~3% · 보습 4~4% · 활성 66~95% · 향 0~1% · 방부 1~1% · 점증/pH 25~30%</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>자주 쓰는 원료:  천연한방보존제×5 · 카보머 프리젤×3 · 아로마베이스95×2 · 식물성 글리세린×2 · 알로에베라겔×2 · 글리세린×2 · 화이트펩타이드×2 · 트라넥삼산×2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>아로마 손소독제젤타입    ↗ 원본</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>408g / (=500ml)</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>95%. 곡물 발효 알콜</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="64" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>카보머 1%을 함유, 알로에모이스트보다 높은 점도. 섞어주는 것만으로 간편하게 젤타입을 만들 수 있도록 만든 원료.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="F8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>22.5g</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>보습제, 향이 오랫동안 머물 수 있도록 고착제 역할을 함</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>레몬에센셜오일</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>5ml</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>천연 레몬 껍질 오일, / 상큼한 향</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 유칼립투스 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+    <row r="11" ht="14" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  보습 4 · 활성 64 · 향 1 · 점증/pH 31</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+    </row>
+    <row r="12" ht="14" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="384" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+    </row>
+    <row r="13" ht="384" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>무제 문서
 셀프 백신 중 하나가 손소독입니다.
@@ -2497,8 +2721,8 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="336" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+    <row r="14" ht="336" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>알콜류의 세균력은....
 세균 막의 지질 복합체를 파괴하고 단백질을 변성ㆍ응고시켜 살균작용을 나타낸답니다.
@@ -2524,18 +2748,20 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="15" ht="14" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="96" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+    </row>
+    <row r="16" ht="96" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>1. 카보머프리젤을 계량해주세요. | 2. 식물성글리세린과 | 3. 에센셜오일을 비롯한 아로마베이스95까지 모든 재료를 계량해주세요.
 |
@@ -2545,205 +2771,301 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="6" customHeight="1"/>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="17" ht="6" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>허니 촉촉 바디젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="20" ht="80" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>68g</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>수분, 자체 점증.</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>워터 코포아수</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>천연 레시틴으로 코포아수 버터를 리포좀화.</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>워터 아르간</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>세라마이드 (수용성)</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>세라마이드 리포좀화</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="F22" s="19" t="inlineStr">
         <is>
           <t>스쿠알란, / 보르피린</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>꿀 추출물</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E23" s="19" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="F23" s="19" t="inlineStr">
         <is>
           <t>원하는 / 추출물</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="inlineStr">
         <is>
           <t>균번식 억제제</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (알로에베라겔의 양을 67g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>스윗 오렌지에센셜오일</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
         <is>
           <t>오렌지 껍질 오일</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="F25" s="19" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>네롤리에센셜오일</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>3방울</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>오렌지꽃오일, / 민감, 모든 피부</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="F26" s="19" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 10 · 활성 88 · 향 1 · 방부 1</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="96" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+    </row>
+    <row r="29" ht="96" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>클레오파트라, 네로의 아내 포파이아 등 전설적인 미인들이 꿀과
 우유로 목욕을 했다는 것은 이미 알려진 사실인데요 그만큼 꿀은 거친
@@ -2753,249 +3075,361 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="14" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-    </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>1. 모든 재료를 계량한 후
 2. 골고루 섞어주세요.
 3. 용기에 넣으면 완성.</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-    </row>
-    <row r="26" ht="6" customHeight="1"/>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="24" t="n"/>
+      <c r="F31" s="24" t="n"/>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>트러블 SSG~필링젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>내추럴 / 셀룰로오즈</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>프랑스산 목화 섬유질로 / 만든 천연 필링제.</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>티트리워터</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>37g</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>티트리 수증기 / 증류법으로 추출</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>로즈마리, / 편백워터</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="37" ht="64" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. / 남은 재료 활용 팁 : 젤타입스킨으로 사용가능, / 헤어에센스로 사용가능.</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>카보폴프리젤</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>알란토인분말</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>진정, 계량스푼 작은 쪽 깎아서 4개면 0.2g</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="F38" s="8" t="inlineStr">
         <is>
           <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>마치현추출물</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>쇠비름, 진정, / 트러블 관리</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>어성초, / 병풀 추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>3.8g</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (티트리워터의 양을 36g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>레몬EO</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
         <is>
           <t>레몬껍질오일,상큼, 아로마테라피</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="F42" s="8" t="inlineStr">
         <is>
           <t>무향 또는 / 원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 38 · 보습 4 · 활성 46 · 향 0 · 방부 1 · 점증/pH 10</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+    </row>
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-    </row>
-    <row r="38" ht="224" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="224" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>누구에게나 '때'는 있습니다.
 이 '때'관리만 잘 해줘도
@@ -3014,18 +3448,20 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="14" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-    </row>
-    <row r="40" ht="96" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+    </row>
+    <row r="47" ht="96" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>1. 알란토인분말 0.2g은 계량스푼 작은 쪽에 깍아서 4개로 해주세요.
 2. 비커에 넣고 내추럴 셀룰로오즈을 비롯 모든 재료를
@@ -3036,157 +3472,233 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="6" customHeight="1"/>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="1" t="inlineStr">
+    <row r="48" ht="6" customHeight="1"/>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>이데베논 수면팩    ↗ 원본</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>재료</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>용량</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>특징</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>대체재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>로즈 플라워젤</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>89g</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>불가리아 다마스크 장미수를 젤타입으로. / 에코보습제, 알란토인 함유</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="inlineStr">
-        <is>
-          <t>허브누리 / 알로에베라겔, / 네롤리플라워겔</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="48" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>이데베논</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="inlineStr">
-        <is>
-          <t>5g</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>코엔자임의 10배, / 항산화효과 / 레시피 처방시 500ppm 함유크림 완성.</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="n"/>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>화이트펩타이드</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t>5g</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>비타민 펩타이드, 화이트닝</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="inlineStr">
-        <is>
-          <t>4GF, / 씨네이크펩타이드</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="48" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>천연한방보존제</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>1g</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>균번식 억제</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="inlineStr">
-        <is>
-          <t>1,2-헥산디올2g / (로즈플라워 겔의 양을 88g으로 줄여주세요.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>다중히아루론산</t>
-        </is>
-      </c>
-      <c r="B48" s="8" t="inlineStr">
-        <is>
-          <t>0~5g</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>고분자, 중분자, 저분자로 이루어짐. / 피부 각층별 수분공급</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>판테놀</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>— 상세내용 —</t>
         </is>
       </c>
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="n"/>
       <c r="D49" s="6" t="n"/>
-    </row>
-    <row r="50" ht="112" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>재료</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>용량</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>특징</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>대체재료</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>로즈 플라워젤</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>89g</t>
+        </is>
+      </c>
+      <c r="C51" s="20" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>불가리아 다마스크 장미수를 젤타입으로. / 에코보습제, 알란토인 함유</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
+        <is>
+          <t>허브누리 / 알로에베라겔, / 네롤리플라워겔</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
+          <t>이데베논</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>5g</t>
+        </is>
+      </c>
+      <c r="C52" s="20" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>코엔자임의 10배, / 항산화효과 / 레시피 처방시 500ppm 함유크림 완성.</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="n"/>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>화이트펩타이드</t>
+        </is>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>5g</t>
+        </is>
+      </c>
+      <c r="C53" s="20" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>비타민 펩타이드, 화이트닝</t>
+        </is>
+      </c>
+      <c r="F53" s="19" t="inlineStr">
+        <is>
+          <t>4GF, / 씨네이크펩타이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="64" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>천연한방보존제</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>1g</t>
+        </is>
+      </c>
+      <c r="C54" s="20" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="E54" s="19" t="inlineStr">
+        <is>
+          <t>균번식 억제</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
+          <t>1,2-헥산디올2g / (로즈플라워 겔의 양을 88g으로 줄여주세요.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>다중히아루론산</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>0~5g</t>
+        </is>
+      </c>
+      <c r="C55" s="20" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>고분자, 중분자, 저분자로 이루어짐. / 피부 각층별 수분공급</t>
+        </is>
+      </c>
+      <c r="F55" s="19" t="inlineStr">
+        <is>
+          <t>판테놀</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  활성 99 · 방부 1</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n"/>
+      <c r="C56" s="15" t="n"/>
+      <c r="D56" s="15" t="n"/>
+      <c r="E56" s="15" t="n"/>
+      <c r="F56" s="15" t="n"/>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="F57" s="17" t="n"/>
+    </row>
+    <row r="58" ht="112" customHeight="1">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t>황금톡스라 불리는 ,이데베논.
 코엔자임Q10의 10배 항산화효과를 가지고 있습니다.
@@ -3197,22 +3709,26 @@
 또 급이 다른 이데베논의 항산화효과로 시간을 되돌리세요.</t>
         </is>
       </c>
-      <c r="B50" s="10" t="n"/>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="10" t="n"/>
-    </row>
-    <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+      <c r="B58" s="24" t="n"/>
+      <c r="C58" s="24" t="n"/>
+      <c r="D58" s="24" t="n"/>
+      <c r="E58" s="24" t="n"/>
+      <c r="F58" s="24" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-    </row>
-    <row r="52" ht="64" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="17" t="n"/>
+      <c r="E59" s="17" t="n"/>
+      <c r="F59" s="17" t="n"/>
+    </row>
+    <row r="60" ht="64" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
         <is>
           <t>만들기 과정
 1.로즈플라워겔을 계량하고
@@ -3220,165 +3736,243 @@
 3.고른 점도가 나오면 용기에 담아주세요.</t>
         </is>
       </c>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-    </row>
-    <row r="53" ht="6" customHeight="1"/>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="B60" s="24" t="n"/>
+      <c r="C60" s="24" t="n"/>
+      <c r="D60" s="24" t="n"/>
+      <c r="E60" s="24" t="n"/>
+      <c r="F60" s="24" t="n"/>
+    </row>
+    <row r="61" ht="6" customHeight="1"/>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>TX 멜라 토닝 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B54" s="2" t="n"/>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n"/>
+      <c r="F62" s="6" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="48" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="64" ht="48" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>로즈 플라워겔</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 듬뿍 담은젤, / 에코보습제, 알란토인 함유</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>알로에베라겔, / 네롤리플라워젤</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="48" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="65" ht="64" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>트라넥삼산 / (펩타이드)</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 / 펩타이드 말단에 합성으로 / 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>화이트 펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="48" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="66" ht="48" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>4GF</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>EGF, FGF, IGF, TGF / 복합 펩타이드</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>아세틸헥사, / 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="48" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="67" ht="64" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>균번식 억제, 식물복합</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="F67" s="8" t="inlineStr">
         <is>
           <t>1.2헥산디올2g / (로즈플라워겔을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="68" ht="48" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
         <is>
           <t>브라이트닝 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>네롤리, 일랑일랑, 버가못FCF, / 프랑킨센스 EO 블렌딩오일, 생략 가능</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="14" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  활성 99 · 향 0 · 방부 1</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="15" t="n"/>
+      <c r="D69" s="15" t="n"/>
+      <c r="E69" s="15" t="n"/>
+      <c r="F69" s="15" t="n"/>
+    </row>
+    <row r="70" ht="14" customHeight="1">
+      <c r="A70" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B61" s="6" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-    </row>
-    <row r="62" ht="384" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
+      <c r="B70" s="17" t="n"/>
+      <c r="C70" s="17" t="n"/>
+      <c r="D70" s="17" t="n"/>
+      <c r="E70" s="17" t="n"/>
+      <c r="F70" s="17" t="n"/>
+    </row>
+    <row r="71" ht="384" customHeight="1">
+      <c r="A71" s="18" t="inlineStr">
         <is>
           <t>트레넥삼산(Tranexamic acid, TX)은 원래 지혈제로 사용되고 있습니다.
 산후 , 외상, 월경, 코피 등 과다 출혈에 사용되는 항플라즈민제로 의약 성분입니다.
@@ -3407,25 +4001,27 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="18" t="inlineStr">
         <is>
           <t>도움을 줍니다.</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="14" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-    </row>
-    <row r="65" ht="64" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="B73" s="17" t="n"/>
+      <c r="C73" s="17" t="n"/>
+      <c r="D73" s="17" t="n"/>
+      <c r="E73" s="17" t="n"/>
+      <c r="F73" s="17" t="n"/>
+    </row>
+    <row r="74" ht="64" customHeight="1">
+      <c r="A74" s="18" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량하고
@@ -3434,161 +4030,237 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="6" customHeight="1"/>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="1" t="inlineStr">
+    <row r="75" ht="6" customHeight="1"/>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>콜라겐 드림 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
+    <row r="78" ht="48" customHeight="1">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>워터 호호바</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B78" s="19" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C78" s="20" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D78" s="21" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E78" s="19" t="inlineStr">
         <is>
           <t>호호바오일에 천연레시틴을 / 이용하여 리포좀화, / 수상에 쉽게 분산</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="F78" s="19" t="inlineStr">
         <is>
           <t>슈퍼 곡물 / 단백질추출물</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="48" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>콜라겐 펩타이드</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B79" s="19" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C79" s="20" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E79" s="19" t="inlineStr">
         <is>
           <t>인체 흡수가 용이한 / 저분자화 순수 단백질 사용, / 18종의 아미노산으로 구성</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="F79" s="19" t="inlineStr">
         <is>
           <t>아카시아, / 마린콜라겐</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C80" s="20" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E80" s="19" t="inlineStr">
         <is>
           <t>비타민 펩타이드, 화이트닝</t>
         </is>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="F80" s="19" t="inlineStr">
         <is>
           <t>트라넥 / 삼산펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B72" s="8" t="inlineStr">
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t>85g</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr">
+      <c r="C81" s="20" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E81" s="19" t="inlineStr">
         <is>
           <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="D72" s="8" t="inlineStr">
+      <c r="F81" s="19" t="inlineStr">
         <is>
           <t>네롤리플라워겔, / 알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="48" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
+    <row r="82" ht="64" customHeight="1">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>1,2 헥산디올</t>
         </is>
       </c>
-      <c r="B73" s="8" t="inlineStr">
+      <c r="B82" s="19" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr">
+      <c r="C82" s="20" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E82" s="19" t="inlineStr">
         <is>
           <t>보습제, 자유수 억제, 균번식억제</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr">
+      <c r="F82" s="19" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="14" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 3 · 보습 2 · 활성 95</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="n"/>
+      <c r="C83" s="15" t="n"/>
+      <c r="D83" s="15" t="n"/>
+      <c r="E83" s="15" t="n"/>
+      <c r="F83" s="15" t="n"/>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="6" t="n"/>
-    </row>
-    <row r="75" ht="112" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="B84" s="17" t="n"/>
+      <c r="C84" s="17" t="n"/>
+      <c r="D84" s="17" t="n"/>
+      <c r="E84" s="17" t="n"/>
+      <c r="F84" s="17" t="n"/>
+    </row>
+    <row r="85" ht="112" customHeight="1">
+      <c r="A85" s="23" t="inlineStr">
         <is>
           <t>25세 이후 콜라겐 합성이 줄어들므로
 피부가 탄력을 잃고 주름이 생기기 시작하며 활기를 잃게 됩니다.
@@ -3599,22 +4271,26 @@
 보습은 물론 탄력관리에 좋고 생기있는 피부를 가꿔줍니다.</t>
         </is>
       </c>
-      <c r="B75" s="10" t="n"/>
-      <c r="C75" s="10" t="n"/>
-      <c r="D75" s="10" t="n"/>
-    </row>
-    <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="B85" s="24" t="n"/>
+      <c r="C85" s="24" t="n"/>
+      <c r="D85" s="24" t="n"/>
+      <c r="E85" s="24" t="n"/>
+      <c r="F85" s="24" t="n"/>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6" t="n"/>
-    </row>
-    <row r="77" ht="64" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="B86" s="17" t="n"/>
+      <c r="C86" s="17" t="n"/>
+      <c r="D86" s="17" t="n"/>
+      <c r="E86" s="17" t="n"/>
+      <c r="F86" s="17" t="n"/>
+    </row>
+    <row r="87" ht="64" customHeight="1">
+      <c r="A87" s="23" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량합니다.
@@ -3622,139 +4298,207 @@
 3. 점도가 고르게 되면 용기에 옮겨 담으면 완성.</t>
         </is>
       </c>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="10" t="n"/>
-    </row>
-    <row r="78" ht="6" customHeight="1"/>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="B87" s="24" t="n"/>
+      <c r="C87" s="24" t="n"/>
+      <c r="D87" s="24" t="n"/>
+      <c r="E87" s="24" t="n"/>
+      <c r="F87" s="24" t="n"/>
+    </row>
+    <row r="88" ht="6" customHeight="1"/>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>셀프백신 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n"/>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n"/>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+      <c r="E89" s="6" t="n"/>
+      <c r="F89" s="6" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="92" ht="48" customHeight="1">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B92" s="8" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C92" s="9" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 / 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="D82" s="4" t="n"/>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
+      <c r="F92" s="8" t="n"/>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="F93" s="8" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="48" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="8" t="inlineStr">
         <is>
           <t>니아울리에센셜오일</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B94" s="8" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
         <is>
           <t>광엽 티트리라 불림. 향과 성분이 / 유칼립투스와 티트리의 부드러운 버전</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
         <is>
           <t>유칼립튜스, 티트리 등</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="14" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  활성 69 · 향 1 · 점증/pH 30</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="n"/>
+      <c r="C95" s="15" t="n"/>
+      <c r="D95" s="15" t="n"/>
+      <c r="E95" s="15" t="n"/>
+      <c r="F95" s="15" t="n"/>
+    </row>
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="6" t="n"/>
-      <c r="D85" s="6" t="n"/>
-    </row>
-    <row r="86" ht="320" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
+      <c r="B96" s="17" t="n"/>
+      <c r="C96" s="17" t="n"/>
+      <c r="D96" s="17" t="n"/>
+      <c r="E96" s="17" t="n"/>
+      <c r="F96" s="17" t="n"/>
+    </row>
+    <row r="97" ht="320" customHeight="1">
+      <c r="A97" s="18" t="inlineStr">
         <is>
           <t>무제 문서
 코로나19 예방을 위해 전문가들이
@@ -3779,18 +4523,20 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="14" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-    </row>
-    <row r="88" ht="80" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+      <c r="B98" s="17" t="n"/>
+      <c r="C98" s="17" t="n"/>
+      <c r="D98" s="17" t="n"/>
+      <c r="E98" s="17" t="n"/>
+      <c r="F98" s="17" t="n"/>
+    </row>
+    <row r="99" ht="80" customHeight="1">
+      <c r="A99" s="18" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -3800,157 +4546,233 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="6" customHeight="1"/>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="1" t="inlineStr">
+    <row r="100" ht="6" customHeight="1"/>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>상큼 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B90" s="2" t="n"/>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n"/>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="B101" s="6" t="n"/>
+      <c r="C101" s="6" t="n"/>
+      <c r="D101" s="6" t="n"/>
+      <c r="E101" s="6" t="n"/>
+      <c r="F101" s="6" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="F102" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="8" t="inlineStr">
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B103" s="19" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="C103" s="20" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E103" s="19" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
+      <c r="F103" s="19" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="32" customHeight="1">
-      <c r="A93" s="8" t="inlineStr">
+    <row r="104" ht="48" customHeight="1">
+      <c r="A104" s="19" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B104" s="19" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E104" s="19" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 / 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="D93" s="8" t="n"/>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
+      <c r="F104" s="19" t="n"/>
+    </row>
+    <row r="105" ht="32" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
         <is>
           <t>알란토인(액상)</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B105" s="19" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="C105" s="20" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E105" s="19" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="D94" s="8" t="inlineStr">
+      <c r="F105" s="19" t="inlineStr">
         <is>
           <t>프로폴리스추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="19" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B106" s="19" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C95" s="8" t="inlineStr">
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E106" s="19" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="F106" s="19" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="48" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
+    <row r="107" ht="48" customHeight="1">
+      <c r="A107" s="19" t="inlineStr">
         <is>
           <t>레몬쥬스EO</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B107" s="19" t="inlineStr">
         <is>
           <t>20~25방울</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C107" s="20" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드에센셜오일 / 블랜딩오일</t>
         </is>
       </c>
-      <c r="D96" s="8" t="inlineStr">
+      <c r="F107" s="19" t="inlineStr">
         <is>
           <t>레몬, 만다린, 그레이프푸룻, 라임, 오렌지에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+    <row r="108" ht="14" customHeight="1">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  활성 74 · 향 1 · 점증/pH 25</t>
+        </is>
+      </c>
+      <c r="B108" s="15" t="n"/>
+      <c r="C108" s="15" t="n"/>
+      <c r="D108" s="15" t="n"/>
+      <c r="E108" s="15" t="n"/>
+      <c r="F108" s="15" t="n"/>
+    </row>
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
-    </row>
-    <row r="98" ht="208" customHeight="1">
-      <c r="A98" s="9" t="inlineStr">
+      <c r="B109" s="17" t="n"/>
+      <c r="C109" s="17" t="n"/>
+      <c r="D109" s="17" t="n"/>
+      <c r="E109" s="17" t="n"/>
+      <c r="F109" s="17" t="n"/>
+    </row>
+    <row r="110" ht="208" customHeight="1">
+      <c r="A110" s="23" t="inlineStr">
         <is>
           <t>무제 문서
 그 어느 때보다 손 청결이 중요한 때입니다.
@@ -3967,22 +4789,26 @@
 '상큼 손소독제 만들기'를 안내해드립니다.</t>
         </is>
       </c>
-      <c r="B98" s="10" t="n"/>
-      <c r="C98" s="10" t="n"/>
-      <c r="D98" s="10" t="n"/>
-    </row>
-    <row r="99" ht="14" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
+      <c r="B110" s="24" t="n"/>
+      <c r="C110" s="24" t="n"/>
+      <c r="D110" s="24" t="n"/>
+      <c r="E110" s="24" t="n"/>
+      <c r="F110" s="24" t="n"/>
+    </row>
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-    </row>
-    <row r="100" ht="80" customHeight="1">
-      <c r="A100" s="9" t="inlineStr">
+      <c r="B111" s="17" t="n"/>
+      <c r="C111" s="17" t="n"/>
+      <c r="D111" s="17" t="n"/>
+      <c r="E111" s="17" t="n"/>
+      <c r="F111" s="17" t="n"/>
+    </row>
+    <row r="112" ht="80" customHeight="1">
+      <c r="A112" s="23" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -3991,205 +4817,295 @@
 언제나 어디서나 사용하세요.</t>
         </is>
       </c>
-      <c r="B100" s="10" t="n"/>
-      <c r="C100" s="10" t="n"/>
-      <c r="D100" s="10" t="n"/>
-    </row>
-    <row r="101" ht="6" customHeight="1"/>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="1" t="inlineStr">
+      <c r="B112" s="24" t="n"/>
+      <c r="C112" s="24" t="n"/>
+      <c r="D112" s="24" t="n"/>
+      <c r="E112" s="24" t="n"/>
+      <c r="F112" s="24" t="n"/>
+    </row>
+    <row r="113" ht="6" customHeight="1"/>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>트러블 잠잠 스팟젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B102" s="2" t="n"/>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="B114" s="6" t="n"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="6" t="n"/>
+      <c r="E114" s="6" t="n"/>
+      <c r="F114" s="6" t="n"/>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B115" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D116" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="F116" s="8" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="32" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
+    <row r="117" ht="32" customHeight="1">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B105" s="4" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D117" s="25" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
         <is>
           <t>가용화제. / 물과요일이 분리되지않도록 하는 역할</t>
         </is>
       </c>
-      <c r="D105" s="4" t="inlineStr">
+      <c r="F117" s="8" t="inlineStr">
         <is>
           <t>솔루벌라이저</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="4" t="inlineStr">
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="8" t="inlineStr">
         <is>
           <t>라벤더워터</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B118" s="8" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="D118" s="21" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E118" s="8" t="inlineStr">
         <is>
           <t>진정,재생</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="F118" s="8" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="32" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C119" s="9" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t>겔타입, 수분공급</t>
         </is>
       </c>
-      <c r="D107" s="4" t="inlineStr">
+      <c r="F119" s="8" t="inlineStr">
         <is>
           <t>로즈플라워겔, / 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="8" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B120" s="8" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C120" s="9" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="D120" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>항균,진정</t>
         </is>
       </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="F120" s="8" t="inlineStr">
         <is>
           <t>카렌듈라추출물</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="8" t="inlineStr">
         <is>
           <t>한방보존제</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C121" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D121" s="22" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
         <is>
           <t>복합한방추출물, 균번식억제</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="F121" s="8" t="inlineStr">
         <is>
           <t>수용성보존제</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="14" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
+    <row r="122" ht="14" customHeight="1">
+      <c r="A122" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 28 · 유화 2 · 활성 66 · 향 2 · 방부 2</t>
+        </is>
+      </c>
+      <c r="B122" s="15" t="n"/>
+      <c r="C122" s="15" t="n"/>
+      <c r="D122" s="15" t="n"/>
+      <c r="E122" s="15" t="n"/>
+      <c r="F122" s="15" t="n"/>
+    </row>
+    <row r="123" ht="14" customHeight="1">
+      <c r="A123" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B110" s="6" t="n"/>
-      <c r="C110" s="6" t="n"/>
-      <c r="D110" s="6" t="n"/>
-    </row>
-    <row r="111" ht="64" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
+      <c r="B123" s="17" t="n"/>
+      <c r="C123" s="17" t="n"/>
+      <c r="D123" s="17" t="n"/>
+      <c r="E123" s="17" t="n"/>
+      <c r="F123" s="17" t="n"/>
+    </row>
+    <row r="124" ht="64" customHeight="1">
+      <c r="A124" s="18" t="inlineStr">
         <is>
           <t>[ 사용법 ]
 티트리에센셜오일은 국소부위에 원액을 발라도 되는 에센셜오일입니다. 스팟젤은 티트리에센셜오일을 전체의 2%를 정도로 희석한 순한 젤타입에센스입니다. 소량을 여드름이 난 부분에 발라주세요.</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="14" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B112" s="6" t="n"/>
-      <c r="C112" s="6" t="n"/>
-      <c r="D112" s="6" t="n"/>
-    </row>
-    <row r="113" ht="112" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
+      <c r="B125" s="17" t="n"/>
+      <c r="C125" s="17" t="n"/>
+      <c r="D125" s="17" t="n"/>
+      <c r="E125" s="17" t="n"/>
+      <c r="F125" s="17" t="n"/>
+    </row>
+    <row r="126" ht="112" customHeight="1">
+      <c r="A126" s="18" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 티트리, 올리브리퀴드를 계량합니다.
@@ -4201,161 +5117,205 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="6" customHeight="1"/>
-    <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="1" t="inlineStr">
+    <row r="127" ht="6" customHeight="1"/>
+    <row r="128" ht="22" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 바디팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B115" s="2" t="n"/>
-      <c r="C115" s="2" t="n"/>
-      <c r="D115" s="2" t="n"/>
-    </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="B128" s="6" t="n"/>
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="6" t="n"/>
+      <c r="E128" s="6" t="n"/>
+      <c r="F128" s="6" t="n"/>
+    </row>
+    <row r="129" ht="15" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C129" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
+      <c r="F129" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
+    <row r="130" ht="32" customHeight="1">
+      <c r="A130" s="19" t="inlineStr">
         <is>
           <t>그린 클레이</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B130" s="19" t="inlineStr">
         <is>
           <t>54.35%</t>
         </is>
       </c>
-      <c r="C117" s="8" t="inlineStr">
+      <c r="C130" s="20" t="inlineStr"/>
+      <c r="D130" s="26" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="E130" s="19" t="inlineStr">
         <is>
           <t>녹색 점토, 피지·노폐물 흡착</t>
         </is>
       </c>
-      <c r="D117" s="8" t="inlineStr">
+      <c r="F130" s="19" t="inlineStr">
         <is>
           <t>핑크클레이, 카올린</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="48" customHeight="1">
-      <c r="A118" s="8" t="inlineStr">
+    <row r="131" ht="64" customHeight="1">
+      <c r="A131" s="19" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B131" s="19" t="inlineStr">
         <is>
           <t>43.48%</t>
         </is>
       </c>
-      <c r="C118" s="8" t="inlineStr">
+      <c r="C131" s="20" t="inlineStr"/>
+      <c r="D131" s="21" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E131" s="19" t="inlineStr">
         <is>
           <t>순수한 물 , / 완성품의 색을 고르게.</t>
         </is>
       </c>
-      <c r="D118" s="8" t="inlineStr">
+      <c r="F131" s="19" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="32" customHeight="1">
-      <c r="A119" s="8" t="inlineStr">
+    <row r="132" ht="32" customHeight="1">
+      <c r="A132" s="19" t="inlineStr">
         <is>
           <t>그레이프프룻EO</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B132" s="19" t="inlineStr">
         <is>
           <t>1.09%</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr">
+      <c r="C132" s="20" t="inlineStr"/>
+      <c r="D132" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E132" s="19" t="inlineStr">
         <is>
           <t>자몽 에센셜오일, 상쾌·수렴</t>
         </is>
       </c>
-      <c r="D119" s="8" t="inlineStr">
+      <c r="F132" s="19" t="inlineStr">
         <is>
           <t>오렌지, 레몬에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="64" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
+    <row r="133" ht="64" customHeight="1">
+      <c r="A133" s="19" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B133" s="19" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
+      <c r="C133" s="20" t="inlineStr"/>
+      <c r="D133" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E133" s="19" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr">
+      <c r="F133" s="19" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="32" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
+    <row r="134" ht="32" customHeight="1">
+      <c r="A134" s="19" t="inlineStr">
         <is>
           <t>싸이프러스</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B134" s="19" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C121" s="8" t="inlineStr">
+      <c r="C134" s="20" t="inlineStr"/>
+      <c r="D134" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E134" s="19" t="inlineStr">
         <is>
           <t>상록 침엽수로 / 스팀 증류법 추출, 숲향</t>
         </is>
       </c>
-      <c r="D121" s="8" t="inlineStr">
+      <c r="F134" s="19" t="inlineStr">
         <is>
           <t>편백</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="14" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B122" s="6" t="n"/>
-      <c r="C122" s="6" t="n"/>
-      <c r="D122" s="6" t="n"/>
-    </row>
-    <row r="123" ht="208" customHeight="1">
-      <c r="A123" s="9" t="inlineStr">
+      <c r="B135" s="17" t="n"/>
+      <c r="C135" s="17" t="n"/>
+      <c r="D135" s="17" t="n"/>
+      <c r="E135" s="17" t="n"/>
+      <c r="F135" s="17" t="n"/>
+    </row>
+    <row r="136" ht="192" customHeight="1">
+      <c r="A136" s="23" t="inlineStr">
         <is>
           <t>그린클레이 - 프랑스 아질레지방에서 채취하는 클레이(흙). 미세한 클레이가 피부 깊숙이 침투 모공속 노폐물 배출, 흡착, 풍부한 미네랄 성분 해독 효과를 줍니다. 셀룰라이트관리, 여드름지성 피부에 사용.
 그레이프프룻(자몽껍질오일), 제라늄, 싸이프러스, 쥬니퍼베리, 레몬, 펜넬에센셜오일이 다이어트에 효과적인 오일이다. 림프자극, 독소배출, 호르몬균형, 해독 등의 효과를 준다.
@@ -4366,165 +5326,237 @@
 4. 이런 오일로 비누, 마사지오일, 젤, 로션/크림류 제품을 만들어 병행하면 좋다.</t>
         </is>
       </c>
-      <c r="B123" s="10" t="n"/>
-      <c r="C123" s="10" t="n"/>
-      <c r="D123" s="10" t="n"/>
-    </row>
-    <row r="124" ht="14" customHeight="1">
-      <c r="A124" s="5" t="inlineStr">
+      <c r="B136" s="24" t="n"/>
+      <c r="C136" s="24" t="n"/>
+      <c r="D136" s="24" t="n"/>
+      <c r="E136" s="24" t="n"/>
+      <c r="F136" s="24" t="n"/>
+    </row>
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B124" s="6" t="n"/>
-      <c r="C124" s="6" t="n"/>
-      <c r="D124" s="6" t="n"/>
-    </row>
-    <row r="125" ht="48" customHeight="1">
-      <c r="A125" s="9" t="inlineStr">
+      <c r="B137" s="17" t="n"/>
+      <c r="C137" s="17" t="n"/>
+      <c r="D137" s="17" t="n"/>
+      <c r="E137" s="17" t="n"/>
+      <c r="F137" s="17" t="n"/>
+    </row>
+    <row r="138" ht="48" customHeight="1">
+      <c r="A138" s="23" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 그린클레이, 물, 에센셜오일을 다 넣고
 2. 잘 섞어줍니다.</t>
         </is>
       </c>
-      <c r="B125" s="10" t="n"/>
-      <c r="C125" s="10" t="n"/>
-      <c r="D125" s="10" t="n"/>
-    </row>
-    <row r="126" ht="6" customHeight="1"/>
-    <row r="127" ht="22" customHeight="1">
-      <c r="A127" s="1" t="inlineStr">
+      <c r="B138" s="24" t="n"/>
+      <c r="C138" s="24" t="n"/>
+      <c r="D138" s="24" t="n"/>
+      <c r="E138" s="24" t="n"/>
+      <c r="F138" s="24" t="n"/>
+    </row>
+    <row r="139" ht="6" customHeight="1"/>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>레몬 손소독제(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B127" s="2" t="n"/>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n"/>
-    </row>
-    <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="3" t="inlineStr">
+      <c r="B140" s="6" t="n"/>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="6" t="n"/>
+      <c r="E140" s="6" t="n"/>
+      <c r="F140" s="6" t="n"/>
+    </row>
+    <row r="141" ht="15" customHeight="1">
+      <c r="A141" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B141" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="F141" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="48" customHeight="1">
-      <c r="A129" s="4" t="inlineStr">
+    <row r="142" ht="64" customHeight="1">
+      <c r="A142" s="8" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B129" s="4" t="inlineStr">
+      <c r="B142" s="8" t="inlineStr">
         <is>
           <t>28g</t>
         </is>
       </c>
-      <c r="C129" s="4" t="inlineStr">
+      <c r="C142" s="9" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="D142" s="21" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E142" s="8" t="inlineStr">
         <is>
           <t>5중 필터링 정제된 물.</t>
         </is>
       </c>
-      <c r="D129" s="4" t="inlineStr">
+      <c r="F142" s="8" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="32" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
+    <row r="143" ht="48" customHeight="1">
+      <c r="A143" s="8" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B130" s="4" t="inlineStr">
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E143" s="8" t="inlineStr">
         <is>
           <t>보습제, 향이 오랫동안 머물 수 / 있도록 고착제 역할을 함.</t>
         </is>
       </c>
-      <c r="D130" s="4" t="inlineStr">
+      <c r="F143" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="32" customHeight="1">
-      <c r="A131" s="4" t="inlineStr">
+    <row r="144" ht="32" customHeight="1">
+      <c r="A144" s="8" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B131" s="4" t="inlineStr">
+      <c r="B144" s="8" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C131" s="4" t="inlineStr">
+      <c r="C144" s="9" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="D144" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E144" s="8" t="inlineStr">
         <is>
           <t>에센셜오일 분산, 방향용으로 사용시 / 공기정화, 소독효과</t>
         </is>
       </c>
-      <c r="D131" s="4" t="inlineStr">
+      <c r="F144" s="8" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="32" customHeight="1">
-      <c r="A132" s="4" t="inlineStr">
+    <row r="145" ht="48" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>15~20방울</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D145" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E145" s="8" t="inlineStr">
         <is>
           <t>레몬껍질에서 추출한 100%천연오일. / 상큼한 향.</t>
         </is>
       </c>
-      <c r="D132" s="4" t="inlineStr">
+      <c r="F145" s="8" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 편백 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="14" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 28 · 보습 5 · 향 67</t>
+        </is>
+      </c>
+      <c r="B146" s="15" t="n"/>
+      <c r="C146" s="15" t="n"/>
+      <c r="D146" s="15" t="n"/>
+      <c r="E146" s="15" t="n"/>
+      <c r="F146" s="15" t="n"/>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B133" s="6" t="n"/>
-      <c r="C133" s="6" t="n"/>
-      <c r="D133" s="6" t="n"/>
-    </row>
-    <row r="134" ht="304" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
+      <c r="B147" s="17" t="n"/>
+      <c r="C147" s="17" t="n"/>
+      <c r="D147" s="17" t="n"/>
+      <c r="E147" s="17" t="n"/>
+      <c r="F147" s="17" t="n"/>
+    </row>
+    <row r="148" ht="304" customHeight="1">
+      <c r="A148" s="18" t="inlineStr">
         <is>
           <t>2009년 젤타입 손소독제 만들기를 위해
 하이셀을 이용해 만든 젤타입 손소독제입니다.
@@ -4548,18 +5580,20 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="14" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B135" s="6" t="n"/>
-      <c r="C135" s="6" t="n"/>
-      <c r="D135" s="6" t="n"/>
-    </row>
-    <row r="136" ht="304" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
+      <c r="B149" s="17" t="n"/>
+      <c r="C149" s="17" t="n"/>
+      <c r="D149" s="17" t="n"/>
+      <c r="E149" s="17" t="n"/>
+      <c r="F149" s="17" t="n"/>
+    </row>
+    <row r="150" ht="288" customHeight="1">
+      <c r="A150" s="18" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 [하이셀 계량하기]
@@ -4582,201 +5616,257 @@
         </is>
       </c>
     </row>
-    <row r="137" ht="6" customHeight="1"/>
-    <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="1" t="inlineStr">
+    <row r="151" ht="6" customHeight="1"/>
+    <row r="152" ht="22" customHeight="1">
+      <c r="A152" s="5" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B138" s="2" t="n"/>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n"/>
-    </row>
-    <row r="139" ht="15" customHeight="1">
-      <c r="A139" s="3" t="inlineStr">
+      <c r="B152" s="6" t="n"/>
+      <c r="C152" s="6" t="n"/>
+      <c r="D152" s="6" t="n"/>
+      <c r="E152" s="6" t="n"/>
+      <c r="F152" s="6" t="n"/>
+    </row>
+    <row r="153" ht="15" customHeight="1">
+      <c r="A153" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B153" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="F153" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="48" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+    <row r="154" ht="48" customHeight="1">
+      <c r="A154" s="19" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B140" s="8" t="inlineStr">
+      <c r="B154" s="19" t="inlineStr">
         <is>
           <t>92.17%</t>
         </is>
       </c>
-      <c r="C140" s="8" t="inlineStr">
+      <c r="C154" s="20" t="inlineStr"/>
+      <c r="D154" s="21" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E154" s="19" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="D140" s="8" t="inlineStr">
+      <c r="F154" s="19" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="19" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B141" s="8" t="inlineStr">
+      <c r="B155" s="19" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C141" s="8" t="inlineStr">
+      <c r="C155" s="20" t="inlineStr"/>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E155" s="19" t="inlineStr">
         <is>
           <t>점증제총량의 1%이하</t>
         </is>
       </c>
-      <c r="D141" s="8" t="n"/>
-    </row>
-    <row r="142" ht="64" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
+      <c r="F155" s="19" t="n"/>
+    </row>
+    <row r="156" ht="64" customHeight="1">
+      <c r="A156" s="19" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B142" s="8" t="inlineStr">
+      <c r="B156" s="19" t="inlineStr">
         <is>
           <t>4.61%</t>
         </is>
       </c>
-      <c r="C142" s="8" t="inlineStr">
+      <c r="C156" s="20" t="inlineStr"/>
+      <c r="D156" s="12" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E156" s="19" t="inlineStr">
         <is>
           <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
-      <c r="D142" s="8" t="inlineStr">
+      <c r="F156" s="19" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="32" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+    <row r="157" ht="32" customHeight="1">
+      <c r="A157" s="19" t="inlineStr">
         <is>
           <t>그레이프프룻EO</t>
         </is>
       </c>
-      <c r="B143" s="8" t="inlineStr">
+      <c r="B157" s="19" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C143" s="8" t="inlineStr">
+      <c r="C157" s="20" t="inlineStr"/>
+      <c r="D157" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E157" s="19" t="inlineStr">
         <is>
           <t>자몽 에센셜오일, 상쾌·수렴</t>
         </is>
       </c>
-      <c r="D143" s="8" t="inlineStr">
+      <c r="F157" s="19" t="inlineStr">
         <is>
           <t>오렌지, 레몬에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="32" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
+    <row r="158" ht="32" customHeight="1">
+      <c r="A158" s="19" t="inlineStr">
         <is>
           <t>페퍼민트오일</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B158" s="19" t="inlineStr">
         <is>
           <t>0.23%</t>
         </is>
       </c>
-      <c r="C144" s="8" t="inlineStr">
+      <c r="C158" s="20" t="inlineStr"/>
+      <c r="D158" s="27" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E158" s="19" t="inlineStr">
         <is>
           <t>허브의 고농축오일, / 시원, 커피와 시너지효과</t>
         </is>
       </c>
-      <c r="D144" s="8" t="inlineStr">
+      <c r="F158" s="19" t="inlineStr">
         <is>
           <t>티트리(항균), / 스피아민트 등</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+    <row r="159" ht="32" customHeight="1">
+      <c r="A159" s="19" t="inlineStr">
         <is>
           <t>주니퍼베리EO</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B159" s="19" t="inlineStr">
         <is>
           <t>0.69%</t>
         </is>
       </c>
-      <c r="C145" s="8" t="inlineStr">
+      <c r="C159" s="20" t="inlineStr"/>
+      <c r="D159" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E159" s="19" t="inlineStr">
         <is>
           <t>주니퍼베리 에센셜오일, 수렴·정화</t>
         </is>
       </c>
-      <c r="D145" s="8" t="inlineStr">
+      <c r="F159" s="19" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="64" customHeight="1">
-      <c r="A146" s="8" t="inlineStr">
+    <row r="160" ht="64" customHeight="1">
+      <c r="A160" s="19" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B146" s="8" t="inlineStr">
+      <c r="B160" s="19" t="inlineStr">
         <is>
           <t>0.46%</t>
         </is>
       </c>
-      <c r="C146" s="8" t="inlineStr">
+      <c r="C160" s="20" t="inlineStr"/>
+      <c r="D160" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E160" s="19" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="D146" s="8" t="inlineStr">
+      <c r="F160" s="19" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="14" customHeight="1">
-      <c r="A147" s="5" t="inlineStr">
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B147" s="6" t="n"/>
-      <c r="C147" s="6" t="n"/>
-      <c r="D147" s="6" t="n"/>
-    </row>
-    <row r="148" ht="112" customHeight="1">
-      <c r="A148" s="9" t="inlineStr">
+      <c r="B161" s="17" t="n"/>
+      <c r="C161" s="17" t="n"/>
+      <c r="D161" s="17" t="n"/>
+      <c r="E161" s="17" t="n"/>
+      <c r="F161" s="17" t="n"/>
+    </row>
+    <row r="162" ht="96" customHeight="1">
+      <c r="A162" s="23" t="inlineStr">
         <is>
           <t>*끈적임없이 흡수되는 다이어트젤
 다이어트에 좋은 에센셜오일 6종: 그레이프프룻, 팬넬, 쥬니퍼베리, 싸이프러스, 레몬, 제라늄
@@ -4786,22 +5876,26 @@
 제라늄 - 호로몬 균형, 피지균형</t>
         </is>
       </c>
-      <c r="B148" s="10" t="n"/>
-      <c r="C148" s="10" t="n"/>
-      <c r="D148" s="10" t="n"/>
-    </row>
-    <row r="149" ht="14" customHeight="1">
-      <c r="A149" s="5" t="inlineStr">
+      <c r="B162" s="24" t="n"/>
+      <c r="C162" s="24" t="n"/>
+      <c r="D162" s="24" t="n"/>
+      <c r="E162" s="24" t="n"/>
+      <c r="F162" s="24" t="n"/>
+    </row>
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B149" s="6" t="n"/>
-      <c r="C149" s="6" t="n"/>
-      <c r="D149" s="6" t="n"/>
-    </row>
-    <row r="150" ht="96" customHeight="1">
-      <c r="A150" s="9" t="inlineStr">
+      <c r="B163" s="17" t="n"/>
+      <c r="C163" s="17" t="n"/>
+      <c r="D163" s="17" t="n"/>
+      <c r="E163" s="17" t="n"/>
+      <c r="F163" s="17" t="n"/>
+    </row>
+    <row r="164" ht="96" customHeight="1">
+      <c r="A164" s="23" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 로즈워터를 계량한다.
@@ -4811,249 +5905,367 @@
 6~7. 손으로 저어서 마무리해주면 끝!</t>
         </is>
       </c>
-      <c r="B150" s="10" t="n"/>
-      <c r="C150" s="10" t="n"/>
-      <c r="D150" s="10" t="n"/>
-    </row>
-    <row r="151" ht="6" customHeight="1"/>
-    <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="1" t="inlineStr">
+      <c r="B164" s="24" t="n"/>
+      <c r="C164" s="24" t="n"/>
+      <c r="D164" s="24" t="n"/>
+      <c r="E164" s="24" t="n"/>
+      <c r="F164" s="24" t="n"/>
+    </row>
+    <row r="165" ht="6" customHeight="1"/>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>뱀독 볼륨 에센스(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B152" s="2" t="n"/>
-      <c r="C152" s="2" t="n"/>
-      <c r="D152" s="2" t="n"/>
-    </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="3" t="inlineStr">
+      <c r="B166" s="6" t="n"/>
+      <c r="C166" s="6" t="n"/>
+      <c r="D166" s="6" t="n"/>
+      <c r="E166" s="6" t="n"/>
+      <c r="F166" s="6" t="n"/>
+    </row>
+    <row r="167" ht="15" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B153" s="3" t="inlineStr">
+      <c r="B167" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr">
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D153" s="3" t="inlineStr">
+      <c r="F167" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="32" customHeight="1">
-      <c r="A154" s="4" t="inlineStr">
+    <row r="168" ht="48" customHeight="1">
+      <c r="A168" s="8" t="inlineStr">
         <is>
           <t>(제주산) / 비정제동백오일</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B168" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D168" s="27" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E168" s="8" t="inlineStr">
         <is>
           <t>올레인산 풍부 고보습, / 청정 섬 국내 제주산 야생동백씨 압착.</t>
         </is>
       </c>
-      <c r="D154" s="4" t="inlineStr">
+      <c r="F168" s="8" t="inlineStr">
         <is>
           <t>아르간, 로즈힙, 마카다미아넛오일 등</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="32" customHeight="1">
-      <c r="A155" s="4" t="inlineStr">
+    <row r="169" ht="32" customHeight="1">
+      <c r="A169" s="8" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C155" s="4" t="inlineStr">
+      <c r="C169" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D169" s="25" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="E169" s="8" t="inlineStr">
         <is>
           <t>가용화제, 물에 오일이 분산되도록 도와줌</t>
         </is>
       </c>
-      <c r="D155" s="4" t="inlineStr">
+      <c r="F169" s="8" t="inlineStr">
         <is>
           <t>솔루벌라이저(Polysorbate 80)동량</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="64" customHeight="1">
-      <c r="A156" s="4" t="inlineStr">
+    <row r="170" ht="64" customHeight="1">
+      <c r="A170" s="8" t="inlineStr">
         <is>
           <t>오가닉7솔루션</t>
         </is>
       </c>
-      <c r="B156" s="4" t="inlineStr">
+      <c r="B170" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C156" s="4" t="inlineStr">
+      <c r="C170" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D170" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E170" s="8" t="inlineStr">
         <is>
           <t>비타민류가 다량 함유되어있는 / 유기농 야채(당근, 토마토,브로컬리,현미, 양배추,샐러리, 현미)를 저온 추출.</t>
         </is>
       </c>
-      <c r="D156" s="4" t="inlineStr">
+      <c r="F170" s="8" t="inlineStr">
         <is>
           <t>콜라겐, 석류,토마토,</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="128" customHeight="1">
-      <c r="A157" s="4" t="inlineStr">
+    <row r="171" ht="144" customHeight="1">
+      <c r="A171" s="8" t="inlineStr">
         <is>
           <t>씨네이크(뱀독) / 펩타이드</t>
         </is>
       </c>
-      <c r="B157" s="4" t="inlineStr">
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C157" s="4" t="inlineStr">
+      <c r="C171" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D171" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E171" s="8" t="inlineStr">
         <is>
           <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. / 임상시 아세틸헥사펩타이드보다 효과적. / 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. / '바르는 보톡스' 등으로 인기</t>
         </is>
       </c>
-      <c r="D157" s="4" t="n"/>
-    </row>
-    <row r="158" ht="32" customHeight="1">
-      <c r="A158" s="4" t="inlineStr">
+      <c r="F171" s="8" t="n"/>
+    </row>
+    <row r="172" ht="32" customHeight="1">
+      <c r="A172" s="8" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B158" s="4" t="inlineStr">
+      <c r="B172" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C158" s="4" t="inlineStr">
+      <c r="C172" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D172" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E172" s="8" t="inlineStr">
         <is>
           <t>녹황색채소에 들어있는 비타민B3. / 식약처 인증 미백원료</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
+      <c r="F172" s="8" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="64" customHeight="1">
-      <c r="A159" s="4" t="inlineStr">
+    <row r="173" ht="80" customHeight="1">
+      <c r="A173" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C159" s="4" t="inlineStr">
+      <c r="C173" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D173" s="22" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="E173" s="8" t="inlineStr">
         <is>
           <t>미생물 번식 억제제.</t>
         </is>
       </c>
-      <c r="D159" s="4" t="inlineStr">
+      <c r="F173" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="32" customHeight="1">
-      <c r="A160" s="4" t="inlineStr">
+    <row r="174" ht="32" customHeight="1">
+      <c r="A174" s="8" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>0~6g</t>
         </is>
       </c>
-      <c r="C160" s="4" t="inlineStr">
+      <c r="C174" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D174" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E174" s="8" t="inlineStr">
         <is>
           <t>보습제. 원하시면 넣어주세요.</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr">
+      <c r="F174" s="8" t="inlineStr">
         <is>
           <t>리피듀어, / 식물성글리세린</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="48" customHeight="1">
-      <c r="A161" s="4" t="inlineStr">
+    <row r="175" ht="64" customHeight="1">
+      <c r="A175" s="8" t="inlineStr">
         <is>
           <t>로즈우드에센셜오일</t>
         </is>
       </c>
-      <c r="B161" s="4" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>4~8방울</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
+      <c r="C175" s="9" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D175" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
         <is>
           <t>아로마테라피, / 장미향이 나는 제라늄, 모든 피부</t>
         </is>
       </c>
-      <c r="D161" s="4" t="inlineStr">
+      <c r="F175" s="8" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈제라늄 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="64" customHeight="1">
-      <c r="A162" s="4" t="inlineStr">
+    <row r="176" ht="80" customHeight="1">
+      <c r="A176" s="8" t="inlineStr">
         <is>
           <t>알로에모이스트</t>
         </is>
       </c>
-      <c r="B162" s="4" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C162" s="4" t="inlineStr">
+      <c r="C176" s="9" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="D176" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E176" s="8" t="inlineStr">
         <is>
           <t>자체점증, 가용화안정, 수분공급 , 진정</t>
         </is>
       </c>
-      <c r="D162" s="4" t="inlineStr">
+      <c r="F176" s="8" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="5" t="inlineStr">
+    <row r="177" ht="14" customHeight="1">
+      <c r="A177" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 4 · 유화 3 · 활성 92 · 향 0 · 방부 1</t>
+        </is>
+      </c>
+      <c r="B177" s="15" t="n"/>
+      <c r="C177" s="15" t="n"/>
+      <c r="D177" s="15" t="n"/>
+      <c r="E177" s="15" t="n"/>
+      <c r="F177" s="15" t="n"/>
+    </row>
+    <row r="178" ht="14" customHeight="1">
+      <c r="A178" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B163" s="6" t="n"/>
-      <c r="C163" s="6" t="n"/>
-      <c r="D163" s="6" t="n"/>
-    </row>
-    <row r="164" ht="384" customHeight="1">
-      <c r="A164" s="7" t="inlineStr">
+      <c r="B178" s="17" t="n"/>
+      <c r="C178" s="17" t="n"/>
+      <c r="D178" s="17" t="n"/>
+      <c r="E178" s="17" t="n"/>
+      <c r="F178" s="17" t="n"/>
+    </row>
+    <row r="179" ht="384" customHeight="1">
+      <c r="A179" s="18" t="inlineStr">
         <is>
           <t>뱀독 볼륨에센스(젤)은
 바르는 보톡스인 씨네이크펩타이드 최대함량인 4%와
@@ -5082,8 +6294,8 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="208" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
+    <row r="180" ht="208" customHeight="1">
+      <c r="A180" s="18" t="inlineStr">
         <is>
           <t>살모사의 뱀독에서 추출한 단백질은
 유방암 세포의 성장을 70%나 억제하는 것으로 밝혀지기도 했습니다.
@@ -5101,18 +6313,20 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="14" customHeight="1">
-      <c r="A166" s="5" t="inlineStr">
+    <row r="181" ht="14" customHeight="1">
+      <c r="A181" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B166" s="6" t="n"/>
-      <c r="C166" s="6" t="n"/>
-      <c r="D166" s="6" t="n"/>
-    </row>
-    <row r="167" ht="80" customHeight="1">
-      <c r="A167" s="7" t="inlineStr">
+      <c r="B181" s="17" t="n"/>
+      <c r="C181" s="17" t="n"/>
+      <c r="D181" s="17" t="n"/>
+      <c r="E181" s="17" t="n"/>
+      <c r="F181" s="17" t="n"/>
+    </row>
+    <row r="182" ht="80" customHeight="1">
+      <c r="A182" s="18" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.동백오일과 올리브리퀴드를 먼저 섞어주세요.
@@ -5121,91 +6335,137 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="6" customHeight="1"/>
-    <row r="169" ht="22" customHeight="1">
-      <c r="A169" s="1" t="inlineStr">
+    <row r="183" ht="6" customHeight="1"/>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="5" t="inlineStr">
         <is>
           <t>아임레알 제주화산송이팩    [(트러블, 모공이 넓은 피부) / 1회분량]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B169" s="2" t="n"/>
-      <c r="C169" s="2" t="n"/>
-      <c r="D169" s="2" t="n"/>
-    </row>
-    <row r="170" ht="15" customHeight="1">
-      <c r="A170" s="3" t="inlineStr">
+      <c r="B184" s="6" t="n"/>
+      <c r="C184" s="6" t="n"/>
+      <c r="D184" s="6" t="n"/>
+      <c r="E184" s="6" t="n"/>
+      <c r="F184" s="6" t="n"/>
+    </row>
+    <row r="185" ht="15" customHeight="1">
+      <c r="A185" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B170" s="3" t="inlineStr">
+      <c r="B185" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C170" s="3" t="inlineStr">
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D170" s="3" t="inlineStr">
+      <c r="F185" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="64" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
+    <row r="186" ht="80" customHeight="1">
+      <c r="A186" s="19" t="inlineStr">
         <is>
           <t>제주 화산송이분말</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B186" s="19" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C171" s="8" t="inlineStr">
+      <c r="C186" s="20" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="D186" s="26" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="E186" s="19" t="inlineStr">
         <is>
           <t>섭씨 2000도의 화산작용이 만든 기능성 미네럴, 제주 화산석 송이 / (먹는 '송이(버섯)' 아니죠^^) / 화산송이 7 : 카오링클레이3</t>
         </is>
       </c>
-      <c r="D171" s="8" t="n"/>
-    </row>
-    <row r="172" ht="48" customHeight="1">
-      <c r="A172" s="8" t="inlineStr">
+      <c r="F186" s="19" t="n"/>
+    </row>
+    <row r="187" ht="64" customHeight="1">
+      <c r="A187" s="19" t="inlineStr">
         <is>
           <t>위치헤이즐워터 / (편백워터)</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B187" s="19" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C172" s="8" t="inlineStr">
+      <c r="C187" s="20" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D187" s="21" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E187" s="19" t="inlineStr">
         <is>
           <t>제주화산송이 양의 반이하의 양, 정제수도 가능, 위치헤즐은 수렴, 트러블, 모공 넓은 피부적합</t>
         </is>
       </c>
-      <c r="D172" s="8" t="inlineStr">
+      <c r="F187" s="19" t="inlineStr">
         <is>
           <t>정수기 물, 수돗물^^, 녹차우린 물. 어성초우린 물</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="14" customHeight="1">
-      <c r="A173" s="5" t="inlineStr">
+    <row r="188" ht="14" customHeight="1">
+      <c r="A188" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 23 · 색소 77</t>
+        </is>
+      </c>
+      <c r="B188" s="15" t="n"/>
+      <c r="C188" s="15" t="n"/>
+      <c r="D188" s="15" t="n"/>
+      <c r="E188" s="15" t="n"/>
+      <c r="F188" s="15" t="n"/>
+    </row>
+    <row r="189" ht="14" customHeight="1">
+      <c r="A189" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B173" s="6" t="n"/>
-      <c r="C173" s="6" t="n"/>
-      <c r="D173" s="6" t="n"/>
-    </row>
-    <row r="174" ht="368" customHeight="1">
-      <c r="A174" s="9" t="inlineStr">
+      <c r="B189" s="17" t="n"/>
+      <c r="C189" s="17" t="n"/>
+      <c r="D189" s="17" t="n"/>
+      <c r="E189" s="17" t="n"/>
+      <c r="F189" s="17" t="n"/>
+    </row>
+    <row r="190" ht="368" customHeight="1">
+      <c r="A190" s="23" t="inlineStr">
         <is>
           <t>제주화산송이,
 먹는 송이가 아니죠^^
@@ -5230,22 +6490,26 @@
 초간단 레알 화산송이팩으로 피부 피지와 노폐물을 관리해보세요.</t>
         </is>
       </c>
-      <c r="B174" s="10" t="n"/>
-      <c r="C174" s="10" t="n"/>
-      <c r="D174" s="10" t="n"/>
-    </row>
-    <row r="175" ht="14" customHeight="1">
-      <c r="A175" s="5" t="inlineStr">
+      <c r="B190" s="24" t="n"/>
+      <c r="C190" s="24" t="n"/>
+      <c r="D190" s="24" t="n"/>
+      <c r="E190" s="24" t="n"/>
+      <c r="F190" s="24" t="n"/>
+    </row>
+    <row r="191" ht="14" customHeight="1">
+      <c r="A191" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B175" s="6" t="n"/>
-      <c r="C175" s="6" t="n"/>
-      <c r="D175" s="6" t="n"/>
-    </row>
-    <row r="176" ht="288" customHeight="1">
-      <c r="A176" s="9" t="inlineStr">
+      <c r="B191" s="17" t="n"/>
+      <c r="C191" s="17" t="n"/>
+      <c r="D191" s="17" t="n"/>
+      <c r="E191" s="17" t="n"/>
+      <c r="F191" s="17" t="n"/>
+    </row>
+    <row r="192" ht="288" customHeight="1">
+      <c r="A192" s="23" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1. 제주화산송이를 두스푼(약10g)계량하시고
@@ -5265,249 +6529,367 @@
 8.팩을 갤때 사용하셨던 플로럴워터로 피부결을 정돈하세요.</t>
         </is>
       </c>
-      <c r="B176" s="10" t="n"/>
-      <c r="C176" s="10" t="n"/>
-      <c r="D176" s="10" t="n"/>
-    </row>
-    <row r="177" ht="6" customHeight="1"/>
-    <row r="178" ht="22" customHeight="1">
-      <c r="A178" s="1" t="inlineStr">
+      <c r="B192" s="24" t="n"/>
+      <c r="C192" s="24" t="n"/>
+      <c r="D192" s="24" t="n"/>
+      <c r="E192" s="24" t="n"/>
+      <c r="F192" s="24" t="n"/>
+    </row>
+    <row r="193" ht="6" customHeight="1"/>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="5" t="inlineStr">
         <is>
           <t>TX 토닝 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B178" s="2" t="n"/>
-      <c r="C178" s="2" t="n"/>
-      <c r="D178" s="2" t="n"/>
-    </row>
-    <row r="179" ht="15" customHeight="1">
-      <c r="A179" s="3" t="inlineStr">
+      <c r="B194" s="6" t="n"/>
+      <c r="C194" s="6" t="n"/>
+      <c r="D194" s="6" t="n"/>
+      <c r="E194" s="6" t="n"/>
+      <c r="F194" s="6" t="n"/>
+    </row>
+    <row r="195" ht="15" customHeight="1">
+      <c r="A195" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr">
+      <c r="B195" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C179" s="3" t="inlineStr">
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="F195" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="32" customHeight="1">
-      <c r="A180" s="4" t="inlineStr">
+    <row r="196" ht="32" customHeight="1">
+      <c r="A196" s="8" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E196" s="8" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수 함유 / 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="F196" s="8" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="32" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
+    <row r="197" ht="48" customHeight="1">
+      <c r="A197" s="8" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>22g</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C197" s="9" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="D197" s="21" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E197" s="8" t="inlineStr">
         <is>
           <t>불가리아 장미수</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="F197" s="8" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="16" customHeight="1">
-      <c r="A182" s="4" t="inlineStr">
+    <row r="198" ht="16" customHeight="1">
+      <c r="A198" s="8" t="inlineStr">
         <is>
           <t>슈퍼시카4</t>
         </is>
       </c>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="B198" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="C198" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D198" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E198" s="8" t="inlineStr">
         <is>
           <t>병풀의 핵심성분 4가지 복합물</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="F198" s="8" t="inlineStr">
         <is>
           <t>병풀추출물</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="16" customHeight="1">
-      <c r="A183" s="4" t="inlineStr">
+    <row r="199" ht="32" customHeight="1">
+      <c r="A199" s="8" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B183" s="4" t="inlineStr">
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C199" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D199" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E199" s="8" t="inlineStr">
         <is>
           <t>비타민B3, 식약처 기능성 고시원료</t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="F199" s="8" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="48" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
+    <row r="200" ht="48" customHeight="1">
+      <c r="A200" s="8" t="inlineStr">
         <is>
           <t>프로바이오틱스3</t>
         </is>
       </c>
-      <c r="B184" s="4" t="inlineStr">
+      <c r="B200" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C200" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D200" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E200" s="8" t="inlineStr">
         <is>
           <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="F200" s="8" t="inlineStr">
         <is>
           <t>사카로, 비피다, 갈락토, 콤부차발효여과물..</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="16" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
+    <row r="201" ht="16" customHeight="1">
+      <c r="A201" s="8" t="inlineStr">
         <is>
           <t>덱스판테놀</t>
         </is>
       </c>
-      <c r="B185" s="4" t="inlineStr">
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="C201" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D201" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E201" s="8" t="inlineStr">
         <is>
           <t>비타민B5, 보습 재생</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="F201" s="8" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="48" customHeight="1">
-      <c r="A186" s="4" t="inlineStr">
+    <row r="202" ht="64" customHeight="1">
+      <c r="A202" s="8" t="inlineStr">
         <is>
           <t>트라넥삼산 (펩타이드)</t>
         </is>
       </c>
-      <c r="B186" s="4" t="inlineStr">
+      <c r="B202" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C186" s="4" t="inlineStr">
+      <c r="C202" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D202" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E202" s="8" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="D186" s="4" t="inlineStr">
+      <c r="F202" s="8" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="16" customHeight="1">
-      <c r="A187" s="4" t="inlineStr">
+    <row r="203" ht="16" customHeight="1">
+      <c r="A203" s="8" t="inlineStr">
         <is>
           <t>글루타치온</t>
         </is>
       </c>
-      <c r="B187" s="4" t="inlineStr">
+      <c r="B203" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C187" s="4" t="inlineStr">
+      <c r="C203" s="9" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D203" s="10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E203" s="8" t="inlineStr">
         <is>
           <t>미백효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="D187" s="4" t="n"/>
-    </row>
-    <row r="188" ht="48" customHeight="1">
-      <c r="A188" s="4" t="inlineStr">
+      <c r="F203" s="8" t="n"/>
+    </row>
+    <row r="204" ht="64" customHeight="1">
+      <c r="A204" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B188" s="4" t="inlineStr">
+      <c r="B204" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C188" s="4" t="inlineStr">
+      <c r="C204" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D204" s="22" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="E204" s="8" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="D188" s="4" t="inlineStr">
+      <c r="F204" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="14" customHeight="1">
-      <c r="A189" s="5" t="inlineStr">
+    <row r="205" ht="14" customHeight="1">
+      <c r="A205" s="14" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 22 · 활성 76 · 방부 2</t>
+        </is>
+      </c>
+      <c r="B205" s="15" t="n"/>
+      <c r="C205" s="15" t="n"/>
+      <c r="D205" s="15" t="n"/>
+      <c r="E205" s="15" t="n"/>
+      <c r="F205" s="15" t="n"/>
+    </row>
+    <row r="206" ht="14" customHeight="1">
+      <c r="A206" s="16" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B189" s="6" t="n"/>
-      <c r="C189" s="6" t="n"/>
-      <c r="D189" s="6" t="n"/>
-    </row>
-    <row r="190" ht="384" customHeight="1">
-      <c r="A190" s="7" t="inlineStr">
+      <c r="B206" s="17" t="n"/>
+      <c r="C206" s="17" t="n"/>
+      <c r="D206" s="17" t="n"/>
+      <c r="E206" s="17" t="n"/>
+      <c r="F206" s="17" t="n"/>
+    </row>
+    <row r="207" ht="384" customHeight="1">
+      <c r="A207" s="18" t="inlineStr">
         <is>
           <t>기미, 잡티 초기 진압에 TX 토닝 젤 (100g)
 난이도 : 하
@@ -5536,8 +6918,8 @@
         </is>
       </c>
     </row>
-    <row r="191" ht="80" customHeight="1">
-      <c r="A191" s="7" t="inlineStr">
+    <row r="208" ht="80" customHeight="1">
+      <c r="A208" s="18" t="inlineStr">
         <is>
           <t>현대약품 계열사 특허 성분)
 트라넥삼산과 나이아신아마이드를
@@ -5547,18 +6929,20 @@
         </is>
       </c>
     </row>
-    <row r="192" ht="14" customHeight="1">
-      <c r="A192" s="5" t="inlineStr">
+    <row r="209" ht="14" customHeight="1">
+      <c r="A209" s="16" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B192" s="6" t="n"/>
-      <c r="C192" s="6" t="n"/>
-      <c r="D192" s="6" t="n"/>
-    </row>
-    <row r="193" ht="64" customHeight="1">
-      <c r="A193" s="7" t="inlineStr">
+      <c r="B209" s="17" t="n"/>
+      <c r="C209" s="17" t="n"/>
+      <c r="D209" s="17" t="n"/>
+      <c r="E209" s="17" t="n"/>
+      <c r="F209" s="17" t="n"/>
+    </row>
+    <row r="210" ht="64" customHeight="1">
+      <c r="A210" s="18" t="inlineStr">
         <is>
           <t>TX 토닝 젤 토너 만들기
 1. 모든 재료를 계량합니다.
@@ -5567,105 +6951,121 @@
         </is>
       </c>
     </row>
-    <row r="194" ht="6" customHeight="1"/>
+    <row r="211" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="79">
-    <mergeCell ref="A150:D150"/>
-    <mergeCell ref="A122:D122"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A152:D152"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A176:D176"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A178:D178"/>
-    <mergeCell ref="A124:D124"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A164:D164"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A149:D149"/>
-    <mergeCell ref="A163:D163"/>
-    <mergeCell ref="A85:D85"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A135:D135"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A125:D125"/>
-    <mergeCell ref="A190:D190"/>
-    <mergeCell ref="A111:D111"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A127:D127"/>
-    <mergeCell ref="A167:D167"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A191:D191"/>
-    <mergeCell ref="A169:D169"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A90:D90"/>
-    <mergeCell ref="A136:D136"/>
-    <mergeCell ref="A192:D192"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A165:D165"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A173:D173"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A166:D166"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A133:D133"/>
-    <mergeCell ref="A193:D193"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A147:D147"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A148:D148"/>
-    <mergeCell ref="A123:D123"/>
-    <mergeCell ref="A138:D138"/>
-    <mergeCell ref="A110:D110"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A174:D174"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A189:D189"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A175:D175"/>
+  <mergeCells count="95">
+    <mergeCell ref="A205:F205"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="A161:F161"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A163:F163"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A206:F206"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A182:F182"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A191:F191"/>
+    <mergeCell ref="A178:F178"/>
+    <mergeCell ref="A162:F162"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A177:F177"/>
+    <mergeCell ref="A208:F208"/>
+    <mergeCell ref="A164:F164"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="A179:F179"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A181:F181"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A111:F111"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A192:F192"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A194:F194"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A123:F123"/>
+    <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A146:F146"/>
+    <mergeCell ref="A69:F69"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A178" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>

--- a/카드_아키타입/02_젤.xlsx
+++ b/카드_아키타입/02_젤.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,10 @@
     </font>
     <font>
       <color rgb="003A3A3A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="007A4A2A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -55,7 +59,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +74,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF6DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECE0"/>
       </patternFill>
     </fill>
     <fill>
@@ -169,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -179,20 +188,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -204,22 +214,22 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -227,17 +237,20 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -319,7 +332,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7848600" y="1092200"/>
+    <pos x="7848600" y="1854200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -339,7 +352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="1092200"/>
+    <pos x="9696450" y="1854200"/>
     <ext cx="1809750" cy="1619250"/>
     <pic>
       <nvPicPr>
@@ -359,7 +372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="1092200"/>
+    <pos x="11544300" y="1854200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -379,7 +392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="1092200"/>
+    <pos x="13392150" y="1854200"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -399,7 +412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="2940050"/>
+    <pos x="7848600" y="3702049"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -419,7 +432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="2940050"/>
+    <pos x="9696450" y="3702049"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -439,7 +452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="2940050"/>
+    <pos x="11544300" y="3702049"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -459,7 +472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="2940050"/>
+    <pos x="13392150" y="3702049"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -479,7 +492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="4787900"/>
+    <pos x="7848600" y="5549900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -499,7 +512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="4787900"/>
+    <pos x="9696450" y="5549900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -519,7 +532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="14973300"/>
+    <pos x="7848600" y="15735300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -539,7 +552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="14973300"/>
+    <pos x="9696450" y="15735300"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -559,7 +572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="14973300"/>
+    <pos x="11544300" y="15735300"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -579,7 +592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="14973300"/>
+    <pos x="13392150" y="15735300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -599,7 +612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="16821150"/>
+    <pos x="7848600" y="17583150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -619,7 +632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="16821150"/>
+    <pos x="9696450" y="17583150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -639,7 +652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="21539200"/>
+    <pos x="7848600" y="22301200"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -659,7 +672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="21539200"/>
+    <pos x="9696450" y="22301200"/>
     <ext cx="1809750" cy="1485900"/>
     <pic>
       <nvPicPr>
@@ -679,7 +692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="21539200"/>
+    <pos x="11544300" y="22301200"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -699,7 +712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="21539200"/>
+    <pos x="13392150" y="22301200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -719,7 +732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="23387050"/>
+    <pos x="7848600" y="24149050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -739,7 +752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="23387050"/>
+    <pos x="9696450" y="24149050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -759,7 +772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="23387050"/>
+    <pos x="11544300" y="24149050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -779,7 +792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="23387050"/>
+    <pos x="13392150" y="24149050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -799,7 +812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="25234900"/>
+    <pos x="7848600" y="25996900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -819,7 +832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="31153100"/>
+    <pos x="7848600" y="31915100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -839,7 +852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="31153100"/>
+    <pos x="9696450" y="31915100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -859,7 +872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="31153100"/>
+    <pos x="11544300" y="31915100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -879,7 +892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="31153100"/>
+    <pos x="13392150" y="31915100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -899,7 +912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="33000950"/>
+    <pos x="7848600" y="33762950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -919,7 +932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="37312600"/>
+    <pos x="7848600" y="38074600"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -939,7 +952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="37312600"/>
+    <pos x="9696450" y="38074600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -959,7 +972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="37312600"/>
+    <pos x="11544300" y="38074600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -979,7 +992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="37312600"/>
+    <pos x="13392150" y="38074600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -999,7 +1012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="47739300"/>
+    <pos x="7848600" y="48501300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1019,7 +1032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="47739300"/>
+    <pos x="9696450" y="48501300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1039,7 +1052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="47739300"/>
+    <pos x="11544300" y="48501300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1059,7 +1072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="47739300"/>
+    <pos x="13392150" y="48501300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1079,7 +1092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="53898800"/>
+    <pos x="7848600" y="54660800"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1099,7 +1112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="53898800"/>
+    <pos x="9696450" y="54660800"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -1119,7 +1132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="53898800"/>
+    <pos x="11544300" y="54660800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1139,7 +1152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="53898800"/>
+    <pos x="13392150" y="54660800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1159,7 +1172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="55746650"/>
+    <pos x="7848600" y="56508650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1179,7 +1192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="61683900"/>
+    <pos x="7848600" y="62445900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1199,7 +1212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="61683900"/>
+    <pos x="9696450" y="62445900"/>
     <ext cx="1809750" cy="752475"/>
     <pic>
       <nvPicPr>
@@ -1219,7 +1232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="61683900"/>
+    <pos x="11544300" y="62445900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1239,7 +1252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="61683900"/>
+    <pos x="13392150" y="62445900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1259,7 +1272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="63531750"/>
+    <pos x="7848600" y="64293750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1279,7 +1292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="68453000"/>
+    <pos x="7848600" y="69215000"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1299,7 +1312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="68453000"/>
+    <pos x="9696450" y="69215000"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1319,7 +1332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="73393300"/>
+    <pos x="7848600" y="74155300"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1339,7 +1352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="80187800"/>
+    <pos x="7848600" y="80949800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1359,7 +1372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="80187800"/>
+    <pos x="9696450" y="80949800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1379,7 +1392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="80187800"/>
+    <pos x="11544300" y="80949800"/>
     <ext cx="1809750" cy="485775"/>
     <pic>
       <nvPicPr>
@@ -1399,7 +1412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="80187800"/>
+    <pos x="13392150" y="80949800"/>
     <ext cx="952500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1419,7 +1432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="82035650"/>
+    <pos x="7848600" y="82797650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1439,7 +1452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="82035650"/>
+    <pos x="9696450" y="82797650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1459,7 +1472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="82035650"/>
+    <pos x="11544300" y="82797650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1479,7 +1492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="82035650"/>
+    <pos x="13392150" y="82797650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1499,7 +1512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="83883500"/>
+    <pos x="7848600" y="84645500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1519,7 +1532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="83883500"/>
+    <pos x="9696450" y="84645500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1539,7 +1552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="83883500"/>
+    <pos x="11544300" y="84645500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1559,7 +1572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="83883500"/>
+    <pos x="13392150" y="84645500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1579,7 +1592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="85731350"/>
+    <pos x="7848600" y="86493350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1599,7 +1612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="85731350"/>
+    <pos x="9696450" y="86493350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1619,7 +1632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="85731350"/>
+    <pos x="11544300" y="86493350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1639,7 +1652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="85731350"/>
+    <pos x="13392150" y="86493350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1659,7 +1672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="87579200"/>
+    <pos x="7848600" y="88341200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1679,7 +1692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="87579200"/>
+    <pos x="9696450" y="88341200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1699,7 +1712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="87579200"/>
+    <pos x="11544300" y="88341200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1719,7 +1732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="91224100"/>
+    <pos x="7848600" y="91986100"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1739,7 +1752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="98221800"/>
+    <pos x="7848600" y="98983800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1759,7 +1772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="98221800"/>
+    <pos x="9696450" y="98983800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1779,7 +1792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="98221800"/>
+    <pos x="11544300" y="98983800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1799,7 +1812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="98221800"/>
+    <pos x="13392150" y="98983800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1819,7 +1832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="100069650"/>
+    <pos x="7848600" y="100831650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1839,7 +1852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="100069650"/>
+    <pos x="9696450" y="100831650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1859,7 +1872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="100069650"/>
+    <pos x="11544300" y="100831650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1879,7 +1892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="115150900"/>
+    <pos x="7848600" y="115912900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1899,7 +1912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="115150900"/>
+    <pos x="9696450" y="115912900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1919,7 +1932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="115150900"/>
+    <pos x="11544300" y="115912900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1939,7 +1952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="115150900"/>
+    <pos x="13392150" y="115912900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1959,7 +1972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="116998750"/>
+    <pos x="7848600" y="117760750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1979,7 +1992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="116998750"/>
+    <pos x="9696450" y="117760750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1999,7 +2012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="116998750"/>
+    <pos x="11544300" y="117760750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2019,7 +2032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="116998750"/>
+    <pos x="13392150" y="117760750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2039,7 +2052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="118846600"/>
+    <pos x="7848600" y="119608600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2059,7 +2072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="118846600"/>
+    <pos x="9696450" y="119608600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2079,7 +2092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="126390400"/>
+    <pos x="7848600" y="127152400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2099,7 +2112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="126390400"/>
+    <pos x="9696450" y="127152400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2119,7 +2132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="126390400"/>
+    <pos x="11544300" y="127152400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2139,7 +2152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="126390400"/>
+    <pos x="13392150" y="127152400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2450,7 +2463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2498,191 +2511,194 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
     </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 이 제형 배합 주의·기본원칙
+· 카보머는 물에 완전 수화 후 중화(pH 조절)해야 젤이 잡힘.
+· 전해질(소금기)·고농도 알콜·산성 활성은 점도를 무너뜨릴 수 있음.
+· 기포 생기면 잠시 두어 빼거나 저속 교반.</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="6" customHeight="1"/>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>아로마 손소독제젤타입    ↗ 원본</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>408g / (=500ml)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>95%. 곡물 발효 알콜</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>카보머 1%을 함유, 알로에모이스트보다 높은 점도. 섞어주는 것만으로 간편하게 젤타입을 만들 수 있도록 만든 원료.</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="F9" s="10" t="n"/>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>22.5g</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>보습제, 향이 오랫동안 머물 수 있도록 고착제 역할을 함</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>레몬에센셜오일</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>5ml</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>천연 레몬 껍질 오일, / 상큼한 향</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 유칼립투스 등 원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  보습 4 · 활성 64 · 향 1 · 점증/pH 31</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  보습 4 · 활성 64 · 향 1 · 점증/pH 31</t>
         </is>
       </c>
       <c r="B12" s="17" t="n"/>
@@ -2691,8 +2707,20 @@
       <c r="E12" s="17" t="n"/>
       <c r="F12" s="17" t="n"/>
     </row>
-    <row r="13" ht="384" customHeight="1">
+    <row r="13" ht="14" customHeight="1">
       <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+    </row>
+    <row r="14" ht="384" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>무제 문서
 셀프 백신 중 하나가 손소독입니다.
@@ -2721,8 +2749,8 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="336" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+    <row r="15" ht="336" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>알콜류의 세균력은....
 세균 막의 지질 복합체를 파괴하고 단백질을 변성ㆍ응고시켜 살균작용을 나타낸답니다.
@@ -2748,20 +2776,20 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="17" t="n"/>
-    </row>
-    <row r="16" ht="96" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="96" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>1. 카보머프리젤을 계량해주세요. | 2. 식물성글리세린과 | 3. 에센셜오일을 비롯한 아로마베이스95까지 모든 재료를 계량해주세요.
 |
@@ -2771,291 +2799,279 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="6" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="18" ht="6" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>허니 촉촉 바디젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="8" t="n"/>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="80" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
+    <row r="21" ht="80" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>68g</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>수분, 자체 점증.</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>워터 코포아수</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>천연 레시틴으로 코포아수 버터를 리포좀화.</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>워터 아르간</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>세라마이드 (수용성)</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>세라마이드 리포좀화</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>스쿠알란, / 보르피린</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>꿀 추출물</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>원하는 / 추출물</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="64" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
+    <row r="25" ht="64" customHeight="1">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>균번식 억제제</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (알로에베라겔의 양을 67g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>스윗 오렌지에센셜오일</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D26" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E25" s="19" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>오렌지 껍질 오일</t>
         </is>
       </c>
-      <c r="F25" s="19" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>네롤리에센셜오일</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>3방울</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E26" s="19" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>오렌지꽃오일, / 민감, 모든 피부</t>
         </is>
       </c>
-      <c r="F26" s="19" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 10 · 활성 88 · 향 1 · 방부 1</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 10 · 활성 88 · 향 1 · 방부 1</t>
         </is>
       </c>
       <c r="B28" s="17" t="n"/>
@@ -3064,8 +3080,20 @@
       <c r="E28" s="17" t="n"/>
       <c r="F28" s="17" t="n"/>
     </row>
-    <row r="29" ht="96" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="n"/>
+      <c r="C29" s="19" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="19" t="n"/>
+      <c r="F29" s="19" t="n"/>
+    </row>
+    <row r="30" ht="96" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>클레오파트라, 네로의 아내 포파이아 등 전설적인 미인들이 꿀과
 우유로 목욕을 했다는 것은 이미 알려진 사실인데요 그만큼 꿀은 거친
@@ -3075,351 +3103,339 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
-    </row>
-    <row r="30" ht="14" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="26" t="n"/>
+    </row>
+    <row r="31" ht="14" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="17" t="n"/>
-    </row>
-    <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="19" t="n"/>
+      <c r="D31" s="19" t="n"/>
+      <c r="E31" s="19" t="n"/>
+      <c r="F31" s="19" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>1. 모든 재료를 계량한 후
 2. 골고루 섞어주세요.
 3. 용기에 넣으면 완성.</t>
         </is>
       </c>
-      <c r="B31" s="24" t="n"/>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
-    </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="26" t="n"/>
+    </row>
+    <row r="33" ht="6" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>트러블 SSG~필링젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>내추럴 / 셀룰로오즈</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>프랑스산 목화 섬유질로 / 만든 천연 필링제.</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>티트리워터</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>37g</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>티트리 수증기 / 증류법으로 추출</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>로즈마리, / 편백워터</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="64" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. / 남은 재료 활용 팁 : 젤타입스킨으로 사용가능, / 헤어에센스로 사용가능.</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>카보폴프리젤</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="48" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>알란토인분말</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D38" s="10" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>진정, 계량스푼 작은 쪽 깎아서 4개면 0.2g</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>마치현추출물</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D39" s="10" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>쇠비름, 진정, / 트러블 관리</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>어성초, / 병풀 추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>3.8g</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="64" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D41" s="22" t="inlineStr">
+      <c r="D42" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (티트리워터의 양을 36g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>레몬EO</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>레몬껍질오일,상큼, 아로마테라피</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>무향 또는 / 원하는 EO</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 38 · 보습 4 · 활성 46 · 향 0 · 방부 1 · 점증/pH 10</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="n"/>
-      <c r="C43" s="15" t="n"/>
-      <c r="D43" s="15" t="n"/>
-      <c r="E43" s="15" t="n"/>
-      <c r="F43" s="15" t="n"/>
     </row>
     <row r="44" ht="14" customHeight="1">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 38 · 보습 4 · 활성 46 · 향 0 · 방부 1 · 점증/pH 10</t>
         </is>
       </c>
       <c r="B44" s="17" t="n"/>
@@ -3428,8 +3444,20 @@
       <c r="E44" s="17" t="n"/>
       <c r="F44" s="17" t="n"/>
     </row>
-    <row r="45" ht="224" customHeight="1">
+    <row r="45" ht="14" customHeight="1">
       <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="n"/>
+      <c r="C45" s="19" t="n"/>
+      <c r="D45" s="19" t="n"/>
+      <c r="E45" s="19" t="n"/>
+      <c r="F45" s="19" t="n"/>
+    </row>
+    <row r="46" ht="224" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>누구에게나 '때'는 있습니다.
 이 '때'관리만 잘 해줘도
@@ -3448,20 +3476,20 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="17" t="n"/>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
-      <c r="F46" s="17" t="n"/>
-    </row>
-    <row r="47" ht="96" customHeight="1">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="B47" s="19" t="n"/>
+      <c r="C47" s="19" t="n"/>
+      <c r="D47" s="19" t="n"/>
+      <c r="E47" s="19" t="n"/>
+      <c r="F47" s="19" t="n"/>
+    </row>
+    <row r="48" ht="96" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>1. 알란토인분말 0.2g은 계량스푼 작은 쪽에 깍아서 4개로 해주세요.
 2. 비커에 넣고 내추럴 셀룰로오즈을 비롯 모든 재료를
@@ -3472,223 +3500,211 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="6" customHeight="1"/>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
+    <row r="49" ht="6" customHeight="1"/>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>이데베논 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="6" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="6" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
+    <row r="52" ht="48" customHeight="1">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>로즈 플라워젤</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr">
+      <c r="B52" s="21" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C52" s="22" t="inlineStr">
         <is>
           <t>87%</t>
         </is>
       </c>
-      <c r="D51" s="10" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E51" s="19" t="inlineStr">
+      <c r="E52" s="21" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 젤타입으로. / 에코보습제, 알란토인 함유</t>
         </is>
       </c>
-      <c r="F51" s="19" t="inlineStr">
+      <c r="F52" s="21" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔, / 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="19" t="inlineStr">
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="21" t="inlineStr">
         <is>
           <t>이데베논</t>
         </is>
       </c>
-      <c r="B52" s="19" t="inlineStr">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C52" s="20" t="inlineStr">
+      <c r="C53" s="22" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D52" s="10" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E52" s="19" t="inlineStr">
+      <c r="E53" s="21" t="inlineStr">
         <is>
           <t>코엔자임의 10배, / 항산화효과 / 레시피 처방시 500ppm 함유크림 완성.</t>
         </is>
       </c>
-      <c r="F52" s="19" t="n"/>
-    </row>
-    <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="19" t="inlineStr">
+      <c r="F53" s="21" t="n"/>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
-      <c r="B53" s="19" t="inlineStr">
+      <c r="B54" s="21" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C53" s="20" t="inlineStr">
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D53" s="10" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E53" s="19" t="inlineStr">
+      <c r="E54" s="21" t="inlineStr">
         <is>
           <t>비타민 펩타이드, 화이트닝</t>
         </is>
       </c>
-      <c r="F53" s="19" t="inlineStr">
+      <c r="F54" s="21" t="inlineStr">
         <is>
           <t>4GF, / 씨네이크펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="64" customHeight="1">
-      <c r="A54" s="19" t="inlineStr">
+    <row r="55" ht="64" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C54" s="20" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D54" s="22" t="inlineStr">
+      <c r="D55" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E54" s="19" t="inlineStr">
+      <c r="E55" s="21" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="F54" s="19" t="inlineStr">
+      <c r="F55" s="21" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (로즈플라워 겔의 양을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>다중히아루론산</t>
         </is>
       </c>
-      <c r="B55" s="19" t="inlineStr">
+      <c r="B56" s="21" t="inlineStr">
         <is>
           <t>0~5g</t>
         </is>
       </c>
-      <c r="C55" s="20" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D55" s="10" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E55" s="19" t="inlineStr">
+      <c r="E56" s="21" t="inlineStr">
         <is>
           <t>고분자, 중분자, 저분자로 이루어짐. / 피부 각층별 수분공급</t>
         </is>
       </c>
-      <c r="F55" s="19" t="inlineStr">
+      <c r="F56" s="21" t="inlineStr">
         <is>
           <t>판테놀</t>
         </is>
       </c>
-    </row>
-    <row r="56" ht="14" customHeight="1">
-      <c r="A56" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  활성 99 · 방부 1</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="n"/>
-      <c r="C56" s="15" t="n"/>
-      <c r="D56" s="15" t="n"/>
-      <c r="E56" s="15" t="n"/>
-      <c r="F56" s="15" t="n"/>
     </row>
     <row r="57" ht="14" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  활성 99 · 방부 1</t>
         </is>
       </c>
       <c r="B57" s="17" t="n"/>
@@ -3697,8 +3713,20 @@
       <c r="E57" s="17" t="n"/>
       <c r="F57" s="17" t="n"/>
     </row>
-    <row r="58" ht="112" customHeight="1">
-      <c r="A58" s="23" t="inlineStr">
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B58" s="19" t="n"/>
+      <c r="C58" s="19" t="n"/>
+      <c r="D58" s="19" t="n"/>
+      <c r="E58" s="19" t="n"/>
+      <c r="F58" s="19" t="n"/>
+    </row>
+    <row r="59" ht="112" customHeight="1">
+      <c r="A59" s="25" t="inlineStr">
         <is>
           <t>황금톡스라 불리는 ,이데베논.
 코엔자임Q10의 10배 항산화효과를 가지고 있습니다.
@@ -3709,26 +3737,26 @@
 또 급이 다른 이데베논의 항산화효과로 시간을 되돌리세요.</t>
         </is>
       </c>
-      <c r="B58" s="24" t="n"/>
-      <c r="C58" s="24" t="n"/>
-      <c r="D58" s="24" t="n"/>
-      <c r="E58" s="24" t="n"/>
-      <c r="F58" s="24" t="n"/>
-    </row>
-    <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="16" t="inlineStr">
+      <c r="B59" s="26" t="n"/>
+      <c r="C59" s="26" t="n"/>
+      <c r="D59" s="26" t="n"/>
+      <c r="E59" s="26" t="n"/>
+      <c r="F59" s="26" t="n"/>
+    </row>
+    <row r="60" ht="14" customHeight="1">
+      <c r="A60" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B59" s="17" t="n"/>
-      <c r="C59" s="17" t="n"/>
-      <c r="D59" s="17" t="n"/>
-      <c r="E59" s="17" t="n"/>
-      <c r="F59" s="17" t="n"/>
-    </row>
-    <row r="60" ht="64" customHeight="1">
-      <c r="A60" s="23" t="inlineStr">
+      <c r="B60" s="19" t="n"/>
+      <c r="C60" s="19" t="n"/>
+      <c r="D60" s="19" t="n"/>
+      <c r="E60" s="19" t="n"/>
+      <c r="F60" s="19" t="n"/>
+    </row>
+    <row r="61" ht="64" customHeight="1">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1.로즈플라워겔을 계량하고
@@ -3736,233 +3764,221 @@
 3.고른 점도가 나오면 용기에 담아주세요.</t>
         </is>
       </c>
-      <c r="B60" s="24" t="n"/>
-      <c r="C60" s="24" t="n"/>
-      <c r="D60" s="24" t="n"/>
-      <c r="E60" s="24" t="n"/>
-      <c r="F60" s="24" t="n"/>
-    </row>
-    <row r="61" ht="6" customHeight="1"/>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="B61" s="26" t="n"/>
+      <c r="C61" s="26" t="n"/>
+      <c r="D61" s="26" t="n"/>
+      <c r="E61" s="26" t="n"/>
+      <c r="F61" s="26" t="n"/>
+    </row>
+    <row r="62" ht="6" customHeight="1"/>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>TX 멜라 토닝 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="B63" s="8" t="n"/>
+      <c r="C63" s="8" t="n"/>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="8" t="n"/>
+      <c r="F63" s="8" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="B64" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E63" s="7" t="inlineStr">
+      <c r="E64" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F63" s="7" t="inlineStr">
+      <c r="F64" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="48" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
+    <row r="65" ht="48" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>로즈 플라워겔</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 듬뿍 담은젤, / 에코보습제, 알란토인 함유</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>알로에베라겔, / 네롤리플라워젤</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="64" customHeight="1">
-      <c r="A65" s="8" t="inlineStr">
+    <row r="66" ht="64" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>트라넥삼산 / (펩타이드)</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D65" s="10" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 / 펩타이드 말단에 합성으로 / 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>화이트 펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="48" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
+    <row r="67" ht="48" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>4GF</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C66" s="9" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D66" s="10" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>EGF, FGF, IGF, TGF / 복합 펩타이드</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>아세틸헥사, / 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="64" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
+    <row r="68" ht="64" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D67" s="22" t="inlineStr">
+      <c r="D68" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>균번식 억제, 식물복합</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>1.2헥산디올2g / (로즈플라워겔을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="48" customHeight="1">
-      <c r="A68" s="8" t="inlineStr">
+    <row r="69" ht="48" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>브라이트닝 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C68" s="9" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D69" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr">
         <is>
           <t>네롤리, 일랑일랑, 버가못FCF, / 프랑킨센스 EO 블렌딩오일, 생략 가능</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
-    </row>
-    <row r="69" ht="14" customHeight="1">
-      <c r="A69" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  활성 99 · 향 0 · 방부 1</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="n"/>
-      <c r="C69" s="15" t="n"/>
-      <c r="D69" s="15" t="n"/>
-      <c r="E69" s="15" t="n"/>
-      <c r="F69" s="15" t="n"/>
     </row>
     <row r="70" ht="14" customHeight="1">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  활성 99 · 향 0 · 방부 1</t>
         </is>
       </c>
       <c r="B70" s="17" t="n"/>
@@ -3971,8 +3987,20 @@
       <c r="E70" s="17" t="n"/>
       <c r="F70" s="17" t="n"/>
     </row>
-    <row r="71" ht="384" customHeight="1">
+    <row r="71" ht="14" customHeight="1">
       <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B71" s="19" t="n"/>
+      <c r="C71" s="19" t="n"/>
+      <c r="D71" s="19" t="n"/>
+      <c r="E71" s="19" t="n"/>
+      <c r="F71" s="19" t="n"/>
+    </row>
+    <row r="72" ht="384" customHeight="1">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t>트레넥삼산(Tranexamic acid, TX)은 원래 지혈제로 사용되고 있습니다.
 산후 , 외상, 월경, 코피 등 과다 출혈에 사용되는 항플라즈민제로 의약 성분입니다.
@@ -4001,27 +4029,27 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="18" t="inlineStr">
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="20" t="inlineStr">
         <is>
           <t>도움을 줍니다.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="14" customHeight="1">
-      <c r="A73" s="16" t="inlineStr">
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B73" s="17" t="n"/>
-      <c r="C73" s="17" t="n"/>
-      <c r="D73" s="17" t="n"/>
-      <c r="E73" s="17" t="n"/>
-      <c r="F73" s="17" t="n"/>
-    </row>
-    <row r="74" ht="64" customHeight="1">
-      <c r="A74" s="18" t="inlineStr">
+      <c r="B74" s="19" t="n"/>
+      <c r="C74" s="19" t="n"/>
+      <c r="D74" s="19" t="n"/>
+      <c r="E74" s="19" t="n"/>
+      <c r="F74" s="19" t="n"/>
+    </row>
+    <row r="75" ht="64" customHeight="1">
+      <c r="A75" s="20" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량하고
@@ -4030,227 +4058,215 @@
         </is>
       </c>
     </row>
-    <row r="75" ht="6" customHeight="1"/>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="76" ht="6" customHeight="1"/>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>콜라겐 드림 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6" t="n"/>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="6" t="n"/>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="B78" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C78" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F77" s="7" t="inlineStr">
+      <c r="F78" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="48" customHeight="1">
-      <c r="A78" s="19" t="inlineStr">
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="21" t="inlineStr">
         <is>
           <t>워터 호호바</t>
         </is>
       </c>
-      <c r="B78" s="19" t="inlineStr">
+      <c r="B79" s="21" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C78" s="20" t="inlineStr">
+      <c r="C79" s="22" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D78" s="21" t="inlineStr">
+      <c r="D79" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E78" s="19" t="inlineStr">
+      <c r="E79" s="21" t="inlineStr">
         <is>
           <t>호호바오일에 천연레시틴을 / 이용하여 리포좀화, / 수상에 쉽게 분산</t>
         </is>
       </c>
-      <c r="F78" s="19" t="inlineStr">
+      <c r="F79" s="21" t="inlineStr">
         <is>
           <t>슈퍼 곡물 / 단백질추출물</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="48" customHeight="1">
-      <c r="A79" s="19" t="inlineStr">
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="21" t="inlineStr">
         <is>
           <t>콜라겐 펩타이드</t>
         </is>
       </c>
-      <c r="B79" s="19" t="inlineStr">
+      <c r="B80" s="21" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C79" s="20" t="inlineStr">
+      <c r="C80" s="22" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D79" s="10" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E79" s="19" t="inlineStr">
+      <c r="E80" s="21" t="inlineStr">
         <is>
           <t>인체 흡수가 용이한 / 저분자화 순수 단백질 사용, / 18종의 아미노산으로 구성</t>
         </is>
       </c>
-      <c r="F79" s="19" t="inlineStr">
+      <c r="F80" s="21" t="inlineStr">
         <is>
           <t>아카시아, / 마린콜라겐</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="32" customHeight="1">
-      <c r="A80" s="19" t="inlineStr">
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="21" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
-      <c r="B80" s="19" t="inlineStr">
+      <c r="B81" s="21" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C80" s="20" t="inlineStr">
+      <c r="C81" s="22" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D80" s="10" t="inlineStr">
+      <c r="D81" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E80" s="19" t="inlineStr">
+      <c r="E81" s="21" t="inlineStr">
         <is>
           <t>비타민 펩타이드, 화이트닝</t>
         </is>
       </c>
-      <c r="F80" s="19" t="inlineStr">
+      <c r="F81" s="21" t="inlineStr">
         <is>
           <t>트라넥 / 삼산펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="19" t="inlineStr">
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="21" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B81" s="19" t="inlineStr">
+      <c r="B82" s="21" t="inlineStr">
         <is>
           <t>85g</t>
         </is>
       </c>
-      <c r="C81" s="20" t="inlineStr">
+      <c r="C82" s="22" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="D81" s="10" t="inlineStr">
+      <c r="D82" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E81" s="19" t="inlineStr">
+      <c r="E82" s="21" t="inlineStr">
         <is>
           <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="F81" s="19" t="inlineStr">
+      <c r="F82" s="21" t="inlineStr">
         <is>
           <t>네롤리플라워겔, / 알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="64" customHeight="1">
-      <c r="A82" s="19" t="inlineStr">
+    <row r="83" ht="64" customHeight="1">
+      <c r="A83" s="21" t="inlineStr">
         <is>
           <t>1,2 헥산디올</t>
         </is>
       </c>
-      <c r="B82" s="19" t="inlineStr">
+      <c r="B83" s="21" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C82" s="20" t="inlineStr">
+      <c r="C83" s="22" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D83" s="14" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E82" s="19" t="inlineStr">
+      <c r="E83" s="21" t="inlineStr">
         <is>
           <t>보습제, 자유수 억제, 균번식억제</t>
         </is>
       </c>
-      <c r="F82" s="19" t="inlineStr">
+      <c r="F83" s="21" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
-    </row>
-    <row r="83" ht="14" customHeight="1">
-      <c r="A83" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 3 · 보습 2 · 활성 95</t>
-        </is>
-      </c>
-      <c r="B83" s="15" t="n"/>
-      <c r="C83" s="15" t="n"/>
-      <c r="D83" s="15" t="n"/>
-      <c r="E83" s="15" t="n"/>
-      <c r="F83" s="15" t="n"/>
     </row>
     <row r="84" ht="14" customHeight="1">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 3 · 보습 2 · 활성 95</t>
         </is>
       </c>
       <c r="B84" s="17" t="n"/>
@@ -4259,8 +4275,20 @@
       <c r="E84" s="17" t="n"/>
       <c r="F84" s="17" t="n"/>
     </row>
-    <row r="85" ht="112" customHeight="1">
-      <c r="A85" s="23" t="inlineStr">
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B85" s="19" t="n"/>
+      <c r="C85" s="19" t="n"/>
+      <c r="D85" s="19" t="n"/>
+      <c r="E85" s="19" t="n"/>
+      <c r="F85" s="19" t="n"/>
+    </row>
+    <row r="86" ht="112" customHeight="1">
+      <c r="A86" s="25" t="inlineStr">
         <is>
           <t>25세 이후 콜라겐 합성이 줄어들므로
 피부가 탄력을 잃고 주름이 생기기 시작하며 활기를 잃게 됩니다.
@@ -4271,26 +4299,26 @@
 보습은 물론 탄력관리에 좋고 생기있는 피부를 가꿔줍니다.</t>
         </is>
       </c>
-      <c r="B85" s="24" t="n"/>
-      <c r="C85" s="24" t="n"/>
-      <c r="D85" s="24" t="n"/>
-      <c r="E85" s="24" t="n"/>
-      <c r="F85" s="24" t="n"/>
-    </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="16" t="inlineStr">
+      <c r="B86" s="26" t="n"/>
+      <c r="C86" s="26" t="n"/>
+      <c r="D86" s="26" t="n"/>
+      <c r="E86" s="26" t="n"/>
+      <c r="F86" s="26" t="n"/>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B86" s="17" t="n"/>
-      <c r="C86" s="17" t="n"/>
-      <c r="D86" s="17" t="n"/>
-      <c r="E86" s="17" t="n"/>
-      <c r="F86" s="17" t="n"/>
-    </row>
-    <row r="87" ht="64" customHeight="1">
-      <c r="A87" s="23" t="inlineStr">
+      <c r="B87" s="19" t="n"/>
+      <c r="C87" s="19" t="n"/>
+      <c r="D87" s="19" t="n"/>
+      <c r="E87" s="19" t="n"/>
+      <c r="F87" s="19" t="n"/>
+    </row>
+    <row r="88" ht="64" customHeight="1">
+      <c r="A88" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량합니다.
@@ -4298,197 +4326,185 @@
 3. 점도가 고르게 되면 용기에 옮겨 담으면 완성.</t>
         </is>
       </c>
-      <c r="B87" s="24" t="n"/>
-      <c r="C87" s="24" t="n"/>
-      <c r="D87" s="24" t="n"/>
-      <c r="E87" s="24" t="n"/>
-      <c r="F87" s="24" t="n"/>
-    </row>
-    <row r="88" ht="6" customHeight="1"/>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="B88" s="26" t="n"/>
+      <c r="C88" s="26" t="n"/>
+      <c r="D88" s="26" t="n"/>
+      <c r="E88" s="26" t="n"/>
+      <c r="F88" s="26" t="n"/>
+    </row>
+    <row r="89" ht="6" customHeight="1"/>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>셀프백신 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="6" t="n"/>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
+      <c r="B90" s="8" t="n"/>
+      <c r="C90" s="8" t="n"/>
+      <c r="D90" s="8" t="n"/>
+      <c r="E90" s="8" t="n"/>
+      <c r="F90" s="8" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B90" s="7" t="inlineStr">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
+      <c r="C91" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D90" s="7" t="inlineStr">
+      <c r="D91" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E91" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F90" s="7" t="inlineStr">
+      <c r="F91" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="8" t="inlineStr">
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="10" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C92" s="11" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D91" s="10" t="inlineStr">
+      <c r="D92" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E91" s="8" t="inlineStr">
+      <c r="E92" s="10" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="F91" s="8" t="inlineStr">
+      <c r="F92" s="10" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="48" customHeight="1">
-      <c r="A92" s="8" t="inlineStr">
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C93" s="11" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="D92" s="11" t="inlineStr">
+      <c r="D93" s="13" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E92" s="8" t="inlineStr">
+      <c r="E93" s="10" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 / 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="F92" s="8" t="n"/>
-    </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="8" t="inlineStr">
+      <c r="F93" s="10" t="n"/>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D93" s="10" t="inlineStr">
+      <c r="D94" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E93" s="8" t="inlineStr">
+      <c r="E94" s="10" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="F93" s="8" t="inlineStr">
+      <c r="F94" s="10" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="48" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>니아울리에센셜오일</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr">
+      <c r="C95" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D94" s="13" t="inlineStr">
+      <c r="D95" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E94" s="8" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr">
         <is>
           <t>광엽 티트리라 불림. 향과 성분이 / 유칼립투스와 티트리의 부드러운 버전</t>
         </is>
       </c>
-      <c r="F94" s="8" t="inlineStr">
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>유칼립튜스, 티트리 등</t>
         </is>
       </c>
-    </row>
-    <row r="95" ht="14" customHeight="1">
-      <c r="A95" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  활성 69 · 향 1 · 점증/pH 30</t>
-        </is>
-      </c>
-      <c r="B95" s="15" t="n"/>
-      <c r="C95" s="15" t="n"/>
-      <c r="D95" s="15" t="n"/>
-      <c r="E95" s="15" t="n"/>
-      <c r="F95" s="15" t="n"/>
     </row>
     <row r="96" ht="14" customHeight="1">
       <c r="A96" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  활성 69 · 향 1 · 점증/pH 30</t>
         </is>
       </c>
       <c r="B96" s="17" t="n"/>
@@ -4497,8 +4513,20 @@
       <c r="E96" s="17" t="n"/>
       <c r="F96" s="17" t="n"/>
     </row>
-    <row r="97" ht="320" customHeight="1">
+    <row r="97" ht="14" customHeight="1">
       <c r="A97" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="n"/>
+      <c r="C97" s="19" t="n"/>
+      <c r="D97" s="19" t="n"/>
+      <c r="E97" s="19" t="n"/>
+      <c r="F97" s="19" t="n"/>
+    </row>
+    <row r="98" ht="320" customHeight="1">
+      <c r="A98" s="20" t="inlineStr">
         <is>
           <t>무제 문서
 코로나19 예방을 위해 전문가들이
@@ -4523,20 +4551,20 @@
         </is>
       </c>
     </row>
-    <row r="98" ht="14" customHeight="1">
-      <c r="A98" s="16" t="inlineStr">
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B98" s="17" t="n"/>
-      <c r="C98" s="17" t="n"/>
-      <c r="D98" s="17" t="n"/>
-      <c r="E98" s="17" t="n"/>
-      <c r="F98" s="17" t="n"/>
-    </row>
-    <row r="99" ht="80" customHeight="1">
-      <c r="A99" s="18" t="inlineStr">
+      <c r="B99" s="19" t="n"/>
+      <c r="C99" s="19" t="n"/>
+      <c r="D99" s="19" t="n"/>
+      <c r="E99" s="19" t="n"/>
+      <c r="F99" s="19" t="n"/>
+    </row>
+    <row r="100" ht="80" customHeight="1">
+      <c r="A100" s="20" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -4546,223 +4574,211 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="6" customHeight="1"/>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
+    <row r="101" ht="6" customHeight="1"/>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>상큼 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B101" s="6" t="n"/>
-      <c r="C101" s="6" t="n"/>
-      <c r="D101" s="6" t="n"/>
-      <c r="E101" s="6" t="n"/>
-      <c r="F101" s="6" t="n"/>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
+      <c r="B102" s="8" t="n"/>
+      <c r="C102" s="8" t="n"/>
+      <c r="D102" s="8" t="n"/>
+      <c r="E102" s="8" t="n"/>
+      <c r="F102" s="8" t="n"/>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B102" s="7" t="inlineStr">
+      <c r="B103" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C102" s="7" t="inlineStr">
+      <c r="C103" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D102" s="7" t="inlineStr">
+      <c r="D103" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E103" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F102" s="7" t="inlineStr">
+      <c r="F103" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="21" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B103" s="19" t="inlineStr">
+      <c r="B104" s="21" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C103" s="20" t="inlineStr">
+      <c r="C104" s="22" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D103" s="10" t="inlineStr">
+      <c r="D104" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E103" s="19" t="inlineStr">
+      <c r="E104" s="21" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="F103" s="19" t="inlineStr">
+      <c r="F104" s="21" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="48" customHeight="1">
-      <c r="A104" s="19" t="inlineStr">
+    <row r="105" ht="48" customHeight="1">
+      <c r="A105" s="21" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B104" s="19" t="inlineStr">
+      <c r="B105" s="21" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C104" s="20" t="inlineStr">
+      <c r="C105" s="22" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D104" s="11" t="inlineStr">
+      <c r="D105" s="13" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E104" s="19" t="inlineStr">
+      <c r="E105" s="21" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 / 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="F104" s="19" t="n"/>
-    </row>
-    <row r="105" ht="32" customHeight="1">
-      <c r="A105" s="19" t="inlineStr">
+      <c r="F105" s="21" t="n"/>
+    </row>
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="21" t="inlineStr">
         <is>
           <t>알란토인(액상)</t>
         </is>
       </c>
-      <c r="B105" s="19" t="inlineStr">
+      <c r="B106" s="21" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C105" s="20" t="inlineStr">
+      <c r="C106" s="22" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D105" s="10" t="inlineStr">
+      <c r="D106" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E105" s="19" t="inlineStr">
+      <c r="E106" s="21" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="F105" s="19" t="inlineStr">
+      <c r="F106" s="21" t="inlineStr">
         <is>
           <t>프로폴리스추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="19" t="inlineStr">
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" s="21" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B106" s="19" t="inlineStr">
+      <c r="B107" s="21" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C106" s="20" t="inlineStr">
+      <c r="C107" s="22" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D106" s="10" t="inlineStr">
+      <c r="D107" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E106" s="19" t="inlineStr">
+      <c r="E107" s="21" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="F106" s="19" t="inlineStr">
+      <c r="F107" s="21" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="48" customHeight="1">
-      <c r="A107" s="19" t="inlineStr">
+    <row r="108" ht="48" customHeight="1">
+      <c r="A108" s="21" t="inlineStr">
         <is>
           <t>레몬쥬스EO</t>
         </is>
       </c>
-      <c r="B107" s="19" t="inlineStr">
+      <c r="B108" s="21" t="inlineStr">
         <is>
           <t>20~25방울</t>
         </is>
       </c>
-      <c r="C107" s="20" t="inlineStr">
+      <c r="C108" s="22" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D107" s="13" t="inlineStr">
+      <c r="D108" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E107" s="19" t="inlineStr">
+      <c r="E108" s="21" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드에센셜오일 / 블랜딩오일</t>
         </is>
       </c>
-      <c r="F107" s="19" t="inlineStr">
+      <c r="F108" s="21" t="inlineStr">
         <is>
           <t>레몬, 만다린, 그레이프푸룻, 라임, 오렌지에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="108" ht="14" customHeight="1">
-      <c r="A108" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  활성 74 · 향 1 · 점증/pH 25</t>
-        </is>
-      </c>
-      <c r="B108" s="15" t="n"/>
-      <c r="C108" s="15" t="n"/>
-      <c r="D108" s="15" t="n"/>
-      <c r="E108" s="15" t="n"/>
-      <c r="F108" s="15" t="n"/>
     </row>
     <row r="109" ht="14" customHeight="1">
       <c r="A109" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  활성 74 · 향 1 · 점증/pH 25</t>
         </is>
       </c>
       <c r="B109" s="17" t="n"/>
@@ -4771,8 +4787,20 @@
       <c r="E109" s="17" t="n"/>
       <c r="F109" s="17" t="n"/>
     </row>
-    <row r="110" ht="208" customHeight="1">
-      <c r="A110" s="23" t="inlineStr">
+    <row r="110" ht="14" customHeight="1">
+      <c r="A110" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B110" s="19" t="n"/>
+      <c r="C110" s="19" t="n"/>
+      <c r="D110" s="19" t="n"/>
+      <c r="E110" s="19" t="n"/>
+      <c r="F110" s="19" t="n"/>
+    </row>
+    <row r="111" ht="208" customHeight="1">
+      <c r="A111" s="25" t="inlineStr">
         <is>
           <t>무제 문서
 그 어느 때보다 손 청결이 중요한 때입니다.
@@ -4789,26 +4817,26 @@
 '상큼 손소독제 만들기'를 안내해드립니다.</t>
         </is>
       </c>
-      <c r="B110" s="24" t="n"/>
-      <c r="C110" s="24" t="n"/>
-      <c r="D110" s="24" t="n"/>
-      <c r="E110" s="24" t="n"/>
-      <c r="F110" s="24" t="n"/>
-    </row>
-    <row r="111" ht="14" customHeight="1">
-      <c r="A111" s="16" t="inlineStr">
+      <c r="B111" s="26" t="n"/>
+      <c r="C111" s="26" t="n"/>
+      <c r="D111" s="26" t="n"/>
+      <c r="E111" s="26" t="n"/>
+      <c r="F111" s="26" t="n"/>
+    </row>
+    <row r="112" ht="14" customHeight="1">
+      <c r="A112" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B111" s="17" t="n"/>
-      <c r="C111" s="17" t="n"/>
-      <c r="D111" s="17" t="n"/>
-      <c r="E111" s="17" t="n"/>
-      <c r="F111" s="17" t="n"/>
-    </row>
-    <row r="112" ht="80" customHeight="1">
-      <c r="A112" s="23" t="inlineStr">
+      <c r="B112" s="19" t="n"/>
+      <c r="C112" s="19" t="n"/>
+      <c r="D112" s="19" t="n"/>
+      <c r="E112" s="19" t="n"/>
+      <c r="F112" s="19" t="n"/>
+    </row>
+    <row r="113" ht="80" customHeight="1">
+      <c r="A113" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -4817,265 +4845,253 @@
 언제나 어디서나 사용하세요.</t>
         </is>
       </c>
-      <c r="B112" s="24" t="n"/>
-      <c r="C112" s="24" t="n"/>
-      <c r="D112" s="24" t="n"/>
-      <c r="E112" s="24" t="n"/>
-      <c r="F112" s="24" t="n"/>
-    </row>
-    <row r="113" ht="6" customHeight="1"/>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="B113" s="26" t="n"/>
+      <c r="C113" s="26" t="n"/>
+      <c r="D113" s="26" t="n"/>
+      <c r="E113" s="26" t="n"/>
+      <c r="F113" s="26" t="n"/>
+    </row>
+    <row r="114" ht="6" customHeight="1"/>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="7" t="inlineStr">
         <is>
           <t>트러블 잠잠 스팟젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="F114" s="6" t="n"/>
-    </row>
-    <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="7" t="inlineStr">
+      <c r="B115" s="8" t="n"/>
+      <c r="C115" s="8" t="n"/>
+      <c r="D115" s="8" t="n"/>
+      <c r="E115" s="8" t="n"/>
+      <c r="F115" s="8" t="n"/>
+    </row>
+    <row r="116" ht="15" customHeight="1">
+      <c r="A116" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="B116" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="C116" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="D116" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E116" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F115" s="7" t="inlineStr">
+      <c r="F116" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="8" t="inlineStr">
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="10" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B117" s="10" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="C117" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D116" s="13" t="inlineStr">
+      <c r="D117" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E116" s="8" t="inlineStr">
+      <c r="E117" s="10" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="F116" s="8" t="inlineStr">
+      <c r="F117" s="10" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="32" customHeight="1">
-      <c r="A117" s="8" t="inlineStr">
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B117" s="8" t="inlineStr">
+      <c r="B118" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D117" s="25" t="inlineStr">
+      <c r="D118" s="27" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E117" s="8" t="inlineStr">
+      <c r="E118" s="10" t="inlineStr">
         <is>
           <t>가용화제. / 물과요일이 분리되지않도록 하는 역할</t>
         </is>
       </c>
-      <c r="F117" s="8" t="inlineStr">
+      <c r="F118" s="10" t="inlineStr">
         <is>
           <t>솔루벌라이저</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="8" t="inlineStr">
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="10" t="inlineStr">
         <is>
           <t>라벤더워터</t>
         </is>
       </c>
-      <c r="B118" s="8" t="inlineStr">
+      <c r="B119" s="10" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C118" s="9" t="inlineStr">
+      <c r="C119" s="11" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D118" s="21" t="inlineStr">
+      <c r="D119" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E118" s="8" t="inlineStr">
+      <c r="E119" s="10" t="inlineStr">
         <is>
           <t>진정,재생</t>
         </is>
       </c>
-      <c r="F118" s="8" t="inlineStr">
+      <c r="F119" s="10" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="32" customHeight="1">
-      <c r="A119" s="8" t="inlineStr">
+    <row r="120" ht="32" customHeight="1">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C119" s="9" t="inlineStr">
+      <c r="C120" s="11" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D119" s="10" t="inlineStr">
+      <c r="D120" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E119" s="8" t="inlineStr">
+      <c r="E120" s="10" t="inlineStr">
         <is>
           <t>겔타입, 수분공급</t>
         </is>
       </c>
-      <c r="F119" s="8" t="inlineStr">
+      <c r="F120" s="10" t="inlineStr">
         <is>
           <t>로즈플라워겔, / 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B121" s="10" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C120" s="9" t="inlineStr">
+      <c r="C121" s="11" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D120" s="10" t="inlineStr">
+      <c r="D121" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E120" s="8" t="inlineStr">
+      <c r="E121" s="10" t="inlineStr">
         <is>
           <t>항균,진정</t>
         </is>
       </c>
-      <c r="F120" s="8" t="inlineStr">
+      <c r="F121" s="10" t="inlineStr">
         <is>
           <t>카렌듈라추출물</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="10" t="inlineStr">
         <is>
           <t>한방보존제</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B122" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C121" s="9" t="inlineStr">
+      <c r="C122" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D121" s="22" t="inlineStr">
+      <c r="D122" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E121" s="8" t="inlineStr">
+      <c r="E122" s="10" t="inlineStr">
         <is>
           <t>복합한방추출물, 균번식억제</t>
         </is>
       </c>
-      <c r="F121" s="8" t="inlineStr">
+      <c r="F122" s="10" t="inlineStr">
         <is>
           <t>수용성보존제</t>
         </is>
       </c>
-    </row>
-    <row r="122" ht="14" customHeight="1">
-      <c r="A122" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 28 · 유화 2 · 활성 66 · 향 2 · 방부 2</t>
-        </is>
-      </c>
-      <c r="B122" s="15" t="n"/>
-      <c r="C122" s="15" t="n"/>
-      <c r="D122" s="15" t="n"/>
-      <c r="E122" s="15" t="n"/>
-      <c r="F122" s="15" t="n"/>
     </row>
     <row r="123" ht="14" customHeight="1">
       <c r="A123" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 28 · 유화 2 · 활성 66 · 향 2 · 방부 2</t>
         </is>
       </c>
       <c r="B123" s="17" t="n"/>
@@ -5084,28 +5100,40 @@
       <c r="E123" s="17" t="n"/>
       <c r="F123" s="17" t="n"/>
     </row>
-    <row r="124" ht="64" customHeight="1">
+    <row r="124" ht="14" customHeight="1">
       <c r="A124" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B124" s="19" t="n"/>
+      <c r="C124" s="19" t="n"/>
+      <c r="D124" s="19" t="n"/>
+      <c r="E124" s="19" t="n"/>
+      <c r="F124" s="19" t="n"/>
+    </row>
+    <row r="125" ht="64" customHeight="1">
+      <c r="A125" s="20" t="inlineStr">
         <is>
           <t>[ 사용법 ]
 티트리에센셜오일은 국소부위에 원액을 발라도 되는 에센셜오일입니다. 스팟젤은 티트리에센셜오일을 전체의 2%를 정도로 희석한 순한 젤타입에센스입니다. 소량을 여드름이 난 부분에 발라주세요.</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="16" t="inlineStr">
+    <row r="126" ht="14" customHeight="1">
+      <c r="A126" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B125" s="17" t="n"/>
-      <c r="C125" s="17" t="n"/>
-      <c r="D125" s="17" t="n"/>
-      <c r="E125" s="17" t="n"/>
-      <c r="F125" s="17" t="n"/>
-    </row>
-    <row r="126" ht="112" customHeight="1">
-      <c r="A126" s="18" t="inlineStr">
+      <c r="B126" s="19" t="n"/>
+      <c r="C126" s="19" t="n"/>
+      <c r="D126" s="19" t="n"/>
+      <c r="E126" s="19" t="n"/>
+      <c r="F126" s="19" t="n"/>
+    </row>
+    <row r="127" ht="112" customHeight="1">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 티트리, 올리브리퀴드를 계량합니다.
@@ -5117,205 +5145,205 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="6" customHeight="1"/>
-    <row r="128" ht="22" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
+    <row r="128" ht="6" customHeight="1"/>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 바디팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B128" s="6" t="n"/>
-      <c r="C128" s="6" t="n"/>
-      <c r="D128" s="6" t="n"/>
-      <c r="E128" s="6" t="n"/>
-      <c r="F128" s="6" t="n"/>
-    </row>
-    <row r="129" ht="15" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="B129" s="8" t="n"/>
+      <c r="C129" s="8" t="n"/>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="8" t="n"/>
+      <c r="F129" s="8" t="n"/>
+    </row>
+    <row r="130" ht="15" customHeight="1">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="B130" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C129" s="7" t="inlineStr">
+      <c r="C130" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D129" s="7" t="inlineStr">
+      <c r="D130" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E129" s="7" t="inlineStr">
+      <c r="E130" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F129" s="7" t="inlineStr">
+      <c r="F130" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="32" customHeight="1">
-      <c r="A130" s="19" t="inlineStr">
+    <row r="131" ht="32" customHeight="1">
+      <c r="A131" s="21" t="inlineStr">
         <is>
           <t>그린 클레이</t>
         </is>
       </c>
-      <c r="B130" s="19" t="inlineStr">
+      <c r="B131" s="21" t="inlineStr">
         <is>
           <t>54.35%</t>
         </is>
       </c>
-      <c r="C130" s="20" t="inlineStr"/>
-      <c r="D130" s="26" t="inlineStr">
+      <c r="C131" s="22" t="inlineStr"/>
+      <c r="D131" s="28" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E130" s="19" t="inlineStr">
+      <c r="E131" s="21" t="inlineStr">
         <is>
           <t>녹색 점토, 피지·노폐물 흡착</t>
         </is>
       </c>
-      <c r="F130" s="19" t="inlineStr">
+      <c r="F131" s="21" t="inlineStr">
         <is>
           <t>핑크클레이, 카올린</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="64" customHeight="1">
-      <c r="A131" s="19" t="inlineStr">
+    <row r="132" ht="64" customHeight="1">
+      <c r="A132" s="21" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B131" s="19" t="inlineStr">
+      <c r="B132" s="21" t="inlineStr">
         <is>
           <t>43.48%</t>
         </is>
       </c>
-      <c r="C131" s="20" t="inlineStr"/>
-      <c r="D131" s="21" t="inlineStr">
+      <c r="C132" s="22" t="inlineStr"/>
+      <c r="D132" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E131" s="19" t="inlineStr">
+      <c r="E132" s="21" t="inlineStr">
         <is>
           <t>순수한 물 , / 완성품의 색을 고르게.</t>
         </is>
       </c>
-      <c r="F131" s="19" t="inlineStr">
+      <c r="F132" s="21" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="32" customHeight="1">
-      <c r="A132" s="19" t="inlineStr">
+    <row r="133" ht="32" customHeight="1">
+      <c r="A133" s="21" t="inlineStr">
         <is>
           <t>그레이프프룻EO</t>
         </is>
       </c>
-      <c r="B132" s="19" t="inlineStr">
+      <c r="B133" s="21" t="inlineStr">
         <is>
           <t>1.09%</t>
         </is>
       </c>
-      <c r="C132" s="20" t="inlineStr"/>
-      <c r="D132" s="13" t="inlineStr">
+      <c r="C133" s="22" t="inlineStr"/>
+      <c r="D133" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E132" s="19" t="inlineStr">
+      <c r="E133" s="21" t="inlineStr">
         <is>
           <t>자몽 에센셜오일, 상쾌·수렴</t>
         </is>
       </c>
-      <c r="F132" s="19" t="inlineStr">
+      <c r="F133" s="21" t="inlineStr">
         <is>
           <t>오렌지, 레몬에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="64" customHeight="1">
-      <c r="A133" s="19" t="inlineStr">
+    <row r="134" ht="64" customHeight="1">
+      <c r="A134" s="21" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B133" s="19" t="inlineStr">
+      <c r="B134" s="21" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C133" s="20" t="inlineStr"/>
-      <c r="D133" s="13" t="inlineStr">
+      <c r="C134" s="22" t="inlineStr"/>
+      <c r="D134" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E133" s="19" t="inlineStr">
+      <c r="E134" s="21" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="F133" s="19" t="inlineStr">
+      <c r="F134" s="21" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="32" customHeight="1">
-      <c r="A134" s="19" t="inlineStr">
+    <row r="135" ht="32" customHeight="1">
+      <c r="A135" s="21" t="inlineStr">
         <is>
           <t>싸이프러스</t>
         </is>
       </c>
-      <c r="B134" s="19" t="inlineStr">
+      <c r="B135" s="21" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C134" s="20" t="inlineStr"/>
-      <c r="D134" s="13" t="inlineStr">
+      <c r="C135" s="22" t="inlineStr"/>
+      <c r="D135" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E134" s="19" t="inlineStr">
+      <c r="E135" s="21" t="inlineStr">
         <is>
           <t>상록 침엽수로 / 스팀 증류법 추출, 숲향</t>
         </is>
       </c>
-      <c r="F134" s="19" t="inlineStr">
+      <c r="F135" s="21" t="inlineStr">
         <is>
           <t>편백</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="14" customHeight="1">
-      <c r="A135" s="16" t="inlineStr">
+    <row r="136" ht="14" customHeight="1">
+      <c r="A136" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B135" s="17" t="n"/>
-      <c r="C135" s="17" t="n"/>
-      <c r="D135" s="17" t="n"/>
-      <c r="E135" s="17" t="n"/>
-      <c r="F135" s="17" t="n"/>
-    </row>
-    <row r="136" ht="192" customHeight="1">
-      <c r="A136" s="23" t="inlineStr">
+      <c r="B136" s="19" t="n"/>
+      <c r="C136" s="19" t="n"/>
+      <c r="D136" s="19" t="n"/>
+      <c r="E136" s="19" t="n"/>
+      <c r="F136" s="19" t="n"/>
+    </row>
+    <row r="137" ht="192" customHeight="1">
+      <c r="A137" s="25" t="inlineStr">
         <is>
           <t>그린클레이 - 프랑스 아질레지방에서 채취하는 클레이(흙). 미세한 클레이가 피부 깊숙이 침투 모공속 노폐물 배출, 흡착, 풍부한 미네랄 성분 해독 효과를 줍니다. 셀룰라이트관리, 여드름지성 피부에 사용.
 그레이프프룻(자몽껍질오일), 제라늄, 싸이프러스, 쥬니퍼베리, 레몬, 펜넬에센셜오일이 다이어트에 효과적인 오일이다. 림프자극, 독소배출, 호르몬균형, 해독 등의 효과를 준다.
@@ -5326,227 +5354,215 @@
 4. 이런 오일로 비누, 마사지오일, 젤, 로션/크림류 제품을 만들어 병행하면 좋다.</t>
         </is>
       </c>
-      <c r="B136" s="24" t="n"/>
-      <c r="C136" s="24" t="n"/>
-      <c r="D136" s="24" t="n"/>
-      <c r="E136" s="24" t="n"/>
-      <c r="F136" s="24" t="n"/>
-    </row>
-    <row r="137" ht="14" customHeight="1">
-      <c r="A137" s="16" t="inlineStr">
+      <c r="B137" s="26" t="n"/>
+      <c r="C137" s="26" t="n"/>
+      <c r="D137" s="26" t="n"/>
+      <c r="E137" s="26" t="n"/>
+      <c r="F137" s="26" t="n"/>
+    </row>
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B137" s="17" t="n"/>
-      <c r="C137" s="17" t="n"/>
-      <c r="D137" s="17" t="n"/>
-      <c r="E137" s="17" t="n"/>
-      <c r="F137" s="17" t="n"/>
-    </row>
-    <row r="138" ht="48" customHeight="1">
-      <c r="A138" s="23" t="inlineStr">
+      <c r="B138" s="19" t="n"/>
+      <c r="C138" s="19" t="n"/>
+      <c r="D138" s="19" t="n"/>
+      <c r="E138" s="19" t="n"/>
+      <c r="F138" s="19" t="n"/>
+    </row>
+    <row r="139" ht="48" customHeight="1">
+      <c r="A139" s="25" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 그린클레이, 물, 에센셜오일을 다 넣고
 2. 잘 섞어줍니다.</t>
         </is>
       </c>
-      <c r="B138" s="24" t="n"/>
-      <c r="C138" s="24" t="n"/>
-      <c r="D138" s="24" t="n"/>
-      <c r="E138" s="24" t="n"/>
-      <c r="F138" s="24" t="n"/>
-    </row>
-    <row r="139" ht="6" customHeight="1"/>
-    <row r="140" ht="22" customHeight="1">
-      <c r="A140" s="5" t="inlineStr">
+      <c r="B139" s="26" t="n"/>
+      <c r="C139" s="26" t="n"/>
+      <c r="D139" s="26" t="n"/>
+      <c r="E139" s="26" t="n"/>
+      <c r="F139" s="26" t="n"/>
+    </row>
+    <row r="140" ht="6" customHeight="1"/>
+    <row r="141" ht="22" customHeight="1">
+      <c r="A141" s="7" t="inlineStr">
         <is>
           <t>레몬 손소독제(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B140" s="6" t="n"/>
-      <c r="C140" s="6" t="n"/>
-      <c r="D140" s="6" t="n"/>
-      <c r="E140" s="6" t="n"/>
-      <c r="F140" s="6" t="n"/>
-    </row>
-    <row r="141" ht="15" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
+      <c r="B141" s="8" t="n"/>
+      <c r="C141" s="8" t="n"/>
+      <c r="D141" s="8" t="n"/>
+      <c r="E141" s="8" t="n"/>
+      <c r="F141" s="8" t="n"/>
+    </row>
+    <row r="142" ht="15" customHeight="1">
+      <c r="A142" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B141" s="7" t="inlineStr">
+      <c r="B142" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C141" s="7" t="inlineStr">
+      <c r="C142" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D141" s="7" t="inlineStr">
+      <c r="D142" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E141" s="7" t="inlineStr">
+      <c r="E142" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F141" s="7" t="inlineStr">
+      <c r="F142" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="64" customHeight="1">
-      <c r="A142" s="8" t="inlineStr">
+    <row r="143" ht="64" customHeight="1">
+      <c r="A143" s="10" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B142" s="8" t="inlineStr">
+      <c r="B143" s="10" t="inlineStr">
         <is>
           <t>28g</t>
         </is>
       </c>
-      <c r="C142" s="9" t="inlineStr">
+      <c r="C143" s="11" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D142" s="21" t="inlineStr">
+      <c r="D143" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E142" s="8" t="inlineStr">
+      <c r="E143" s="10" t="inlineStr">
         <is>
           <t>5중 필터링 정제된 물.</t>
         </is>
       </c>
-      <c r="F142" s="8" t="inlineStr">
+      <c r="F143" s="10" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="48" customHeight="1">
-      <c r="A143" s="8" t="inlineStr">
+    <row r="144" ht="48" customHeight="1">
+      <c r="A144" s="10" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B143" s="8" t="inlineStr">
+      <c r="B144" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="C144" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D143" s="12" t="inlineStr">
+      <c r="D144" s="14" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E143" s="8" t="inlineStr">
+      <c r="E144" s="10" t="inlineStr">
         <is>
           <t>보습제, 향이 오랫동안 머물 수 / 있도록 고착제 역할을 함.</t>
         </is>
       </c>
-      <c r="F143" s="8" t="inlineStr">
+      <c r="F144" s="10" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="32" customHeight="1">
-      <c r="A144" s="8" t="inlineStr">
+    <row r="145" ht="32" customHeight="1">
+      <c r="A145" s="10" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B144" s="8" t="inlineStr">
+      <c r="B145" s="10" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="C145" s="11" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D144" s="13" t="inlineStr">
+      <c r="D145" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E144" s="8" t="inlineStr">
+      <c r="E145" s="10" t="inlineStr">
         <is>
           <t>에센셜오일 분산, 방향용으로 사용시 / 공기정화, 소독효과</t>
         </is>
       </c>
-      <c r="F144" s="8" t="inlineStr">
+      <c r="F145" s="10" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="48" customHeight="1">
-      <c r="A145" s="8" t="inlineStr">
+    <row r="146" ht="48" customHeight="1">
+      <c r="A146" s="10" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B145" s="8" t="inlineStr">
+      <c r="B146" s="10" t="inlineStr">
         <is>
           <t>15~20방울</t>
         </is>
       </c>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="C146" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D145" s="13" t="inlineStr">
+      <c r="D146" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E145" s="8" t="inlineStr">
+      <c r="E146" s="10" t="inlineStr">
         <is>
           <t>레몬껍질에서 추출한 100%천연오일. / 상큼한 향.</t>
         </is>
       </c>
-      <c r="F145" s="8" t="inlineStr">
+      <c r="F146" s="10" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 편백 등 원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="146" ht="14" customHeight="1">
-      <c r="A146" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 28 · 보습 5 · 향 67</t>
-        </is>
-      </c>
-      <c r="B146" s="15" t="n"/>
-      <c r="C146" s="15" t="n"/>
-      <c r="D146" s="15" t="n"/>
-      <c r="E146" s="15" t="n"/>
-      <c r="F146" s="15" t="n"/>
     </row>
     <row r="147" ht="14" customHeight="1">
       <c r="A147" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 28 · 보습 5 · 향 67</t>
         </is>
       </c>
       <c r="B147" s="17" t="n"/>
@@ -5555,8 +5571,20 @@
       <c r="E147" s="17" t="n"/>
       <c r="F147" s="17" t="n"/>
     </row>
-    <row r="148" ht="304" customHeight="1">
+    <row r="148" ht="14" customHeight="1">
       <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B148" s="19" t="n"/>
+      <c r="C148" s="19" t="n"/>
+      <c r="D148" s="19" t="n"/>
+      <c r="E148" s="19" t="n"/>
+      <c r="F148" s="19" t="n"/>
+    </row>
+    <row r="149" ht="304" customHeight="1">
+      <c r="A149" s="20" t="inlineStr">
         <is>
           <t>2009년 젤타입 손소독제 만들기를 위해
 하이셀을 이용해 만든 젤타입 손소독제입니다.
@@ -5580,20 +5608,20 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="14" customHeight="1">
-      <c r="A149" s="16" t="inlineStr">
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B149" s="17" t="n"/>
-      <c r="C149" s="17" t="n"/>
-      <c r="D149" s="17" t="n"/>
-      <c r="E149" s="17" t="n"/>
-      <c r="F149" s="17" t="n"/>
-    </row>
-    <row r="150" ht="288" customHeight="1">
-      <c r="A150" s="18" t="inlineStr">
+      <c r="B150" s="19" t="n"/>
+      <c r="C150" s="19" t="n"/>
+      <c r="D150" s="19" t="n"/>
+      <c r="E150" s="19" t="n"/>
+      <c r="F150" s="19" t="n"/>
+    </row>
+    <row r="151" ht="288" customHeight="1">
+      <c r="A151" s="20" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 [하이셀 계량하기]
@@ -5616,257 +5644,257 @@
         </is>
       </c>
     </row>
-    <row r="151" ht="6" customHeight="1"/>
-    <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="5" t="inlineStr">
+    <row r="152" ht="6" customHeight="1"/>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="7" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B152" s="6" t="n"/>
-      <c r="C152" s="6" t="n"/>
-      <c r="D152" s="6" t="n"/>
-      <c r="E152" s="6" t="n"/>
-      <c r="F152" s="6" t="n"/>
-    </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="7" t="inlineStr">
+      <c r="B153" s="8" t="n"/>
+      <c r="C153" s="8" t="n"/>
+      <c r="D153" s="8" t="n"/>
+      <c r="E153" s="8" t="n"/>
+      <c r="F153" s="8" t="n"/>
+    </row>
+    <row r="154" ht="15" customHeight="1">
+      <c r="A154" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B153" s="7" t="inlineStr">
+      <c r="B154" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C153" s="7" t="inlineStr">
+      <c r="C154" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D153" s="7" t="inlineStr">
+      <c r="D154" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E153" s="7" t="inlineStr">
+      <c r="E154" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F153" s="7" t="inlineStr">
+      <c r="F154" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="48" customHeight="1">
-      <c r="A154" s="19" t="inlineStr">
+    <row r="155" ht="48" customHeight="1">
+      <c r="A155" s="21" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B154" s="19" t="inlineStr">
+      <c r="B155" s="21" t="inlineStr">
         <is>
           <t>92.17%</t>
         </is>
       </c>
-      <c r="C154" s="20" t="inlineStr"/>
-      <c r="D154" s="21" t="inlineStr">
+      <c r="C155" s="22" t="inlineStr"/>
+      <c r="D155" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E154" s="19" t="inlineStr">
+      <c r="E155" s="21" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="F154" s="19" t="inlineStr">
+      <c r="F155" s="21" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="16" customHeight="1">
-      <c r="A155" s="19" t="inlineStr">
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="21" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B155" s="19" t="inlineStr">
+      <c r="B156" s="21" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C155" s="20" t="inlineStr"/>
-      <c r="D155" s="11" t="inlineStr">
+      <c r="C156" s="22" t="inlineStr"/>
+      <c r="D156" s="13" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E155" s="19" t="inlineStr">
+      <c r="E156" s="21" t="inlineStr">
         <is>
           <t>점증제총량의 1%이하</t>
         </is>
       </c>
-      <c r="F155" s="19" t="n"/>
-    </row>
-    <row r="156" ht="64" customHeight="1">
-      <c r="A156" s="19" t="inlineStr">
+      <c r="F156" s="21" t="n"/>
+    </row>
+    <row r="157" ht="64" customHeight="1">
+      <c r="A157" s="21" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B156" s="19" t="inlineStr">
+      <c r="B157" s="21" t="inlineStr">
         <is>
           <t>4.61%</t>
         </is>
       </c>
-      <c r="C156" s="20" t="inlineStr"/>
-      <c r="D156" s="12" t="inlineStr">
+      <c r="C157" s="22" t="inlineStr"/>
+      <c r="D157" s="14" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E156" s="19" t="inlineStr">
+      <c r="E157" s="21" t="inlineStr">
         <is>
           <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
-      <c r="F156" s="19" t="inlineStr">
+      <c r="F157" s="21" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="32" customHeight="1">
-      <c r="A157" s="19" t="inlineStr">
+    <row r="158" ht="32" customHeight="1">
+      <c r="A158" s="21" t="inlineStr">
         <is>
           <t>그레이프프룻EO</t>
         </is>
       </c>
-      <c r="B157" s="19" t="inlineStr">
+      <c r="B158" s="21" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C157" s="20" t="inlineStr"/>
-      <c r="D157" s="13" t="inlineStr">
+      <c r="C158" s="22" t="inlineStr"/>
+      <c r="D158" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E157" s="19" t="inlineStr">
+      <c r="E158" s="21" t="inlineStr">
         <is>
           <t>자몽 에센셜오일, 상쾌·수렴</t>
         </is>
       </c>
-      <c r="F157" s="19" t="inlineStr">
+      <c r="F158" s="21" t="inlineStr">
         <is>
           <t>오렌지, 레몬에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="32" customHeight="1">
-      <c r="A158" s="19" t="inlineStr">
+    <row r="159" ht="32" customHeight="1">
+      <c r="A159" s="21" t="inlineStr">
         <is>
           <t>페퍼민트오일</t>
         </is>
       </c>
-      <c r="B158" s="19" t="inlineStr">
+      <c r="B159" s="21" t="inlineStr">
         <is>
           <t>0.23%</t>
         </is>
       </c>
-      <c r="C158" s="20" t="inlineStr"/>
-      <c r="D158" s="27" t="inlineStr">
+      <c r="C159" s="22" t="inlineStr"/>
+      <c r="D159" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E158" s="19" t="inlineStr">
+      <c r="E159" s="21" t="inlineStr">
         <is>
           <t>허브의 고농축오일, / 시원, 커피와 시너지효과</t>
         </is>
       </c>
-      <c r="F158" s="19" t="inlineStr">
+      <c r="F159" s="21" t="inlineStr">
         <is>
           <t>티트리(항균), / 스피아민트 등</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="32" customHeight="1">
-      <c r="A159" s="19" t="inlineStr">
+    <row r="160" ht="32" customHeight="1">
+      <c r="A160" s="21" t="inlineStr">
         <is>
           <t>주니퍼베리EO</t>
         </is>
       </c>
-      <c r="B159" s="19" t="inlineStr">
+      <c r="B160" s="21" t="inlineStr">
         <is>
           <t>0.69%</t>
         </is>
       </c>
-      <c r="C159" s="20" t="inlineStr"/>
-      <c r="D159" s="13" t="inlineStr">
+      <c r="C160" s="22" t="inlineStr"/>
+      <c r="D160" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E159" s="19" t="inlineStr">
+      <c r="E160" s="21" t="inlineStr">
         <is>
           <t>주니퍼베리 에센셜오일, 수렴·정화</t>
         </is>
       </c>
-      <c r="F159" s="19" t="inlineStr">
+      <c r="F160" s="21" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="64" customHeight="1">
-      <c r="A160" s="19" t="inlineStr">
+    <row r="161" ht="64" customHeight="1">
+      <c r="A161" s="21" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B160" s="19" t="inlineStr">
+      <c r="B161" s="21" t="inlineStr">
         <is>
           <t>0.46%</t>
         </is>
       </c>
-      <c r="C160" s="20" t="inlineStr"/>
-      <c r="D160" s="13" t="inlineStr">
+      <c r="C161" s="22" t="inlineStr"/>
+      <c r="D161" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E160" s="19" t="inlineStr">
+      <c r="E161" s="21" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="F160" s="19" t="inlineStr">
+      <c r="F161" s="21" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="14" customHeight="1">
-      <c r="A161" s="16" t="inlineStr">
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B161" s="17" t="n"/>
-      <c r="C161" s="17" t="n"/>
-      <c r="D161" s="17" t="n"/>
-      <c r="E161" s="17" t="n"/>
-      <c r="F161" s="17" t="n"/>
-    </row>
-    <row r="162" ht="96" customHeight="1">
-      <c r="A162" s="23" t="inlineStr">
+      <c r="B162" s="19" t="n"/>
+      <c r="C162" s="19" t="n"/>
+      <c r="D162" s="19" t="n"/>
+      <c r="E162" s="19" t="n"/>
+      <c r="F162" s="19" t="n"/>
+    </row>
+    <row r="163" ht="96" customHeight="1">
+      <c r="A163" s="25" t="inlineStr">
         <is>
           <t>*끈적임없이 흡수되는 다이어트젤
 다이어트에 좋은 에센셜오일 6종: 그레이프프룻, 팬넬, 쥬니퍼베리, 싸이프러스, 레몬, 제라늄
@@ -5876,26 +5904,26 @@
 제라늄 - 호로몬 균형, 피지균형</t>
         </is>
       </c>
-      <c r="B162" s="24" t="n"/>
-      <c r="C162" s="24" t="n"/>
-      <c r="D162" s="24" t="n"/>
-      <c r="E162" s="24" t="n"/>
-      <c r="F162" s="24" t="n"/>
-    </row>
-    <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="16" t="inlineStr">
+      <c r="B163" s="26" t="n"/>
+      <c r="C163" s="26" t="n"/>
+      <c r="D163" s="26" t="n"/>
+      <c r="E163" s="26" t="n"/>
+      <c r="F163" s="26" t="n"/>
+    </row>
+    <row r="164" ht="14" customHeight="1">
+      <c r="A164" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B163" s="17" t="n"/>
-      <c r="C163" s="17" t="n"/>
-      <c r="D163" s="17" t="n"/>
-      <c r="E163" s="17" t="n"/>
-      <c r="F163" s="17" t="n"/>
-    </row>
-    <row r="164" ht="96" customHeight="1">
-      <c r="A164" s="23" t="inlineStr">
+      <c r="B164" s="19" t="n"/>
+      <c r="C164" s="19" t="n"/>
+      <c r="D164" s="19" t="n"/>
+      <c r="E164" s="19" t="n"/>
+      <c r="F164" s="19" t="n"/>
+    </row>
+    <row r="165" ht="96" customHeight="1">
+      <c r="A165" s="25" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 로즈워터를 계량한다.
@@ -5905,357 +5933,345 @@
 6~7. 손으로 저어서 마무리해주면 끝!</t>
         </is>
       </c>
-      <c r="B164" s="24" t="n"/>
-      <c r="C164" s="24" t="n"/>
-      <c r="D164" s="24" t="n"/>
-      <c r="E164" s="24" t="n"/>
-      <c r="F164" s="24" t="n"/>
-    </row>
-    <row r="165" ht="6" customHeight="1"/>
-    <row r="166" ht="22" customHeight="1">
-      <c r="A166" s="5" t="inlineStr">
+      <c r="B165" s="26" t="n"/>
+      <c r="C165" s="26" t="n"/>
+      <c r="D165" s="26" t="n"/>
+      <c r="E165" s="26" t="n"/>
+      <c r="F165" s="26" t="n"/>
+    </row>
+    <row r="166" ht="6" customHeight="1"/>
+    <row r="167" ht="22" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t>뱀독 볼륨 에센스(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B166" s="6" t="n"/>
-      <c r="C166" s="6" t="n"/>
-      <c r="D166" s="6" t="n"/>
-      <c r="E166" s="6" t="n"/>
-      <c r="F166" s="6" t="n"/>
-    </row>
-    <row r="167" ht="15" customHeight="1">
-      <c r="A167" s="7" t="inlineStr">
+      <c r="B167" s="8" t="n"/>
+      <c r="C167" s="8" t="n"/>
+      <c r="D167" s="8" t="n"/>
+      <c r="E167" s="8" t="n"/>
+      <c r="F167" s="8" t="n"/>
+    </row>
+    <row r="168" ht="15" customHeight="1">
+      <c r="A168" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B167" s="7" t="inlineStr">
+      <c r="B168" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C167" s="7" t="inlineStr">
+      <c r="C168" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D167" s="7" t="inlineStr">
+      <c r="D168" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E167" s="7" t="inlineStr">
+      <c r="E168" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F167" s="7" t="inlineStr">
+      <c r="F168" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="48" customHeight="1">
-      <c r="A168" s="8" t="inlineStr">
+    <row r="169" ht="48" customHeight="1">
+      <c r="A169" s="10" t="inlineStr">
         <is>
           <t>(제주산) / 비정제동백오일</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B169" s="10" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C168" s="9" t="inlineStr">
+      <c r="C169" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D168" s="27" t="inlineStr">
+      <c r="D169" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E168" s="8" t="inlineStr">
+      <c r="E169" s="10" t="inlineStr">
         <is>
           <t>올레인산 풍부 고보습, / 청정 섬 국내 제주산 야생동백씨 압착.</t>
         </is>
       </c>
-      <c r="F168" s="8" t="inlineStr">
+      <c r="F169" s="10" t="inlineStr">
         <is>
           <t>아르간, 로즈힙, 마카다미아넛오일 등</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="32" customHeight="1">
-      <c r="A169" s="8" t="inlineStr">
+    <row r="170" ht="32" customHeight="1">
+      <c r="A170" s="10" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B170" s="10" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C169" s="9" t="inlineStr">
+      <c r="C170" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D169" s="25" t="inlineStr">
+      <c r="D170" s="27" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E169" s="8" t="inlineStr">
+      <c r="E170" s="10" t="inlineStr">
         <is>
           <t>가용화제, 물에 오일이 분산되도록 도와줌</t>
         </is>
       </c>
-      <c r="F169" s="8" t="inlineStr">
+      <c r="F170" s="10" t="inlineStr">
         <is>
           <t>솔루벌라이저(Polysorbate 80)동량</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="64" customHeight="1">
-      <c r="A170" s="8" t="inlineStr">
+    <row r="171" ht="64" customHeight="1">
+      <c r="A171" s="10" t="inlineStr">
         <is>
           <t>오가닉7솔루션</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B171" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C170" s="9" t="inlineStr">
+      <c r="C171" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D170" s="10" t="inlineStr">
+      <c r="D171" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E170" s="8" t="inlineStr">
+      <c r="E171" s="10" t="inlineStr">
         <is>
           <t>비타민류가 다량 함유되어있는 / 유기농 야채(당근, 토마토,브로컬리,현미, 양배추,샐러리, 현미)를 저온 추출.</t>
         </is>
       </c>
-      <c r="F170" s="8" t="inlineStr">
+      <c r="F171" s="10" t="inlineStr">
         <is>
           <t>콜라겐, 석류,토마토,</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="144" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
+    <row r="172" ht="144" customHeight="1">
+      <c r="A172" s="10" t="inlineStr">
         <is>
           <t>씨네이크(뱀독) / 펩타이드</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B172" s="10" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C171" s="9" t="inlineStr">
+      <c r="C172" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D171" s="10" t="inlineStr">
+      <c r="D172" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E171" s="8" t="inlineStr">
+      <c r="E172" s="10" t="inlineStr">
         <is>
           <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. / 임상시 아세틸헥사펩타이드보다 효과적. / 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. / '바르는 보톡스' 등으로 인기</t>
         </is>
       </c>
-      <c r="F171" s="8" t="n"/>
-    </row>
-    <row r="172" ht="32" customHeight="1">
-      <c r="A172" s="8" t="inlineStr">
+      <c r="F172" s="10" t="n"/>
+    </row>
+    <row r="173" ht="32" customHeight="1">
+      <c r="A173" s="10" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B172" s="8" t="inlineStr">
+      <c r="B173" s="10" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C172" s="9" t="inlineStr">
+      <c r="C173" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D172" s="10" t="inlineStr">
+      <c r="D173" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E172" s="8" t="inlineStr">
+      <c r="E173" s="10" t="inlineStr">
         <is>
           <t>녹황색채소에 들어있는 비타민B3. / 식약처 인증 미백원료</t>
         </is>
       </c>
-      <c r="F172" s="8" t="inlineStr">
+      <c r="F173" s="10" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="80" customHeight="1">
-      <c r="A173" s="8" t="inlineStr">
+    <row r="174" ht="80" customHeight="1">
+      <c r="A174" s="10" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B173" s="8" t="inlineStr">
+      <c r="B174" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C173" s="9" t="inlineStr">
+      <c r="C174" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D173" s="22" t="inlineStr">
+      <c r="D174" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E173" s="8" t="inlineStr">
+      <c r="E174" s="10" t="inlineStr">
         <is>
           <t>미생물 번식 억제제.</t>
         </is>
       </c>
-      <c r="F173" s="8" t="inlineStr">
+      <c r="F174" s="10" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="32" customHeight="1">
-      <c r="A174" s="8" t="inlineStr">
+    <row r="175" ht="32" customHeight="1">
+      <c r="A175" s="10" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="10" t="inlineStr">
         <is>
           <t>0~6g</t>
         </is>
       </c>
-      <c r="C174" s="9" t="inlineStr">
+      <c r="C175" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D174" s="10" t="inlineStr">
+      <c r="D175" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E174" s="8" t="inlineStr">
+      <c r="E175" s="10" t="inlineStr">
         <is>
           <t>보습제. 원하시면 넣어주세요.</t>
         </is>
       </c>
-      <c r="F174" s="8" t="inlineStr">
+      <c r="F175" s="10" t="inlineStr">
         <is>
           <t>리피듀어, / 식물성글리세린</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="64" customHeight="1">
-      <c r="A175" s="8" t="inlineStr">
+    <row r="176" ht="64" customHeight="1">
+      <c r="A176" s="10" t="inlineStr">
         <is>
           <t>로즈우드에센셜오일</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="10" t="inlineStr">
         <is>
           <t>4~8방울</t>
         </is>
       </c>
-      <c r="C175" s="9" t="inlineStr">
+      <c r="C176" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D175" s="13" t="inlineStr">
+      <c r="D176" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E175" s="8" t="inlineStr">
+      <c r="E176" s="10" t="inlineStr">
         <is>
           <t>아로마테라피, / 장미향이 나는 제라늄, 모든 피부</t>
         </is>
       </c>
-      <c r="F175" s="8" t="inlineStr">
+      <c r="F176" s="10" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈제라늄 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="80" customHeight="1">
-      <c r="A176" s="8" t="inlineStr">
+    <row r="177" ht="80" customHeight="1">
+      <c r="A177" s="10" t="inlineStr">
         <is>
           <t>알로에모이스트</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="10" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C176" s="9" t="inlineStr">
+      <c r="C177" s="11" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D176" s="10" t="inlineStr">
+      <c r="D177" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E176" s="8" t="inlineStr">
+      <c r="E177" s="10" t="inlineStr">
         <is>
           <t>자체점증, 가용화안정, 수분공급 , 진정</t>
         </is>
       </c>
-      <c r="F176" s="8" t="inlineStr">
+      <c r="F177" s="10" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
-    </row>
-    <row r="177" ht="14" customHeight="1">
-      <c r="A177" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 4 · 유화 3 · 활성 92 · 향 0 · 방부 1</t>
-        </is>
-      </c>
-      <c r="B177" s="15" t="n"/>
-      <c r="C177" s="15" t="n"/>
-      <c r="D177" s="15" t="n"/>
-      <c r="E177" s="15" t="n"/>
-      <c r="F177" s="15" t="n"/>
     </row>
     <row r="178" ht="14" customHeight="1">
       <c r="A178" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 4 · 유화 3 · 활성 92 · 향 0 · 방부 1</t>
         </is>
       </c>
       <c r="B178" s="17" t="n"/>
@@ -6264,8 +6280,20 @@
       <c r="E178" s="17" t="n"/>
       <c r="F178" s="17" t="n"/>
     </row>
-    <row r="179" ht="384" customHeight="1">
+    <row r="179" ht="14" customHeight="1">
       <c r="A179" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B179" s="19" t="n"/>
+      <c r="C179" s="19" t="n"/>
+      <c r="D179" s="19" t="n"/>
+      <c r="E179" s="19" t="n"/>
+      <c r="F179" s="19" t="n"/>
+    </row>
+    <row r="180" ht="384" customHeight="1">
+      <c r="A180" s="20" t="inlineStr">
         <is>
           <t>뱀독 볼륨에센스(젤)은
 바르는 보톡스인 씨네이크펩타이드 최대함량인 4%와
@@ -6294,8 +6322,8 @@
         </is>
       </c>
     </row>
-    <row r="180" ht="208" customHeight="1">
-      <c r="A180" s="18" t="inlineStr">
+    <row r="181" ht="208" customHeight="1">
+      <c r="A181" s="20" t="inlineStr">
         <is>
           <t>살모사의 뱀독에서 추출한 단백질은
 유방암 세포의 성장을 70%나 억제하는 것으로 밝혀지기도 했습니다.
@@ -6313,20 +6341,20 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="14" customHeight="1">
-      <c r="A181" s="16" t="inlineStr">
+    <row r="182" ht="14" customHeight="1">
+      <c r="A182" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B181" s="17" t="n"/>
-      <c r="C181" s="17" t="n"/>
-      <c r="D181" s="17" t="n"/>
-      <c r="E181" s="17" t="n"/>
-      <c r="F181" s="17" t="n"/>
-    </row>
-    <row r="182" ht="80" customHeight="1">
-      <c r="A182" s="18" t="inlineStr">
+      <c r="B182" s="19" t="n"/>
+      <c r="C182" s="19" t="n"/>
+      <c r="D182" s="19" t="n"/>
+      <c r="E182" s="19" t="n"/>
+      <c r="F182" s="19" t="n"/>
+    </row>
+    <row r="183" ht="80" customHeight="1">
+      <c r="A183" s="20" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.동백오일과 올리브리퀴드를 먼저 섞어주세요.
@@ -6335,127 +6363,115 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="6" customHeight="1"/>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="5" t="inlineStr">
+    <row r="184" ht="6" customHeight="1"/>
+    <row r="185" ht="22" customHeight="1">
+      <c r="A185" s="7" t="inlineStr">
         <is>
           <t>아임레알 제주화산송이팩    [(트러블, 모공이 넓은 피부) / 1회분량]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B184" s="6" t="n"/>
-      <c r="C184" s="6" t="n"/>
-      <c r="D184" s="6" t="n"/>
-      <c r="E184" s="6" t="n"/>
-      <c r="F184" s="6" t="n"/>
-    </row>
-    <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="7" t="inlineStr">
+      <c r="B185" s="8" t="n"/>
+      <c r="C185" s="8" t="n"/>
+      <c r="D185" s="8" t="n"/>
+      <c r="E185" s="8" t="n"/>
+      <c r="F185" s="8" t="n"/>
+    </row>
+    <row r="186" ht="15" customHeight="1">
+      <c r="A186" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B185" s="7" t="inlineStr">
+      <c r="B186" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C185" s="7" t="inlineStr">
+      <c r="C186" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D185" s="7" t="inlineStr">
+      <c r="D186" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E185" s="7" t="inlineStr">
+      <c r="E186" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
+      <c r="F186" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="80" customHeight="1">
-      <c r="A186" s="19" t="inlineStr">
+    <row r="187" ht="80" customHeight="1">
+      <c r="A187" s="21" t="inlineStr">
         <is>
           <t>제주 화산송이분말</t>
         </is>
       </c>
-      <c r="B186" s="19" t="inlineStr">
+      <c r="B187" s="21" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C186" s="20" t="inlineStr">
+      <c r="C187" s="22" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D186" s="26" t="inlineStr">
+      <c r="D187" s="28" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E186" s="19" t="inlineStr">
+      <c r="E187" s="21" t="inlineStr">
         <is>
           <t>섭씨 2000도의 화산작용이 만든 기능성 미네럴, 제주 화산석 송이 / (먹는 '송이(버섯)' 아니죠^^) / 화산송이 7 : 카오링클레이3</t>
         </is>
       </c>
-      <c r="F186" s="19" t="n"/>
-    </row>
-    <row r="187" ht="64" customHeight="1">
-      <c r="A187" s="19" t="inlineStr">
+      <c r="F187" s="21" t="n"/>
+    </row>
+    <row r="188" ht="64" customHeight="1">
+      <c r="A188" s="21" t="inlineStr">
         <is>
           <t>위치헤이즐워터 / (편백워터)</t>
         </is>
       </c>
-      <c r="B187" s="19" t="inlineStr">
+      <c r="B188" s="21" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C187" s="20" t="inlineStr">
+      <c r="C188" s="22" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D187" s="21" t="inlineStr">
+      <c r="D188" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E187" s="19" t="inlineStr">
+      <c r="E188" s="21" t="inlineStr">
         <is>
           <t>제주화산송이 양의 반이하의 양, 정제수도 가능, 위치헤즐은 수렴, 트러블, 모공 넓은 피부적합</t>
         </is>
       </c>
-      <c r="F187" s="19" t="inlineStr">
+      <c r="F188" s="21" t="inlineStr">
         <is>
           <t>정수기 물, 수돗물^^, 녹차우린 물. 어성초우린 물</t>
         </is>
       </c>
-    </row>
-    <row r="188" ht="14" customHeight="1">
-      <c r="A188" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 23 · 색소 77</t>
-        </is>
-      </c>
-      <c r="B188" s="15" t="n"/>
-      <c r="C188" s="15" t="n"/>
-      <c r="D188" s="15" t="n"/>
-      <c r="E188" s="15" t="n"/>
-      <c r="F188" s="15" t="n"/>
     </row>
     <row r="189" ht="14" customHeight="1">
       <c r="A189" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 23 · 색소 77</t>
         </is>
       </c>
       <c r="B189" s="17" t="n"/>
@@ -6464,8 +6480,20 @@
       <c r="E189" s="17" t="n"/>
       <c r="F189" s="17" t="n"/>
     </row>
-    <row r="190" ht="368" customHeight="1">
-      <c r="A190" s="23" t="inlineStr">
+    <row r="190" ht="14" customHeight="1">
+      <c r="A190" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B190" s="19" t="n"/>
+      <c r="C190" s="19" t="n"/>
+      <c r="D190" s="19" t="n"/>
+      <c r="E190" s="19" t="n"/>
+      <c r="F190" s="19" t="n"/>
+    </row>
+    <row r="191" ht="368" customHeight="1">
+      <c r="A191" s="25" t="inlineStr">
         <is>
           <t>제주화산송이,
 먹는 송이가 아니죠^^
@@ -6490,26 +6518,26 @@
 초간단 레알 화산송이팩으로 피부 피지와 노폐물을 관리해보세요.</t>
         </is>
       </c>
-      <c r="B190" s="24" t="n"/>
-      <c r="C190" s="24" t="n"/>
-      <c r="D190" s="24" t="n"/>
-      <c r="E190" s="24" t="n"/>
-      <c r="F190" s="24" t="n"/>
-    </row>
-    <row r="191" ht="14" customHeight="1">
-      <c r="A191" s="16" t="inlineStr">
+      <c r="B191" s="26" t="n"/>
+      <c r="C191" s="26" t="n"/>
+      <c r="D191" s="26" t="n"/>
+      <c r="E191" s="26" t="n"/>
+      <c r="F191" s="26" t="n"/>
+    </row>
+    <row r="192" ht="14" customHeight="1">
+      <c r="A192" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B191" s="17" t="n"/>
-      <c r="C191" s="17" t="n"/>
-      <c r="D191" s="17" t="n"/>
-      <c r="E191" s="17" t="n"/>
-      <c r="F191" s="17" t="n"/>
-    </row>
-    <row r="192" ht="288" customHeight="1">
-      <c r="A192" s="23" t="inlineStr">
+      <c r="B192" s="19" t="n"/>
+      <c r="C192" s="19" t="n"/>
+      <c r="D192" s="19" t="n"/>
+      <c r="E192" s="19" t="n"/>
+      <c r="F192" s="19" t="n"/>
+    </row>
+    <row r="193" ht="288" customHeight="1">
+      <c r="A193" s="25" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1. 제주화산송이를 두스푼(약10g)계량하시고
@@ -6529,357 +6557,345 @@
 8.팩을 갤때 사용하셨던 플로럴워터로 피부결을 정돈하세요.</t>
         </is>
       </c>
-      <c r="B192" s="24" t="n"/>
-      <c r="C192" s="24" t="n"/>
-      <c r="D192" s="24" t="n"/>
-      <c r="E192" s="24" t="n"/>
-      <c r="F192" s="24" t="n"/>
-    </row>
-    <row r="193" ht="6" customHeight="1"/>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="5" t="inlineStr">
+      <c r="B193" s="26" t="n"/>
+      <c r="C193" s="26" t="n"/>
+      <c r="D193" s="26" t="n"/>
+      <c r="E193" s="26" t="n"/>
+      <c r="F193" s="26" t="n"/>
+    </row>
+    <row r="194" ht="6" customHeight="1"/>
+    <row r="195" ht="22" customHeight="1">
+      <c r="A195" s="7" t="inlineStr">
         <is>
           <t>TX 토닝 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B194" s="6" t="n"/>
-      <c r="C194" s="6" t="n"/>
-      <c r="D194" s="6" t="n"/>
-      <c r="E194" s="6" t="n"/>
-      <c r="F194" s="6" t="n"/>
-    </row>
-    <row r="195" ht="15" customHeight="1">
-      <c r="A195" s="7" t="inlineStr">
+      <c r="B195" s="8" t="n"/>
+      <c r="C195" s="8" t="n"/>
+      <c r="D195" s="8" t="n"/>
+      <c r="E195" s="8" t="n"/>
+      <c r="F195" s="8" t="n"/>
+    </row>
+    <row r="196" ht="15" customHeight="1">
+      <c r="A196" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B195" s="7" t="inlineStr">
+      <c r="B196" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C195" s="7" t="inlineStr">
+      <c r="C196" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D195" s="7" t="inlineStr">
+      <c r="D196" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E195" s="7" t="inlineStr">
+      <c r="E196" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F195" s="7" t="inlineStr">
+      <c r="F196" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="32" customHeight="1">
-      <c r="A196" s="8" t="inlineStr">
+    <row r="197" ht="32" customHeight="1">
+      <c r="A197" s="10" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="10" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C196" s="9" t="inlineStr">
+      <c r="C197" s="11" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D196" s="10" t="inlineStr">
+      <c r="D197" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E196" s="8" t="inlineStr">
+      <c r="E197" s="10" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수 함유 / 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="F196" s="8" t="inlineStr">
+      <c r="F197" s="10" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="48" customHeight="1">
-      <c r="A197" s="8" t="inlineStr">
+    <row r="198" ht="48" customHeight="1">
+      <c r="A198" s="10" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B198" s="10" t="inlineStr">
         <is>
           <t>22g</t>
         </is>
       </c>
-      <c r="C197" s="9" t="inlineStr">
+      <c r="C198" s="11" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="D197" s="21" t="inlineStr">
+      <c r="D198" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E197" s="8" t="inlineStr">
+      <c r="E198" s="10" t="inlineStr">
         <is>
           <t>불가리아 장미수</t>
         </is>
       </c>
-      <c r="F197" s="8" t="inlineStr">
+      <c r="F198" s="10" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="16" customHeight="1">
-      <c r="A198" s="8" t="inlineStr">
+    <row r="199" ht="16" customHeight="1">
+      <c r="A199" s="10" t="inlineStr">
         <is>
           <t>슈퍼시카4</t>
         </is>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B199" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C198" s="9" t="inlineStr">
+      <c r="C199" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D198" s="10" t="inlineStr">
+      <c r="D199" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E198" s="8" t="inlineStr">
+      <c r="E199" s="10" t="inlineStr">
         <is>
           <t>병풀의 핵심성분 4가지 복합물</t>
         </is>
       </c>
-      <c r="F198" s="8" t="inlineStr">
+      <c r="F199" s="10" t="inlineStr">
         <is>
           <t>병풀추출물</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="32" customHeight="1">
-      <c r="A199" s="8" t="inlineStr">
+    <row r="200" ht="32" customHeight="1">
+      <c r="A200" s="10" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B199" s="8" t="inlineStr">
+      <c r="B200" s="10" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C199" s="9" t="inlineStr">
+      <c r="C200" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D199" s="10" t="inlineStr">
+      <c r="D200" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E199" s="8" t="inlineStr">
+      <c r="E200" s="10" t="inlineStr">
         <is>
           <t>비타민B3, 식약처 기능성 고시원료</t>
         </is>
       </c>
-      <c r="F199" s="8" t="inlineStr">
+      <c r="F200" s="10" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="48" customHeight="1">
-      <c r="A200" s="8" t="inlineStr">
+    <row r="201" ht="48" customHeight="1">
+      <c r="A201" s="10" t="inlineStr">
         <is>
           <t>프로바이오틱스3</t>
         </is>
       </c>
-      <c r="B200" s="8" t="inlineStr">
+      <c r="B201" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C200" s="9" t="inlineStr">
+      <c r="C201" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D200" s="10" t="inlineStr">
+      <c r="D201" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E200" s="8" t="inlineStr">
+      <c r="E201" s="10" t="inlineStr">
         <is>
           <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
         </is>
       </c>
-      <c r="F200" s="8" t="inlineStr">
+      <c r="F201" s="10" t="inlineStr">
         <is>
           <t>사카로, 비피다, 갈락토, 콤부차발효여과물..</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="16" customHeight="1">
-      <c r="A201" s="8" t="inlineStr">
+    <row r="202" ht="16" customHeight="1">
+      <c r="A202" s="10" t="inlineStr">
         <is>
           <t>덱스판테놀</t>
         </is>
       </c>
-      <c r="B201" s="8" t="inlineStr">
+      <c r="B202" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C201" s="9" t="inlineStr">
+      <c r="C202" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D201" s="10" t="inlineStr">
+      <c r="D202" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E201" s="8" t="inlineStr">
+      <c r="E202" s="10" t="inlineStr">
         <is>
           <t>비타민B5, 보습 재생</t>
         </is>
       </c>
-      <c r="F201" s="8" t="inlineStr">
+      <c r="F202" s="10" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="64" customHeight="1">
-      <c r="A202" s="8" t="inlineStr">
+    <row r="203" ht="64" customHeight="1">
+      <c r="A203" s="10" t="inlineStr">
         <is>
           <t>트라넥삼산 (펩타이드)</t>
         </is>
       </c>
-      <c r="B202" s="8" t="inlineStr">
+      <c r="B203" s="10" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C202" s="9" t="inlineStr">
+      <c r="C203" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D202" s="10" t="inlineStr">
+      <c r="D203" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E202" s="8" t="inlineStr">
+      <c r="E203" s="10" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="F202" s="8" t="inlineStr">
+      <c r="F203" s="10" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="16" customHeight="1">
-      <c r="A203" s="8" t="inlineStr">
+    <row r="204" ht="16" customHeight="1">
+      <c r="A204" s="10" t="inlineStr">
         <is>
           <t>글루타치온</t>
         </is>
       </c>
-      <c r="B203" s="8" t="inlineStr">
+      <c r="B204" s="10" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C203" s="9" t="inlineStr">
+      <c r="C204" s="11" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D203" s="10" t="inlineStr">
+      <c r="D204" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E203" s="8" t="inlineStr">
+      <c r="E204" s="10" t="inlineStr">
         <is>
           <t>미백효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="F203" s="8" t="n"/>
-    </row>
-    <row r="204" ht="64" customHeight="1">
-      <c r="A204" s="8" t="inlineStr">
+      <c r="F204" s="10" t="n"/>
+    </row>
+    <row r="205" ht="64" customHeight="1">
+      <c r="A205" s="10" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B204" s="8" t="inlineStr">
+      <c r="B205" s="10" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C204" s="9" t="inlineStr">
+      <c r="C205" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D204" s="22" t="inlineStr">
+      <c r="D205" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E204" s="8" t="inlineStr">
+      <c r="E205" s="10" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="F204" s="8" t="inlineStr">
+      <c r="F205" s="10" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
-    </row>
-    <row r="205" ht="14" customHeight="1">
-      <c r="A205" s="14" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 22 · 활성 76 · 방부 2</t>
-        </is>
-      </c>
-      <c r="B205" s="15" t="n"/>
-      <c r="C205" s="15" t="n"/>
-      <c r="D205" s="15" t="n"/>
-      <c r="E205" s="15" t="n"/>
-      <c r="F205" s="15" t="n"/>
     </row>
     <row r="206" ht="14" customHeight="1">
       <c r="A206" s="16" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 22 · 활성 76 · 방부 2</t>
         </is>
       </c>
       <c r="B206" s="17" t="n"/>
@@ -6888,8 +6904,20 @@
       <c r="E206" s="17" t="n"/>
       <c r="F206" s="17" t="n"/>
     </row>
-    <row r="207" ht="384" customHeight="1">
+    <row r="207" ht="14" customHeight="1">
       <c r="A207" s="18" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B207" s="19" t="n"/>
+      <c r="C207" s="19" t="n"/>
+      <c r="D207" s="19" t="n"/>
+      <c r="E207" s="19" t="n"/>
+      <c r="F207" s="19" t="n"/>
+    </row>
+    <row r="208" ht="384" customHeight="1">
+      <c r="A208" s="20" t="inlineStr">
         <is>
           <t>기미, 잡티 초기 진압에 TX 토닝 젤 (100g)
 난이도 : 하
@@ -6918,8 +6946,8 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="80" customHeight="1">
-      <c r="A208" s="18" t="inlineStr">
+    <row r="209" ht="80" customHeight="1">
+      <c r="A209" s="20" t="inlineStr">
         <is>
           <t>현대약품 계열사 특허 성분)
 트라넥삼산과 나이아신아마이드를
@@ -6929,20 +6957,20 @@
         </is>
       </c>
     </row>
-    <row r="209" ht="14" customHeight="1">
-      <c r="A209" s="16" t="inlineStr">
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B209" s="17" t="n"/>
-      <c r="C209" s="17" t="n"/>
-      <c r="D209" s="17" t="n"/>
-      <c r="E209" s="17" t="n"/>
-      <c r="F209" s="17" t="n"/>
-    </row>
-    <row r="210" ht="64" customHeight="1">
-      <c r="A210" s="18" t="inlineStr">
+      <c r="B210" s="19" t="n"/>
+      <c r="C210" s="19" t="n"/>
+      <c r="D210" s="19" t="n"/>
+      <c r="E210" s="19" t="n"/>
+      <c r="F210" s="19" t="n"/>
+    </row>
+    <row r="211" ht="64" customHeight="1">
+      <c r="A211" s="20" t="inlineStr">
         <is>
           <t>TX 토닝 젤 토너 만들기
 1. 모든 재료를 계량합니다.
@@ -6951,23 +6979,22 @@
         </is>
       </c>
     </row>
-    <row r="211" ht="6" customHeight="1"/>
+    <row r="212" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="95">
-    <mergeCell ref="A205:F205"/>
+  <mergeCells count="96">
+    <mergeCell ref="A183:F183"/>
     <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A75:F75"/>
     <mergeCell ref="A189:F189"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A95:F95"/>
     <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A5:F5"/>
     <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A152:F152"/>
-    <mergeCell ref="A161:F161"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
@@ -6979,93 +7006,95 @@
     <mergeCell ref="A124:F124"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A108:F108"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A149:F149"/>
-    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A163:F163"/>
-    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A195:F195"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A85:F85"/>
-    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A151:F151"/>
     <mergeCell ref="A126:F126"/>
-    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A141:F141"/>
     <mergeCell ref="A206:F206"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="A122:F122"/>
     <mergeCell ref="A125:F125"/>
     <mergeCell ref="A190:F190"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A167:F167"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A114:F114"/>
     <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A182:F182"/>
     <mergeCell ref="A98:F98"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A178:F178"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A153:F153"/>
     <mergeCell ref="A162:F162"/>
     <mergeCell ref="A137:F137"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A177:F177"/>
+    <mergeCell ref="A90:F90"/>
     <mergeCell ref="A208:F208"/>
     <mergeCell ref="A164:F164"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A139:F139"/>
     <mergeCell ref="A210:F210"/>
     <mergeCell ref="A179:F179"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A129:F129"/>
     <mergeCell ref="A181:F181"/>
-    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A100:F100"/>
     <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A165:F165"/>
     <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A111:F111"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="A166:F166"/>
-    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A207:F207"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
     <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A193:F193"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A192:F192"/>
     <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A194:F194"/>
+    <mergeCell ref="A185:F185"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A96:F96"/>
-    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="A209:F209"/>
     <mergeCell ref="A147:F147"/>
-    <mergeCell ref="A209:F209"/>
-    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A211:F211"/>
+    <mergeCell ref="A77:F77"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="A123:F123"/>
     <mergeCell ref="A138:F138"/>
     <mergeCell ref="A110:F110"/>
-    <mergeCell ref="A146:F146"/>
-    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A152" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A166" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>

--- a/카드_아키타입/02_젤.xlsx
+++ b/카드_아키타입/02_젤.xlsx
@@ -2629,7 +2629,7 @@
           <t>카보머 1%을 함유, 알로에모이스트보다 높은 점도. 섞어주는 것만으로 간편하게 젤타입을 만들 수 있도록 만든 원료.</t>
         </is>
       </c>
-      <c r="F9" s="10" t="n"/>
+      <c r="F9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="48" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>천연 레몬 껍질 오일, / 상큼한 향</t>
+          <t>천연 레몬 껍질 오일 · 상큼한 향</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>원하는 / 추출물</t>
+          <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (알로에베라겔의 양을 67g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (알로에베라겔의 양을 67g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>오렌지꽃오일, / 민감, 모든 피부</t>
+          <t>오렌지꽃오일 · 민감, 모든 피부</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -3203,10 +3203,10 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>프랑스산 목화 섬유질로 / 만든 천연 필링제.</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="n"/>
+          <t>프랑스산 목화 섬유질로 · 만든 천연 필링제.</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>티트리 수증기 / 증류법으로 추출</t>
+          <t>티트리 수증기 · 증류법으로 추출</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
         <is>
-          <t>로즈마리, / 편백워터</t>
+          <t>로즈마리 · 편백워터</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. / 남은 재료 활용 팁 : 젤타입스킨으로 사용가능, / 헤어에센스로 사용가능.</t>
+          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. · 남은 재료 활용 팁 : 젤타입스킨으로 사용가능 · 헤어에센스로 사용가능.</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3327,12 @@
       </c>
       <c r="E40" s="10" t="inlineStr">
         <is>
-          <t>쇠비름, 진정, / 트러블 관리</t>
+          <t>쇠비름, 진정 · 트러블 관리</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>어성초, / 병풀 추출물 등</t>
+          <t>어성초 · 병풀 추출물 등</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (티트리워터의 양을 36g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (티트리워터의 양을 36g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>무향 또는 / 원하는 EO</t>
+          <t>무향 또는 · 원하는 EO</t>
         </is>
       </c>
     </row>
@@ -3568,12 +3568,12 @@
       </c>
       <c r="E52" s="21" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 장미수를 젤타입으로. / 에코보습제, 알란토인 함유</t>
+          <t>불가리아 다마스크 장미수를 젤타입으로. · 에코보습제, 알란토인 함유</t>
         </is>
       </c>
       <c r="F52" s="21" t="inlineStr">
         <is>
-          <t>허브누리 / 알로에베라겔, / 네롤리플라워겔</t>
+          <t>허브누리 · 알로에베라겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -3600,10 +3600,10 @@
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
-          <t>코엔자임의 10배, / 항산화효과 / 레시피 처방시 500ppm 함유크림 완성.</t>
-        </is>
-      </c>
-      <c r="F53" s="21" t="n"/>
+          <t>코엔자임의 10배 · 항산화효과 · 레시피 처방시 500ppm 함유크림 완성.</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr"/>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="21" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="F54" s="21" t="inlineStr">
         <is>
-          <t>4GF, / 씨네이크펩타이드</t>
+          <t>4GF · 씨네이크펩타이드</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="F55" s="21" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈플라워 겔의 양을 88g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈플라워 겔의 양을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="E56" s="21" t="inlineStr">
         <is>
-          <t>고분자, 중분자, 저분자로 이루어짐. / 피부 각층별 수분공급</t>
+          <t>고분자, 중분자, 저분자로 이루어짐. · 피부 각층별 수분공급</t>
         </is>
       </c>
       <c r="F56" s="21" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="E65" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 장미수를 듬뿍 담은젤, / 에코보습제, 알란토인 함유</t>
+          <t>불가리아 다마스크 장미수를 듬뿍 담은젤 · 에코보습제, 알란토인 함유</t>
         </is>
       </c>
       <c r="F65" s="10" t="inlineStr">
         <is>
-          <t>알로에베라겔, / 네롤리플라워젤</t>
+          <t>알로에베라겔 · 네롤리플라워젤</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="E66" s="10" t="inlineStr">
         <is>
-          <t>기미 개선효과가 뛰어난 트라넥사민산(을 / 펩타이드 말단에 합성으로 / 도입시킨 비타민 펩타이드)</t>
+          <t>기미 개선효과가 뛰어난 트라넥사민산(을 · 펩타이드 말단에 합성으로 · 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
       <c r="F66" s="10" t="inlineStr">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="E67" s="10" t="inlineStr">
         <is>
-          <t>EGF, FGF, IGF, TGF / 복합 펩타이드</t>
+          <t>EGF, FGF, IGF, TGF · 복합 펩타이드</t>
         </is>
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>아세틸헥사, / 씨네이크펩타이드, 화이트펩타이드 등</t>
+          <t>아세틸헥사 · 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>1.2헥산디올2g / (로즈플라워겔을 88g으로 줄여주세요.)</t>
+          <t>1.2헥산디올2g · (로즈플라워겔을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>네롤리, 일랑일랑, 버가못FCF, / 프랑킨센스 EO 블렌딩오일, 생략 가능</t>
+          <t>네롤리, 일랑일랑, 버가못FCF · 프랑킨센스 EO 블렌딩오일, 생략 가능</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E79" s="21" t="inlineStr">
         <is>
-          <t>호호바오일에 천연레시틴을 / 이용하여 리포좀화, / 수상에 쉽게 분산</t>
+          <t>호호바오일에 천연레시틴을 · 이용하여 리포좀화 · 수상에 쉽게 분산</t>
         </is>
       </c>
       <c r="F79" s="21" t="inlineStr">
         <is>
-          <t>슈퍼 곡물 / 단백질추출물</t>
+          <t>슈퍼 곡물 · 단백질추출물</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E80" s="21" t="inlineStr">
         <is>
-          <t>인체 흡수가 용이한 / 저분자화 순수 단백질 사용, / 18종의 아미노산으로 구성</t>
+          <t>인체 흡수가 용이한 · 저분자화 순수 단백질 사용 · 18종의 아미노산으로 구성</t>
         </is>
       </c>
       <c r="F80" s="21" t="inlineStr">
         <is>
-          <t>아카시아, / 마린콜라겐</t>
+          <t>아카시아 · 마린콜라겐</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="F81" s="21" t="inlineStr">
         <is>
-          <t>트라넥 / 삼산펩타이드</t>
+          <t>트라넥 · 삼산펩타이드</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="E82" s="21" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 / 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F82" s="21" t="inlineStr">
         <is>
-          <t>네롤리플라워겔, / 알로에베라겔</t>
+          <t>네롤리플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="F83" s="21" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -4432,10 +4432,10 @@
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>손쉬운 이용을 위해 / 미리 카보머를 젤타입으로 만들어놓은 것.</t>
-        </is>
-      </c>
-      <c r="F93" s="10" t="n"/>
+          <t>손쉬운 이용을 위해 · 미리 카보머를 젤타입으로 만들어놓은 것.</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr"/>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>광엽 티트리라 불림. 향과 성분이 / 유칼립투스와 티트리의 부드러운 버전</t>
+          <t>광엽 티트리라 불림. 향과 성분이 · 유칼립투스와 티트리의 부드러운 버전</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
@@ -4674,10 +4674,10 @@
       </c>
       <c r="E105" s="21" t="inlineStr">
         <is>
-          <t>손쉬운 이용을 위해 / 미리 카보머를 젤타입으로 만들어놓은 것.</t>
-        </is>
-      </c>
-      <c r="F105" s="21" t="n"/>
+          <t>손쉬운 이용을 위해 · 미리 카보머를 젤타입으로 만들어놓은 것.</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="inlineStr"/>
     </row>
     <row r="106" ht="32" customHeight="1">
       <c r="A106" s="21" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="E108" s="21" t="inlineStr">
         <is>
-          <t>레몬, 레몬글라스, 로즈우드에센셜오일 / 블랜딩오일</t>
+          <t>레몬, 레몬글라스, 로즈우드에센셜오일 · 블랜딩오일</t>
         </is>
       </c>
       <c r="F108" s="21" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="E118" s="10" t="inlineStr">
         <is>
-          <t>가용화제. / 물과요일이 분리되지않도록 하는 역할</t>
+          <t>가용화제. · 물과요일이 분리되지않도록 하는 역할</t>
         </is>
       </c>
       <c r="F118" s="10" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -5237,12 +5237,12 @@
       </c>
       <c r="E132" s="21" t="inlineStr">
         <is>
-          <t>순수한 물 , / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F132" s="21" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="E135" s="21" t="inlineStr">
         <is>
-          <t>상록 침엽수로 / 스팀 증류법 추출, 숲향</t>
+          <t>상록 침엽수로 · 스팀 증류법 추출, 숲향</t>
         </is>
       </c>
       <c r="F135" s="21" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="F143" s="10" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="E144" s="10" t="inlineStr">
         <is>
-          <t>보습제, 향이 오랫동안 머물 수 / 있도록 고착제 역할을 함.</t>
+          <t>보습제, 향이 오랫동안 머물 수 · 있도록 고착제 역할을 함.</t>
         </is>
       </c>
       <c r="F144" s="10" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="E145" s="10" t="inlineStr">
         <is>
-          <t>에센셜오일 분산, 방향용으로 사용시 / 공기정화, 소독효과</t>
+          <t>에센셜오일 분산, 방향용으로 사용시 · 공기정화, 소독효과</t>
         </is>
       </c>
       <c r="F145" s="10" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="E146" s="10" t="inlineStr">
         <is>
-          <t>레몬껍질에서 추출한 100%천연오일. / 상큼한 향.</t>
+          <t>레몬껍질에서 추출한 100%천연오일. · 상큼한 향.</t>
         </is>
       </c>
       <c r="F146" s="10" t="inlineStr">
@@ -5739,7 +5739,7 @@
           <t>점증제총량의 1%이하</t>
         </is>
       </c>
-      <c r="F156" s="21" t="n"/>
+      <c r="F156" s="21" t="inlineStr"/>
     </row>
     <row r="157" ht="64" customHeight="1">
       <c r="A157" s="21" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="E157" s="21" t="inlineStr">
         <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 / ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
       <c r="F157" s="21" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="E159" s="21" t="inlineStr">
         <is>
-          <t>허브의 고농축오일, / 시원, 커피와 시너지효과</t>
+          <t>허브의 고농축오일 · 시원, 커피와 시너지효과</t>
         </is>
       </c>
       <c r="F159" s="21" t="inlineStr">
         <is>
-          <t>티트리(항균), / 스피아민트 등</t>
+          <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="E169" s="10" t="inlineStr">
         <is>
-          <t>올레인산 풍부 고보습, / 청정 섬 국내 제주산 야생동백씨 압착.</t>
+          <t>올레인산 풍부 고보습 · 청정 섬 국내 제주산 야생동백씨 압착.</t>
         </is>
       </c>
       <c r="F169" s="10" t="inlineStr">
@@ -6071,12 +6071,12 @@
       </c>
       <c r="E171" s="10" t="inlineStr">
         <is>
-          <t>비타민류가 다량 함유되어있는 / 유기농 야채(당근, 토마토,브로컬리,현미, 양배추,샐러리, 현미)를 저온 추출.</t>
+          <t>비타민류가 다량 함유되어있는 · 유기농 야채(당근, 토마토,브로컬리,현미, 양배추,샐러리, 현미)를 저온 추출.</t>
         </is>
       </c>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>콜라겐, 석류,토마토,</t>
+          <t>콜라겐, 석류,토마토</t>
         </is>
       </c>
     </row>
@@ -6103,10 +6103,10 @@
       </c>
       <c r="E172" s="10" t="inlineStr">
         <is>
-          <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. / 임상시 아세틸헥사펩타이드보다 효과적. / 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. / '바르는 보톡스' 등으로 인기</t>
-        </is>
-      </c>
-      <c r="F172" s="10" t="n"/>
+          <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. · 임상시 아세틸헥사펩타이드보다 효과적. · 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. · '바르는 보톡스' 등으로 인기</t>
+        </is>
+      </c>
+      <c r="F172" s="10" t="inlineStr"/>
     </row>
     <row r="173" ht="32" customHeight="1">
       <c r="A173" s="10" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="E173" s="10" t="inlineStr">
         <is>
-          <t>녹황색채소에 들어있는 비타민B3. / 식약처 인증 미백원료</t>
+          <t>녹황색채소에 들어있는 비타민B3. · 식약처 인증 미백원료</t>
         </is>
       </c>
       <c r="F173" s="10" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="F174" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>리피듀어, / 식물성글리세린</t>
+          <t>리피듀어 · 식물성글리세린</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E176" s="10" t="inlineStr">
         <is>
-          <t>아로마테라피, / 장미향이 나는 제라늄, 모든 피부</t>
+          <t>아로마테라피 · 장미향이 나는 제라늄, 모든 피부</t>
         </is>
       </c>
       <c r="F176" s="10" t="inlineStr">
@@ -6431,10 +6431,10 @@
       </c>
       <c r="E187" s="21" t="inlineStr">
         <is>
-          <t>섭씨 2000도의 화산작용이 만든 기능성 미네럴, 제주 화산석 송이 / (먹는 '송이(버섯)' 아니죠^^) / 화산송이 7 : 카오링클레이3</t>
-        </is>
-      </c>
-      <c r="F187" s="21" t="n"/>
+          <t>섭씨 2000도의 화산작용이 만든 기능성 미네럴, 제주 화산석 송이 · (먹는 '송이(버섯)' 아니죠^^) · 화산송이 7 : 카오링클레이3</t>
+        </is>
+      </c>
+      <c r="F187" s="21" t="inlineStr"/>
     </row>
     <row r="188" ht="64" customHeight="1">
       <c r="A188" s="21" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>불가리아 다마스크 장미수 함유 / 점증, 수분공급, 진정</t>
+          <t>불가리아 다마스크 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
       <c r="F197" s="10" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="E201" s="10" t="inlineStr">
         <is>
-          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 / 3가지 유산균 복합 성분</t>
+          <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
       <c r="F201" s="10" t="inlineStr">
@@ -6858,7 +6858,7 @@
           <t>미백효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="F204" s="10" t="n"/>
+      <c r="F204" s="10" t="inlineStr"/>
     </row>
     <row r="205" ht="64" customHeight="1">
       <c r="A205" s="10" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="F205" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>

--- a/카드_아키타입/02_젤.xlsx
+++ b/카드_아키타입/02_젤.xlsx
@@ -353,7 +353,7 @@
   </absoluteAnchor>
   <absoluteAnchor>
     <pos x="9696450" y="1854200"/>
-    <ext cx="1809750" cy="1619250"/>
+    <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -373,7 +373,7 @@
   </absoluteAnchor>
   <absoluteAnchor>
     <pos x="11544300" y="1854200"/>
-    <ext cx="1809750" cy="571500"/>
+    <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -393,7 +393,7 @@
   </absoluteAnchor>
   <absoluteAnchor>
     <pos x="13392150" y="1854200"/>
-    <ext cx="1809750" cy="752475"/>
+    <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -472,8 +472,8 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="3702049"/>
-    <ext cx="1809750" cy="1809750"/>
+    <pos x="7848600" y="5549900"/>
+    <ext cx="5143500" cy="4591050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -492,8 +492,8 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="5549900"/>
-    <ext cx="1809750" cy="1809750"/>
+    <pos x="7848600" y="10179049"/>
+    <ext cx="5143500" cy="1628775"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -512,8 +512,8 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="5549900"/>
-    <ext cx="1809750" cy="1809750"/>
+    <pos x="7848600" y="11845924"/>
+    <ext cx="5143500" cy="2143125"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -553,7 +553,7 @@
   </absoluteAnchor>
   <absoluteAnchor>
     <pos x="9696450" y="15735300"/>
-    <ext cx="1809750" cy="1352550"/>
+    <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -573,7 +573,7 @@
   </absoluteAnchor>
   <absoluteAnchor>
     <pos x="11544300" y="15735300"/>
-    <ext cx="1809750" cy="857250"/>
+    <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -632,1510 +632,1510 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="17583150"/>
+    <pos x="7848600" y="19431000"/>
+    <ext cx="5143500" cy="3857625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="23402925"/>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="23402925"/>
+    <ext cx="1809750" cy="1485900"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="23402925"/>
+    <ext cx="1809750" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="23402925"/>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="25250775"/>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="25250775"/>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="25250775"/>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="25250775"/>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="27098625"/>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="33016825"/>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="33016825"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="33016825"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="33016825"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="34864675"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="39176325"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="39176325"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="39176325"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="41024175"/>
+    <ext cx="3857625" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="49603025"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="49603025"/>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="49603025"/>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="49603025"/>
+    <ext cx="1238250" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="55762525"/>
+    <ext cx="1628775" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="55762525"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="55762525"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="55762525"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="57610375"/>
+    <ext cx="5143500" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="63547625"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="63547625"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="63547625"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="63547625"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="65395475"/>
+    <ext cx="5143500" cy="2143125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="70316725"/>
+    <ext cx="5143500" cy="3857625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="74212450"/>
+    <ext cx="5143500" cy="4019550"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="78346299"/>
+    <ext cx="3200400" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="85140800"/>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="85140800"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="85140800"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="85140800"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="86988650"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="86988650"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="86988650"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="86988650"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="88836500"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="88836500"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="88836500"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="88836500"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="90684350"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="90684350"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="90684350"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="90684350"/>
+    <ext cx="1724025" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="92532200"/>
+    <ext cx="5143500" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="97713800"/>
+    <ext cx="5143500" cy="1390650"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="99142550"/>
+    <ext cx="2695575" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="104400350"/>
+    <ext cx="3200400" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="111398050"/>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="111398050"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="111398050"/>
+    <ext cx="1809750" cy="1809750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="111398050"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="22301200"/>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="113245900"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="113245900"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="115093750"/>
+    <ext cx="5143500" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="128327150"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="22301200"/>
-    <ext cx="1809750" cy="1485900"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="18" name="Image 18" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="22301200"/>
-    <ext cx="1809750" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="19" name="Image 19" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="22301200"/>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="20" name="Image 20" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="24149050"/>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="21" name="Image 21" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="24149050"/>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="22" name="Image 22" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="24149050"/>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="23" name="Image 23" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="24149050"/>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="24" name="Image 24" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="25996900"/>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="25" name="Image 25" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="31915100"/>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="26" name="Image 26" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="31915100"/>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="128327150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="27" name="Image 27" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="31915100"/>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="128327150"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="128327150"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="130175000"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="130175000"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="130175000"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="130175000"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="132022850"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="132022850"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="139566650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="28" name="Image 28" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="31915100"/>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="139566650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="29" name="Image 29" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="33762950"/>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId90"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="139566650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="30" name="Image 30" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="38074600"/>
-    <ext cx="1352550" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="31" name="Image 31" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="38074600"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="32" name="Image 32" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="38074600"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="38074600"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="48501300"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="48501300"/>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="48501300"/>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="48501300"/>
-    <ext cx="1238250" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="54660800"/>
-    <ext cx="1628775" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="54660800"/>
-    <ext cx="1809750" cy="752475"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="54660800"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="54660800"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="56508650"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="62445900"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="62445900"/>
-    <ext cx="1809750" cy="752475"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId45"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="62445900"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId46"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="62445900"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId47"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="64293750"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId48"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="69215000"/>
-    <ext cx="1809750" cy="1352550"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId49"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="69215000"/>
-    <ext cx="1809750" cy="1409700"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId50"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="74155300"/>
-    <ext cx="1123950" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="51" name="Image 51" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId51"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="80949800"/>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId52"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="80949800"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId53"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="80949800"/>
-    <ext cx="1809750" cy="485775"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId54"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="80949800"/>
-    <ext cx="952500" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="55" name="Image 55" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId55"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="82797650"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="56" name="Image 56" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId56"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="82797650"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="57" name="Image 57" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId57"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="82797650"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="58" name="Image 58" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId58"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="82797650"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="59" name="Image 59" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId59"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="84645500"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId60"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="84645500"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId61"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="84645500"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId62"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="84645500"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId63"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="86493350"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="64" name="Image 64" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId64"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="86493350"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId65"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="86493350"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId66"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="86493350"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId67"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="88341200"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId68"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="88341200"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId69"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="88341200"/>
-    <ext cx="1724025" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="70" name="Image 70" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId70"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="91986100"/>
-    <ext cx="1123950" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="71" name="Image 71" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId71"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="98983800"/>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="72" name="Image 72" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId72"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="98983800"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="73" name="Image 73" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId73"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="98983800"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId74"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="98983800"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="75" name="Image 75" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId75"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="100831650"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId76"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="100831650"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId77"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="100831650"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId78"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="115912900"/>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId79"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="115912900"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId80"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="115912900"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId81"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="115912900"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="82" name="Image 82" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId82"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="117760750"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="83" name="Image 83" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId83"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="117760750"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="84" name="Image 84" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId84"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="117760750"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="85" name="Image 85" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId85"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="117760750"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="86" name="Image 86" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId86"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="119608600"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId87"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="119608600"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="88" name="Image 88" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId88"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="127152400"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="89" name="Image 89" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId89"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="127152400"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="90" name="Image 90" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId90"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="127152400"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
         <cNvPr id="91" name="Image 91" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -2152,8 +2152,8 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="127152400"/>
-    <ext cx="1809750" cy="1809750"/>
+    <pos x="7848600" y="141414500"/>
+    <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="92" name="Image 92" descr="Picture"/>
@@ -2463,7 +2463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F211"/>
+  <dimension ref="A1:F215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3135,329 +3135,337 @@
       <c r="E32" s="26" t="n"/>
       <c r="F32" s="26" t="n"/>
     </row>
-    <row r="33" ht="6" customHeight="1"/>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="33" ht="86.74999999999997" customHeight="1">
+      <c r="A33" s="26" t="n"/>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="26" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>트러블 SSG~필링젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>내추럴 / 셀룰로오즈</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>10g</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>점증/pH</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>프랑스산 목화 섬유질로 · 만든 천연 필링제.</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
+          <t>내추럴 / 셀룰로오즈</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>10g</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>프랑스산 목화 섬유질로 · 만든 천연 필링제.</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
           <t>티트리워터</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>37g</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="D37" s="23" t="inlineStr">
+      <c r="D38" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>티트리 수증기 · 증류법으로 추출</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>로즈마리 · 편백워터</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="64" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. · 남은 재료 활용 팁 : 젤타입스킨으로 사용가능 · 헤어에센스로 사용가능.</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>카보폴프리젤</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="48" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="40" ht="48" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>알란토인분말</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>진정, 계량스푼 작은 쪽 깎아서 4개면 0.2g</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>마치현추출물</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>쇠비름, 진정 · 트러블 관리</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>어성초 · 병풀 추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="42" ht="48" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>3.8g</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="64" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D42" s="24" t="inlineStr">
+      <c r="D43" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g · (티트리워터의 양을 36g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>레몬EO</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D44" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>레몬껍질오일,상큼, 아로마테라피</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F44" s="10" t="inlineStr">
         <is>
           <t>무향 또는 · 원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 38 · 보습 4 · 활성 46 · 향 0 · 방부 1 · 점증/pH 10</t>
         </is>
       </c>
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="17" t="n"/>
-      <c r="E44" s="17" t="n"/>
-      <c r="F44" s="17" t="n"/>
-    </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+    </row>
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="19" t="n"/>
-      <c r="D45" s="19" t="n"/>
-      <c r="E45" s="19" t="n"/>
-      <c r="F45" s="19" t="n"/>
-    </row>
-    <row r="46" ht="224" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="19" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="19" t="n"/>
+    </row>
+    <row r="47" ht="224" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>누구에게나 '때'는 있습니다.
 이 '때'관리만 잘 해줘도
@@ -3476,20 +3484,20 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1">
-      <c r="A47" s="18" t="inlineStr">
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B47" s="19" t="n"/>
-      <c r="C47" s="19" t="n"/>
-      <c r="D47" s="19" t="n"/>
-      <c r="E47" s="19" t="n"/>
-      <c r="F47" s="19" t="n"/>
-    </row>
-    <row r="48" ht="96" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="B48" s="19" t="n"/>
+      <c r="C48" s="19" t="n"/>
+      <c r="D48" s="19" t="n"/>
+      <c r="E48" s="19" t="n"/>
+      <c r="F48" s="19" t="n"/>
+    </row>
+    <row r="49" ht="96" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>1. 알란토인분말 0.2g은 계량스푼 작은 쪽에 깍아서 4개로 해주세요.
 2. 비커에 넣고 내추럴 셀룰로오즈을 비롯 모든 재료를
@@ -3500,233 +3508,233 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="6" customHeight="1"/>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="50" ht="6" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>이데베논 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="B51" s="8" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="8" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F52" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="21" t="inlineStr">
-        <is>
-          <t>로즈 플라워젤</t>
-        </is>
-      </c>
-      <c r="B52" s="21" t="inlineStr">
-        <is>
-          <t>89g</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
-      </c>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="E52" s="21" t="inlineStr">
-        <is>
-          <t>불가리아 다마스크 장미수를 젤타입으로. · 에코보습제, 알란토인 함유</t>
-        </is>
-      </c>
-      <c r="F52" s="21" t="inlineStr">
-        <is>
-          <t>허브누리 · 알로에베라겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
     <row r="53" ht="48" customHeight="1">
       <c r="A53" s="21" t="inlineStr">
         <is>
+          <t>로즈 플라워젤</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>89g</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>불가리아 다마스크 장미수를 젤타입으로. · 에코보습제, 알란토인 함유</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t>허브누리 · 알로에베라겔 · 네롤리플라워겔</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
           <t>이데베논</t>
         </is>
       </c>
-      <c r="B53" s="21" t="inlineStr">
+      <c r="B54" s="21" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C53" s="22" t="inlineStr">
+      <c r="C54" s="22" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E53" s="21" t="inlineStr">
+      <c r="E54" s="21" t="inlineStr">
         <is>
           <t>코엔자임의 10배 · 항산화효과 · 레시피 처방시 500ppm 함유크림 완성.</t>
         </is>
       </c>
-      <c r="F53" s="21" t="inlineStr"/>
-    </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="21" t="inlineStr">
+      <c r="F54" s="21" t="inlineStr"/>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="21" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
-      <c r="B54" s="21" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C54" s="22" t="inlineStr">
+      <c r="C55" s="22" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E54" s="21" t="inlineStr">
+      <c r="E55" s="21" t="inlineStr">
         <is>
           <t>비타민 펩타이드, 화이트닝</t>
         </is>
       </c>
-      <c r="F54" s="21" t="inlineStr">
+      <c r="F55" s="21" t="inlineStr">
         <is>
           <t>4GF · 씨네이크펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="64" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
+    <row r="56" ht="64" customHeight="1">
+      <c r="A56" s="21" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B55" s="21" t="inlineStr">
+      <c r="B56" s="21" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C55" s="22" t="inlineStr">
+      <c r="C56" s="22" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D55" s="24" t="inlineStr">
+      <c r="D56" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E55" s="21" t="inlineStr">
+      <c r="E56" s="21" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="F55" s="21" t="inlineStr">
+      <c r="F56" s="21" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g · (로즈플라워 겔의 양을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="21" t="inlineStr">
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>다중히아루론산</t>
         </is>
       </c>
-      <c r="B56" s="21" t="inlineStr">
+      <c r="B57" s="21" t="inlineStr">
         <is>
           <t>0~5g</t>
         </is>
       </c>
-      <c r="C56" s="22" t="inlineStr">
+      <c r="C57" s="22" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E56" s="21" t="inlineStr">
+      <c r="E57" s="21" t="inlineStr">
         <is>
           <t>고분자, 중분자, 저분자로 이루어짐. · 피부 각층별 수분공급</t>
         </is>
       </c>
-      <c r="F56" s="21" t="inlineStr">
+      <c r="F57" s="21" t="inlineStr">
         <is>
           <t>판테놀</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
+    <row r="58" ht="14" customHeight="1">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 99 · 방부 1</t>
         </is>
       </c>
-      <c r="B57" s="17" t="n"/>
-      <c r="C57" s="17" t="n"/>
-      <c r="D57" s="17" t="n"/>
-      <c r="E57" s="17" t="n"/>
-      <c r="F57" s="17" t="n"/>
-    </row>
-    <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="n"/>
+      <c r="E58" s="17" t="n"/>
+      <c r="F58" s="17" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B58" s="19" t="n"/>
-      <c r="C58" s="19" t="n"/>
-      <c r="D58" s="19" t="n"/>
-      <c r="E58" s="19" t="n"/>
-      <c r="F58" s="19" t="n"/>
-    </row>
-    <row r="59" ht="112" customHeight="1">
-      <c r="A59" s="25" t="inlineStr">
+      <c r="B59" s="19" t="n"/>
+      <c r="C59" s="19" t="n"/>
+      <c r="D59" s="19" t="n"/>
+      <c r="E59" s="19" t="n"/>
+      <c r="F59" s="19" t="n"/>
+    </row>
+    <row r="60" ht="112" customHeight="1">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>황금톡스라 불리는 ,이데베논.
 코엔자임Q10의 10배 항산화효과를 가지고 있습니다.
@@ -3737,26 +3745,26 @@
 또 급이 다른 이데베논의 항산화효과로 시간을 되돌리세요.</t>
         </is>
       </c>
-      <c r="B59" s="26" t="n"/>
-      <c r="C59" s="26" t="n"/>
-      <c r="D59" s="26" t="n"/>
-      <c r="E59" s="26" t="n"/>
-      <c r="F59" s="26" t="n"/>
-    </row>
-    <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="B60" s="26" t="n"/>
+      <c r="C60" s="26" t="n"/>
+      <c r="D60" s="26" t="n"/>
+      <c r="E60" s="26" t="n"/>
+      <c r="F60" s="26" t="n"/>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B60" s="19" t="n"/>
-      <c r="C60" s="19" t="n"/>
-      <c r="D60" s="19" t="n"/>
-      <c r="E60" s="19" t="n"/>
-      <c r="F60" s="19" t="n"/>
-    </row>
-    <row r="61" ht="64" customHeight="1">
-      <c r="A61" s="25" t="inlineStr">
+      <c r="B61" s="19" t="n"/>
+      <c r="C61" s="19" t="n"/>
+      <c r="D61" s="19" t="n"/>
+      <c r="E61" s="19" t="n"/>
+      <c r="F61" s="19" t="n"/>
+    </row>
+    <row r="62" ht="64" customHeight="1">
+      <c r="A62" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1.로즈플라워겔을 계량하고
@@ -3764,243 +3772,243 @@
 3.고른 점도가 나오면 용기에 담아주세요.</t>
         </is>
       </c>
-      <c r="B61" s="26" t="n"/>
-      <c r="C61" s="26" t="n"/>
-      <c r="D61" s="26" t="n"/>
-      <c r="E61" s="26" t="n"/>
-      <c r="F61" s="26" t="n"/>
-    </row>
-    <row r="62" ht="6" customHeight="1"/>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="B62" s="26" t="n"/>
+      <c r="C62" s="26" t="n"/>
+      <c r="D62" s="26" t="n"/>
+      <c r="E62" s="26" t="n"/>
+      <c r="F62" s="26" t="n"/>
+    </row>
+    <row r="63" ht="6" customHeight="1"/>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>TX 멜라 토닝 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="9" t="inlineStr">
+      <c r="B64" s="8" t="n"/>
+      <c r="C64" s="8" t="n"/>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="8" t="n"/>
+      <c r="F64" s="8" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B64" s="9" t="inlineStr">
+      <c r="B65" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C64" s="9" t="inlineStr">
+      <c r="C65" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D64" s="9" t="inlineStr">
+      <c r="D65" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F64" s="9" t="inlineStr">
+      <c r="F65" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="48" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+    <row r="66" ht="48" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>로즈 플라워겔</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B66" s="10" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="E66" s="10" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 듬뿍 담은젤 · 에코보습제, 알란토인 함유</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr">
+      <c r="F66" s="10" t="inlineStr">
         <is>
           <t>알로에베라겔 · 네롤리플라워젤</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="64" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+    <row r="67" ht="64" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
         <is>
           <t>트라넥삼산 / (펩타이드)</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C67" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 · 펩타이드 말단에 합성으로 · 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F67" s="10" t="inlineStr">
         <is>
           <t>화이트 펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="48" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
+    <row r="68" ht="48" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
         <is>
           <t>4GF</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>EGF, FGF, IGF, TGF · 복합 펩타이드</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F68" s="10" t="inlineStr">
         <is>
           <t>아세틸헥사 · 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="64" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
+    <row r="69" ht="64" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
+      <c r="C69" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D68" s="24" t="inlineStr">
+      <c r="D69" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E69" s="10" t="inlineStr">
         <is>
           <t>균번식 억제, 식물복합</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="F69" s="10" t="inlineStr">
         <is>
           <t>1.2헥산디올2g · (로즈플라워겔을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="48" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
+    <row r="70" ht="48" customHeight="1">
+      <c r="A70" s="10" t="inlineStr">
         <is>
           <t>브라이트닝 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr">
+      <c r="C70" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D69" s="15" t="inlineStr">
+      <c r="D70" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr">
+      <c r="E70" s="10" t="inlineStr">
         <is>
           <t>네롤리, 일랑일랑, 버가못FCF · 프랑킨센스 EO 블렌딩오일, 생략 가능</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="14" customHeight="1">
-      <c r="A70" s="16" t="inlineStr">
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 99 · 향 0 · 방부 1</t>
         </is>
       </c>
-      <c r="B70" s="17" t="n"/>
-      <c r="C70" s="17" t="n"/>
-      <c r="D70" s="17" t="n"/>
-      <c r="E70" s="17" t="n"/>
-      <c r="F70" s="17" t="n"/>
-    </row>
-    <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="18" t="inlineStr">
+      <c r="B71" s="17" t="n"/>
+      <c r="C71" s="17" t="n"/>
+      <c r="D71" s="17" t="n"/>
+      <c r="E71" s="17" t="n"/>
+      <c r="F71" s="17" t="n"/>
+    </row>
+    <row r="72" ht="14" customHeight="1">
+      <c r="A72" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B71" s="19" t="n"/>
-      <c r="C71" s="19" t="n"/>
-      <c r="D71" s="19" t="n"/>
-      <c r="E71" s="19" t="n"/>
-      <c r="F71" s="19" t="n"/>
-    </row>
-    <row r="72" ht="384" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
+      <c r="B72" s="19" t="n"/>
+      <c r="C72" s="19" t="n"/>
+      <c r="D72" s="19" t="n"/>
+      <c r="E72" s="19" t="n"/>
+      <c r="F72" s="19" t="n"/>
+    </row>
+    <row r="73" ht="384" customHeight="1">
+      <c r="A73" s="20" t="inlineStr">
         <is>
           <t>트레넥삼산(Tranexamic acid, TX)은 원래 지혈제로 사용되고 있습니다.
 산후 , 외상, 월경, 코피 등 과다 출혈에 사용되는 항플라즈민제로 의약 성분입니다.
@@ -4029,27 +4037,27 @@
         </is>
       </c>
     </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="20" t="inlineStr">
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="20" t="inlineStr">
         <is>
           <t>도움을 줍니다.</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="14" customHeight="1">
-      <c r="A74" s="18" t="inlineStr">
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B74" s="19" t="n"/>
-      <c r="C74" s="19" t="n"/>
-      <c r="D74" s="19" t="n"/>
-      <c r="E74" s="19" t="n"/>
-      <c r="F74" s="19" t="n"/>
-    </row>
-    <row r="75" ht="64" customHeight="1">
-      <c r="A75" s="20" t="inlineStr">
+      <c r="B75" s="19" t="n"/>
+      <c r="C75" s="19" t="n"/>
+      <c r="D75" s="19" t="n"/>
+      <c r="E75" s="19" t="n"/>
+      <c r="F75" s="19" t="n"/>
+    </row>
+    <row r="76" ht="64" customHeight="1">
+      <c r="A76" s="20" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량하고
@@ -4058,237 +4066,237 @@
         </is>
       </c>
     </row>
-    <row r="76" ht="6" customHeight="1"/>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+    <row r="77" ht="6" customHeight="1"/>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>콜라겐 드림 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="9" t="inlineStr">
+      <c r="B78" s="8" t="n"/>
+      <c r="C78" s="8" t="n"/>
+      <c r="D78" s="8" t="n"/>
+      <c r="E78" s="8" t="n"/>
+      <c r="F78" s="8" t="n"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D78" s="9" t="inlineStr">
+      <c r="D79" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E78" s="9" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F78" s="9" t="inlineStr">
+      <c r="F79" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="48" customHeight="1">
-      <c r="A79" s="21" t="inlineStr">
-        <is>
-          <t>워터 호호바</t>
-        </is>
-      </c>
-      <c r="B79" s="21" t="inlineStr">
-        <is>
-          <t>3g</t>
-        </is>
-      </c>
-      <c r="C79" s="22" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="D79" s="23" t="inlineStr">
-        <is>
-          <t>수상</t>
-        </is>
-      </c>
-      <c r="E79" s="21" t="inlineStr">
-        <is>
-          <t>호호바오일에 천연레시틴을 · 이용하여 리포좀화 · 수상에 쉽게 분산</t>
-        </is>
-      </c>
-      <c r="F79" s="21" t="inlineStr">
-        <is>
-          <t>슈퍼 곡물 · 단백질추출물</t>
         </is>
       </c>
     </row>
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="21" t="inlineStr">
         <is>
+          <t>워터 호호바</t>
+        </is>
+      </c>
+      <c r="B80" s="21" t="inlineStr">
+        <is>
+          <t>3g</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D80" s="23" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E80" s="21" t="inlineStr">
+        <is>
+          <t>호호바오일에 천연레시틴을 · 이용하여 리포좀화 · 수상에 쉽게 분산</t>
+        </is>
+      </c>
+      <c r="F80" s="21" t="inlineStr">
+        <is>
+          <t>슈퍼 곡물 · 단백질추출물</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="48" customHeight="1">
+      <c r="A81" s="21" t="inlineStr">
+        <is>
           <t>콜라겐 펩타이드</t>
         </is>
       </c>
-      <c r="B80" s="21" t="inlineStr">
+      <c r="B81" s="21" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C80" s="22" t="inlineStr">
+      <c r="C81" s="22" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D80" s="12" t="inlineStr">
+      <c r="D81" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E80" s="21" t="inlineStr">
+      <c r="E81" s="21" t="inlineStr">
         <is>
           <t>인체 흡수가 용이한 · 저분자화 순수 단백질 사용 · 18종의 아미노산으로 구성</t>
         </is>
       </c>
-      <c r="F80" s="21" t="inlineStr">
+      <c r="F81" s="21" t="inlineStr">
         <is>
           <t>아카시아 · 마린콜라겐</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="21" t="inlineStr">
-        <is>
-          <t>화이트펩타이드</t>
-        </is>
-      </c>
-      <c r="B81" s="21" t="inlineStr">
-        <is>
-          <t>5g</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="E81" s="21" t="inlineStr">
-        <is>
-          <t>비타민 펩타이드, 화이트닝</t>
-        </is>
-      </c>
-      <c r="F81" s="21" t="inlineStr">
-        <is>
-          <t>트라넥 · 삼산펩타이드</t>
         </is>
       </c>
     </row>
     <row r="82" ht="32" customHeight="1">
       <c r="A82" s="21" t="inlineStr">
         <is>
+          <t>화이트펩타이드</t>
+        </is>
+      </c>
+      <c r="B82" s="21" t="inlineStr">
+        <is>
+          <t>5g</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E82" s="21" t="inlineStr">
+        <is>
+          <t>비타민 펩타이드, 화이트닝</t>
+        </is>
+      </c>
+      <c r="F82" s="21" t="inlineStr">
+        <is>
+          <t>트라넥 · 삼산펩타이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="21" t="inlineStr">
+        <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B82" s="21" t="inlineStr">
+      <c r="B83" s="21" t="inlineStr">
         <is>
           <t>85g</t>
         </is>
       </c>
-      <c r="C82" s="22" t="inlineStr">
+      <c r="C83" s="22" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D83" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E82" s="21" t="inlineStr">
+      <c r="E83" s="21" t="inlineStr">
         <is>
           <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="F82" s="21" t="inlineStr">
+      <c r="F83" s="21" t="inlineStr">
         <is>
           <t>네롤리플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="64" customHeight="1">
-      <c r="A83" s="21" t="inlineStr">
+    <row r="84" ht="64" customHeight="1">
+      <c r="A84" s="21" t="inlineStr">
         <is>
           <t>1,2 헥산디올</t>
         </is>
       </c>
-      <c r="B83" s="21" t="inlineStr">
+      <c r="B84" s="21" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C83" s="22" t="inlineStr">
+      <c r="C84" s="22" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D83" s="14" t="inlineStr">
+      <c r="D84" s="14" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E83" s="21" t="inlineStr">
+      <c r="E84" s="21" t="inlineStr">
         <is>
           <t>보습제, 자유수 억제, 균번식억제</t>
         </is>
       </c>
-      <c r="F83" s="21" t="inlineStr">
+      <c r="F84" s="21" t="inlineStr">
         <is>
           <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="16" t="inlineStr">
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 3 · 보습 2 · 활성 95</t>
         </is>
       </c>
-      <c r="B84" s="17" t="n"/>
-      <c r="C84" s="17" t="n"/>
-      <c r="D84" s="17" t="n"/>
-      <c r="E84" s="17" t="n"/>
-      <c r="F84" s="17" t="n"/>
-    </row>
-    <row r="85" ht="14" customHeight="1">
-      <c r="A85" s="18" t="inlineStr">
+      <c r="B85" s="17" t="n"/>
+      <c r="C85" s="17" t="n"/>
+      <c r="D85" s="17" t="n"/>
+      <c r="E85" s="17" t="n"/>
+      <c r="F85" s="17" t="n"/>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B85" s="19" t="n"/>
-      <c r="C85" s="19" t="n"/>
-      <c r="D85" s="19" t="n"/>
-      <c r="E85" s="19" t="n"/>
-      <c r="F85" s="19" t="n"/>
-    </row>
-    <row r="86" ht="112" customHeight="1">
-      <c r="A86" s="25" t="inlineStr">
+      <c r="B86" s="19" t="n"/>
+      <c r="C86" s="19" t="n"/>
+      <c r="D86" s="19" t="n"/>
+      <c r="E86" s="19" t="n"/>
+      <c r="F86" s="19" t="n"/>
+    </row>
+    <row r="87" ht="112" customHeight="1">
+      <c r="A87" s="25" t="inlineStr">
         <is>
           <t>25세 이후 콜라겐 합성이 줄어들므로
 피부가 탄력을 잃고 주름이 생기기 시작하며 활기를 잃게 됩니다.
@@ -4299,26 +4307,26 @@
 보습은 물론 탄력관리에 좋고 생기있는 피부를 가꿔줍니다.</t>
         </is>
       </c>
-      <c r="B86" s="26" t="n"/>
-      <c r="C86" s="26" t="n"/>
-      <c r="D86" s="26" t="n"/>
-      <c r="E86" s="26" t="n"/>
-      <c r="F86" s="26" t="n"/>
-    </row>
-    <row r="87" ht="14" customHeight="1">
-      <c r="A87" s="18" t="inlineStr">
+      <c r="B87" s="26" t="n"/>
+      <c r="C87" s="26" t="n"/>
+      <c r="D87" s="26" t="n"/>
+      <c r="E87" s="26" t="n"/>
+      <c r="F87" s="26" t="n"/>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B87" s="19" t="n"/>
-      <c r="C87" s="19" t="n"/>
-      <c r="D87" s="19" t="n"/>
-      <c r="E87" s="19" t="n"/>
-      <c r="F87" s="19" t="n"/>
-    </row>
-    <row r="88" ht="64" customHeight="1">
-      <c r="A88" s="25" t="inlineStr">
+      <c r="B88" s="19" t="n"/>
+      <c r="C88" s="19" t="n"/>
+      <c r="D88" s="19" t="n"/>
+      <c r="E88" s="19" t="n"/>
+      <c r="F88" s="19" t="n"/>
+    </row>
+    <row r="89" ht="64" customHeight="1">
+      <c r="A89" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량합니다.
@@ -4326,207 +4334,207 @@
 3. 점도가 고르게 되면 용기에 옮겨 담으면 완성.</t>
         </is>
       </c>
-      <c r="B88" s="26" t="n"/>
-      <c r="C88" s="26" t="n"/>
-      <c r="D88" s="26" t="n"/>
-      <c r="E88" s="26" t="n"/>
-      <c r="F88" s="26" t="n"/>
-    </row>
-    <row r="89" ht="6" customHeight="1"/>
-    <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
+      <c r="B89" s="26" t="n"/>
+      <c r="C89" s="26" t="n"/>
+      <c r="D89" s="26" t="n"/>
+      <c r="E89" s="26" t="n"/>
+      <c r="F89" s="26" t="n"/>
+    </row>
+    <row r="90" ht="6" customHeight="1"/>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>셀프백신 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B90" s="8" t="n"/>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
-      <c r="E90" s="8" t="n"/>
-      <c r="F90" s="8" t="n"/>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="9" t="inlineStr">
+      <c r="B91" s="8" t="n"/>
+      <c r="C91" s="8" t="n"/>
+      <c r="D91" s="8" t="n"/>
+      <c r="E91" s="8" t="n"/>
+      <c r="F91" s="8" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B91" s="9" t="inlineStr">
+      <c r="B92" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C92" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D91" s="9" t="inlineStr">
+      <c r="D92" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr">
+      <c r="E92" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F91" s="9" t="inlineStr">
+      <c r="F92" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="10" t="inlineStr">
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B92" s="10" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C92" s="11" t="inlineStr">
+      <c r="C93" s="11" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D92" s="12" t="inlineStr">
+      <c r="D93" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E92" s="10" t="inlineStr">
+      <c r="E93" s="10" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="F92" s="10" t="inlineStr">
+      <c r="F93" s="10" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="48" customHeight="1">
-      <c r="A93" s="10" t="inlineStr">
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C93" s="11" t="inlineStr">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="D93" s="13" t="inlineStr">
+      <c r="D94" s="13" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr">
+      <c r="E94" s="10" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 · 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr"/>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="F94" s="10" t="inlineStr"/>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B95" s="10" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C94" s="11" t="inlineStr">
+      <c r="C95" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D94" s="12" t="inlineStr">
+      <c r="D95" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E94" s="10" t="inlineStr">
+      <c r="E95" s="10" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr">
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="48" customHeight="1">
-      <c r="A95" s="10" t="inlineStr">
+    <row r="96" ht="48" customHeight="1">
+      <c r="A96" s="10" t="inlineStr">
         <is>
           <t>니아울리에센셜오일</t>
         </is>
       </c>
-      <c r="B95" s="10" t="inlineStr">
+      <c r="B96" s="10" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C95" s="11" t="inlineStr">
+      <c r="C96" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D95" s="15" t="inlineStr">
+      <c r="D96" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E95" s="10" t="inlineStr">
+      <c r="E96" s="10" t="inlineStr">
         <is>
           <t>광엽 티트리라 불림. 향과 성분이 · 유칼립투스와 티트리의 부드러운 버전</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F96" s="10" t="inlineStr">
         <is>
           <t>유칼립튜스, 티트리 등</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="14" customHeight="1">
-      <c r="A96" s="16" t="inlineStr">
+    <row r="97" ht="14" customHeight="1">
+      <c r="A97" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 69 · 향 1 · 점증/pH 30</t>
         </is>
       </c>
-      <c r="B96" s="17" t="n"/>
-      <c r="C96" s="17" t="n"/>
-      <c r="D96" s="17" t="n"/>
-      <c r="E96" s="17" t="n"/>
-      <c r="F96" s="17" t="n"/>
-    </row>
-    <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="18" t="inlineStr">
+      <c r="B97" s="17" t="n"/>
+      <c r="C97" s="17" t="n"/>
+      <c r="D97" s="17" t="n"/>
+      <c r="E97" s="17" t="n"/>
+      <c r="F97" s="17" t="n"/>
+    </row>
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B97" s="19" t="n"/>
-      <c r="C97" s="19" t="n"/>
-      <c r="D97" s="19" t="n"/>
-      <c r="E97" s="19" t="n"/>
-      <c r="F97" s="19" t="n"/>
-    </row>
-    <row r="98" ht="320" customHeight="1">
-      <c r="A98" s="20" t="inlineStr">
+      <c r="B98" s="19" t="n"/>
+      <c r="C98" s="19" t="n"/>
+      <c r="D98" s="19" t="n"/>
+      <c r="E98" s="19" t="n"/>
+      <c r="F98" s="19" t="n"/>
+    </row>
+    <row r="99" ht="320" customHeight="1">
+      <c r="A99" s="20" t="inlineStr">
         <is>
           <t>무제 문서
 코로나19 예방을 위해 전문가들이
@@ -4551,20 +4559,20 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="14" customHeight="1">
-      <c r="A99" s="18" t="inlineStr">
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B99" s="19" t="n"/>
-      <c r="C99" s="19" t="n"/>
-      <c r="D99" s="19" t="n"/>
-      <c r="E99" s="19" t="n"/>
-      <c r="F99" s="19" t="n"/>
-    </row>
-    <row r="100" ht="80" customHeight="1">
-      <c r="A100" s="20" t="inlineStr">
+      <c r="B100" s="19" t="n"/>
+      <c r="C100" s="19" t="n"/>
+      <c r="D100" s="19" t="n"/>
+      <c r="E100" s="19" t="n"/>
+      <c r="F100" s="19" t="n"/>
+    </row>
+    <row r="101" ht="80" customHeight="1">
+      <c r="A101" s="20" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -4574,233 +4582,233 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="6" customHeight="1"/>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
+    <row r="102" ht="6" customHeight="1"/>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
         <is>
           <t>상큼 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B102" s="8" t="n"/>
-      <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
-      <c r="E102" s="8" t="n"/>
-      <c r="F102" s="8" t="n"/>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="9" t="inlineStr">
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="8" t="n"/>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B103" s="9" t="inlineStr">
+      <c r="B104" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C103" s="9" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D103" s="9" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E103" s="9" t="inlineStr">
+      <c r="E104" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F103" s="9" t="inlineStr">
+      <c r="F104" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="21" t="inlineStr">
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="21" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B104" s="21" t="inlineStr">
+      <c r="B105" s="21" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C104" s="22" t="inlineStr">
+      <c r="C105" s="22" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D104" s="12" t="inlineStr">
+      <c r="D105" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E104" s="21" t="inlineStr">
+      <c r="E105" s="21" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="F104" s="21" t="inlineStr">
+      <c r="F105" s="21" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="48" customHeight="1">
-      <c r="A105" s="21" t="inlineStr">
+    <row r="106" ht="48" customHeight="1">
+      <c r="A106" s="21" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B105" s="21" t="inlineStr">
+      <c r="B106" s="21" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C105" s="22" t="inlineStr">
+      <c r="C106" s="22" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D105" s="13" t="inlineStr">
+      <c r="D106" s="13" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E105" s="21" t="inlineStr">
+      <c r="E106" s="21" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 · 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="F105" s="21" t="inlineStr"/>
-    </row>
-    <row r="106" ht="32" customHeight="1">
-      <c r="A106" s="21" t="inlineStr">
+      <c r="F106" s="21" t="inlineStr"/>
+    </row>
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="21" t="inlineStr">
         <is>
           <t>알란토인(액상)</t>
         </is>
       </c>
-      <c r="B106" s="21" t="inlineStr">
+      <c r="B107" s="21" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C106" s="22" t="inlineStr">
+      <c r="C107" s="22" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D106" s="12" t="inlineStr">
+      <c r="D107" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E106" s="21" t="inlineStr">
+      <c r="E107" s="21" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="F106" s="21" t="inlineStr">
+      <c r="F107" s="21" t="inlineStr">
         <is>
           <t>프로폴리스추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="21" t="inlineStr">
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="21" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B107" s="21" t="inlineStr">
+      <c r="B108" s="21" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C107" s="22" t="inlineStr">
+      <c r="C108" s="22" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D107" s="12" t="inlineStr">
+      <c r="D108" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E107" s="21" t="inlineStr">
+      <c r="E108" s="21" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="F107" s="21" t="inlineStr">
+      <c r="F108" s="21" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="48" customHeight="1">
-      <c r="A108" s="21" t="inlineStr">
+    <row r="109" ht="48" customHeight="1">
+      <c r="A109" s="21" t="inlineStr">
         <is>
           <t>레몬쥬스EO</t>
         </is>
       </c>
-      <c r="B108" s="21" t="inlineStr">
+      <c r="B109" s="21" t="inlineStr">
         <is>
           <t>20~25방울</t>
         </is>
       </c>
-      <c r="C108" s="22" t="inlineStr">
+      <c r="C109" s="22" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D108" s="15" t="inlineStr">
+      <c r="D109" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E108" s="21" t="inlineStr">
+      <c r="E109" s="21" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드에센셜오일 · 블랜딩오일</t>
         </is>
       </c>
-      <c r="F108" s="21" t="inlineStr">
+      <c r="F109" s="21" t="inlineStr">
         <is>
           <t>레몬, 만다린, 그레이프푸룻, 라임, 오렌지에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="14" customHeight="1">
-      <c r="A109" s="16" t="inlineStr">
+    <row r="110" ht="14" customHeight="1">
+      <c r="A110" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 74 · 향 1 · 점증/pH 25</t>
         </is>
       </c>
-      <c r="B109" s="17" t="n"/>
-      <c r="C109" s="17" t="n"/>
-      <c r="D109" s="17" t="n"/>
-      <c r="E109" s="17" t="n"/>
-      <c r="F109" s="17" t="n"/>
-    </row>
-    <row r="110" ht="14" customHeight="1">
-      <c r="A110" s="18" t="inlineStr">
+      <c r="B110" s="17" t="n"/>
+      <c r="C110" s="17" t="n"/>
+      <c r="D110" s="17" t="n"/>
+      <c r="E110" s="17" t="n"/>
+      <c r="F110" s="17" t="n"/>
+    </row>
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B110" s="19" t="n"/>
-      <c r="C110" s="19" t="n"/>
-      <c r="D110" s="19" t="n"/>
-      <c r="E110" s="19" t="n"/>
-      <c r="F110" s="19" t="n"/>
-    </row>
-    <row r="111" ht="208" customHeight="1">
-      <c r="A111" s="25" t="inlineStr">
+      <c r="B111" s="19" t="n"/>
+      <c r="C111" s="19" t="n"/>
+      <c r="D111" s="19" t="n"/>
+      <c r="E111" s="19" t="n"/>
+      <c r="F111" s="19" t="n"/>
+    </row>
+    <row r="112" ht="208" customHeight="1">
+      <c r="A112" s="25" t="inlineStr">
         <is>
           <t>무제 문서
 그 어느 때보다 손 청결이 중요한 때입니다.
@@ -4817,26 +4825,26 @@
 '상큼 손소독제 만들기'를 안내해드립니다.</t>
         </is>
       </c>
-      <c r="B111" s="26" t="n"/>
-      <c r="C111" s="26" t="n"/>
-      <c r="D111" s="26" t="n"/>
-      <c r="E111" s="26" t="n"/>
-      <c r="F111" s="26" t="n"/>
-    </row>
-    <row r="112" ht="14" customHeight="1">
-      <c r="A112" s="18" t="inlineStr">
+      <c r="B112" s="26" t="n"/>
+      <c r="C112" s="26" t="n"/>
+      <c r="D112" s="26" t="n"/>
+      <c r="E112" s="26" t="n"/>
+      <c r="F112" s="26" t="n"/>
+    </row>
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B112" s="19" t="n"/>
-      <c r="C112" s="19" t="n"/>
-      <c r="D112" s="19" t="n"/>
-      <c r="E112" s="19" t="n"/>
-      <c r="F112" s="19" t="n"/>
-    </row>
-    <row r="113" ht="80" customHeight="1">
-      <c r="A113" s="25" t="inlineStr">
+      <c r="B113" s="19" t="n"/>
+      <c r="C113" s="19" t="n"/>
+      <c r="D113" s="19" t="n"/>
+      <c r="E113" s="19" t="n"/>
+      <c r="F113" s="19" t="n"/>
+    </row>
+    <row r="114" ht="80" customHeight="1">
+      <c r="A114" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -4845,295 +4853,295 @@
 언제나 어디서나 사용하세요.</t>
         </is>
       </c>
-      <c r="B113" s="26" t="n"/>
-      <c r="C113" s="26" t="n"/>
-      <c r="D113" s="26" t="n"/>
-      <c r="E113" s="26" t="n"/>
-      <c r="F113" s="26" t="n"/>
-    </row>
-    <row r="114" ht="6" customHeight="1"/>
-    <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="7" t="inlineStr">
+      <c r="B114" s="26" t="n"/>
+      <c r="C114" s="26" t="n"/>
+      <c r="D114" s="26" t="n"/>
+      <c r="E114" s="26" t="n"/>
+      <c r="F114" s="26" t="n"/>
+    </row>
+    <row r="115" ht="6" customHeight="1"/>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>트러블 잠잠 스팟젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B115" s="8" t="n"/>
-      <c r="C115" s="8" t="n"/>
-      <c r="D115" s="8" t="n"/>
-      <c r="E115" s="8" t="n"/>
-      <c r="F115" s="8" t="n"/>
-    </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="9" t="inlineStr">
+      <c r="B116" s="8" t="n"/>
+      <c r="C116" s="8" t="n"/>
+      <c r="D116" s="8" t="n"/>
+      <c r="E116" s="8" t="n"/>
+      <c r="F116" s="8" t="n"/>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B116" s="9" t="inlineStr">
+      <c r="B117" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C116" s="9" t="inlineStr">
+      <c r="C117" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D116" s="9" t="inlineStr">
+      <c r="D117" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E116" s="9" t="inlineStr">
+      <c r="E117" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F116" s="9" t="inlineStr">
+      <c r="F117" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="10" t="inlineStr">
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="10" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B117" s="10" t="inlineStr">
+      <c r="B118" s="10" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C117" s="11" t="inlineStr">
+      <c r="C118" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D117" s="15" t="inlineStr">
+      <c r="D118" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E117" s="10" t="inlineStr">
+      <c r="E118" s="10" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="F117" s="10" t="inlineStr">
+      <c r="F118" s="10" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="32" customHeight="1">
-      <c r="A118" s="10" t="inlineStr">
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="10" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B118" s="10" t="inlineStr">
+      <c r="B119" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C118" s="11" t="inlineStr">
+      <c r="C119" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D118" s="27" t="inlineStr">
+      <c r="D119" s="27" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E118" s="10" t="inlineStr">
+      <c r="E119" s="10" t="inlineStr">
         <is>
           <t>가용화제. · 물과요일이 분리되지않도록 하는 역할</t>
         </is>
       </c>
-      <c r="F118" s="10" t="inlineStr">
+      <c r="F119" s="10" t="inlineStr">
         <is>
           <t>솔루벌라이저</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="10" t="inlineStr">
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="10" t="inlineStr">
         <is>
           <t>라벤더워터</t>
         </is>
       </c>
-      <c r="B119" s="10" t="inlineStr">
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C119" s="11" t="inlineStr">
+      <c r="C120" s="11" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D119" s="23" t="inlineStr">
+      <c r="D120" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E119" s="10" t="inlineStr">
+      <c r="E120" s="10" t="inlineStr">
         <is>
           <t>진정,재생</t>
         </is>
       </c>
-      <c r="F119" s="10" t="inlineStr">
+      <c r="F120" s="10" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="32" customHeight="1">
-      <c r="A120" s="10" t="inlineStr">
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="10" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔</t>
         </is>
       </c>
-      <c r="B120" s="10" t="inlineStr">
+      <c r="B121" s="10" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C120" s="11" t="inlineStr">
+      <c r="C121" s="11" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D120" s="12" t="inlineStr">
+      <c r="D121" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E120" s="10" t="inlineStr">
+      <c r="E121" s="10" t="inlineStr">
         <is>
           <t>겔타입, 수분공급</t>
         </is>
       </c>
-      <c r="F120" s="10" t="inlineStr">
+      <c r="F121" s="10" t="inlineStr">
         <is>
           <t>로즈플라워겔 · 네롤리플라워겔</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="10" t="inlineStr">
-        <is>
-          <t>어성초추출물</t>
-        </is>
-      </c>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t>8g</t>
-        </is>
-      </c>
-      <c r="C121" s="11" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="D121" s="12" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="E121" s="10" t="inlineStr">
-        <is>
-          <t>항균,진정</t>
-        </is>
-      </c>
-      <c r="F121" s="10" t="inlineStr">
-        <is>
-          <t>카렌듈라추출물</t>
         </is>
       </c>
     </row>
     <row r="122" ht="16" customHeight="1">
       <c r="A122" s="10" t="inlineStr">
         <is>
+          <t>어성초추출물</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>8g</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E122" s="10" t="inlineStr">
+        <is>
+          <t>항균,진정</t>
+        </is>
+      </c>
+      <c r="F122" s="10" t="inlineStr">
+        <is>
+          <t>카렌듈라추출물</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="16" customHeight="1">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
           <t>한방보존제</t>
         </is>
       </c>
-      <c r="B122" s="10" t="inlineStr">
+      <c r="B123" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C122" s="11" t="inlineStr">
+      <c r="C123" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D122" s="24" t="inlineStr">
+      <c r="D123" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E122" s="10" t="inlineStr">
+      <c r="E123" s="10" t="inlineStr">
         <is>
           <t>복합한방추출물, 균번식억제</t>
         </is>
       </c>
-      <c r="F122" s="10" t="inlineStr">
+      <c r="F123" s="10" t="inlineStr">
         <is>
           <t>수용성보존제</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="14" customHeight="1">
-      <c r="A123" s="16" t="inlineStr">
+    <row r="124" ht="14" customHeight="1">
+      <c r="A124" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 28 · 유화 2 · 활성 66 · 향 2 · 방부 2</t>
         </is>
       </c>
-      <c r="B123" s="17" t="n"/>
-      <c r="C123" s="17" t="n"/>
-      <c r="D123" s="17" t="n"/>
-      <c r="E123" s="17" t="n"/>
-      <c r="F123" s="17" t="n"/>
-    </row>
-    <row r="124" ht="14" customHeight="1">
-      <c r="A124" s="18" t="inlineStr">
+      <c r="B124" s="17" t="n"/>
+      <c r="C124" s="17" t="n"/>
+      <c r="D124" s="17" t="n"/>
+      <c r="E124" s="17" t="n"/>
+      <c r="F124" s="17" t="n"/>
+    </row>
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B124" s="19" t="n"/>
-      <c r="C124" s="19" t="n"/>
-      <c r="D124" s="19" t="n"/>
-      <c r="E124" s="19" t="n"/>
-      <c r="F124" s="19" t="n"/>
-    </row>
-    <row r="125" ht="64" customHeight="1">
-      <c r="A125" s="20" t="inlineStr">
+      <c r="B125" s="19" t="n"/>
+      <c r="C125" s="19" t="n"/>
+      <c r="D125" s="19" t="n"/>
+      <c r="E125" s="19" t="n"/>
+      <c r="F125" s="19" t="n"/>
+    </row>
+    <row r="126" ht="64" customHeight="1">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>[ 사용법 ]
 티트리에센셜오일은 국소부위에 원액을 발라도 되는 에센셜오일입니다. 스팟젤은 티트리에센셜오일을 전체의 2%를 정도로 희석한 순한 젤타입에센스입니다. 소량을 여드름이 난 부분에 발라주세요.</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="18" t="inlineStr">
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B126" s="19" t="n"/>
-      <c r="C126" s="19" t="n"/>
-      <c r="D126" s="19" t="n"/>
-      <c r="E126" s="19" t="n"/>
-      <c r="F126" s="19" t="n"/>
-    </row>
-    <row r="127" ht="112" customHeight="1">
-      <c r="A127" s="20" t="inlineStr">
+      <c r="B127" s="19" t="n"/>
+      <c r="C127" s="19" t="n"/>
+      <c r="D127" s="19" t="n"/>
+      <c r="E127" s="19" t="n"/>
+      <c r="F127" s="19" t="n"/>
+    </row>
+    <row r="128" ht="112" customHeight="1">
+      <c r="A128" s="20" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 티트리, 올리브리퀴드를 계량합니다.
@@ -5145,172 +5153,117 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="6" customHeight="1"/>
-    <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+    <row r="129" ht="243.2499999999993" customHeight="1"/>
+    <row r="130" ht="6" customHeight="1"/>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 바디팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B129" s="8" t="n"/>
-      <c r="C129" s="8" t="n"/>
-      <c r="D129" s="8" t="n"/>
-      <c r="E129" s="8" t="n"/>
-      <c r="F129" s="8" t="n"/>
-    </row>
-    <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="9" t="inlineStr">
+      <c r="B131" s="8" t="n"/>
+      <c r="C131" s="8" t="n"/>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="8" t="n"/>
+      <c r="F131" s="8" t="n"/>
+    </row>
+    <row r="132" ht="15" customHeight="1">
+      <c r="A132" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B130" s="9" t="inlineStr">
+      <c r="B132" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C130" s="9" t="inlineStr">
+      <c r="C132" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D130" s="9" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E130" s="9" t="inlineStr">
+      <c r="E132" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F130" s="9" t="inlineStr">
+      <c r="F132" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="32" customHeight="1">
-      <c r="A131" s="21" t="inlineStr">
-        <is>
-          <t>그린 클레이</t>
-        </is>
-      </c>
-      <c r="B131" s="21" t="inlineStr">
-        <is>
-          <t>54.35%</t>
-        </is>
-      </c>
-      <c r="C131" s="22" t="inlineStr"/>
-      <c r="D131" s="28" t="inlineStr">
-        <is>
-          <t>색소</t>
-        </is>
-      </c>
-      <c r="E131" s="21" t="inlineStr">
-        <is>
-          <t>녹색 점토, 피지·노폐물 흡착</t>
-        </is>
-      </c>
-      <c r="F131" s="21" t="inlineStr">
-        <is>
-          <t>핑크클레이, 카올린</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="64" customHeight="1">
-      <c r="A132" s="21" t="inlineStr">
-        <is>
-          <t>정제수</t>
-        </is>
-      </c>
-      <c r="B132" s="21" t="inlineStr">
-        <is>
-          <t>43.48%</t>
-        </is>
-      </c>
-      <c r="C132" s="22" t="inlineStr"/>
-      <c r="D132" s="23" t="inlineStr">
-        <is>
-          <t>수상</t>
-        </is>
-      </c>
-      <c r="E132" s="21" t="inlineStr">
-        <is>
-          <t>순수한 물 · 완성품의 색을 고르게.</t>
-        </is>
-      </c>
-      <c r="F132" s="21" t="inlineStr">
-        <is>
-          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
     <row r="133" ht="32" customHeight="1">
       <c r="A133" s="21" t="inlineStr">
         <is>
-          <t>그레이프프룻EO</t>
+          <t>그린 클레이</t>
         </is>
       </c>
       <c r="B133" s="21" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>54.35%</t>
         </is>
       </c>
       <c r="C133" s="22" t="inlineStr"/>
-      <c r="D133" s="15" t="inlineStr">
-        <is>
-          <t>향</t>
+      <c r="D133" s="28" t="inlineStr">
+        <is>
+          <t>색소</t>
         </is>
       </c>
       <c r="E133" s="21" t="inlineStr">
         <is>
-          <t>자몽 에센셜오일, 상쾌·수렴</t>
+          <t>녹색 점토, 피지·노폐물 흡착</t>
         </is>
       </c>
       <c r="F133" s="21" t="inlineStr">
         <is>
-          <t>오렌지, 레몬에센셜오일</t>
+          <t>핑크클레이, 카올린</t>
         </is>
       </c>
     </row>
     <row r="134" ht="64" customHeight="1">
       <c r="A134" s="21" t="inlineStr">
         <is>
-          <t>로즈제라늄EO</t>
+          <t>정제수</t>
         </is>
       </c>
       <c r="B134" s="21" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>43.48%</t>
         </is>
       </c>
       <c r="C134" s="22" t="inlineStr"/>
-      <c r="D134" s="15" t="inlineStr">
-        <is>
-          <t>향</t>
+      <c r="D134" s="23" t="inlineStr">
+        <is>
+          <t>수상</t>
         </is>
       </c>
       <c r="E134" s="21" t="inlineStr">
         <is>
-          <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F134" s="21" t="inlineStr">
         <is>
-          <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
     <row r="135" ht="32" customHeight="1">
       <c r="A135" s="21" t="inlineStr">
         <is>
-          <t>싸이프러스</t>
+          <t>그레이프프룻EO</t>
         </is>
       </c>
       <c r="B135" s="21" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="C135" s="22" t="inlineStr"/>
@@ -5321,29 +5274,85 @@
       </c>
       <c r="E135" s="21" t="inlineStr">
         <is>
+          <t>자몽 에센셜오일, 상쾌·수렴</t>
+        </is>
+      </c>
+      <c r="F135" s="21" t="inlineStr">
+        <is>
+          <t>오렌지, 레몬에센셜오일</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="64" customHeight="1">
+      <c r="A136" s="21" t="inlineStr">
+        <is>
+          <t>로즈제라늄EO</t>
+        </is>
+      </c>
+      <c r="B136" s="21" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="inlineStr"/>
+      <c r="D136" s="15" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E136" s="21" t="inlineStr">
+        <is>
+          <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
+        </is>
+      </c>
+      <c r="F136" s="21" t="inlineStr">
+        <is>
+          <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="21" t="inlineStr">
+        <is>
+          <t>싸이프러스</t>
+        </is>
+      </c>
+      <c r="B137" s="21" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="C137" s="22" t="inlineStr"/>
+      <c r="D137" s="15" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E137" s="21" t="inlineStr">
+        <is>
           <t>상록 침엽수로 · 스팀 증류법 추출, 숲향</t>
         </is>
       </c>
-      <c r="F135" s="21" t="inlineStr">
+      <c r="F137" s="21" t="inlineStr">
         <is>
           <t>편백</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="14" customHeight="1">
-      <c r="A136" s="18" t="inlineStr">
+    <row r="138" ht="14" customHeight="1">
+      <c r="A138" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B136" s="19" t="n"/>
-      <c r="C136" s="19" t="n"/>
-      <c r="D136" s="19" t="n"/>
-      <c r="E136" s="19" t="n"/>
-      <c r="F136" s="19" t="n"/>
-    </row>
-    <row r="137" ht="192" customHeight="1">
-      <c r="A137" s="25" t="inlineStr">
+      <c r="B138" s="19" t="n"/>
+      <c r="C138" s="19" t="n"/>
+      <c r="D138" s="19" t="n"/>
+      <c r="E138" s="19" t="n"/>
+      <c r="F138" s="19" t="n"/>
+    </row>
+    <row r="139" ht="192" customHeight="1">
+      <c r="A139" s="25" t="inlineStr">
         <is>
           <t>그린클레이 - 프랑스 아질레지방에서 채취하는 클레이(흙). 미세한 클레이가 피부 깊숙이 침투 모공속 노폐물 배출, 흡착, 풍부한 미네랄 성분 해독 효과를 줍니다. 셀룰라이트관리, 여드름지성 피부에 사용.
 그레이프프룻(자몽껍질오일), 제라늄, 싸이프러스, 쥬니퍼베리, 레몬, 펜넬에센셜오일이 다이어트에 효과적인 오일이다. 림프자극, 독소배출, 호르몬균형, 해독 등의 효과를 준다.
@@ -5354,237 +5363,237 @@
 4. 이런 오일로 비누, 마사지오일, 젤, 로션/크림류 제품을 만들어 병행하면 좋다.</t>
         </is>
       </c>
-      <c r="B137" s="26" t="n"/>
-      <c r="C137" s="26" t="n"/>
-      <c r="D137" s="26" t="n"/>
-      <c r="E137" s="26" t="n"/>
-      <c r="F137" s="26" t="n"/>
-    </row>
-    <row r="138" ht="14" customHeight="1">
-      <c r="A138" s="18" t="inlineStr">
-        <is>
-          <t>— 만들기 —</t>
-        </is>
-      </c>
-      <c r="B138" s="19" t="n"/>
-      <c r="C138" s="19" t="n"/>
-      <c r="D138" s="19" t="n"/>
-      <c r="E138" s="19" t="n"/>
-      <c r="F138" s="19" t="n"/>
-    </row>
-    <row r="139" ht="48" customHeight="1">
-      <c r="A139" s="25" t="inlineStr">
-        <is>
-          <t>만들기 방법
-1. 그린클레이, 물, 에센셜오일을 다 넣고
-2. 잘 섞어줍니다.</t>
-        </is>
-      </c>
       <c r="B139" s="26" t="n"/>
       <c r="C139" s="26" t="n"/>
       <c r="D139" s="26" t="n"/>
       <c r="E139" s="26" t="n"/>
       <c r="F139" s="26" t="n"/>
     </row>
-    <row r="140" ht="6" customHeight="1"/>
-    <row r="141" ht="22" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="18" t="inlineStr">
+        <is>
+          <t>— 만들기 —</t>
+        </is>
+      </c>
+      <c r="B140" s="19" t="n"/>
+      <c r="C140" s="19" t="n"/>
+      <c r="D140" s="19" t="n"/>
+      <c r="E140" s="19" t="n"/>
+      <c r="F140" s="19" t="n"/>
+    </row>
+    <row r="141" ht="48" customHeight="1">
+      <c r="A141" s="25" t="inlineStr">
+        <is>
+          <t>만들기 방법
+1. 그린클레이, 물, 에센셜오일을 다 넣고
+2. 잘 섞어줍니다.</t>
+        </is>
+      </c>
+      <c r="B141" s="26" t="n"/>
+      <c r="C141" s="26" t="n"/>
+      <c r="D141" s="26" t="n"/>
+      <c r="E141" s="26" t="n"/>
+      <c r="F141" s="26" t="n"/>
+    </row>
+    <row r="142" ht="6" customHeight="1"/>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>레몬 손소독제(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B141" s="8" t="n"/>
-      <c r="C141" s="8" t="n"/>
-      <c r="D141" s="8" t="n"/>
-      <c r="E141" s="8" t="n"/>
-      <c r="F141" s="8" t="n"/>
-    </row>
-    <row r="142" ht="15" customHeight="1">
-      <c r="A142" s="9" t="inlineStr">
+      <c r="B143" s="8" t="n"/>
+      <c r="C143" s="8" t="n"/>
+      <c r="D143" s="8" t="n"/>
+      <c r="E143" s="8" t="n"/>
+      <c r="F143" s="8" t="n"/>
+    </row>
+    <row r="144" ht="15" customHeight="1">
+      <c r="A144" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B142" s="9" t="inlineStr">
+      <c r="B144" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C142" s="9" t="inlineStr">
+      <c r="C144" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D142" s="9" t="inlineStr">
+      <c r="D144" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E142" s="9" t="inlineStr">
+      <c r="E144" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F142" s="9" t="inlineStr">
+      <c r="F144" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="64" customHeight="1">
-      <c r="A143" s="10" t="inlineStr">
+    <row r="145" ht="64" customHeight="1">
+      <c r="A145" s="10" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B143" s="10" t="inlineStr">
+      <c r="B145" s="10" t="inlineStr">
         <is>
           <t>28g</t>
         </is>
       </c>
-      <c r="C143" s="11" t="inlineStr">
+      <c r="C145" s="11" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D143" s="23" t="inlineStr">
+      <c r="D145" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E143" s="10" t="inlineStr">
+      <c r="E145" s="10" t="inlineStr">
         <is>
           <t>5중 필터링 정제된 물.</t>
         </is>
       </c>
-      <c r="F143" s="10" t="inlineStr">
+      <c r="F145" s="10" t="inlineStr">
         <is>
           <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="48" customHeight="1">
-      <c r="A144" s="10" t="inlineStr">
-        <is>
-          <t>식물성 글리세린</t>
-        </is>
-      </c>
-      <c r="B144" s="10" t="inlineStr">
-        <is>
-          <t>5g</t>
-        </is>
-      </c>
-      <c r="C144" s="11" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="D144" s="14" t="inlineStr">
-        <is>
-          <t>보습</t>
-        </is>
-      </c>
-      <c r="E144" s="10" t="inlineStr">
-        <is>
-          <t>보습제, 향이 오랫동안 머물 수 · 있도록 고착제 역할을 함.</t>
-        </is>
-      </c>
-      <c r="F144" s="10" t="inlineStr">
-        <is>
-          <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="32" customHeight="1">
-      <c r="A145" s="10" t="inlineStr">
-        <is>
-          <t>아로마베이스95</t>
-        </is>
-      </c>
-      <c r="B145" s="10" t="inlineStr">
-        <is>
-          <t>66g</t>
-        </is>
-      </c>
-      <c r="C145" s="11" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="D145" s="15" t="inlineStr">
-        <is>
-          <t>향</t>
-        </is>
-      </c>
-      <c r="E145" s="10" t="inlineStr">
-        <is>
-          <t>에센셜오일 분산, 방향용으로 사용시 · 공기정화, 소독효과</t>
-        </is>
-      </c>
-      <c r="F145" s="10" t="inlineStr">
-        <is>
-          <t>에탄올</t>
         </is>
       </c>
     </row>
     <row r="146" ht="48" customHeight="1">
       <c r="A146" s="10" t="inlineStr">
         <is>
+          <t>식물성 글리세린</t>
+        </is>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>5g</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E146" s="10" t="inlineStr">
+        <is>
+          <t>보습제, 향이 오랫동안 머물 수 · 있도록 고착제 역할을 함.</t>
+        </is>
+      </c>
+      <c r="F146" s="10" t="inlineStr">
+        <is>
+          <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="32" customHeight="1">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>아로마베이스95</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
+        <is>
+          <t>66g</t>
+        </is>
+      </c>
+      <c r="C147" s="11" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="D147" s="15" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E147" s="10" t="inlineStr">
+        <is>
+          <t>에센셜오일 분산, 방향용으로 사용시 · 공기정화, 소독효과</t>
+        </is>
+      </c>
+      <c r="F147" s="10" t="inlineStr">
+        <is>
+          <t>에탄올</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="48" customHeight="1">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B146" s="10" t="inlineStr">
+      <c r="B148" s="10" t="inlineStr">
         <is>
           <t>15~20방울</t>
         </is>
       </c>
-      <c r="C146" s="11" t="inlineStr">
+      <c r="C148" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D146" s="15" t="inlineStr">
+      <c r="D148" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E146" s="10" t="inlineStr">
+      <c r="E148" s="10" t="inlineStr">
         <is>
           <t>레몬껍질에서 추출한 100%천연오일. · 상큼한 향.</t>
         </is>
       </c>
-      <c r="F146" s="10" t="inlineStr">
+      <c r="F148" s="10" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 편백 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="14" customHeight="1">
-      <c r="A147" s="16" t="inlineStr">
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 28 · 보습 5 · 향 67</t>
         </is>
       </c>
-      <c r="B147" s="17" t="n"/>
-      <c r="C147" s="17" t="n"/>
-      <c r="D147" s="17" t="n"/>
-      <c r="E147" s="17" t="n"/>
-      <c r="F147" s="17" t="n"/>
-    </row>
-    <row r="148" ht="14" customHeight="1">
-      <c r="A148" s="18" t="inlineStr">
+      <c r="B149" s="17" t="n"/>
+      <c r="C149" s="17" t="n"/>
+      <c r="D149" s="17" t="n"/>
+      <c r="E149" s="17" t="n"/>
+      <c r="F149" s="17" t="n"/>
+    </row>
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B148" s="19" t="n"/>
-      <c r="C148" s="19" t="n"/>
-      <c r="D148" s="19" t="n"/>
-      <c r="E148" s="19" t="n"/>
-      <c r="F148" s="19" t="n"/>
-    </row>
-    <row r="149" ht="304" customHeight="1">
-      <c r="A149" s="20" t="inlineStr">
+      <c r="B150" s="19" t="n"/>
+      <c r="C150" s="19" t="n"/>
+      <c r="D150" s="19" t="n"/>
+      <c r="E150" s="19" t="n"/>
+      <c r="F150" s="19" t="n"/>
+    </row>
+    <row r="151" ht="304" customHeight="1">
+      <c r="A151" s="20" t="inlineStr">
         <is>
           <t>2009년 젤타입 손소독제 만들기를 위해
 하이셀을 이용해 만든 젤타입 손소독제입니다.
@@ -5608,20 +5617,20 @@
         </is>
       </c>
     </row>
-    <row r="150" ht="14" customHeight="1">
-      <c r="A150" s="18" t="inlineStr">
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B150" s="19" t="n"/>
-      <c r="C150" s="19" t="n"/>
-      <c r="D150" s="19" t="n"/>
-      <c r="E150" s="19" t="n"/>
-      <c r="F150" s="19" t="n"/>
-    </row>
-    <row r="151" ht="288" customHeight="1">
-      <c r="A151" s="20" t="inlineStr">
+      <c r="B152" s="19" t="n"/>
+      <c r="C152" s="19" t="n"/>
+      <c r="D152" s="19" t="n"/>
+      <c r="E152" s="19" t="n"/>
+      <c r="F152" s="19" t="n"/>
+    </row>
+    <row r="153" ht="288" customHeight="1">
+      <c r="A153" s="20" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 [하이셀 계량하기]
@@ -5644,257 +5653,259 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="6" customHeight="1"/>
-    <row r="153" ht="22" customHeight="1">
-      <c r="A153" s="7" t="inlineStr">
+    <row r="154" ht="409" customHeight="1"/>
+    <row r="155" ht="238.4999999999999" customHeight="1"/>
+    <row r="156" ht="6" customHeight="1"/>
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B153" s="8" t="n"/>
-      <c r="C153" s="8" t="n"/>
-      <c r="D153" s="8" t="n"/>
-      <c r="E153" s="8" t="n"/>
-      <c r="F153" s="8" t="n"/>
-    </row>
-    <row r="154" ht="15" customHeight="1">
-      <c r="A154" s="9" t="inlineStr">
+      <c r="B157" s="8" t="n"/>
+      <c r="C157" s="8" t="n"/>
+      <c r="D157" s="8" t="n"/>
+      <c r="E157" s="8" t="n"/>
+      <c r="F157" s="8" t="n"/>
+    </row>
+    <row r="158" ht="15" customHeight="1">
+      <c r="A158" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B154" s="9" t="inlineStr">
+      <c r="B158" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C154" s="9" t="inlineStr">
+      <c r="C158" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D154" s="9" t="inlineStr">
+      <c r="D158" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E154" s="9" t="inlineStr">
+      <c r="E158" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F154" s="9" t="inlineStr">
+      <c r="F158" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="48" customHeight="1">
-      <c r="A155" s="21" t="inlineStr">
+    <row r="159" ht="48" customHeight="1">
+      <c r="A159" s="21" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B155" s="21" t="inlineStr">
+      <c r="B159" s="21" t="inlineStr">
         <is>
           <t>92.17%</t>
         </is>
       </c>
-      <c r="C155" s="22" t="inlineStr"/>
-      <c r="D155" s="23" t="inlineStr">
+      <c r="C159" s="22" t="inlineStr"/>
+      <c r="D159" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E155" s="21" t="inlineStr">
+      <c r="E159" s="21" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="F155" s="21" t="inlineStr">
+      <c r="F159" s="21" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="21" t="inlineStr">
+    <row r="160" ht="16" customHeight="1">
+      <c r="A160" s="21" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B156" s="21" t="inlineStr">
+      <c r="B160" s="21" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C156" s="22" t="inlineStr"/>
-      <c r="D156" s="13" t="inlineStr">
+      <c r="C160" s="22" t="inlineStr"/>
+      <c r="D160" s="13" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E156" s="21" t="inlineStr">
+      <c r="E160" s="21" t="inlineStr">
         <is>
           <t>점증제총량의 1%이하</t>
         </is>
       </c>
-      <c r="F156" s="21" t="inlineStr"/>
-    </row>
-    <row r="157" ht="64" customHeight="1">
-      <c r="A157" s="21" t="inlineStr">
-        <is>
-          <t>글리세린</t>
-        </is>
-      </c>
-      <c r="B157" s="21" t="inlineStr">
-        <is>
-          <t>4.61%</t>
-        </is>
-      </c>
-      <c r="C157" s="22" t="inlineStr"/>
-      <c r="D157" s="14" t="inlineStr">
-        <is>
-          <t>보습</t>
-        </is>
-      </c>
-      <c r="E157" s="21" t="inlineStr">
-        <is>
-          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
-        </is>
-      </c>
-      <c r="F157" s="21" t="inlineStr">
-        <is>
-          <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="32" customHeight="1">
-      <c r="A158" s="21" t="inlineStr">
-        <is>
-          <t>그레이프프룻EO</t>
-        </is>
-      </c>
-      <c r="B158" s="21" t="inlineStr">
-        <is>
-          <t>0.92%</t>
-        </is>
-      </c>
-      <c r="C158" s="22" t="inlineStr"/>
-      <c r="D158" s="15" t="inlineStr">
-        <is>
-          <t>향</t>
-        </is>
-      </c>
-      <c r="E158" s="21" t="inlineStr">
-        <is>
-          <t>자몽 에센셜오일, 상쾌·수렴</t>
-        </is>
-      </c>
-      <c r="F158" s="21" t="inlineStr">
-        <is>
-          <t>오렌지, 레몬에센셜오일</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="32" customHeight="1">
-      <c r="A159" s="21" t="inlineStr">
-        <is>
-          <t>페퍼민트오일</t>
-        </is>
-      </c>
-      <c r="B159" s="21" t="inlineStr">
-        <is>
-          <t>0.23%</t>
-        </is>
-      </c>
-      <c r="C159" s="22" t="inlineStr"/>
-      <c r="D159" s="29" t="inlineStr">
-        <is>
-          <t>유상</t>
-        </is>
-      </c>
-      <c r="E159" s="21" t="inlineStr">
-        <is>
-          <t>허브의 고농축오일 · 시원, 커피와 시너지효과</t>
-        </is>
-      </c>
-      <c r="F159" s="21" t="inlineStr">
-        <is>
-          <t>티트리(항균) · 스피아민트 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="32" customHeight="1">
-      <c r="A160" s="21" t="inlineStr">
-        <is>
-          <t>주니퍼베리EO</t>
-        </is>
-      </c>
-      <c r="B160" s="21" t="inlineStr">
-        <is>
-          <t>0.69%</t>
-        </is>
-      </c>
-      <c r="C160" s="22" t="inlineStr"/>
-      <c r="D160" s="15" t="inlineStr">
-        <is>
-          <t>향</t>
-        </is>
-      </c>
-      <c r="E160" s="21" t="inlineStr">
-        <is>
-          <t>주니퍼베리 에센셜오일, 수렴·정화</t>
-        </is>
-      </c>
-      <c r="F160" s="21" t="inlineStr">
-        <is>
-          <t>원하는 에센셜오일</t>
-        </is>
-      </c>
+      <c r="F160" s="21" t="inlineStr"/>
     </row>
     <row r="161" ht="64" customHeight="1">
       <c r="A161" s="21" t="inlineStr">
         <is>
+          <t>글리세린</t>
+        </is>
+      </c>
+      <c r="B161" s="21" t="inlineStr">
+        <is>
+          <t>4.61%</t>
+        </is>
+      </c>
+      <c r="C161" s="22" t="inlineStr"/>
+      <c r="D161" s="14" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E161" s="21" t="inlineStr">
+        <is>
+          <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
+        </is>
+      </c>
+      <c r="F161" s="21" t="inlineStr">
+        <is>
+          <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="32" customHeight="1">
+      <c r="A162" s="21" t="inlineStr">
+        <is>
+          <t>그레이프프룻EO</t>
+        </is>
+      </c>
+      <c r="B162" s="21" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="C162" s="22" t="inlineStr"/>
+      <c r="D162" s="15" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E162" s="21" t="inlineStr">
+        <is>
+          <t>자몽 에센셜오일, 상쾌·수렴</t>
+        </is>
+      </c>
+      <c r="F162" s="21" t="inlineStr">
+        <is>
+          <t>오렌지, 레몬에센셜오일</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="32" customHeight="1">
+      <c r="A163" s="21" t="inlineStr">
+        <is>
+          <t>페퍼민트오일</t>
+        </is>
+      </c>
+      <c r="B163" s="21" t="inlineStr">
+        <is>
+          <t>0.23%</t>
+        </is>
+      </c>
+      <c r="C163" s="22" t="inlineStr"/>
+      <c r="D163" s="29" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E163" s="21" t="inlineStr">
+        <is>
+          <t>허브의 고농축오일 · 시원, 커피와 시너지효과</t>
+        </is>
+      </c>
+      <c r="F163" s="21" t="inlineStr">
+        <is>
+          <t>티트리(항균) · 스피아민트 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="32" customHeight="1">
+      <c r="A164" s="21" t="inlineStr">
+        <is>
+          <t>주니퍼베리EO</t>
+        </is>
+      </c>
+      <c r="B164" s="21" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="C164" s="22" t="inlineStr"/>
+      <c r="D164" s="15" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E164" s="21" t="inlineStr">
+        <is>
+          <t>주니퍼베리 에센셜오일, 수렴·정화</t>
+        </is>
+      </c>
+      <c r="F164" s="21" t="inlineStr">
+        <is>
+          <t>원하는 에센셜오일</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="64" customHeight="1">
+      <c r="A165" s="21" t="inlineStr">
+        <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B161" s="21" t="inlineStr">
+      <c r="B165" s="21" t="inlineStr">
         <is>
           <t>0.46%</t>
         </is>
       </c>
-      <c r="C161" s="22" t="inlineStr"/>
-      <c r="D161" s="15" t="inlineStr">
+      <c r="C165" s="22" t="inlineStr"/>
+      <c r="D165" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E161" s="21" t="inlineStr">
+      <c r="E165" s="21" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="F161" s="21" t="inlineStr">
+      <c r="F165" s="21" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="14" customHeight="1">
-      <c r="A162" s="18" t="inlineStr">
+    <row r="166" ht="14" customHeight="1">
+      <c r="A166" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B162" s="19" t="n"/>
-      <c r="C162" s="19" t="n"/>
-      <c r="D162" s="19" t="n"/>
-      <c r="E162" s="19" t="n"/>
-      <c r="F162" s="19" t="n"/>
-    </row>
-    <row r="163" ht="96" customHeight="1">
-      <c r="A163" s="25" t="inlineStr">
+      <c r="B166" s="19" t="n"/>
+      <c r="C166" s="19" t="n"/>
+      <c r="D166" s="19" t="n"/>
+      <c r="E166" s="19" t="n"/>
+      <c r="F166" s="19" t="n"/>
+    </row>
+    <row r="167" ht="96" customHeight="1">
+      <c r="A167" s="25" t="inlineStr">
         <is>
           <t>*끈적임없이 흡수되는 다이어트젤
 다이어트에 좋은 에센셜오일 6종: 그레이프프룻, 팬넬, 쥬니퍼베리, 싸이프러스, 레몬, 제라늄
@@ -5904,26 +5915,26 @@
 제라늄 - 호로몬 균형, 피지균형</t>
         </is>
       </c>
-      <c r="B163" s="26" t="n"/>
-      <c r="C163" s="26" t="n"/>
-      <c r="D163" s="26" t="n"/>
-      <c r="E163" s="26" t="n"/>
-      <c r="F163" s="26" t="n"/>
-    </row>
-    <row r="164" ht="14" customHeight="1">
-      <c r="A164" s="18" t="inlineStr">
+      <c r="B167" s="26" t="n"/>
+      <c r="C167" s="26" t="n"/>
+      <c r="D167" s="26" t="n"/>
+      <c r="E167" s="26" t="n"/>
+      <c r="F167" s="26" t="n"/>
+    </row>
+    <row r="168" ht="14" customHeight="1">
+      <c r="A168" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B164" s="19" t="n"/>
-      <c r="C164" s="19" t="n"/>
-      <c r="D164" s="19" t="n"/>
-      <c r="E164" s="19" t="n"/>
-      <c r="F164" s="19" t="n"/>
-    </row>
-    <row r="165" ht="96" customHeight="1">
-      <c r="A165" s="25" t="inlineStr">
+      <c r="B168" s="19" t="n"/>
+      <c r="C168" s="19" t="n"/>
+      <c r="D168" s="19" t="n"/>
+      <c r="E168" s="19" t="n"/>
+      <c r="F168" s="19" t="n"/>
+    </row>
+    <row r="169" ht="96" customHeight="1">
+      <c r="A169" s="25" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 로즈워터를 계량한다.
@@ -5933,367 +5944,367 @@
 6~7. 손으로 저어서 마무리해주면 끝!</t>
         </is>
       </c>
-      <c r="B165" s="26" t="n"/>
-      <c r="C165" s="26" t="n"/>
-      <c r="D165" s="26" t="n"/>
-      <c r="E165" s="26" t="n"/>
-      <c r="F165" s="26" t="n"/>
-    </row>
-    <row r="166" ht="6" customHeight="1"/>
-    <row r="167" ht="22" customHeight="1">
-      <c r="A167" s="7" t="inlineStr">
+      <c r="B169" s="26" t="n"/>
+      <c r="C169" s="26" t="n"/>
+      <c r="D169" s="26" t="n"/>
+      <c r="E169" s="26" t="n"/>
+      <c r="F169" s="26" t="n"/>
+    </row>
+    <row r="170" ht="6" customHeight="1"/>
+    <row r="171" ht="22" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
         <is>
           <t>뱀독 볼륨 에센스(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B167" s="8" t="n"/>
-      <c r="C167" s="8" t="n"/>
-      <c r="D167" s="8" t="n"/>
-      <c r="E167" s="8" t="n"/>
-      <c r="F167" s="8" t="n"/>
-    </row>
-    <row r="168" ht="15" customHeight="1">
-      <c r="A168" s="9" t="inlineStr">
+      <c r="B171" s="8" t="n"/>
+      <c r="C171" s="8" t="n"/>
+      <c r="D171" s="8" t="n"/>
+      <c r="E171" s="8" t="n"/>
+      <c r="F171" s="8" t="n"/>
+    </row>
+    <row r="172" ht="15" customHeight="1">
+      <c r="A172" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B168" s="9" t="inlineStr">
+      <c r="B172" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C168" s="9" t="inlineStr">
+      <c r="C172" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D168" s="9" t="inlineStr">
+      <c r="D172" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E168" s="9" t="inlineStr">
+      <c r="E172" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F168" s="9" t="inlineStr">
+      <c r="F172" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="48" customHeight="1">
-      <c r="A169" s="10" t="inlineStr">
+    <row r="173" ht="48" customHeight="1">
+      <c r="A173" s="10" t="inlineStr">
         <is>
           <t>(제주산) / 비정제동백오일</t>
         </is>
       </c>
-      <c r="B169" s="10" t="inlineStr">
+      <c r="B173" s="10" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C169" s="11" t="inlineStr">
+      <c r="C173" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D169" s="29" t="inlineStr">
+      <c r="D173" s="29" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E169" s="10" t="inlineStr">
+      <c r="E173" s="10" t="inlineStr">
         <is>
           <t>올레인산 풍부 고보습 · 청정 섬 국내 제주산 야생동백씨 압착.</t>
         </is>
       </c>
-      <c r="F169" s="10" t="inlineStr">
+      <c r="F173" s="10" t="inlineStr">
         <is>
           <t>아르간, 로즈힙, 마카다미아넛오일 등</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="32" customHeight="1">
-      <c r="A170" s="10" t="inlineStr">
+    <row r="174" ht="32" customHeight="1">
+      <c r="A174" s="10" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B170" s="10" t="inlineStr">
+      <c r="B174" s="10" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C170" s="11" t="inlineStr">
+      <c r="C174" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D170" s="27" t="inlineStr">
+      <c r="D174" s="27" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E170" s="10" t="inlineStr">
+      <c r="E174" s="10" t="inlineStr">
         <is>
           <t>가용화제, 물에 오일이 분산되도록 도와줌</t>
         </is>
       </c>
-      <c r="F170" s="10" t="inlineStr">
+      <c r="F174" s="10" t="inlineStr">
         <is>
           <t>솔루벌라이저(Polysorbate 80)동량</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="64" customHeight="1">
-      <c r="A171" s="10" t="inlineStr">
+    <row r="175" ht="64" customHeight="1">
+      <c r="A175" s="10" t="inlineStr">
         <is>
           <t>오가닉7솔루션</t>
         </is>
       </c>
-      <c r="B171" s="10" t="inlineStr">
+      <c r="B175" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C171" s="11" t="inlineStr">
+      <c r="C175" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D171" s="12" t="inlineStr">
+      <c r="D175" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E171" s="10" t="inlineStr">
+      <c r="E175" s="10" t="inlineStr">
         <is>
           <t>비타민류가 다량 함유되어있는 · 유기농 야채(당근, 토마토,브로컬리,현미, 양배추,샐러리, 현미)를 저온 추출.</t>
         </is>
       </c>
-      <c r="F171" s="10" t="inlineStr">
+      <c r="F175" s="10" t="inlineStr">
         <is>
           <t>콜라겐, 석류,토마토</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="144" customHeight="1">
-      <c r="A172" s="10" t="inlineStr">
+    <row r="176" ht="144" customHeight="1">
+      <c r="A176" s="10" t="inlineStr">
         <is>
           <t>씨네이크(뱀독) / 펩타이드</t>
         </is>
       </c>
-      <c r="B172" s="10" t="inlineStr">
+      <c r="B176" s="10" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C172" s="11" t="inlineStr">
+      <c r="C176" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D172" s="12" t="inlineStr">
+      <c r="D176" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E172" s="10" t="inlineStr">
+      <c r="E176" s="10" t="inlineStr">
         <is>
           <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. · 임상시 아세틸헥사펩타이드보다 효과적. · 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. · '바르는 보톡스' 등으로 인기</t>
         </is>
       </c>
-      <c r="F172" s="10" t="inlineStr"/>
-    </row>
-    <row r="173" ht="32" customHeight="1">
-      <c r="A173" s="10" t="inlineStr">
+      <c r="F176" s="10" t="inlineStr"/>
+    </row>
+    <row r="177" ht="32" customHeight="1">
+      <c r="A177" s="10" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B173" s="10" t="inlineStr">
+      <c r="B177" s="10" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C173" s="11" t="inlineStr">
+      <c r="C177" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D173" s="12" t="inlineStr">
+      <c r="D177" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E173" s="10" t="inlineStr">
+      <c r="E177" s="10" t="inlineStr">
         <is>
           <t>녹황색채소에 들어있는 비타민B3. · 식약처 인증 미백원료</t>
         </is>
       </c>
-      <c r="F173" s="10" t="inlineStr">
+      <c r="F177" s="10" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="80" customHeight="1">
-      <c r="A174" s="10" t="inlineStr">
+    <row r="178" ht="80" customHeight="1">
+      <c r="A178" s="10" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B174" s="10" t="inlineStr">
+      <c r="B178" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C174" s="11" t="inlineStr">
+      <c r="C178" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D174" s="24" t="inlineStr">
+      <c r="D178" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E174" s="10" t="inlineStr">
+      <c r="E178" s="10" t="inlineStr">
         <is>
           <t>미생물 번식 억제제.</t>
         </is>
       </c>
-      <c r="F174" s="10" t="inlineStr">
+      <c r="F178" s="10" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="32" customHeight="1">
-      <c r="A175" s="10" t="inlineStr">
+    <row r="179" ht="32" customHeight="1">
+      <c r="A179" s="10" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
-      <c r="B175" s="10" t="inlineStr">
+      <c r="B179" s="10" t="inlineStr">
         <is>
           <t>0~6g</t>
         </is>
       </c>
-      <c r="C175" s="11" t="inlineStr">
+      <c r="C179" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D175" s="12" t="inlineStr">
+      <c r="D179" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E175" s="10" t="inlineStr">
+      <c r="E179" s="10" t="inlineStr">
         <is>
           <t>보습제. 원하시면 넣어주세요.</t>
         </is>
       </c>
-      <c r="F175" s="10" t="inlineStr">
+      <c r="F179" s="10" t="inlineStr">
         <is>
           <t>리피듀어 · 식물성글리세린</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="64" customHeight="1">
-      <c r="A176" s="10" t="inlineStr">
+    <row r="180" ht="64" customHeight="1">
+      <c r="A180" s="10" t="inlineStr">
         <is>
           <t>로즈우드에센셜오일</t>
         </is>
       </c>
-      <c r="B176" s="10" t="inlineStr">
+      <c r="B180" s="10" t="inlineStr">
         <is>
           <t>4~8방울</t>
         </is>
       </c>
-      <c r="C176" s="11" t="inlineStr">
+      <c r="C180" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D176" s="15" t="inlineStr">
+      <c r="D180" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E176" s="10" t="inlineStr">
+      <c r="E180" s="10" t="inlineStr">
         <is>
           <t>아로마테라피 · 장미향이 나는 제라늄, 모든 피부</t>
         </is>
       </c>
-      <c r="F176" s="10" t="inlineStr">
+      <c r="F180" s="10" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈제라늄 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="80" customHeight="1">
-      <c r="A177" s="10" t="inlineStr">
+    <row r="181" ht="80" customHeight="1">
+      <c r="A181" s="10" t="inlineStr">
         <is>
           <t>알로에모이스트</t>
         </is>
       </c>
-      <c r="B177" s="10" t="inlineStr">
+      <c r="B181" s="10" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C177" s="11" t="inlineStr">
+      <c r="C181" s="11" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D177" s="12" t="inlineStr">
+      <c r="D181" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E177" s="10" t="inlineStr">
+      <c r="E181" s="10" t="inlineStr">
         <is>
           <t>자체점증, 가용화안정, 수분공급 , 진정</t>
         </is>
       </c>
-      <c r="F177" s="10" t="inlineStr">
+      <c r="F181" s="10" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="14" customHeight="1">
-      <c r="A178" s="16" t="inlineStr">
+    <row r="182" ht="14" customHeight="1">
+      <c r="A182" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 4 · 유화 3 · 활성 92 · 향 0 · 방부 1</t>
         </is>
       </c>
-      <c r="B178" s="17" t="n"/>
-      <c r="C178" s="17" t="n"/>
-      <c r="D178" s="17" t="n"/>
-      <c r="E178" s="17" t="n"/>
-      <c r="F178" s="17" t="n"/>
-    </row>
-    <row r="179" ht="14" customHeight="1">
-      <c r="A179" s="18" t="inlineStr">
+      <c r="B182" s="17" t="n"/>
+      <c r="C182" s="17" t="n"/>
+      <c r="D182" s="17" t="n"/>
+      <c r="E182" s="17" t="n"/>
+      <c r="F182" s="17" t="n"/>
+    </row>
+    <row r="183" ht="14" customHeight="1">
+      <c r="A183" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B179" s="19" t="n"/>
-      <c r="C179" s="19" t="n"/>
-      <c r="D179" s="19" t="n"/>
-      <c r="E179" s="19" t="n"/>
-      <c r="F179" s="19" t="n"/>
-    </row>
-    <row r="180" ht="384" customHeight="1">
-      <c r="A180" s="20" t="inlineStr">
+      <c r="B183" s="19" t="n"/>
+      <c r="C183" s="19" t="n"/>
+      <c r="D183" s="19" t="n"/>
+      <c r="E183" s="19" t="n"/>
+      <c r="F183" s="19" t="n"/>
+    </row>
+    <row r="184" ht="384" customHeight="1">
+      <c r="A184" s="20" t="inlineStr">
         <is>
           <t>뱀독 볼륨에센스(젤)은
 바르는 보톡스인 씨네이크펩타이드 최대함량인 4%와
@@ -6322,8 +6333,8 @@
         </is>
       </c>
     </row>
-    <row r="181" ht="208" customHeight="1">
-      <c r="A181" s="20" t="inlineStr">
+    <row r="185" ht="208" customHeight="1">
+      <c r="A185" s="20" t="inlineStr">
         <is>
           <t>살모사의 뱀독에서 추출한 단백질은
 유방암 세포의 성장을 70%나 억제하는 것으로 밝혀지기도 했습니다.
@@ -6341,20 +6352,20 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="14" customHeight="1">
-      <c r="A182" s="18" t="inlineStr">
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B182" s="19" t="n"/>
-      <c r="C182" s="19" t="n"/>
-      <c r="D182" s="19" t="n"/>
-      <c r="E182" s="19" t="n"/>
-      <c r="F182" s="19" t="n"/>
-    </row>
-    <row r="183" ht="80" customHeight="1">
-      <c r="A183" s="20" t="inlineStr">
+      <c r="B186" s="19" t="n"/>
+      <c r="C186" s="19" t="n"/>
+      <c r="D186" s="19" t="n"/>
+      <c r="E186" s="19" t="n"/>
+      <c r="F186" s="19" t="n"/>
+    </row>
+    <row r="187" ht="80" customHeight="1">
+      <c r="A187" s="20" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.동백오일과 올리브리퀴드를 먼저 섞어주세요.
@@ -6363,137 +6374,137 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="6" customHeight="1"/>
-    <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="7" t="inlineStr">
+    <row r="188" ht="6" customHeight="1"/>
+    <row r="189" ht="22" customHeight="1">
+      <c r="A189" s="7" t="inlineStr">
         <is>
           <t>아임레알 제주화산송이팩    [(트러블, 모공이 넓은 피부) / 1회분량]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B185" s="8" t="n"/>
-      <c r="C185" s="8" t="n"/>
-      <c r="D185" s="8" t="n"/>
-      <c r="E185" s="8" t="n"/>
-      <c r="F185" s="8" t="n"/>
-    </row>
-    <row r="186" ht="15" customHeight="1">
-      <c r="A186" s="9" t="inlineStr">
+      <c r="B189" s="8" t="n"/>
+      <c r="C189" s="8" t="n"/>
+      <c r="D189" s="8" t="n"/>
+      <c r="E189" s="8" t="n"/>
+      <c r="F189" s="8" t="n"/>
+    </row>
+    <row r="190" ht="15" customHeight="1">
+      <c r="A190" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B186" s="9" t="inlineStr">
+      <c r="B190" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C186" s="9" t="inlineStr">
+      <c r="C190" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D186" s="9" t="inlineStr">
+      <c r="D190" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E186" s="9" t="inlineStr">
+      <c r="E190" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F186" s="9" t="inlineStr">
+      <c r="F190" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="80" customHeight="1">
-      <c r="A187" s="21" t="inlineStr">
+    <row r="191" ht="80" customHeight="1">
+      <c r="A191" s="21" t="inlineStr">
         <is>
           <t>제주 화산송이분말</t>
         </is>
       </c>
-      <c r="B187" s="21" t="inlineStr">
+      <c r="B191" s="21" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C187" s="22" t="inlineStr">
+      <c r="C191" s="22" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D187" s="28" t="inlineStr">
+      <c r="D191" s="28" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E187" s="21" t="inlineStr">
+      <c r="E191" s="21" t="inlineStr">
         <is>
           <t>섭씨 2000도의 화산작용이 만든 기능성 미네럴, 제주 화산석 송이 · (먹는 '송이(버섯)' 아니죠^^) · 화산송이 7 : 카오링클레이3</t>
         </is>
       </c>
-      <c r="F187" s="21" t="inlineStr"/>
-    </row>
-    <row r="188" ht="64" customHeight="1">
-      <c r="A188" s="21" t="inlineStr">
+      <c r="F191" s="21" t="inlineStr"/>
+    </row>
+    <row r="192" ht="64" customHeight="1">
+      <c r="A192" s="21" t="inlineStr">
         <is>
           <t>위치헤이즐워터 / (편백워터)</t>
         </is>
       </c>
-      <c r="B188" s="21" t="inlineStr">
+      <c r="B192" s="21" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C188" s="22" t="inlineStr">
+      <c r="C192" s="22" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D188" s="23" t="inlineStr">
+      <c r="D192" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E188" s="21" t="inlineStr">
+      <c r="E192" s="21" t="inlineStr">
         <is>
           <t>제주화산송이 양의 반이하의 양, 정제수도 가능, 위치헤즐은 수렴, 트러블, 모공 넓은 피부적합</t>
         </is>
       </c>
-      <c r="F188" s="21" t="inlineStr">
+      <c r="F192" s="21" t="inlineStr">
         <is>
           <t>정수기 물, 수돗물^^, 녹차우린 물. 어성초우린 물</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="14" customHeight="1">
-      <c r="A189" s="16" t="inlineStr">
+    <row r="193" ht="14" customHeight="1">
+      <c r="A193" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 23 · 색소 77</t>
         </is>
       </c>
-      <c r="B189" s="17" t="n"/>
-      <c r="C189" s="17" t="n"/>
-      <c r="D189" s="17" t="n"/>
-      <c r="E189" s="17" t="n"/>
-      <c r="F189" s="17" t="n"/>
-    </row>
-    <row r="190" ht="14" customHeight="1">
-      <c r="A190" s="18" t="inlineStr">
+      <c r="B193" s="17" t="n"/>
+      <c r="C193" s="17" t="n"/>
+      <c r="D193" s="17" t="n"/>
+      <c r="E193" s="17" t="n"/>
+      <c r="F193" s="17" t="n"/>
+    </row>
+    <row r="194" ht="14" customHeight="1">
+      <c r="A194" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B190" s="19" t="n"/>
-      <c r="C190" s="19" t="n"/>
-      <c r="D190" s="19" t="n"/>
-      <c r="E190" s="19" t="n"/>
-      <c r="F190" s="19" t="n"/>
-    </row>
-    <row r="191" ht="368" customHeight="1">
-      <c r="A191" s="25" t="inlineStr">
+      <c r="B194" s="19" t="n"/>
+      <c r="C194" s="19" t="n"/>
+      <c r="D194" s="19" t="n"/>
+      <c r="E194" s="19" t="n"/>
+      <c r="F194" s="19" t="n"/>
+    </row>
+    <row r="195" ht="368" customHeight="1">
+      <c r="A195" s="25" t="inlineStr">
         <is>
           <t>제주화산송이,
 먹는 송이가 아니죠^^
@@ -6518,26 +6529,26 @@
 초간단 레알 화산송이팩으로 피부 피지와 노폐물을 관리해보세요.</t>
         </is>
       </c>
-      <c r="B191" s="26" t="n"/>
-      <c r="C191" s="26" t="n"/>
-      <c r="D191" s="26" t="n"/>
-      <c r="E191" s="26" t="n"/>
-      <c r="F191" s="26" t="n"/>
-    </row>
-    <row r="192" ht="14" customHeight="1">
-      <c r="A192" s="18" t="inlineStr">
+      <c r="B195" s="26" t="n"/>
+      <c r="C195" s="26" t="n"/>
+      <c r="D195" s="26" t="n"/>
+      <c r="E195" s="26" t="n"/>
+      <c r="F195" s="26" t="n"/>
+    </row>
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B192" s="19" t="n"/>
-      <c r="C192" s="19" t="n"/>
-      <c r="D192" s="19" t="n"/>
-      <c r="E192" s="19" t="n"/>
-      <c r="F192" s="19" t="n"/>
-    </row>
-    <row r="193" ht="288" customHeight="1">
-      <c r="A193" s="25" t="inlineStr">
+      <c r="B196" s="19" t="n"/>
+      <c r="C196" s="19" t="n"/>
+      <c r="D196" s="19" t="n"/>
+      <c r="E196" s="19" t="n"/>
+      <c r="F196" s="19" t="n"/>
+    </row>
+    <row r="197" ht="288" customHeight="1">
+      <c r="A197" s="25" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1. 제주화산송이를 두스푼(약10g)계량하시고
@@ -6557,367 +6568,367 @@
 8.팩을 갤때 사용하셨던 플로럴워터로 피부결을 정돈하세요.</t>
         </is>
       </c>
-      <c r="B193" s="26" t="n"/>
-      <c r="C193" s="26" t="n"/>
-      <c r="D193" s="26" t="n"/>
-      <c r="E193" s="26" t="n"/>
-      <c r="F193" s="26" t="n"/>
-    </row>
-    <row r="194" ht="6" customHeight="1"/>
-    <row r="195" ht="22" customHeight="1">
-      <c r="A195" s="7" t="inlineStr">
+      <c r="B197" s="26" t="n"/>
+      <c r="C197" s="26" t="n"/>
+      <c r="D197" s="26" t="n"/>
+      <c r="E197" s="26" t="n"/>
+      <c r="F197" s="26" t="n"/>
+    </row>
+    <row r="198" ht="6" customHeight="1"/>
+    <row r="199" ht="22" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
         <is>
           <t>TX 토닝 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B195" s="8" t="n"/>
-      <c r="C195" s="8" t="n"/>
-      <c r="D195" s="8" t="n"/>
-      <c r="E195" s="8" t="n"/>
-      <c r="F195" s="8" t="n"/>
-    </row>
-    <row r="196" ht="15" customHeight="1">
-      <c r="A196" s="9" t="inlineStr">
+      <c r="B199" s="8" t="n"/>
+      <c r="C199" s="8" t="n"/>
+      <c r="D199" s="8" t="n"/>
+      <c r="E199" s="8" t="n"/>
+      <c r="F199" s="8" t="n"/>
+    </row>
+    <row r="200" ht="15" customHeight="1">
+      <c r="A200" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B196" s="9" t="inlineStr">
+      <c r="B200" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C196" s="9" t="inlineStr">
+      <c r="C200" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D196" s="9" t="inlineStr">
+      <c r="D200" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E196" s="9" t="inlineStr">
+      <c r="E200" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F196" s="9" t="inlineStr">
+      <c r="F200" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="32" customHeight="1">
-      <c r="A197" s="10" t="inlineStr">
+    <row r="201" ht="32" customHeight="1">
+      <c r="A201" s="10" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B197" s="10" t="inlineStr">
+      <c r="B201" s="10" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C197" s="11" t="inlineStr">
+      <c r="C201" s="11" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D197" s="12" t="inlineStr">
+      <c r="D201" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E197" s="10" t="inlineStr">
+      <c r="E201" s="10" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="F197" s="10" t="inlineStr">
+      <c r="F201" s="10" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="48" customHeight="1">
-      <c r="A198" s="10" t="inlineStr">
+    <row r="202" ht="48" customHeight="1">
+      <c r="A202" s="10" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B198" s="10" t="inlineStr">
+      <c r="B202" s="10" t="inlineStr">
         <is>
           <t>22g</t>
         </is>
       </c>
-      <c r="C198" s="11" t="inlineStr">
+      <c r="C202" s="11" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="D198" s="23" t="inlineStr">
+      <c r="D202" s="23" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E198" s="10" t="inlineStr">
+      <c r="E202" s="10" t="inlineStr">
         <is>
           <t>불가리아 장미수</t>
         </is>
       </c>
-      <c r="F198" s="10" t="inlineStr">
+      <c r="F202" s="10" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="16" customHeight="1">
-      <c r="A199" s="10" t="inlineStr">
+    <row r="203" ht="16" customHeight="1">
+      <c r="A203" s="10" t="inlineStr">
         <is>
           <t>슈퍼시카4</t>
         </is>
       </c>
-      <c r="B199" s="10" t="inlineStr">
+      <c r="B203" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C199" s="11" t="inlineStr">
+      <c r="C203" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D199" s="12" t="inlineStr">
+      <c r="D203" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E199" s="10" t="inlineStr">
+      <c r="E203" s="10" t="inlineStr">
         <is>
           <t>병풀의 핵심성분 4가지 복합물</t>
         </is>
       </c>
-      <c r="F199" s="10" t="inlineStr">
+      <c r="F203" s="10" t="inlineStr">
         <is>
           <t>병풀추출물</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="32" customHeight="1">
-      <c r="A200" s="10" t="inlineStr">
+    <row r="204" ht="32" customHeight="1">
+      <c r="A204" s="10" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B200" s="10" t="inlineStr">
+      <c r="B204" s="10" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C200" s="11" t="inlineStr">
+      <c r="C204" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D200" s="12" t="inlineStr">
+      <c r="D204" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E200" s="10" t="inlineStr">
+      <c r="E204" s="10" t="inlineStr">
         <is>
           <t>비타민B3, 식약처 기능성 고시원료</t>
         </is>
       </c>
-      <c r="F200" s="10" t="inlineStr">
+      <c r="F204" s="10" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="48" customHeight="1">
-      <c r="A201" s="10" t="inlineStr">
+    <row r="205" ht="48" customHeight="1">
+      <c r="A205" s="10" t="inlineStr">
         <is>
           <t>프로바이오틱스3</t>
         </is>
       </c>
-      <c r="B201" s="10" t="inlineStr">
+      <c r="B205" s="10" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C201" s="11" t="inlineStr">
+      <c r="C205" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D201" s="12" t="inlineStr">
+      <c r="D205" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E201" s="10" t="inlineStr">
+      <c r="E205" s="10" t="inlineStr">
         <is>
           <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
-      <c r="F201" s="10" t="inlineStr">
+      <c r="F205" s="10" t="inlineStr">
         <is>
           <t>사카로, 비피다, 갈락토, 콤부차발효여과물..</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="16" customHeight="1">
-      <c r="A202" s="10" t="inlineStr">
+    <row r="206" ht="16" customHeight="1">
+      <c r="A206" s="10" t="inlineStr">
         <is>
           <t>덱스판테놀</t>
         </is>
       </c>
-      <c r="B202" s="10" t="inlineStr">
+      <c r="B206" s="10" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C202" s="11" t="inlineStr">
+      <c r="C206" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D202" s="12" t="inlineStr">
+      <c r="D206" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E202" s="10" t="inlineStr">
+      <c r="E206" s="10" t="inlineStr">
         <is>
           <t>비타민B5, 보습 재생</t>
         </is>
       </c>
-      <c r="F202" s="10" t="inlineStr">
+      <c r="F206" s="10" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="64" customHeight="1">
-      <c r="A203" s="10" t="inlineStr">
+    <row r="207" ht="64" customHeight="1">
+      <c r="A207" s="10" t="inlineStr">
         <is>
           <t>트라넥삼산 (펩타이드)</t>
         </is>
       </c>
-      <c r="B203" s="10" t="inlineStr">
+      <c r="B207" s="10" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C203" s="11" t="inlineStr">
+      <c r="C207" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D203" s="12" t="inlineStr">
+      <c r="D207" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E203" s="10" t="inlineStr">
+      <c r="E207" s="10" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="F203" s="10" t="inlineStr">
+      <c r="F207" s="10" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="16" customHeight="1">
-      <c r="A204" s="10" t="inlineStr">
+    <row r="208" ht="16" customHeight="1">
+      <c r="A208" s="10" t="inlineStr">
         <is>
           <t>글루타치온</t>
         </is>
       </c>
-      <c r="B204" s="10" t="inlineStr">
+      <c r="B208" s="10" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C204" s="11" t="inlineStr">
+      <c r="C208" s="11" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D204" s="12" t="inlineStr">
+      <c r="D208" s="12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E204" s="10" t="inlineStr">
+      <c r="E208" s="10" t="inlineStr">
         <is>
           <t>미백효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="F204" s="10" t="inlineStr"/>
-    </row>
-    <row r="205" ht="64" customHeight="1">
-      <c r="A205" s="10" t="inlineStr">
+      <c r="F208" s="10" t="inlineStr"/>
+    </row>
+    <row r="209" ht="64" customHeight="1">
+      <c r="A209" s="10" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B205" s="10" t="inlineStr">
+      <c r="B209" s="10" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C205" s="11" t="inlineStr">
+      <c r="C209" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D205" s="24" t="inlineStr">
+      <c r="D209" s="24" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E205" s="10" t="inlineStr">
+      <c r="E209" s="10" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="F205" s="10" t="inlineStr">
+      <c r="F209" s="10" t="inlineStr">
         <is>
           <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="14" customHeight="1">
-      <c r="A206" s="16" t="inlineStr">
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="16" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 22 · 활성 76 · 방부 2</t>
         </is>
       </c>
-      <c r="B206" s="17" t="n"/>
-      <c r="C206" s="17" t="n"/>
-      <c r="D206" s="17" t="n"/>
-      <c r="E206" s="17" t="n"/>
-      <c r="F206" s="17" t="n"/>
-    </row>
-    <row r="207" ht="14" customHeight="1">
-      <c r="A207" s="18" t="inlineStr">
+      <c r="B210" s="17" t="n"/>
+      <c r="C210" s="17" t="n"/>
+      <c r="D210" s="17" t="n"/>
+      <c r="E210" s="17" t="n"/>
+      <c r="F210" s="17" t="n"/>
+    </row>
+    <row r="211" ht="14" customHeight="1">
+      <c r="A211" s="18" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B207" s="19" t="n"/>
-      <c r="C207" s="19" t="n"/>
-      <c r="D207" s="19" t="n"/>
-      <c r="E207" s="19" t="n"/>
-      <c r="F207" s="19" t="n"/>
-    </row>
-    <row r="208" ht="384" customHeight="1">
-      <c r="A208" s="20" t="inlineStr">
+      <c r="B211" s="19" t="n"/>
+      <c r="C211" s="19" t="n"/>
+      <c r="D211" s="19" t="n"/>
+      <c r="E211" s="19" t="n"/>
+      <c r="F211" s="19" t="n"/>
+    </row>
+    <row r="212" ht="384" customHeight="1">
+      <c r="A212" s="20" t="inlineStr">
         <is>
           <t>기미, 잡티 초기 진압에 TX 토닝 젤 (100g)
 난이도 : 하
@@ -6946,8 +6957,8 @@
         </is>
       </c>
     </row>
-    <row r="209" ht="80" customHeight="1">
-      <c r="A209" s="20" t="inlineStr">
+    <row r="213" ht="80" customHeight="1">
+      <c r="A213" s="20" t="inlineStr">
         <is>
           <t>현대약품 계열사 특허 성분)
 트라넥삼산과 나이아신아마이드를
@@ -6957,20 +6968,20 @@
         </is>
       </c>
     </row>
-    <row r="210" ht="14" customHeight="1">
-      <c r="A210" s="18" t="inlineStr">
+    <row r="214" ht="14" customHeight="1">
+      <c r="A214" s="18" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B210" s="19" t="n"/>
-      <c r="C210" s="19" t="n"/>
-      <c r="D210" s="19" t="n"/>
-      <c r="E210" s="19" t="n"/>
-      <c r="F210" s="19" t="n"/>
-    </row>
-    <row r="211" ht="64" customHeight="1">
-      <c r="A211" s="20" t="inlineStr">
+      <c r="B214" s="19" t="n"/>
+      <c r="C214" s="19" t="n"/>
+      <c r="D214" s="19" t="n"/>
+      <c r="E214" s="19" t="n"/>
+      <c r="F214" s="19" t="n"/>
+    </row>
+    <row r="215" ht="64" customHeight="1">
+      <c r="A215" s="20" t="inlineStr">
         <is>
           <t>TX 토닝 젤 토너 만들기
 1. 모든 재료를 계량합니다.
@@ -6979,14 +6990,12 @@
         </is>
       </c>
     </row>
-    <row r="212" ht="6" customHeight="1"/>
+    <row r="216" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="96">
     <mergeCell ref="A183:F183"/>
-    <mergeCell ref="A84:F84"/>
     <mergeCell ref="A75:F75"/>
     <mergeCell ref="A189:F189"/>
-    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A86:F86"/>
     <mergeCell ref="A47:F47"/>
@@ -6995,106 +7004,108 @@
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A152:F152"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A44:F44"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A186:F186"/>
     <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A70:F70"/>
     <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A212:F212"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A99:F99"/>
     <mergeCell ref="A149:F149"/>
-    <mergeCell ref="A163:F163"/>
+    <mergeCell ref="A214:F214"/>
+    <mergeCell ref="A101:F101"/>
     <mergeCell ref="A195:F195"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A213:F213"/>
     <mergeCell ref="A151:F151"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A141:F141"/>
-    <mergeCell ref="A206:F206"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A215:F215"/>
     <mergeCell ref="A125:F125"/>
-    <mergeCell ref="A190:F190"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A199:F199"/>
     <mergeCell ref="A127:F127"/>
     <mergeCell ref="A167:F167"/>
     <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A114:F114"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="A182:F182"/>
     <mergeCell ref="A98:F98"/>
-    <mergeCell ref="A191:F191"/>
-    <mergeCell ref="A178:F178"/>
+    <mergeCell ref="A169:F169"/>
     <mergeCell ref="A61:F61"/>
     <mergeCell ref="A88:F88"/>
     <mergeCell ref="A153:F153"/>
-    <mergeCell ref="A162:F162"/>
-    <mergeCell ref="A137:F137"/>
     <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A208:F208"/>
-    <mergeCell ref="A164:F164"/>
-    <mergeCell ref="A136:F136"/>
     <mergeCell ref="A74:F74"/>
     <mergeCell ref="A139:F139"/>
     <mergeCell ref="A210:F210"/>
-    <mergeCell ref="A179:F179"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A129:F129"/>
-    <mergeCell ref="A181:F181"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A116:F116"/>
     <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A131:F131"/>
     <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A165:F165"/>
-    <mergeCell ref="A180:F180"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A171:F171"/>
     <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A111:F111"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A207:F207"/>
+    <mergeCell ref="A143:F143"/>
+    <mergeCell ref="A157:F157"/>
+    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A78:F78"/>
     <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A128:F128"/>
     <mergeCell ref="A193:F193"/>
+    <mergeCell ref="A89:F89"/>
     <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A192:F192"/>
-    <mergeCell ref="A57:F57"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A185:F185"/>
+    <mergeCell ref="A194:F194"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A96:F96"/>
-    <mergeCell ref="A209:F209"/>
-    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A184:F184"/>
     <mergeCell ref="A211:F211"/>
-    <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A148:F148"/>
-    <mergeCell ref="A123:F123"/>
     <mergeCell ref="A138:F138"/>
+    <mergeCell ref="A197:F197"/>
     <mergeCell ref="A110:F110"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A187:F187"/>
+    <mergeCell ref="A196:F196"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A153" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A185" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A195" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>

--- a/카드_아키타입/02_젤.xlsx
+++ b/카드_아키타입/02_젤.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,13 +40,25 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001155CC"/>
-      <sz val="12"/>
-      <u val="single"/>
+      <color rgb="0033475B"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="003A3A3A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001155CC"/>
+      <sz val="12"/>
+      <u val="single"/>
     </font>
     <font>
       <b val="1"/>
@@ -59,7 +71,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +95,76 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EFF4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF0CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8F5D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E0D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6DAF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFF3F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD9F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBD9E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5D9C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9F0D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8EEF7"/>
       </patternFill>
     </fill>
@@ -93,57 +175,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAD9F7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E9F0D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CFF3F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBD9E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EEF3F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7FAFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCEBFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2E5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8F5D8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5D9C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF0CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -154,11 +186,6 @@
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="008A94A6"/>
-      </top>
     </border>
     <border>
       <left style="thin">
@@ -174,11 +201,16 @@
         <color rgb="00D0D5DD"/>
       </bottom>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="008A94A6"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -192,65 +224,111 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -332,7 +410,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7848600" y="1854200"/>
+    <pos x="7848600" y="9398000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -352,7 +430,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="1854200"/>
+    <pos x="9696450" y="9398000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -372,7 +450,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="1854200"/>
+    <pos x="11544300" y="9398000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -392,7 +470,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="1854200"/>
+    <pos x="13392150" y="9398000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -412,7 +490,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="3702049"/>
+    <pos x="7848600" y="11245849"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -432,7 +510,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="3702049"/>
+    <pos x="9696450" y="11245849"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -452,7 +530,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="3702049"/>
+    <pos x="11544300" y="11245849"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -472,7 +550,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="5549900"/>
+    <pos x="7848600" y="13093699"/>
     <ext cx="5143500" cy="4591050"/>
     <pic>
       <nvPicPr>
@@ -492,7 +570,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="10179049"/>
+    <pos x="7848600" y="17722850"/>
     <ext cx="5143500" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -512,7 +590,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="11845924"/>
+    <pos x="7848600" y="19389725"/>
     <ext cx="5143500" cy="2143125"/>
     <pic>
       <nvPicPr>
@@ -532,7 +610,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="15735300"/>
+    <pos x="7848600" y="23279100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -552,7 +630,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="15735300"/>
+    <pos x="9696450" y="23279100"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -572,7 +650,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="15735300"/>
+    <pos x="11544300" y="23279100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -592,7 +670,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="15735300"/>
+    <pos x="13392150" y="23279100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -612,7 +690,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="17583150"/>
+    <pos x="7848600" y="25126950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -632,7 +710,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="19431000"/>
+    <pos x="7848600" y="26974800"/>
     <ext cx="5143500" cy="3857625"/>
     <pic>
       <nvPicPr>
@@ -652,7 +730,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="23402925"/>
+    <pos x="7848600" y="30946725"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -672,7 +750,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="23402925"/>
+    <pos x="9696450" y="30946725"/>
     <ext cx="1809750" cy="1485900"/>
     <pic>
       <nvPicPr>
@@ -692,7 +770,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="23402925"/>
+    <pos x="11544300" y="30946725"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -712,7 +790,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="23402925"/>
+    <pos x="13392150" y="30946725"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -732,7 +810,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="25250775"/>
+    <pos x="7848600" y="32794575"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -752,7 +830,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="25250775"/>
+    <pos x="9696450" y="32794575"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -772,7 +850,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="25250775"/>
+    <pos x="11544300" y="32794575"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -792,7 +870,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="25250775"/>
+    <pos x="13392150" y="32794575"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -812,7 +890,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="27098625"/>
+    <pos x="7848600" y="34642425"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -832,7 +910,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="33016825"/>
+    <pos x="7848600" y="40560625"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -852,7 +930,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="33016825"/>
+    <pos x="9696450" y="40560625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -872,7 +950,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="33016825"/>
+    <pos x="11544300" y="40560625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -892,7 +970,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="33016825"/>
+    <pos x="13392150" y="40560625"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -912,7 +990,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="34864675"/>
+    <pos x="7848600" y="42408475"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -932,7 +1010,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="39176325"/>
+    <pos x="7848600" y="46720125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -952,7 +1030,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="39176325"/>
+    <pos x="9696450" y="46720125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -972,7 +1050,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="39176325"/>
+    <pos x="11544300" y="46720125"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -992,7 +1070,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="41024175"/>
+    <pos x="7848600" y="48567975"/>
     <ext cx="3857625" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1012,7 +1090,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="49603025"/>
+    <pos x="7848600" y="57146825"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1032,7 +1110,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="49603025"/>
+    <pos x="9696450" y="57146825"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1052,7 +1130,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="49603025"/>
+    <pos x="11544300" y="57146825"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1072,7 +1150,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="49603025"/>
+    <pos x="13392150" y="57146825"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1092,7 +1170,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="55762525"/>
+    <pos x="7848600" y="63306325"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1112,7 +1190,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="55762525"/>
+    <pos x="9696450" y="63306325"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1132,7 +1210,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="55762525"/>
+    <pos x="11544300" y="63306325"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1152,7 +1230,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="55762525"/>
+    <pos x="13392150" y="63306325"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1172,7 +1250,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="57610375"/>
+    <pos x="7848600" y="65154175"/>
     <ext cx="5143500" cy="2143125"/>
     <pic>
       <nvPicPr>
@@ -1192,7 +1270,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="63547625"/>
+    <pos x="7848600" y="71091425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1212,7 +1290,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="63547625"/>
+    <pos x="9696450" y="71091425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1232,7 +1310,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="63547625"/>
+    <pos x="11544300" y="71091425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1252,7 +1330,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="63547625"/>
+    <pos x="13392150" y="71091425"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1272,7 +1350,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="65395475"/>
+    <pos x="7848600" y="72939275"/>
     <ext cx="5143500" cy="2143125"/>
     <pic>
       <nvPicPr>
@@ -1292,7 +1370,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="70316725"/>
+    <pos x="7848600" y="77860525"/>
     <ext cx="5143500" cy="3857625"/>
     <pic>
       <nvPicPr>
@@ -1312,7 +1390,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="74212450"/>
+    <pos x="7848600" y="81756249"/>
     <ext cx="5143500" cy="4019550"/>
     <pic>
       <nvPicPr>
@@ -1332,7 +1410,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="78346299"/>
+    <pos x="7848600" y="85890099"/>
     <ext cx="3200400" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1352,7 +1430,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="85140800"/>
+    <pos x="7848600" y="92684600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1372,7 +1450,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="85140800"/>
+    <pos x="9696450" y="92684600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1392,7 +1470,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="85140800"/>
+    <pos x="11544300" y="92684600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1412,7 +1490,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="85140800"/>
+    <pos x="13392150" y="92684600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1432,7 +1510,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="86988650"/>
+    <pos x="7848600" y="94532450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1452,7 +1530,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="86988650"/>
+    <pos x="9696450" y="94532450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1472,7 +1550,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="86988650"/>
+    <pos x="11544300" y="94532450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1492,7 +1570,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="86988650"/>
+    <pos x="13392150" y="94532450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1512,7 +1590,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="88836500"/>
+    <pos x="7848600" y="96380300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1532,7 +1610,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="88836500"/>
+    <pos x="9696450" y="96380300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1552,7 +1630,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="88836500"/>
+    <pos x="11544300" y="96380300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1572,7 +1650,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="88836500"/>
+    <pos x="13392150" y="96380300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1592,7 +1670,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="90684350"/>
+    <pos x="7848600" y="98228150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1612,7 +1690,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="90684350"/>
+    <pos x="9696450" y="98228150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1632,7 +1710,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="90684350"/>
+    <pos x="11544300" y="98228150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1652,7 +1730,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="90684350"/>
+    <pos x="13392150" y="98228150"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1672,7 +1750,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="92532200"/>
+    <pos x="7848600" y="100076000"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1692,7 +1770,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="97713800"/>
+    <pos x="7848600" y="105257600"/>
     <ext cx="5143500" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -1712,7 +1790,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="99142550"/>
+    <pos x="7848600" y="106686350"/>
     <ext cx="2695575" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1732,7 +1810,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="104400350"/>
+    <pos x="7848600" y="111944150"/>
     <ext cx="3200400" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1752,7 +1830,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="111398050"/>
+    <pos x="7848600" y="118941850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1772,7 +1850,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="111398050"/>
+    <pos x="9696450" y="118941850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1792,7 +1870,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="111398050"/>
+    <pos x="11544300" y="118941850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1812,7 +1890,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="111398050"/>
+    <pos x="13392150" y="118941850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1832,7 +1910,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="113245900"/>
+    <pos x="7848600" y="120789700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1852,7 +1930,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="113245900"/>
+    <pos x="9696450" y="120789700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1872,7 +1950,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="115093750"/>
+    <pos x="7848600" y="122637550"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1892,7 +1970,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="128327150"/>
+    <pos x="7848600" y="135870950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1912,7 +1990,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="128327150"/>
+    <pos x="9696450" y="135870950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1932,7 +2010,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="128327150"/>
+    <pos x="11544300" y="135870950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1952,7 +2030,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="128327150"/>
+    <pos x="13392150" y="135870950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1972,7 +2050,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="130175000"/>
+    <pos x="7848600" y="137718800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1992,7 +2070,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="130175000"/>
+    <pos x="9696450" y="137718800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2012,7 +2090,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="130175000"/>
+    <pos x="11544300" y="137718800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2032,7 +2110,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="130175000"/>
+    <pos x="13392150" y="137718800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2052,7 +2130,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="132022850"/>
+    <pos x="7848600" y="139566650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2072,7 +2150,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="132022850"/>
+    <pos x="9696450" y="139566650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2092,7 +2170,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="139566650"/>
+    <pos x="7848600" y="147110450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2112,7 +2190,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="139566650"/>
+    <pos x="9696450" y="147110450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2132,7 +2210,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="139566650"/>
+    <pos x="11544300" y="147110450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2152,7 +2230,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="141414500"/>
+    <pos x="7848600" y="148958300"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2463,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F215"/>
+  <dimension ref="A1:F235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2526,201 +2604,447 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
-    <row r="5" ht="6" customHeight="1"/>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>🎨 역할(phase) 읽는 법 — 아래 미니표 '역할' 색상의 뜻</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>물·수용성 베이스. 제형의 대부분을 차지하는 뼈대이고, 수용성 활성·보습제가 여기 녹는다.   예) 정제수, 로즈워터, 알로에워터</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>오일·버터 등 지용성. 피부에 유연·보습막·영양을 주고 발림성·리치함을 결정한다.   예) 호호바오일, 시어버터, 스쿠알란</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>안 섞이는 물과 오일을 하나로 묶는 '다리'. 없으면 분리된다. 양으로 로션↔크림 점도도 좌우.   예) 올리브유화왁스, 몬타노브68</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>왁스·고형. 제형을 굳혀 밤·스틱 형태를 만든다. 비율로 말랑↔단단이 갈린다.   예) 밀랍, 칸데릴라왁스</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>피지·노폐물을 물에 씻겨나가게 하는 세정 성분. 거품·세정력을 담당.   예) 코코베타인, 데실글루코사이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>공기·진피의 수분을 끌어와 붙잡는 습윤제. 촉촉함을 유지.   예) 글리세린, 프로판다이올, 솔비톨</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>특정 효능(미백·진정·탄력 등)을 노리는 기능 성분. '이 제품의 컨셉'을 만든다.   예) 나이아신아마이드, 세라마이드, 추출물</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>향·아로마(에센셜오일 등). 소량(보통 ≤1%)으로 감성·아로마테라피.   예) 라벤더EO, 네롤리</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>색을 내는 안료·펄. 색조·틴트 제형의 핵심.   예) 마이카, 산화철, 이산화티탄</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>세균·곰팡이 번식을 억제. 물 있는 제형엔 사실상 필수.   예) 1,2-헥산디올, 천연한방보존제</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>점도 조절(젤화)과 산도(pH) 조절. 사용감·안정성·방부 효력에 영향.   예) 잔탄검, 카보머, 구연산</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>위 분류에 안 잡힌 것(완제 베이스·충전제 등).   예) 크림베이스, 옥수수전분</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>📖 배합 기본원리 — 왜 그렇게 하나</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Q. 유화는 왜 같은 온도(65~75℃)에서?
+→ 오일상 왁스가 녹아 액체이고 수상도 같은 온도여야 미세하게 섞인다. 온도차가 크면 닿는 순간 왁스가 굳어 알갱이·분리가 생긴다.</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Q. 왜 식으며 저어주나 / 핸드블렌더?
+→ 유화 입자를 더 잘고 고르게 쪼개면 분리가 줄고 발림·안정성이 좋아진다. 찬물에 받쳐 식히면 유화가 빨리·안정적으로 잡힌다.</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Q. 물 있는 제형은 왜 방부 필수?
+→ 물은 세균·곰팡이의 번식 배지다. 무방부는 수일 내 변질 → 냉장·소량 제조만. 방부력은 실제 챌린지(방부력) 테스트로 확인해야 한다.</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Q. 왜 약산성(pH 5~6)?
+→ 건강한 피부는 pH 4.5~5.5. 알칼리는 장벽을 들뜨게 하고, 적정 산성은 방부 효력과 일부 활성(산성 영역) 안정에 유리하다.</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Q. 가루(점증·활성)는 왜 미리 분산?
+→ 가루가 물에 닿자마자 겉만 수화돼 '덩어리(fish-eye)'가 진다. 글리세린 등에 미리 적셔 분산하거나 천천히 뿌리며 교반해야 곱게 풀린다.</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Q. 무수(오일·밤)는 왜 방부 불필요하지만 물 유입 금지?
+→ 물이 없으면 미생물이 못 큰다. 대신 사용 중 물이 들어가면 그 지점부터 상한다. 산패는 비타민E 등 항산화와 차광·밀폐로 늦춘다.</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>아로마 손소독제젤타입    ↗ 원본</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F27" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>408g / (=500ml)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>95%. 곡물 발효 알콜</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="29" ht="64" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>31%</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D29" s="30" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>카보머 1%을 함유, 알로에모이스트보다 높은 점도. 섞어주는 것만으로 간편하게 젤타입을 만들 수 있도록 만든 원료.</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr"/>
-    </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="F29" s="27" t="inlineStr"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>22.5g</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D30" s="31" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>보습제, 향이 오랫동안 머물 수 있도록 고착제 역할을 함</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F30" s="27" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>레몬에센셜오일</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>5ml</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D31" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>천연 레몬 껍질 오일 · 상큼한 향</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F31" s="27" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 유칼립투스 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="32" ht="14" customHeight="1">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  보습 4 · 활성 64 · 향 1 · 점증/pH 31</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="17" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="17" t="n"/>
-    </row>
-    <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="34" t="n"/>
+      <c r="D32" s="34" t="n"/>
+      <c r="E32" s="34" t="n"/>
+      <c r="F32" s="34" t="n"/>
+    </row>
+    <row r="33" ht="14" customHeight="1">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n"/>
-      <c r="C13" s="19" t="n"/>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="19" t="n"/>
-      <c r="F13" s="19" t="n"/>
-    </row>
-    <row r="14" ht="384" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="B33" s="36" t="n"/>
+      <c r="C33" s="36" t="n"/>
+      <c r="D33" s="36" t="n"/>
+      <c r="E33" s="36" t="n"/>
+      <c r="F33" s="36" t="n"/>
+    </row>
+    <row r="34" ht="384" customHeight="1">
+      <c r="A34" s="37" t="inlineStr">
         <is>
           <t>무제 문서
 셀프 백신 중 하나가 손소독입니다.
@@ -2749,8 +3073,8 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="336" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+    <row r="35" ht="336" customHeight="1">
+      <c r="A35" s="37" t="inlineStr">
         <is>
           <t>알콜류의 세균력은....
 세균 막의 지질 복합체를 파괴하고 단백질을 변성ㆍ응고시켜 살균작용을 나타낸답니다.
@@ -2776,20 +3100,20 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+    <row r="36" ht="14" customHeight="1">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n"/>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="19" t="n"/>
-      <c r="F16" s="19" t="n"/>
-    </row>
-    <row r="17" ht="96" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="B36" s="36" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+    </row>
+    <row r="37" ht="96" customHeight="1">
+      <c r="A37" s="37" t="inlineStr">
         <is>
           <t>1. 카보머프리젤을 계량해주세요. | 2. 식물성글리세린과 | 3. 에센셜오일을 비롯한 아로마베이스95까지 모든 재료를 계량해주세요.
 |
@@ -2799,301 +3123,301 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="6" customHeight="1"/>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="38" ht="6" customHeight="1"/>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
         <is>
           <t>허니 촉촉 바디젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="B39" s="25" t="n"/>
+      <c r="C39" s="25" t="n"/>
+      <c r="D39" s="25" t="n"/>
+      <c r="E39" s="25" t="n"/>
+      <c r="F39" s="25" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D40" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E40" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F40" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="80" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B41" s="38" t="inlineStr">
         <is>
           <t>68g</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C41" s="39" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D41" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E41" s="38" t="inlineStr">
         <is>
           <t>수분, 자체 점증.</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F41" s="38" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="38" t="inlineStr">
         <is>
           <t>워터 코포아수</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B42" s="38" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C42" s="39" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D42" s="40" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
+      <c r="E42" s="38" t="inlineStr">
         <is>
           <t>천연 레시틴으로 코포아수 버터를 리포좀화.</t>
         </is>
       </c>
-      <c r="F22" s="21" t="inlineStr">
+      <c r="F42" s="38" t="inlineStr">
         <is>
           <t>워터 아르간</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>세라마이드 (수용성)</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C43" s="39" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D43" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E43" s="38" t="inlineStr">
         <is>
           <t>세라마이드 리포좀화</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F43" s="38" t="inlineStr">
         <is>
           <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="21" t="inlineStr">
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
         <is>
           <t>꿀 추출물</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B44" s="38" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C44" s="39" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D44" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="E44" s="38" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F44" s="38" t="inlineStr">
         <is>
           <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="64" customHeight="1">
-      <c r="A25" s="21" t="inlineStr">
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C45" s="39" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D25" s="24" t="inlineStr">
+      <c r="D45" s="41" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E45" s="38" t="inlineStr">
         <is>
           <t>균번식 억제제</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F45" s="38" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g · (알로에베라겔의 양을 67g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="38" t="inlineStr">
         <is>
           <t>스윗 오렌지에센셜오일</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B46" s="38" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C46" s="39" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D46" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E46" s="38" t="inlineStr">
         <is>
           <t>오렌지 껍질 오일</t>
         </is>
       </c>
-      <c r="F26" s="21" t="inlineStr">
+      <c r="F46" s="38" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="21" t="inlineStr">
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="38" t="inlineStr">
         <is>
           <t>네롤리에센셜오일</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B47" s="38" t="inlineStr">
         <is>
           <t>3방울</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C47" s="39" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D47" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E47" s="38" t="inlineStr">
         <is>
           <t>오렌지꽃오일 · 민감, 모든 피부</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F47" s="38" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="48" ht="14" customHeight="1">
+      <c r="A48" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 10 · 활성 88 · 향 1 · 방부 1</t>
         </is>
       </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-    </row>
-    <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="B48" s="34" t="n"/>
+      <c r="C48" s="34" t="n"/>
+      <c r="D48" s="34" t="n"/>
+      <c r="E48" s="34" t="n"/>
+      <c r="F48" s="34" t="n"/>
+    </row>
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-    </row>
-    <row r="30" ht="96" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="B49" s="36" t="n"/>
+      <c r="C49" s="36" t="n"/>
+      <c r="D49" s="36" t="n"/>
+      <c r="E49" s="36" t="n"/>
+      <c r="F49" s="36" t="n"/>
+    </row>
+    <row r="50" ht="96" customHeight="1">
+      <c r="A50" s="42" t="inlineStr">
         <is>
           <t>클레오파트라, 네로의 아내 포파이아 등 전설적인 미인들이 꿀과
 우유로 목욕을 했다는 것은 이미 알려진 사실인데요 그만큼 꿀은 거친
@@ -3103,369 +3427,369 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="26" t="n"/>
-    </row>
-    <row r="31" ht="14" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="B50" s="23" t="n"/>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="23" t="n"/>
+      <c r="F50" s="23" t="n"/>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-    </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="B51" s="36" t="n"/>
+      <c r="C51" s="36" t="n"/>
+      <c r="D51" s="36" t="n"/>
+      <c r="E51" s="36" t="n"/>
+      <c r="F51" s="36" t="n"/>
+    </row>
+    <row r="52" ht="48" customHeight="1">
+      <c r="A52" s="42" t="inlineStr">
         <is>
           <t>1. 모든 재료를 계량한 후
 2. 골고루 섞어주세요.
 3. 용기에 넣으면 완성.</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-    </row>
-    <row r="33" ht="86.74999999999997" customHeight="1">
-      <c r="A33" s="26" t="n"/>
-      <c r="B33" s="26" t="n"/>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="26" t="n"/>
-    </row>
-    <row r="34" ht="6" customHeight="1"/>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="B52" s="23" t="n"/>
+      <c r="C52" s="23" t="n"/>
+      <c r="D52" s="23" t="n"/>
+      <c r="E52" s="23" t="n"/>
+      <c r="F52" s="23" t="n"/>
+    </row>
+    <row r="53" ht="86.74999999999997" customHeight="1">
+      <c r="A53" s="23" t="n"/>
+      <c r="B53" s="23" t="n"/>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="23" t="n"/>
+      <c r="E53" s="23" t="n"/>
+      <c r="F53" s="23" t="n"/>
+    </row>
+    <row r="54" ht="6" customHeight="1"/>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="24" t="inlineStr">
         <is>
           <t>트러블 SSG~필링젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="B55" s="25" t="n"/>
+      <c r="C55" s="25" t="n"/>
+      <c r="D55" s="25" t="n"/>
+      <c r="E55" s="25" t="n"/>
+      <c r="F55" s="25" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C56" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F56" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
         <is>
           <t>내추럴 / 셀룰로오즈</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B57" s="27" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C57" s="28" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D57" s="30" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E57" s="27" t="inlineStr">
         <is>
           <t>프랑스산 목화 섬유질로 · 만든 천연 필링제.</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="F57" s="27" t="inlineStr"/>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
         <is>
           <t>티트리워터</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B58" s="27" t="inlineStr">
         <is>
           <t>37g</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C58" s="28" t="inlineStr">
         <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="D38" s="23" t="inlineStr">
+      <c r="D58" s="40" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E58" s="27" t="inlineStr">
         <is>
           <t>티트리 수증기 · 증류법으로 추출</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F58" s="27" t="inlineStr">
         <is>
           <t>로즈마리 · 편백워터</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="64" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="59" ht="64" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C59" s="28" t="inlineStr">
         <is>
           <t>41%</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D59" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E59" s="27" t="inlineStr">
         <is>
           <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. · 남은 재료 활용 팁 : 젤타입스킨으로 사용가능 · 헤어에센스로 사용가능.</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F59" s="27" t="inlineStr">
         <is>
           <t>카보폴프리젤</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>알란토인분말</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C60" s="28" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D40" s="12" t="inlineStr">
+      <c r="D60" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>진정, 계량스푼 작은 쪽 깎아서 4개면 0.2g</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F60" s="27" t="inlineStr">
         <is>
           <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>마치현추출물</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C61" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D41" s="12" t="inlineStr">
+      <c r="D61" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E61" s="27" t="inlineStr">
         <is>
           <t>쇠비름, 진정 · 트러블 관리</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F61" s="27" t="inlineStr">
         <is>
           <t>어성초 · 병풀 추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="62" ht="48" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>3.8g</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C62" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D62" s="31" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E62" s="27" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F62" s="27" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="64" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="63" ht="64" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B63" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C63" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D43" s="24" t="inlineStr">
+      <c r="D63" s="41" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E63" s="27" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F63" s="27" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g · (티트리워터의 양을 36g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="32" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>레몬EO</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B64" s="27" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C64" s="28" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D64" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr">
+      <c r="E64" s="27" t="inlineStr">
         <is>
           <t>레몬껍질오일,상큼, 아로마테라피</t>
         </is>
       </c>
-      <c r="F44" s="10" t="inlineStr">
+      <c r="F64" s="27" t="inlineStr">
         <is>
           <t>무향 또는 · 원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="16" t="inlineStr">
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 38 · 보습 4 · 활성 46 · 향 0 · 방부 1 · 점증/pH 10</t>
         </is>
       </c>
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="17" t="n"/>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="17" t="n"/>
-      <c r="F45" s="17" t="n"/>
-    </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="B65" s="34" t="n"/>
+      <c r="C65" s="34" t="n"/>
+      <c r="D65" s="34" t="n"/>
+      <c r="E65" s="34" t="n"/>
+      <c r="F65" s="34" t="n"/>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B46" s="19" t="n"/>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="19" t="n"/>
-      <c r="E46" s="19" t="n"/>
-      <c r="F46" s="19" t="n"/>
-    </row>
-    <row r="47" ht="224" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="B66" s="36" t="n"/>
+      <c r="C66" s="36" t="n"/>
+      <c r="D66" s="36" t="n"/>
+      <c r="E66" s="36" t="n"/>
+      <c r="F66" s="36" t="n"/>
+    </row>
+    <row r="67" ht="224" customHeight="1">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>누구에게나 '때'는 있습니다.
 이 '때'관리만 잘 해줘도
@@ -3484,20 +3808,20 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="18" t="inlineStr">
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B48" s="19" t="n"/>
-      <c r="C48" s="19" t="n"/>
-      <c r="D48" s="19" t="n"/>
-      <c r="E48" s="19" t="n"/>
-      <c r="F48" s="19" t="n"/>
-    </row>
-    <row r="49" ht="96" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="B68" s="36" t="n"/>
+      <c r="C68" s="36" t="n"/>
+      <c r="D68" s="36" t="n"/>
+      <c r="E68" s="36" t="n"/>
+      <c r="F68" s="36" t="n"/>
+    </row>
+    <row r="69" ht="96" customHeight="1">
+      <c r="A69" s="37" t="inlineStr">
         <is>
           <t>1. 알란토인분말 0.2g은 계량스푼 작은 쪽에 깍아서 4개로 해주세요.
 2. 비커에 넣고 내추럴 셀룰로오즈을 비롯 모든 재료를
@@ -3508,233 +3832,233 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="6" customHeight="1"/>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+    <row r="70" ht="6" customHeight="1"/>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="24" t="inlineStr">
         <is>
           <t>이데베논 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="9" t="inlineStr">
+      <c r="B71" s="25" t="n"/>
+      <c r="C71" s="25" t="n"/>
+      <c r="D71" s="25" t="n"/>
+      <c r="E71" s="25" t="n"/>
+      <c r="F71" s="25" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B72" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C72" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D52" s="9" t="inlineStr">
+      <c r="D72" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
+      <c r="E72" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F52" s="9" t="inlineStr">
+      <c r="F72" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="48" customHeight="1">
-      <c r="A53" s="21" t="inlineStr">
+    <row r="73" ht="48" customHeight="1">
+      <c r="A73" s="38" t="inlineStr">
         <is>
           <t>로즈 플라워젤</t>
         </is>
       </c>
-      <c r="B53" s="21" t="inlineStr">
+      <c r="B73" s="38" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="C53" s="22" t="inlineStr">
+      <c r="C73" s="39" t="inlineStr">
         <is>
           <t>87%</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D73" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E53" s="21" t="inlineStr">
+      <c r="E73" s="38" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 젤타입으로. · 에코보습제, 알란토인 함유</t>
         </is>
       </c>
-      <c r="F53" s="21" t="inlineStr">
+      <c r="F73" s="38" t="inlineStr">
         <is>
           <t>허브누리 · 알로에베라겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="48" customHeight="1">
-      <c r="A54" s="21" t="inlineStr">
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="38" t="inlineStr">
         <is>
           <t>이데베논</t>
         </is>
       </c>
-      <c r="B54" s="21" t="inlineStr">
+      <c r="B74" s="38" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C54" s="22" t="inlineStr">
+      <c r="C74" s="39" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D74" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E54" s="21" t="inlineStr">
+      <c r="E74" s="38" t="inlineStr">
         <is>
           <t>코엔자임의 10배 · 항산화효과 · 레시피 처방시 500ppm 함유크림 완성.</t>
         </is>
       </c>
-      <c r="F54" s="21" t="inlineStr"/>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="21" t="inlineStr">
+      <c r="F74" s="38" t="inlineStr"/>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="38" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
-      <c r="B55" s="21" t="inlineStr">
+      <c r="B75" s="38" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C55" s="22" t="inlineStr">
+      <c r="C75" s="39" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D75" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E55" s="21" t="inlineStr">
+      <c r="E75" s="38" t="inlineStr">
         <is>
           <t>비타민 펩타이드, 화이트닝</t>
         </is>
       </c>
-      <c r="F55" s="21" t="inlineStr">
+      <c r="F75" s="38" t="inlineStr">
         <is>
           <t>4GF · 씨네이크펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="64" customHeight="1">
-      <c r="A56" s="21" t="inlineStr">
+    <row r="76" ht="64" customHeight="1">
+      <c r="A76" s="38" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B56" s="21" t="inlineStr">
+      <c r="B76" s="38" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C56" s="22" t="inlineStr">
+      <c r="C76" s="39" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D56" s="24" t="inlineStr">
+      <c r="D76" s="41" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E56" s="21" t="inlineStr">
+      <c r="E76" s="38" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="F56" s="21" t="inlineStr">
+      <c r="F76" s="38" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g · (로즈플라워 겔의 양을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="21" t="inlineStr">
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="38" t="inlineStr">
         <is>
           <t>다중히아루론산</t>
         </is>
       </c>
-      <c r="B57" s="21" t="inlineStr">
+      <c r="B77" s="38" t="inlineStr">
         <is>
           <t>0~5g</t>
         </is>
       </c>
-      <c r="C57" s="22" t="inlineStr">
+      <c r="C77" s="39" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr">
+      <c r="D77" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E57" s="21" t="inlineStr">
+      <c r="E77" s="38" t="inlineStr">
         <is>
           <t>고분자, 중분자, 저분자로 이루어짐. · 피부 각층별 수분공급</t>
         </is>
       </c>
-      <c r="F57" s="21" t="inlineStr">
+      <c r="F77" s="38" t="inlineStr">
         <is>
           <t>판테놀</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 99 · 방부 1</t>
         </is>
       </c>
-      <c r="B58" s="17" t="n"/>
-      <c r="C58" s="17" t="n"/>
-      <c r="D58" s="17" t="n"/>
-      <c r="E58" s="17" t="n"/>
-      <c r="F58" s="17" t="n"/>
-    </row>
-    <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="B78" s="34" t="n"/>
+      <c r="C78" s="34" t="n"/>
+      <c r="D78" s="34" t="n"/>
+      <c r="E78" s="34" t="n"/>
+      <c r="F78" s="34" t="n"/>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B59" s="19" t="n"/>
-      <c r="C59" s="19" t="n"/>
-      <c r="D59" s="19" t="n"/>
-      <c r="E59" s="19" t="n"/>
-      <c r="F59" s="19" t="n"/>
-    </row>
-    <row r="60" ht="112" customHeight="1">
-      <c r="A60" s="25" t="inlineStr">
+      <c r="B79" s="36" t="n"/>
+      <c r="C79" s="36" t="n"/>
+      <c r="D79" s="36" t="n"/>
+      <c r="E79" s="36" t="n"/>
+      <c r="F79" s="36" t="n"/>
+    </row>
+    <row r="80" ht="112" customHeight="1">
+      <c r="A80" s="42" t="inlineStr">
         <is>
           <t>황금톡스라 불리는 ,이데베논.
 코엔자임Q10의 10배 항산화효과를 가지고 있습니다.
@@ -3745,26 +4069,26 @@
 또 급이 다른 이데베논의 항산화효과로 시간을 되돌리세요.</t>
         </is>
       </c>
-      <c r="B60" s="26" t="n"/>
-      <c r="C60" s="26" t="n"/>
-      <c r="D60" s="26" t="n"/>
-      <c r="E60" s="26" t="n"/>
-      <c r="F60" s="26" t="n"/>
-    </row>
-    <row r="61" ht="14" customHeight="1">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="B80" s="23" t="n"/>
+      <c r="C80" s="23" t="n"/>
+      <c r="D80" s="23" t="n"/>
+      <c r="E80" s="23" t="n"/>
+      <c r="F80" s="23" t="n"/>
+    </row>
+    <row r="81" ht="14" customHeight="1">
+      <c r="A81" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B61" s="19" t="n"/>
-      <c r="C61" s="19" t="n"/>
-      <c r="D61" s="19" t="n"/>
-      <c r="E61" s="19" t="n"/>
-      <c r="F61" s="19" t="n"/>
-    </row>
-    <row r="62" ht="64" customHeight="1">
-      <c r="A62" s="25" t="inlineStr">
+      <c r="B81" s="36" t="n"/>
+      <c r="C81" s="36" t="n"/>
+      <c r="D81" s="36" t="n"/>
+      <c r="E81" s="36" t="n"/>
+      <c r="F81" s="36" t="n"/>
+    </row>
+    <row r="82" ht="64" customHeight="1">
+      <c r="A82" s="42" t="inlineStr">
         <is>
           <t>만들기 과정
 1.로즈플라워겔을 계량하고
@@ -3772,243 +4096,243 @@
 3.고른 점도가 나오면 용기에 담아주세요.</t>
         </is>
       </c>
-      <c r="B62" s="26" t="n"/>
-      <c r="C62" s="26" t="n"/>
-      <c r="D62" s="26" t="n"/>
-      <c r="E62" s="26" t="n"/>
-      <c r="F62" s="26" t="n"/>
-    </row>
-    <row r="63" ht="6" customHeight="1"/>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="B82" s="23" t="n"/>
+      <c r="C82" s="23" t="n"/>
+      <c r="D82" s="23" t="n"/>
+      <c r="E82" s="23" t="n"/>
+      <c r="F82" s="23" t="n"/>
+    </row>
+    <row r="83" ht="6" customHeight="1"/>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="24" t="inlineStr">
         <is>
           <t>TX 멜라 토닝 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="B84" s="25" t="n"/>
+      <c r="C84" s="25" t="n"/>
+      <c r="D84" s="25" t="n"/>
+      <c r="E84" s="25" t="n"/>
+      <c r="F84" s="25" t="n"/>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B65" s="9" t="inlineStr">
+      <c r="B85" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C85" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D85" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
+      <c r="E85" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F65" s="9" t="inlineStr">
+      <c r="F85" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="48" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+    <row r="86" ht="48" customHeight="1">
+      <c r="A86" s="27" t="inlineStr">
         <is>
           <t>로즈 플라워겔</t>
         </is>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B86" s="27" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C86" s="28" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D86" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E66" s="10" t="inlineStr">
+      <c r="E86" s="27" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 듬뿍 담은젤 · 에코보습제, 알란토인 함유</t>
         </is>
       </c>
-      <c r="F66" s="10" t="inlineStr">
+      <c r="F86" s="27" t="inlineStr">
         <is>
           <t>알로에베라겔 · 네롤리플라워젤</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="64" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
+    <row r="87" ht="64" customHeight="1">
+      <c r="A87" s="27" t="inlineStr">
         <is>
           <t>트라넥삼산 / (펩타이드)</t>
         </is>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B87" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C67" s="11" t="inlineStr">
+      <c r="C87" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D67" s="12" t="inlineStr">
+      <c r="D87" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E67" s="10" t="inlineStr">
+      <c r="E87" s="27" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 · 펩타이드 말단에 합성으로 · 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="F67" s="10" t="inlineStr">
+      <c r="F87" s="27" t="inlineStr">
         <is>
           <t>화이트 펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="48" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
+    <row r="88" ht="48" customHeight="1">
+      <c r="A88" s="27" t="inlineStr">
         <is>
           <t>4GF</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B88" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C68" s="11" t="inlineStr">
+      <c r="C88" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D68" s="12" t="inlineStr">
+      <c r="D88" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr">
+      <c r="E88" s="27" t="inlineStr">
         <is>
           <t>EGF, FGF, IGF, TGF · 복합 펩타이드</t>
         </is>
       </c>
-      <c r="F68" s="10" t="inlineStr">
+      <c r="F88" s="27" t="inlineStr">
         <is>
           <t>아세틸헥사 · 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="64" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
+    <row r="89" ht="64" customHeight="1">
+      <c r="A89" s="27" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B89" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C69" s="11" t="inlineStr">
+      <c r="C89" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D69" s="24" t="inlineStr">
+      <c r="D89" s="41" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E69" s="10" t="inlineStr">
+      <c r="E89" s="27" t="inlineStr">
         <is>
           <t>균번식 억제, 식물복합</t>
         </is>
       </c>
-      <c r="F69" s="10" t="inlineStr">
+      <c r="F89" s="27" t="inlineStr">
         <is>
           <t>1.2헥산디올2g · (로즈플라워겔을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="48" customHeight="1">
-      <c r="A70" s="10" t="inlineStr">
+    <row r="90" ht="48" customHeight="1">
+      <c r="A90" s="27" t="inlineStr">
         <is>
           <t>브라이트닝 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B90" s="27" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C70" s="11" t="inlineStr">
+      <c r="C90" s="28" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D70" s="15" t="inlineStr">
+      <c r="D90" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
+      <c r="E90" s="27" t="inlineStr">
         <is>
           <t>네롤리, 일랑일랑, 버가못FCF · 프랑킨센스 EO 블렌딩오일, 생략 가능</t>
         </is>
       </c>
-      <c r="F70" s="10" t="inlineStr">
+      <c r="F90" s="27" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="16" t="inlineStr">
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 99 · 향 0 · 방부 1</t>
         </is>
       </c>
-      <c r="B71" s="17" t="n"/>
-      <c r="C71" s="17" t="n"/>
-      <c r="D71" s="17" t="n"/>
-      <c r="E71" s="17" t="n"/>
-      <c r="F71" s="17" t="n"/>
-    </row>
-    <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="18" t="inlineStr">
+      <c r="B91" s="34" t="n"/>
+      <c r="C91" s="34" t="n"/>
+      <c r="D91" s="34" t="n"/>
+      <c r="E91" s="34" t="n"/>
+      <c r="F91" s="34" t="n"/>
+    </row>
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B72" s="19" t="n"/>
-      <c r="C72" s="19" t="n"/>
-      <c r="D72" s="19" t="n"/>
-      <c r="E72" s="19" t="n"/>
-      <c r="F72" s="19" t="n"/>
-    </row>
-    <row r="73" ht="384" customHeight="1">
-      <c r="A73" s="20" t="inlineStr">
+      <c r="B92" s="36" t="n"/>
+      <c r="C92" s="36" t="n"/>
+      <c r="D92" s="36" t="n"/>
+      <c r="E92" s="36" t="n"/>
+      <c r="F92" s="36" t="n"/>
+    </row>
+    <row r="93" ht="384" customHeight="1">
+      <c r="A93" s="37" t="inlineStr">
         <is>
           <t>트레넥삼산(Tranexamic acid, TX)은 원래 지혈제로 사용되고 있습니다.
 산후 , 외상, 월경, 코피 등 과다 출혈에 사용되는 항플라즈민제로 의약 성분입니다.
@@ -4037,27 +4361,27 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="20" t="inlineStr">
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="37" t="inlineStr">
         <is>
           <t>도움을 줍니다.</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="14" customHeight="1">
-      <c r="A75" s="18" t="inlineStr">
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B75" s="19" t="n"/>
-      <c r="C75" s="19" t="n"/>
-      <c r="D75" s="19" t="n"/>
-      <c r="E75" s="19" t="n"/>
-      <c r="F75" s="19" t="n"/>
-    </row>
-    <row r="76" ht="64" customHeight="1">
-      <c r="A76" s="20" t="inlineStr">
+      <c r="B95" s="36" t="n"/>
+      <c r="C95" s="36" t="n"/>
+      <c r="D95" s="36" t="n"/>
+      <c r="E95" s="36" t="n"/>
+      <c r="F95" s="36" t="n"/>
+    </row>
+    <row r="96" ht="64" customHeight="1">
+      <c r="A96" s="37" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량하고
@@ -4066,237 +4390,237 @@
         </is>
       </c>
     </row>
-    <row r="77" ht="6" customHeight="1"/>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
+    <row r="97" ht="6" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="24" t="inlineStr">
         <is>
           <t>콜라겐 드림 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
-      <c r="F78" s="8" t="n"/>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="9" t="inlineStr">
+      <c r="B98" s="25" t="n"/>
+      <c r="C98" s="25" t="n"/>
+      <c r="D98" s="25" t="n"/>
+      <c r="E98" s="25" t="n"/>
+      <c r="F98" s="25" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B79" s="9" t="inlineStr">
+      <c r="B99" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C79" s="9" t="inlineStr">
+      <c r="C99" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D79" s="9" t="inlineStr">
+      <c r="D99" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr">
+      <c r="E99" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F79" s="9" t="inlineStr">
+      <c r="F99" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="48" customHeight="1">
-      <c r="A80" s="21" t="inlineStr">
+    <row r="100" ht="48" customHeight="1">
+      <c r="A100" s="38" t="inlineStr">
         <is>
           <t>워터 호호바</t>
         </is>
       </c>
-      <c r="B80" s="21" t="inlineStr">
+      <c r="B100" s="38" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C80" s="22" t="inlineStr">
+      <c r="C100" s="39" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D80" s="23" t="inlineStr">
+      <c r="D100" s="40" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E80" s="21" t="inlineStr">
+      <c r="E100" s="38" t="inlineStr">
         <is>
           <t>호호바오일에 천연레시틴을 · 이용하여 리포좀화 · 수상에 쉽게 분산</t>
         </is>
       </c>
-      <c r="F80" s="21" t="inlineStr">
+      <c r="F100" s="38" t="inlineStr">
         <is>
           <t>슈퍼 곡물 · 단백질추출물</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="48" customHeight="1">
-      <c r="A81" s="21" t="inlineStr">
+    <row r="101" ht="48" customHeight="1">
+      <c r="A101" s="38" t="inlineStr">
         <is>
           <t>콜라겐 펩타이드</t>
         </is>
       </c>
-      <c r="B81" s="21" t="inlineStr">
+      <c r="B101" s="38" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C81" s="22" t="inlineStr">
+      <c r="C101" s="39" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D101" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E81" s="21" t="inlineStr">
+      <c r="E101" s="38" t="inlineStr">
         <is>
           <t>인체 흡수가 용이한 · 저분자화 순수 단백질 사용 · 18종의 아미노산으로 구성</t>
         </is>
       </c>
-      <c r="F81" s="21" t="inlineStr">
+      <c r="F101" s="38" t="inlineStr">
         <is>
           <t>아카시아 · 마린콜라겐</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="32" customHeight="1">
-      <c r="A82" s="21" t="inlineStr">
+    <row r="102" ht="32" customHeight="1">
+      <c r="A102" s="38" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
-      <c r="B82" s="21" t="inlineStr">
+      <c r="B102" s="38" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C82" s="22" t="inlineStr">
+      <c r="C102" s="39" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D82" s="12" t="inlineStr">
+      <c r="D102" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E82" s="21" t="inlineStr">
+      <c r="E102" s="38" t="inlineStr">
         <is>
           <t>비타민 펩타이드, 화이트닝</t>
         </is>
       </c>
-      <c r="F82" s="21" t="inlineStr">
+      <c r="F102" s="38" t="inlineStr">
         <is>
           <t>트라넥 · 삼산펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="21" t="inlineStr">
+    <row r="103" ht="32" customHeight="1">
+      <c r="A103" s="38" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B83" s="21" t="inlineStr">
+      <c r="B103" s="38" t="inlineStr">
         <is>
           <t>85g</t>
         </is>
       </c>
-      <c r="C83" s="22" t="inlineStr">
+      <c r="C103" s="39" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="D83" s="12" t="inlineStr">
+      <c r="D103" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E83" s="21" t="inlineStr">
+      <c r="E103" s="38" t="inlineStr">
         <is>
           <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="F83" s="21" t="inlineStr">
+      <c r="F103" s="38" t="inlineStr">
         <is>
           <t>네롤리플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="64" customHeight="1">
-      <c r="A84" s="21" t="inlineStr">
+    <row r="104" ht="64" customHeight="1">
+      <c r="A104" s="38" t="inlineStr">
         <is>
           <t>1,2 헥산디올</t>
         </is>
       </c>
-      <c r="B84" s="21" t="inlineStr">
+      <c r="B104" s="38" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C84" s="22" t="inlineStr">
+      <c r="C104" s="39" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D84" s="14" t="inlineStr">
+      <c r="D104" s="31" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E84" s="21" t="inlineStr">
+      <c r="E104" s="38" t="inlineStr">
         <is>
           <t>보습제, 자유수 억제, 균번식억제</t>
         </is>
       </c>
-      <c r="F84" s="21" t="inlineStr">
+      <c r="F104" s="38" t="inlineStr">
         <is>
           <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="14" customHeight="1">
-      <c r="A85" s="16" t="inlineStr">
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 3 · 보습 2 · 활성 95</t>
         </is>
       </c>
-      <c r="B85" s="17" t="n"/>
-      <c r="C85" s="17" t="n"/>
-      <c r="D85" s="17" t="n"/>
-      <c r="E85" s="17" t="n"/>
-      <c r="F85" s="17" t="n"/>
-    </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="18" t="inlineStr">
+      <c r="B105" s="34" t="n"/>
+      <c r="C105" s="34" t="n"/>
+      <c r="D105" s="34" t="n"/>
+      <c r="E105" s="34" t="n"/>
+      <c r="F105" s="34" t="n"/>
+    </row>
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B86" s="19" t="n"/>
-      <c r="C86" s="19" t="n"/>
-      <c r="D86" s="19" t="n"/>
-      <c r="E86" s="19" t="n"/>
-      <c r="F86" s="19" t="n"/>
-    </row>
-    <row r="87" ht="112" customHeight="1">
-      <c r="A87" s="25" t="inlineStr">
+      <c r="B106" s="36" t="n"/>
+      <c r="C106" s="36" t="n"/>
+      <c r="D106" s="36" t="n"/>
+      <c r="E106" s="36" t="n"/>
+      <c r="F106" s="36" t="n"/>
+    </row>
+    <row r="107" ht="112" customHeight="1">
+      <c r="A107" s="42" t="inlineStr">
         <is>
           <t>25세 이후 콜라겐 합성이 줄어들므로
 피부가 탄력을 잃고 주름이 생기기 시작하며 활기를 잃게 됩니다.
@@ -4307,26 +4631,26 @@
 보습은 물론 탄력관리에 좋고 생기있는 피부를 가꿔줍니다.</t>
         </is>
       </c>
-      <c r="B87" s="26" t="n"/>
-      <c r="C87" s="26" t="n"/>
-      <c r="D87" s="26" t="n"/>
-      <c r="E87" s="26" t="n"/>
-      <c r="F87" s="26" t="n"/>
-    </row>
-    <row r="88" ht="14" customHeight="1">
-      <c r="A88" s="18" t="inlineStr">
+      <c r="B107" s="23" t="n"/>
+      <c r="C107" s="23" t="n"/>
+      <c r="D107" s="23" t="n"/>
+      <c r="E107" s="23" t="n"/>
+      <c r="F107" s="23" t="n"/>
+    </row>
+    <row r="108" ht="14" customHeight="1">
+      <c r="A108" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B88" s="19" t="n"/>
-      <c r="C88" s="19" t="n"/>
-      <c r="D88" s="19" t="n"/>
-      <c r="E88" s="19" t="n"/>
-      <c r="F88" s="19" t="n"/>
-    </row>
-    <row r="89" ht="64" customHeight="1">
-      <c r="A89" s="25" t="inlineStr">
+      <c r="B108" s="36" t="n"/>
+      <c r="C108" s="36" t="n"/>
+      <c r="D108" s="36" t="n"/>
+      <c r="E108" s="36" t="n"/>
+      <c r="F108" s="36" t="n"/>
+    </row>
+    <row r="109" ht="64" customHeight="1">
+      <c r="A109" s="42" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량합니다.
@@ -4334,207 +4658,207 @@
 3. 점도가 고르게 되면 용기에 옮겨 담으면 완성.</t>
         </is>
       </c>
-      <c r="B89" s="26" t="n"/>
-      <c r="C89" s="26" t="n"/>
-      <c r="D89" s="26" t="n"/>
-      <c r="E89" s="26" t="n"/>
-      <c r="F89" s="26" t="n"/>
-    </row>
-    <row r="90" ht="6" customHeight="1"/>
-    <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
+      <c r="B109" s="23" t="n"/>
+      <c r="C109" s="23" t="n"/>
+      <c r="D109" s="23" t="n"/>
+      <c r="E109" s="23" t="n"/>
+      <c r="F109" s="23" t="n"/>
+    </row>
+    <row r="110" ht="6" customHeight="1"/>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="24" t="inlineStr">
         <is>
           <t>셀프백신 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
-      <c r="E91" s="8" t="n"/>
-      <c r="F91" s="8" t="n"/>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="9" t="inlineStr">
+      <c r="B111" s="25" t="n"/>
+      <c r="C111" s="25" t="n"/>
+      <c r="D111" s="25" t="n"/>
+      <c r="E111" s="25" t="n"/>
+      <c r="F111" s="25" t="n"/>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B92" s="9" t="inlineStr">
+      <c r="B112" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C92" s="9" t="inlineStr">
+      <c r="C112" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D92" s="9" t="inlineStr">
+      <c r="D112" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E92" s="9" t="inlineStr">
+      <c r="E112" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F92" s="9" t="inlineStr">
+      <c r="F112" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="10" t="inlineStr">
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B113" s="27" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C93" s="11" t="inlineStr">
+      <c r="C113" s="28" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D93" s="12" t="inlineStr">
+      <c r="D113" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E93" s="10" t="inlineStr">
+      <c r="E113" s="27" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="F93" s="10" t="inlineStr">
+      <c r="F113" s="27" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="48" customHeight="1">
-      <c r="A94" s="10" t="inlineStr">
+    <row r="114" ht="48" customHeight="1">
+      <c r="A114" s="27" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B114" s="27" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C94" s="11" t="inlineStr">
+      <c r="C114" s="28" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="D94" s="13" t="inlineStr">
+      <c r="D114" s="30" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E94" s="10" t="inlineStr">
+      <c r="E114" s="27" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 · 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="F94" s="10" t="inlineStr"/>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="F114" s="27" t="inlineStr"/>
+    </row>
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="27" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B95" s="10" t="inlineStr">
+      <c r="B115" s="27" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C95" s="11" t="inlineStr">
+      <c r="C115" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D95" s="12" t="inlineStr">
+      <c r="D115" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E95" s="10" t="inlineStr">
+      <c r="E115" s="27" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="F115" s="27" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="48" customHeight="1">
-      <c r="A96" s="10" t="inlineStr">
+    <row r="116" ht="48" customHeight="1">
+      <c r="A116" s="27" t="inlineStr">
         <is>
           <t>니아울리에센셜오일</t>
         </is>
       </c>
-      <c r="B96" s="10" t="inlineStr">
+      <c r="B116" s="27" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C96" s="11" t="inlineStr">
+      <c r="C116" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D96" s="15" t="inlineStr">
+      <c r="D116" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E96" s="10" t="inlineStr">
+      <c r="E116" s="27" t="inlineStr">
         <is>
           <t>광엽 티트리라 불림. 향과 성분이 · 유칼립투스와 티트리의 부드러운 버전</t>
         </is>
       </c>
-      <c r="F96" s="10" t="inlineStr">
+      <c r="F116" s="27" t="inlineStr">
         <is>
           <t>유칼립튜스, 티트리 등</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="16" t="inlineStr">
+    <row r="117" ht="14" customHeight="1">
+      <c r="A117" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 69 · 향 1 · 점증/pH 30</t>
         </is>
       </c>
-      <c r="B97" s="17" t="n"/>
-      <c r="C97" s="17" t="n"/>
-      <c r="D97" s="17" t="n"/>
-      <c r="E97" s="17" t="n"/>
-      <c r="F97" s="17" t="n"/>
-    </row>
-    <row r="98" ht="14" customHeight="1">
-      <c r="A98" s="18" t="inlineStr">
+      <c r="B117" s="34" t="n"/>
+      <c r="C117" s="34" t="n"/>
+      <c r="D117" s="34" t="n"/>
+      <c r="E117" s="34" t="n"/>
+      <c r="F117" s="34" t="n"/>
+    </row>
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B98" s="19" t="n"/>
-      <c r="C98" s="19" t="n"/>
-      <c r="D98" s="19" t="n"/>
-      <c r="E98" s="19" t="n"/>
-      <c r="F98" s="19" t="n"/>
-    </row>
-    <row r="99" ht="320" customHeight="1">
-      <c r="A99" s="20" t="inlineStr">
+      <c r="B118" s="36" t="n"/>
+      <c r="C118" s="36" t="n"/>
+      <c r="D118" s="36" t="n"/>
+      <c r="E118" s="36" t="n"/>
+      <c r="F118" s="36" t="n"/>
+    </row>
+    <row r="119" ht="320" customHeight="1">
+      <c r="A119" s="37" t="inlineStr">
         <is>
           <t>무제 문서
 코로나19 예방을 위해 전문가들이
@@ -4559,20 +4883,20 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="14" customHeight="1">
-      <c r="A100" s="18" t="inlineStr">
+    <row r="120" ht="14" customHeight="1">
+      <c r="A120" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B100" s="19" t="n"/>
-      <c r="C100" s="19" t="n"/>
-      <c r="D100" s="19" t="n"/>
-      <c r="E100" s="19" t="n"/>
-      <c r="F100" s="19" t="n"/>
-    </row>
-    <row r="101" ht="80" customHeight="1">
-      <c r="A101" s="20" t="inlineStr">
+      <c r="B120" s="36" t="n"/>
+      <c r="C120" s="36" t="n"/>
+      <c r="D120" s="36" t="n"/>
+      <c r="E120" s="36" t="n"/>
+      <c r="F120" s="36" t="n"/>
+    </row>
+    <row r="121" ht="80" customHeight="1">
+      <c r="A121" s="37" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -4582,233 +4906,233 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="6" customHeight="1"/>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="7" t="inlineStr">
+    <row r="122" ht="6" customHeight="1"/>
+    <row r="123" ht="22" customHeight="1">
+      <c r="A123" s="24" t="inlineStr">
         <is>
           <t>상큼 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B103" s="8" t="n"/>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="8" t="n"/>
-      <c r="F103" s="8" t="n"/>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="9" t="inlineStr">
+      <c r="B123" s="25" t="n"/>
+      <c r="C123" s="25" t="n"/>
+      <c r="D123" s="25" t="n"/>
+      <c r="E123" s="25" t="n"/>
+      <c r="F123" s="25" t="n"/>
+    </row>
+    <row r="124" ht="15" customHeight="1">
+      <c r="A124" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B104" s="9" t="inlineStr">
+      <c r="B124" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C104" s="9" t="inlineStr">
+      <c r="C124" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D104" s="9" t="inlineStr">
+      <c r="D124" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E104" s="9" t="inlineStr">
+      <c r="E124" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F104" s="9" t="inlineStr">
+      <c r="F124" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="21" t="inlineStr">
+    <row r="125" ht="16" customHeight="1">
+      <c r="A125" s="38" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B105" s="21" t="inlineStr">
+      <c r="B125" s="38" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C105" s="22" t="inlineStr">
+      <c r="C125" s="39" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D105" s="12" t="inlineStr">
+      <c r="D125" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E105" s="21" t="inlineStr">
+      <c r="E125" s="38" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="F105" s="21" t="inlineStr">
+      <c r="F125" s="38" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="48" customHeight="1">
-      <c r="A106" s="21" t="inlineStr">
+    <row r="126" ht="48" customHeight="1">
+      <c r="A126" s="38" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B106" s="21" t="inlineStr">
+      <c r="B126" s="38" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C106" s="22" t="inlineStr">
+      <c r="C126" s="39" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D106" s="13" t="inlineStr">
+      <c r="D126" s="30" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E106" s="21" t="inlineStr">
+      <c r="E126" s="38" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 · 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="F106" s="21" t="inlineStr"/>
-    </row>
-    <row r="107" ht="32" customHeight="1">
-      <c r="A107" s="21" t="inlineStr">
+      <c r="F126" s="38" t="inlineStr"/>
+    </row>
+    <row r="127" ht="32" customHeight="1">
+      <c r="A127" s="38" t="inlineStr">
         <is>
           <t>알란토인(액상)</t>
         </is>
       </c>
-      <c r="B107" s="21" t="inlineStr">
+      <c r="B127" s="38" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C107" s="22" t="inlineStr">
+      <c r="C127" s="39" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D107" s="12" t="inlineStr">
+      <c r="D127" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E107" s="21" t="inlineStr">
+      <c r="E127" s="38" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="F107" s="21" t="inlineStr">
+      <c r="F127" s="38" t="inlineStr">
         <is>
           <t>프로폴리스추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="21" t="inlineStr">
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="38" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B108" s="21" t="inlineStr">
+      <c r="B128" s="38" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C108" s="22" t="inlineStr">
+      <c r="C128" s="39" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D108" s="12" t="inlineStr">
+      <c r="D128" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E108" s="21" t="inlineStr">
+      <c r="E128" s="38" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="F108" s="21" t="inlineStr">
+      <c r="F128" s="38" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="48" customHeight="1">
-      <c r="A109" s="21" t="inlineStr">
+    <row r="129" ht="48" customHeight="1">
+      <c r="A129" s="38" t="inlineStr">
         <is>
           <t>레몬쥬스EO</t>
         </is>
       </c>
-      <c r="B109" s="21" t="inlineStr">
+      <c r="B129" s="38" t="inlineStr">
         <is>
           <t>20~25방울</t>
         </is>
       </c>
-      <c r="C109" s="22" t="inlineStr">
+      <c r="C129" s="39" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D109" s="15" t="inlineStr">
+      <c r="D129" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E109" s="21" t="inlineStr">
+      <c r="E129" s="38" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드에센셜오일 · 블랜딩오일</t>
         </is>
       </c>
-      <c r="F109" s="21" t="inlineStr">
+      <c r="F129" s="38" t="inlineStr">
         <is>
           <t>레몬, 만다린, 그레이프푸룻, 라임, 오렌지에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="14" customHeight="1">
-      <c r="A110" s="16" t="inlineStr">
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 74 · 향 1 · 점증/pH 25</t>
         </is>
       </c>
-      <c r="B110" s="17" t="n"/>
-      <c r="C110" s="17" t="n"/>
-      <c r="D110" s="17" t="n"/>
-      <c r="E110" s="17" t="n"/>
-      <c r="F110" s="17" t="n"/>
-    </row>
-    <row r="111" ht="14" customHeight="1">
-      <c r="A111" s="18" t="inlineStr">
+      <c r="B130" s="34" t="n"/>
+      <c r="C130" s="34" t="n"/>
+      <c r="D130" s="34" t="n"/>
+      <c r="E130" s="34" t="n"/>
+      <c r="F130" s="34" t="n"/>
+    </row>
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B111" s="19" t="n"/>
-      <c r="C111" s="19" t="n"/>
-      <c r="D111" s="19" t="n"/>
-      <c r="E111" s="19" t="n"/>
-      <c r="F111" s="19" t="n"/>
-    </row>
-    <row r="112" ht="208" customHeight="1">
-      <c r="A112" s="25" t="inlineStr">
+      <c r="B131" s="36" t="n"/>
+      <c r="C131" s="36" t="n"/>
+      <c r="D131" s="36" t="n"/>
+      <c r="E131" s="36" t="n"/>
+      <c r="F131" s="36" t="n"/>
+    </row>
+    <row r="132" ht="208" customHeight="1">
+      <c r="A132" s="42" t="inlineStr">
         <is>
           <t>무제 문서
 그 어느 때보다 손 청결이 중요한 때입니다.
@@ -4825,26 +5149,26 @@
 '상큼 손소독제 만들기'를 안내해드립니다.</t>
         </is>
       </c>
-      <c r="B112" s="26" t="n"/>
-      <c r="C112" s="26" t="n"/>
-      <c r="D112" s="26" t="n"/>
-      <c r="E112" s="26" t="n"/>
-      <c r="F112" s="26" t="n"/>
-    </row>
-    <row r="113" ht="14" customHeight="1">
-      <c r="A113" s="18" t="inlineStr">
+      <c r="B132" s="23" t="n"/>
+      <c r="C132" s="23" t="n"/>
+      <c r="D132" s="23" t="n"/>
+      <c r="E132" s="23" t="n"/>
+      <c r="F132" s="23" t="n"/>
+    </row>
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B113" s="19" t="n"/>
-      <c r="C113" s="19" t="n"/>
-      <c r="D113" s="19" t="n"/>
-      <c r="E113" s="19" t="n"/>
-      <c r="F113" s="19" t="n"/>
-    </row>
-    <row r="114" ht="80" customHeight="1">
-      <c r="A114" s="25" t="inlineStr">
+      <c r="B133" s="36" t="n"/>
+      <c r="C133" s="36" t="n"/>
+      <c r="D133" s="36" t="n"/>
+      <c r="E133" s="36" t="n"/>
+      <c r="F133" s="36" t="n"/>
+    </row>
+    <row r="134" ht="80" customHeight="1">
+      <c r="A134" s="42" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -4853,295 +5177,295 @@
 언제나 어디서나 사용하세요.</t>
         </is>
       </c>
-      <c r="B114" s="26" t="n"/>
-      <c r="C114" s="26" t="n"/>
-      <c r="D114" s="26" t="n"/>
-      <c r="E114" s="26" t="n"/>
-      <c r="F114" s="26" t="n"/>
-    </row>
-    <row r="115" ht="6" customHeight="1"/>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="7" t="inlineStr">
+      <c r="B134" s="23" t="n"/>
+      <c r="C134" s="23" t="n"/>
+      <c r="D134" s="23" t="n"/>
+      <c r="E134" s="23" t="n"/>
+      <c r="F134" s="23" t="n"/>
+    </row>
+    <row r="135" ht="6" customHeight="1"/>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="24" t="inlineStr">
         <is>
           <t>트러블 잠잠 스팟젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B116" s="8" t="n"/>
-      <c r="C116" s="8" t="n"/>
-      <c r="D116" s="8" t="n"/>
-      <c r="E116" s="8" t="n"/>
-      <c r="F116" s="8" t="n"/>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="9" t="inlineStr">
+      <c r="B136" s="25" t="n"/>
+      <c r="C136" s="25" t="n"/>
+      <c r="D136" s="25" t="n"/>
+      <c r="E136" s="25" t="n"/>
+      <c r="F136" s="25" t="n"/>
+    </row>
+    <row r="137" ht="15" customHeight="1">
+      <c r="A137" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B117" s="9" t="inlineStr">
+      <c r="B137" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C117" s="9" t="inlineStr">
+      <c r="C137" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D117" s="9" t="inlineStr">
+      <c r="D137" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E117" s="9" t="inlineStr">
+      <c r="E137" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F117" s="9" t="inlineStr">
+      <c r="F137" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="10" t="inlineStr">
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="27" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B118" s="10" t="inlineStr">
+      <c r="B138" s="27" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C118" s="11" t="inlineStr">
+      <c r="C138" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D118" s="15" t="inlineStr">
+      <c r="D138" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E118" s="10" t="inlineStr">
+      <c r="E138" s="27" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="F118" s="10" t="inlineStr">
+      <c r="F138" s="27" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="32" customHeight="1">
-      <c r="A119" s="10" t="inlineStr">
+    <row r="139" ht="32" customHeight="1">
+      <c r="A139" s="27" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B119" s="10" t="inlineStr">
+      <c r="B139" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C119" s="11" t="inlineStr">
+      <c r="C139" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D119" s="27" t="inlineStr">
+      <c r="D139" s="43" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E119" s="10" t="inlineStr">
+      <c r="E139" s="27" t="inlineStr">
         <is>
           <t>가용화제. · 물과요일이 분리되지않도록 하는 역할</t>
         </is>
       </c>
-      <c r="F119" s="10" t="inlineStr">
+      <c r="F139" s="27" t="inlineStr">
         <is>
           <t>솔루벌라이저</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="10" t="inlineStr">
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="27" t="inlineStr">
         <is>
           <t>라벤더워터</t>
         </is>
       </c>
-      <c r="B120" s="10" t="inlineStr">
+      <c r="B140" s="27" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C120" s="11" t="inlineStr">
+      <c r="C140" s="28" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D120" s="23" t="inlineStr">
+      <c r="D140" s="40" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E120" s="10" t="inlineStr">
+      <c r="E140" s="27" t="inlineStr">
         <is>
           <t>진정,재생</t>
         </is>
       </c>
-      <c r="F120" s="10" t="inlineStr">
+      <c r="F140" s="27" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="32" customHeight="1">
-      <c r="A121" s="10" t="inlineStr">
+    <row r="141" ht="32" customHeight="1">
+      <c r="A141" s="27" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔</t>
         </is>
       </c>
-      <c r="B121" s="10" t="inlineStr">
+      <c r="B141" s="27" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C121" s="11" t="inlineStr">
+      <c r="C141" s="28" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D121" s="12" t="inlineStr">
+      <c r="D141" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E121" s="10" t="inlineStr">
+      <c r="E141" s="27" t="inlineStr">
         <is>
           <t>겔타입, 수분공급</t>
         </is>
       </c>
-      <c r="F121" s="10" t="inlineStr">
+      <c r="F141" s="27" t="inlineStr">
         <is>
           <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="10" t="inlineStr">
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="27" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
-      <c r="B122" s="10" t="inlineStr">
+      <c r="B142" s="27" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C122" s="11" t="inlineStr">
+      <c r="C142" s="28" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D122" s="12" t="inlineStr">
+      <c r="D142" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E122" s="10" t="inlineStr">
+      <c r="E142" s="27" t="inlineStr">
         <is>
           <t>항균,진정</t>
         </is>
       </c>
-      <c r="F122" s="10" t="inlineStr">
+      <c r="F142" s="27" t="inlineStr">
         <is>
           <t>카렌듈라추출물</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="10" t="inlineStr">
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="27" t="inlineStr">
         <is>
           <t>한방보존제</t>
         </is>
       </c>
-      <c r="B123" s="10" t="inlineStr">
+      <c r="B143" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C123" s="11" t="inlineStr">
+      <c r="C143" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D123" s="24" t="inlineStr">
+      <c r="D143" s="41" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E123" s="10" t="inlineStr">
+      <c r="E143" s="27" t="inlineStr">
         <is>
           <t>복합한방추출물, 균번식억제</t>
         </is>
       </c>
-      <c r="F123" s="10" t="inlineStr">
+      <c r="F143" s="27" t="inlineStr">
         <is>
           <t>수용성보존제</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="14" customHeight="1">
-      <c r="A124" s="16" t="inlineStr">
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 28 · 유화 2 · 활성 66 · 향 2 · 방부 2</t>
         </is>
       </c>
-      <c r="B124" s="17" t="n"/>
-      <c r="C124" s="17" t="n"/>
-      <c r="D124" s="17" t="n"/>
-      <c r="E124" s="17" t="n"/>
-      <c r="F124" s="17" t="n"/>
-    </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="18" t="inlineStr">
+      <c r="B144" s="34" t="n"/>
+      <c r="C144" s="34" t="n"/>
+      <c r="D144" s="34" t="n"/>
+      <c r="E144" s="34" t="n"/>
+      <c r="F144" s="34" t="n"/>
+    </row>
+    <row r="145" ht="14" customHeight="1">
+      <c r="A145" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B125" s="19" t="n"/>
-      <c r="C125" s="19" t="n"/>
-      <c r="D125" s="19" t="n"/>
-      <c r="E125" s="19" t="n"/>
-      <c r="F125" s="19" t="n"/>
-    </row>
-    <row r="126" ht="64" customHeight="1">
-      <c r="A126" s="20" t="inlineStr">
+      <c r="B145" s="36" t="n"/>
+      <c r="C145" s="36" t="n"/>
+      <c r="D145" s="36" t="n"/>
+      <c r="E145" s="36" t="n"/>
+      <c r="F145" s="36" t="n"/>
+    </row>
+    <row r="146" ht="64" customHeight="1">
+      <c r="A146" s="37" t="inlineStr">
         <is>
           <t>[ 사용법 ]
 티트리에센셜오일은 국소부위에 원액을 발라도 되는 에센셜오일입니다. 스팟젤은 티트리에센셜오일을 전체의 2%를 정도로 희석한 순한 젤타입에센스입니다. 소량을 여드름이 난 부분에 발라주세요.</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="14" customHeight="1">
-      <c r="A127" s="18" t="inlineStr">
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B127" s="19" t="n"/>
-      <c r="C127" s="19" t="n"/>
-      <c r="D127" s="19" t="n"/>
-      <c r="E127" s="19" t="n"/>
-      <c r="F127" s="19" t="n"/>
-    </row>
-    <row r="128" ht="112" customHeight="1">
-      <c r="A128" s="20" t="inlineStr">
+      <c r="B147" s="36" t="n"/>
+      <c r="C147" s="36" t="n"/>
+      <c r="D147" s="36" t="n"/>
+      <c r="E147" s="36" t="n"/>
+      <c r="F147" s="36" t="n"/>
+    </row>
+    <row r="148" ht="112" customHeight="1">
+      <c r="A148" s="37" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 티트리, 올리브리퀴드를 계량합니다.
@@ -5153,206 +5477,206 @@
         </is>
       </c>
     </row>
-    <row r="129" ht="243.2499999999993" customHeight="1"/>
-    <row r="130" ht="6" customHeight="1"/>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
+    <row r="149" ht="243.2499999999993" customHeight="1"/>
+    <row r="150" ht="6" customHeight="1"/>
+    <row r="151" ht="22" customHeight="1">
+      <c r="A151" s="24" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 바디팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B131" s="8" t="n"/>
-      <c r="C131" s="8" t="n"/>
-      <c r="D131" s="8" t="n"/>
-      <c r="E131" s="8" t="n"/>
-      <c r="F131" s="8" t="n"/>
-    </row>
-    <row r="132" ht="15" customHeight="1">
-      <c r="A132" s="9" t="inlineStr">
+      <c r="B151" s="25" t="n"/>
+      <c r="C151" s="25" t="n"/>
+      <c r="D151" s="25" t="n"/>
+      <c r="E151" s="25" t="n"/>
+      <c r="F151" s="25" t="n"/>
+    </row>
+    <row r="152" ht="15" customHeight="1">
+      <c r="A152" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B132" s="9" t="inlineStr">
+      <c r="B152" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C152" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D132" s="9" t="inlineStr">
+      <c r="D152" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E132" s="9" t="inlineStr">
+      <c r="E152" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F132" s="9" t="inlineStr">
+      <c r="F152" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="32" customHeight="1">
-      <c r="A133" s="21" t="inlineStr">
+    <row r="153" ht="32" customHeight="1">
+      <c r="A153" s="38" t="inlineStr">
         <is>
           <t>그린 클레이</t>
         </is>
       </c>
-      <c r="B133" s="21" t="inlineStr">
+      <c r="B153" s="38" t="inlineStr">
         <is>
           <t>54.35%</t>
         </is>
       </c>
-      <c r="C133" s="22" t="inlineStr"/>
-      <c r="D133" s="28" t="inlineStr">
+      <c r="C153" s="39" t="inlineStr"/>
+      <c r="D153" s="44" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E133" s="21" t="inlineStr">
+      <c r="E153" s="38" t="inlineStr">
         <is>
           <t>녹색 점토, 피지·노폐물 흡착</t>
         </is>
       </c>
-      <c r="F133" s="21" t="inlineStr">
+      <c r="F153" s="38" t="inlineStr">
         <is>
           <t>핑크클레이, 카올린</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="64" customHeight="1">
-      <c r="A134" s="21" t="inlineStr">
+    <row r="154" ht="64" customHeight="1">
+      <c r="A154" s="38" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B134" s="21" t="inlineStr">
+      <c r="B154" s="38" t="inlineStr">
         <is>
           <t>43.48%</t>
         </is>
       </c>
-      <c r="C134" s="22" t="inlineStr"/>
-      <c r="D134" s="23" t="inlineStr">
+      <c r="C154" s="39" t="inlineStr"/>
+      <c r="D154" s="40" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E134" s="21" t="inlineStr">
+      <c r="E154" s="38" t="inlineStr">
         <is>
           <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
-      <c r="F134" s="21" t="inlineStr">
+      <c r="F154" s="38" t="inlineStr">
         <is>
           <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="32" customHeight="1">
-      <c r="A135" s="21" t="inlineStr">
+    <row r="155" ht="32" customHeight="1">
+      <c r="A155" s="38" t="inlineStr">
         <is>
           <t>그레이프프룻EO</t>
         </is>
       </c>
-      <c r="B135" s="21" t="inlineStr">
+      <c r="B155" s="38" t="inlineStr">
         <is>
           <t>1.09%</t>
         </is>
       </c>
-      <c r="C135" s="22" t="inlineStr"/>
-      <c r="D135" s="15" t="inlineStr">
+      <c r="C155" s="39" t="inlineStr"/>
+      <c r="D155" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E135" s="21" t="inlineStr">
+      <c r="E155" s="38" t="inlineStr">
         <is>
           <t>자몽 에센셜오일, 상쾌·수렴</t>
         </is>
       </c>
-      <c r="F135" s="21" t="inlineStr">
+      <c r="F155" s="38" t="inlineStr">
         <is>
           <t>오렌지, 레몬에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="64" customHeight="1">
-      <c r="A136" s="21" t="inlineStr">
+    <row r="156" ht="64" customHeight="1">
+      <c r="A156" s="38" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B136" s="21" t="inlineStr">
+      <c r="B156" s="38" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C136" s="22" t="inlineStr"/>
-      <c r="D136" s="15" t="inlineStr">
+      <c r="C156" s="39" t="inlineStr"/>
+      <c r="D156" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E136" s="21" t="inlineStr">
+      <c r="E156" s="38" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="F136" s="21" t="inlineStr">
+      <c r="F156" s="38" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="32" customHeight="1">
-      <c r="A137" s="21" t="inlineStr">
+    <row r="157" ht="32" customHeight="1">
+      <c r="A157" s="38" t="inlineStr">
         <is>
           <t>싸이프러스</t>
         </is>
       </c>
-      <c r="B137" s="21" t="inlineStr">
+      <c r="B157" s="38" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C137" s="22" t="inlineStr"/>
-      <c r="D137" s="15" t="inlineStr">
+      <c r="C157" s="39" t="inlineStr"/>
+      <c r="D157" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E137" s="21" t="inlineStr">
+      <c r="E157" s="38" t="inlineStr">
         <is>
           <t>상록 침엽수로 · 스팀 증류법 추출, 숲향</t>
         </is>
       </c>
-      <c r="F137" s="21" t="inlineStr">
+      <c r="F157" s="38" t="inlineStr">
         <is>
           <t>편백</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="14" customHeight="1">
-      <c r="A138" s="18" t="inlineStr">
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B138" s="19" t="n"/>
-      <c r="C138" s="19" t="n"/>
-      <c r="D138" s="19" t="n"/>
-      <c r="E138" s="19" t="n"/>
-      <c r="F138" s="19" t="n"/>
-    </row>
-    <row r="139" ht="192" customHeight="1">
-      <c r="A139" s="25" t="inlineStr">
+      <c r="B158" s="36" t="n"/>
+      <c r="C158" s="36" t="n"/>
+      <c r="D158" s="36" t="n"/>
+      <c r="E158" s="36" t="n"/>
+      <c r="F158" s="36" t="n"/>
+    </row>
+    <row r="159" ht="192" customHeight="1">
+      <c r="A159" s="42" t="inlineStr">
         <is>
           <t>그린클레이 - 프랑스 아질레지방에서 채취하는 클레이(흙). 미세한 클레이가 피부 깊숙이 침투 모공속 노폐물 배출, 흡착, 풍부한 미네랄 성분 해독 효과를 줍니다. 셀룰라이트관리, 여드름지성 피부에 사용.
 그레이프프룻(자몽껍질오일), 제라늄, 싸이프러스, 쥬니퍼베리, 레몬, 펜넬에센셜오일이 다이어트에 효과적인 오일이다. 림프자극, 독소배출, 호르몬균형, 해독 등의 효과를 준다.
@@ -5363,237 +5687,237 @@
 4. 이런 오일로 비누, 마사지오일, 젤, 로션/크림류 제품을 만들어 병행하면 좋다.</t>
         </is>
       </c>
-      <c r="B139" s="26" t="n"/>
-      <c r="C139" s="26" t="n"/>
-      <c r="D139" s="26" t="n"/>
-      <c r="E139" s="26" t="n"/>
-      <c r="F139" s="26" t="n"/>
-    </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="A140" s="18" t="inlineStr">
+      <c r="B159" s="23" t="n"/>
+      <c r="C159" s="23" t="n"/>
+      <c r="D159" s="23" t="n"/>
+      <c r="E159" s="23" t="n"/>
+      <c r="F159" s="23" t="n"/>
+    </row>
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B140" s="19" t="n"/>
-      <c r="C140" s="19" t="n"/>
-      <c r="D140" s="19" t="n"/>
-      <c r="E140" s="19" t="n"/>
-      <c r="F140" s="19" t="n"/>
-    </row>
-    <row r="141" ht="48" customHeight="1">
-      <c r="A141" s="25" t="inlineStr">
+      <c r="B160" s="36" t="n"/>
+      <c r="C160" s="36" t="n"/>
+      <c r="D160" s="36" t="n"/>
+      <c r="E160" s="36" t="n"/>
+      <c r="F160" s="36" t="n"/>
+    </row>
+    <row r="161" ht="48" customHeight="1">
+      <c r="A161" s="42" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 그린클레이, 물, 에센셜오일을 다 넣고
 2. 잘 섞어줍니다.</t>
         </is>
       </c>
-      <c r="B141" s="26" t="n"/>
-      <c r="C141" s="26" t="n"/>
-      <c r="D141" s="26" t="n"/>
-      <c r="E141" s="26" t="n"/>
-      <c r="F141" s="26" t="n"/>
-    </row>
-    <row r="142" ht="6" customHeight="1"/>
-    <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="7" t="inlineStr">
+      <c r="B161" s="23" t="n"/>
+      <c r="C161" s="23" t="n"/>
+      <c r="D161" s="23" t="n"/>
+      <c r="E161" s="23" t="n"/>
+      <c r="F161" s="23" t="n"/>
+    </row>
+    <row r="162" ht="6" customHeight="1"/>
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="24" t="inlineStr">
         <is>
           <t>레몬 손소독제(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B143" s="8" t="n"/>
-      <c r="C143" s="8" t="n"/>
-      <c r="D143" s="8" t="n"/>
-      <c r="E143" s="8" t="n"/>
-      <c r="F143" s="8" t="n"/>
-    </row>
-    <row r="144" ht="15" customHeight="1">
-      <c r="A144" s="9" t="inlineStr">
+      <c r="B163" s="25" t="n"/>
+      <c r="C163" s="25" t="n"/>
+      <c r="D163" s="25" t="n"/>
+      <c r="E163" s="25" t="n"/>
+      <c r="F163" s="25" t="n"/>
+    </row>
+    <row r="164" ht="15" customHeight="1">
+      <c r="A164" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B144" s="9" t="inlineStr">
+      <c r="B164" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C144" s="9" t="inlineStr">
+      <c r="C164" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D144" s="9" t="inlineStr">
+      <c r="D164" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E144" s="9" t="inlineStr">
+      <c r="E164" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F144" s="9" t="inlineStr">
+      <c r="F164" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="64" customHeight="1">
-      <c r="A145" s="10" t="inlineStr">
+    <row r="165" ht="64" customHeight="1">
+      <c r="A165" s="27" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B145" s="10" t="inlineStr">
+      <c r="B165" s="27" t="inlineStr">
         <is>
           <t>28g</t>
         </is>
       </c>
-      <c r="C145" s="11" t="inlineStr">
+      <c r="C165" s="28" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D145" s="23" t="inlineStr">
+      <c r="D165" s="40" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E145" s="10" t="inlineStr">
+      <c r="E165" s="27" t="inlineStr">
         <is>
           <t>5중 필터링 정제된 물.</t>
         </is>
       </c>
-      <c r="F145" s="10" t="inlineStr">
+      <c r="F165" s="27" t="inlineStr">
         <is>
           <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="48" customHeight="1">
-      <c r="A146" s="10" t="inlineStr">
+    <row r="166" ht="48" customHeight="1">
+      <c r="A166" s="27" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B146" s="10" t="inlineStr">
+      <c r="B166" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C146" s="11" t="inlineStr">
+      <c r="C166" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D146" s="14" t="inlineStr">
+      <c r="D166" s="31" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E146" s="10" t="inlineStr">
+      <c r="E166" s="27" t="inlineStr">
         <is>
           <t>보습제, 향이 오랫동안 머물 수 · 있도록 고착제 역할을 함.</t>
         </is>
       </c>
-      <c r="F146" s="10" t="inlineStr">
+      <c r="F166" s="27" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="32" customHeight="1">
-      <c r="A147" s="10" t="inlineStr">
+    <row r="167" ht="32" customHeight="1">
+      <c r="A167" s="27" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B147" s="10" t="inlineStr">
+      <c r="B167" s="27" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C147" s="11" t="inlineStr">
+      <c r="C167" s="28" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D147" s="15" t="inlineStr">
+      <c r="D167" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E147" s="10" t="inlineStr">
+      <c r="E167" s="27" t="inlineStr">
         <is>
           <t>에센셜오일 분산, 방향용으로 사용시 · 공기정화, 소독효과</t>
         </is>
       </c>
-      <c r="F147" s="10" t="inlineStr">
+      <c r="F167" s="27" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="48" customHeight="1">
-      <c r="A148" s="10" t="inlineStr">
+    <row r="168" ht="48" customHeight="1">
+      <c r="A168" s="27" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B148" s="10" t="inlineStr">
+      <c r="B168" s="27" t="inlineStr">
         <is>
           <t>15~20방울</t>
         </is>
       </c>
-      <c r="C148" s="11" t="inlineStr">
+      <c r="C168" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D148" s="15" t="inlineStr">
+      <c r="D168" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E148" s="10" t="inlineStr">
+      <c r="E168" s="27" t="inlineStr">
         <is>
           <t>레몬껍질에서 추출한 100%천연오일. · 상큼한 향.</t>
         </is>
       </c>
-      <c r="F148" s="10" t="inlineStr">
+      <c r="F168" s="27" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 편백 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="14" customHeight="1">
-      <c r="A149" s="16" t="inlineStr">
+    <row r="169" ht="14" customHeight="1">
+      <c r="A169" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 28 · 보습 5 · 향 67</t>
         </is>
       </c>
-      <c r="B149" s="17" t="n"/>
-      <c r="C149" s="17" t="n"/>
-      <c r="D149" s="17" t="n"/>
-      <c r="E149" s="17" t="n"/>
-      <c r="F149" s="17" t="n"/>
-    </row>
-    <row r="150" ht="14" customHeight="1">
-      <c r="A150" s="18" t="inlineStr">
+      <c r="B169" s="34" t="n"/>
+      <c r="C169" s="34" t="n"/>
+      <c r="D169" s="34" t="n"/>
+      <c r="E169" s="34" t="n"/>
+      <c r="F169" s="34" t="n"/>
+    </row>
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B150" s="19" t="n"/>
-      <c r="C150" s="19" t="n"/>
-      <c r="D150" s="19" t="n"/>
-      <c r="E150" s="19" t="n"/>
-      <c r="F150" s="19" t="n"/>
-    </row>
-    <row r="151" ht="304" customHeight="1">
-      <c r="A151" s="20" t="inlineStr">
+      <c r="B170" s="36" t="n"/>
+      <c r="C170" s="36" t="n"/>
+      <c r="D170" s="36" t="n"/>
+      <c r="E170" s="36" t="n"/>
+      <c r="F170" s="36" t="n"/>
+    </row>
+    <row r="171" ht="304" customHeight="1">
+      <c r="A171" s="37" t="inlineStr">
         <is>
           <t>2009년 젤타입 손소독제 만들기를 위해
 하이셀을 이용해 만든 젤타입 손소독제입니다.
@@ -5617,20 +5941,20 @@
         </is>
       </c>
     </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="18" t="inlineStr">
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B152" s="19" t="n"/>
-      <c r="C152" s="19" t="n"/>
-      <c r="D152" s="19" t="n"/>
-      <c r="E152" s="19" t="n"/>
-      <c r="F152" s="19" t="n"/>
-    </row>
-    <row r="153" ht="288" customHeight="1">
-      <c r="A153" s="20" t="inlineStr">
+      <c r="B172" s="36" t="n"/>
+      <c r="C172" s="36" t="n"/>
+      <c r="D172" s="36" t="n"/>
+      <c r="E172" s="36" t="n"/>
+      <c r="F172" s="36" t="n"/>
+    </row>
+    <row r="173" ht="288" customHeight="1">
+      <c r="A173" s="37" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 [하이셀 계량하기]
@@ -5653,259 +5977,259 @@
         </is>
       </c>
     </row>
-    <row r="154" ht="409" customHeight="1"/>
-    <row r="155" ht="238.4999999999999" customHeight="1"/>
-    <row r="156" ht="6" customHeight="1"/>
-    <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="7" t="inlineStr">
+    <row r="174" ht="409" customHeight="1"/>
+    <row r="175" ht="238.4999999999999" customHeight="1"/>
+    <row r="176" ht="6" customHeight="1"/>
+    <row r="177" ht="22" customHeight="1">
+      <c r="A177" s="24" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B157" s="8" t="n"/>
-      <c r="C157" s="8" t="n"/>
-      <c r="D157" s="8" t="n"/>
-      <c r="E157" s="8" t="n"/>
-      <c r="F157" s="8" t="n"/>
-    </row>
-    <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="9" t="inlineStr">
+      <c r="B177" s="25" t="n"/>
+      <c r="C177" s="25" t="n"/>
+      <c r="D177" s="25" t="n"/>
+      <c r="E177" s="25" t="n"/>
+      <c r="F177" s="25" t="n"/>
+    </row>
+    <row r="178" ht="15" customHeight="1">
+      <c r="A178" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B158" s="9" t="inlineStr">
+      <c r="B178" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C158" s="9" t="inlineStr">
+      <c r="C178" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D158" s="9" t="inlineStr">
+      <c r="D178" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E158" s="9" t="inlineStr">
+      <c r="E178" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F158" s="9" t="inlineStr">
+      <c r="F178" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="48" customHeight="1">
-      <c r="A159" s="21" t="inlineStr">
+    <row r="179" ht="48" customHeight="1">
+      <c r="A179" s="38" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B159" s="21" t="inlineStr">
+      <c r="B179" s="38" t="inlineStr">
         <is>
           <t>92.17%</t>
         </is>
       </c>
-      <c r="C159" s="22" t="inlineStr"/>
-      <c r="D159" s="23" t="inlineStr">
+      <c r="C179" s="39" t="inlineStr"/>
+      <c r="D179" s="40" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E159" s="21" t="inlineStr">
+      <c r="E179" s="38" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="F159" s="21" t="inlineStr">
+      <c r="F179" s="38" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="16" customHeight="1">
-      <c r="A160" s="21" t="inlineStr">
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" s="38" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B160" s="21" t="inlineStr">
+      <c r="B180" s="38" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C160" s="22" t="inlineStr"/>
-      <c r="D160" s="13" t="inlineStr">
+      <c r="C180" s="39" t="inlineStr"/>
+      <c r="D180" s="30" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E160" s="21" t="inlineStr">
+      <c r="E180" s="38" t="inlineStr">
         <is>
           <t>점증제총량의 1%이하</t>
         </is>
       </c>
-      <c r="F160" s="21" t="inlineStr"/>
-    </row>
-    <row r="161" ht="64" customHeight="1">
-      <c r="A161" s="21" t="inlineStr">
+      <c r="F180" s="38" t="inlineStr"/>
+    </row>
+    <row r="181" ht="64" customHeight="1">
+      <c r="A181" s="38" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B161" s="21" t="inlineStr">
+      <c r="B181" s="38" t="inlineStr">
         <is>
           <t>4.61%</t>
         </is>
       </c>
-      <c r="C161" s="22" t="inlineStr"/>
-      <c r="D161" s="14" t="inlineStr">
+      <c r="C181" s="39" t="inlineStr"/>
+      <c r="D181" s="31" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E161" s="21" t="inlineStr">
+      <c r="E181" s="38" t="inlineStr">
         <is>
           <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
-      <c r="F161" s="21" t="inlineStr">
+      <c r="F181" s="38" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="32" customHeight="1">
-      <c r="A162" s="21" t="inlineStr">
+    <row r="182" ht="32" customHeight="1">
+      <c r="A182" s="38" t="inlineStr">
         <is>
           <t>그레이프프룻EO</t>
         </is>
       </c>
-      <c r="B162" s="21" t="inlineStr">
+      <c r="B182" s="38" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C162" s="22" t="inlineStr"/>
-      <c r="D162" s="15" t="inlineStr">
+      <c r="C182" s="39" t="inlineStr"/>
+      <c r="D182" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E162" s="21" t="inlineStr">
+      <c r="E182" s="38" t="inlineStr">
         <is>
           <t>자몽 에센셜오일, 상쾌·수렴</t>
         </is>
       </c>
-      <c r="F162" s="21" t="inlineStr">
+      <c r="F182" s="38" t="inlineStr">
         <is>
           <t>오렌지, 레몬에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="32" customHeight="1">
-      <c r="A163" s="21" t="inlineStr">
+    <row r="183" ht="32" customHeight="1">
+      <c r="A183" s="38" t="inlineStr">
         <is>
           <t>페퍼민트오일</t>
         </is>
       </c>
-      <c r="B163" s="21" t="inlineStr">
+      <c r="B183" s="38" t="inlineStr">
         <is>
           <t>0.23%</t>
         </is>
       </c>
-      <c r="C163" s="22" t="inlineStr"/>
-      <c r="D163" s="29" t="inlineStr">
+      <c r="C183" s="39" t="inlineStr"/>
+      <c r="D183" s="45" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E163" s="21" t="inlineStr">
+      <c r="E183" s="38" t="inlineStr">
         <is>
           <t>허브의 고농축오일 · 시원, 커피와 시너지효과</t>
         </is>
       </c>
-      <c r="F163" s="21" t="inlineStr">
+      <c r="F183" s="38" t="inlineStr">
         <is>
           <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="32" customHeight="1">
-      <c r="A164" s="21" t="inlineStr">
+    <row r="184" ht="32" customHeight="1">
+      <c r="A184" s="38" t="inlineStr">
         <is>
           <t>주니퍼베리EO</t>
         </is>
       </c>
-      <c r="B164" s="21" t="inlineStr">
+      <c r="B184" s="38" t="inlineStr">
         <is>
           <t>0.69%</t>
         </is>
       </c>
-      <c r="C164" s="22" t="inlineStr"/>
-      <c r="D164" s="15" t="inlineStr">
+      <c r="C184" s="39" t="inlineStr"/>
+      <c r="D184" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E164" s="21" t="inlineStr">
+      <c r="E184" s="38" t="inlineStr">
         <is>
           <t>주니퍼베리 에센셜오일, 수렴·정화</t>
         </is>
       </c>
-      <c r="F164" s="21" t="inlineStr">
+      <c r="F184" s="38" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="64" customHeight="1">
-      <c r="A165" s="21" t="inlineStr">
+    <row r="185" ht="64" customHeight="1">
+      <c r="A185" s="38" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B165" s="21" t="inlineStr">
+      <c r="B185" s="38" t="inlineStr">
         <is>
           <t>0.46%</t>
         </is>
       </c>
-      <c r="C165" s="22" t="inlineStr"/>
-      <c r="D165" s="15" t="inlineStr">
+      <c r="C185" s="39" t="inlineStr"/>
+      <c r="D185" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E165" s="21" t="inlineStr">
+      <c r="E185" s="38" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="F165" s="21" t="inlineStr">
+      <c r="F185" s="38" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="14" customHeight="1">
-      <c r="A166" s="18" t="inlineStr">
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B166" s="19" t="n"/>
-      <c r="C166" s="19" t="n"/>
-      <c r="D166" s="19" t="n"/>
-      <c r="E166" s="19" t="n"/>
-      <c r="F166" s="19" t="n"/>
-    </row>
-    <row r="167" ht="96" customHeight="1">
-      <c r="A167" s="25" t="inlineStr">
+      <c r="B186" s="36" t="n"/>
+      <c r="C186" s="36" t="n"/>
+      <c r="D186" s="36" t="n"/>
+      <c r="E186" s="36" t="n"/>
+      <c r="F186" s="36" t="n"/>
+    </row>
+    <row r="187" ht="96" customHeight="1">
+      <c r="A187" s="42" t="inlineStr">
         <is>
           <t>*끈적임없이 흡수되는 다이어트젤
 다이어트에 좋은 에센셜오일 6종: 그레이프프룻, 팬넬, 쥬니퍼베리, 싸이프러스, 레몬, 제라늄
@@ -5915,26 +6239,26 @@
 제라늄 - 호로몬 균형, 피지균형</t>
         </is>
       </c>
-      <c r="B167" s="26" t="n"/>
-      <c r="C167" s="26" t="n"/>
-      <c r="D167" s="26" t="n"/>
-      <c r="E167" s="26" t="n"/>
-      <c r="F167" s="26" t="n"/>
-    </row>
-    <row r="168" ht="14" customHeight="1">
-      <c r="A168" s="18" t="inlineStr">
+      <c r="B187" s="23" t="n"/>
+      <c r="C187" s="23" t="n"/>
+      <c r="D187" s="23" t="n"/>
+      <c r="E187" s="23" t="n"/>
+      <c r="F187" s="23" t="n"/>
+    </row>
+    <row r="188" ht="14" customHeight="1">
+      <c r="A188" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B168" s="19" t="n"/>
-      <c r="C168" s="19" t="n"/>
-      <c r="D168" s="19" t="n"/>
-      <c r="E168" s="19" t="n"/>
-      <c r="F168" s="19" t="n"/>
-    </row>
-    <row r="169" ht="96" customHeight="1">
-      <c r="A169" s="25" t="inlineStr">
+      <c r="B188" s="36" t="n"/>
+      <c r="C188" s="36" t="n"/>
+      <c r="D188" s="36" t="n"/>
+      <c r="E188" s="36" t="n"/>
+      <c r="F188" s="36" t="n"/>
+    </row>
+    <row r="189" ht="96" customHeight="1">
+      <c r="A189" s="42" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 로즈워터를 계량한다.
@@ -5944,367 +6268,367 @@
 6~7. 손으로 저어서 마무리해주면 끝!</t>
         </is>
       </c>
-      <c r="B169" s="26" t="n"/>
-      <c r="C169" s="26" t="n"/>
-      <c r="D169" s="26" t="n"/>
-      <c r="E169" s="26" t="n"/>
-      <c r="F169" s="26" t="n"/>
-    </row>
-    <row r="170" ht="6" customHeight="1"/>
-    <row r="171" ht="22" customHeight="1">
-      <c r="A171" s="7" t="inlineStr">
+      <c r="B189" s="23" t="n"/>
+      <c r="C189" s="23" t="n"/>
+      <c r="D189" s="23" t="n"/>
+      <c r="E189" s="23" t="n"/>
+      <c r="F189" s="23" t="n"/>
+    </row>
+    <row r="190" ht="6" customHeight="1"/>
+    <row r="191" ht="22" customHeight="1">
+      <c r="A191" s="24" t="inlineStr">
         <is>
           <t>뱀독 볼륨 에센스(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B171" s="8" t="n"/>
-      <c r="C171" s="8" t="n"/>
-      <c r="D171" s="8" t="n"/>
-      <c r="E171" s="8" t="n"/>
-      <c r="F171" s="8" t="n"/>
-    </row>
-    <row r="172" ht="15" customHeight="1">
-      <c r="A172" s="9" t="inlineStr">
+      <c r="B191" s="25" t="n"/>
+      <c r="C191" s="25" t="n"/>
+      <c r="D191" s="25" t="n"/>
+      <c r="E191" s="25" t="n"/>
+      <c r="F191" s="25" t="n"/>
+    </row>
+    <row r="192" ht="15" customHeight="1">
+      <c r="A192" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B172" s="9" t="inlineStr">
+      <c r="B192" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C172" s="9" t="inlineStr">
+      <c r="C192" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D172" s="9" t="inlineStr">
+      <c r="D192" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E172" s="9" t="inlineStr">
+      <c r="E192" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F172" s="9" t="inlineStr">
+      <c r="F192" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="48" customHeight="1">
-      <c r="A173" s="10" t="inlineStr">
+    <row r="193" ht="48" customHeight="1">
+      <c r="A193" s="27" t="inlineStr">
         <is>
           <t>(제주산) / 비정제동백오일</t>
         </is>
       </c>
-      <c r="B173" s="10" t="inlineStr">
+      <c r="B193" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C173" s="11" t="inlineStr">
+      <c r="C193" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D173" s="29" t="inlineStr">
+      <c r="D193" s="45" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E173" s="10" t="inlineStr">
+      <c r="E193" s="27" t="inlineStr">
         <is>
           <t>올레인산 풍부 고보습 · 청정 섬 국내 제주산 야생동백씨 압착.</t>
         </is>
       </c>
-      <c r="F173" s="10" t="inlineStr">
+      <c r="F193" s="27" t="inlineStr">
         <is>
           <t>아르간, 로즈힙, 마카다미아넛오일 등</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="32" customHeight="1">
-      <c r="A174" s="10" t="inlineStr">
+    <row r="194" ht="32" customHeight="1">
+      <c r="A194" s="27" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B174" s="10" t="inlineStr">
+      <c r="B194" s="27" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C174" s="11" t="inlineStr">
+      <c r="C194" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D174" s="27" t="inlineStr">
+      <c r="D194" s="43" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E174" s="10" t="inlineStr">
+      <c r="E194" s="27" t="inlineStr">
         <is>
           <t>가용화제, 물에 오일이 분산되도록 도와줌</t>
         </is>
       </c>
-      <c r="F174" s="10" t="inlineStr">
+      <c r="F194" s="27" t="inlineStr">
         <is>
           <t>솔루벌라이저(Polysorbate 80)동량</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="64" customHeight="1">
-      <c r="A175" s="10" t="inlineStr">
+    <row r="195" ht="64" customHeight="1">
+      <c r="A195" s="27" t="inlineStr">
         <is>
           <t>오가닉7솔루션</t>
         </is>
       </c>
-      <c r="B175" s="10" t="inlineStr">
+      <c r="B195" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C175" s="11" t="inlineStr">
+      <c r="C195" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D175" s="12" t="inlineStr">
+      <c r="D195" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E175" s="10" t="inlineStr">
+      <c r="E195" s="27" t="inlineStr">
         <is>
           <t>비타민류가 다량 함유되어있는 · 유기농 야채(당근, 토마토,브로컬리,현미, 양배추,샐러리, 현미)를 저온 추출.</t>
         </is>
       </c>
-      <c r="F175" s="10" t="inlineStr">
+      <c r="F195" s="27" t="inlineStr">
         <is>
           <t>콜라겐, 석류,토마토</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="144" customHeight="1">
-      <c r="A176" s="10" t="inlineStr">
+    <row r="196" ht="144" customHeight="1">
+      <c r="A196" s="27" t="inlineStr">
         <is>
           <t>씨네이크(뱀독) / 펩타이드</t>
         </is>
       </c>
-      <c r="B176" s="10" t="inlineStr">
+      <c r="B196" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C176" s="11" t="inlineStr">
+      <c r="C196" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D176" s="12" t="inlineStr">
+      <c r="D196" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E176" s="10" t="inlineStr">
+      <c r="E196" s="27" t="inlineStr">
         <is>
           <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. · 임상시 아세틸헥사펩타이드보다 효과적. · 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. · '바르는 보톡스' 등으로 인기</t>
         </is>
       </c>
-      <c r="F176" s="10" t="inlineStr"/>
-    </row>
-    <row r="177" ht="32" customHeight="1">
-      <c r="A177" s="10" t="inlineStr">
+      <c r="F196" s="27" t="inlineStr"/>
+    </row>
+    <row r="197" ht="32" customHeight="1">
+      <c r="A197" s="27" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B177" s="10" t="inlineStr">
+      <c r="B197" s="27" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C177" s="11" t="inlineStr">
+      <c r="C197" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D177" s="12" t="inlineStr">
+      <c r="D197" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E177" s="10" t="inlineStr">
+      <c r="E197" s="27" t="inlineStr">
         <is>
           <t>녹황색채소에 들어있는 비타민B3. · 식약처 인증 미백원료</t>
         </is>
       </c>
-      <c r="F177" s="10" t="inlineStr">
+      <c r="F197" s="27" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="80" customHeight="1">
-      <c r="A178" s="10" t="inlineStr">
+    <row r="198" ht="80" customHeight="1">
+      <c r="A198" s="27" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B178" s="10" t="inlineStr">
+      <c r="B198" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C178" s="11" t="inlineStr">
+      <c r="C198" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D178" s="24" t="inlineStr">
+      <c r="D198" s="41" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E178" s="10" t="inlineStr">
+      <c r="E198" s="27" t="inlineStr">
         <is>
           <t>미생물 번식 억제제.</t>
         </is>
       </c>
-      <c r="F178" s="10" t="inlineStr">
+      <c r="F198" s="27" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="32" customHeight="1">
-      <c r="A179" s="10" t="inlineStr">
+    <row r="199" ht="32" customHeight="1">
+      <c r="A199" s="27" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
-      <c r="B179" s="10" t="inlineStr">
+      <c r="B199" s="27" t="inlineStr">
         <is>
           <t>0~6g</t>
         </is>
       </c>
-      <c r="C179" s="11" t="inlineStr">
+      <c r="C199" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D179" s="12" t="inlineStr">
+      <c r="D199" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E179" s="10" t="inlineStr">
+      <c r="E199" s="27" t="inlineStr">
         <is>
           <t>보습제. 원하시면 넣어주세요.</t>
         </is>
       </c>
-      <c r="F179" s="10" t="inlineStr">
+      <c r="F199" s="27" t="inlineStr">
         <is>
           <t>리피듀어 · 식물성글리세린</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="64" customHeight="1">
-      <c r="A180" s="10" t="inlineStr">
+    <row r="200" ht="64" customHeight="1">
+      <c r="A200" s="27" t="inlineStr">
         <is>
           <t>로즈우드에센셜오일</t>
         </is>
       </c>
-      <c r="B180" s="10" t="inlineStr">
+      <c r="B200" s="27" t="inlineStr">
         <is>
           <t>4~8방울</t>
         </is>
       </c>
-      <c r="C180" s="11" t="inlineStr">
+      <c r="C200" s="28" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D180" s="15" t="inlineStr">
+      <c r="D200" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E180" s="10" t="inlineStr">
+      <c r="E200" s="27" t="inlineStr">
         <is>
           <t>아로마테라피 · 장미향이 나는 제라늄, 모든 피부</t>
         </is>
       </c>
-      <c r="F180" s="10" t="inlineStr">
+      <c r="F200" s="27" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈제라늄 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="80" customHeight="1">
-      <c r="A181" s="10" t="inlineStr">
+    <row r="201" ht="80" customHeight="1">
+      <c r="A201" s="27" t="inlineStr">
         <is>
           <t>알로에모이스트</t>
         </is>
       </c>
-      <c r="B181" s="10" t="inlineStr">
+      <c r="B201" s="27" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C181" s="11" t="inlineStr">
+      <c r="C201" s="28" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D181" s="12" t="inlineStr">
+      <c r="D201" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E181" s="10" t="inlineStr">
+      <c r="E201" s="27" t="inlineStr">
         <is>
           <t>자체점증, 가용화안정, 수분공급 , 진정</t>
         </is>
       </c>
-      <c r="F181" s="10" t="inlineStr">
+      <c r="F201" s="27" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="14" customHeight="1">
-      <c r="A182" s="16" t="inlineStr">
+    <row r="202" ht="14" customHeight="1">
+      <c r="A202" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 4 · 유화 3 · 활성 92 · 향 0 · 방부 1</t>
         </is>
       </c>
-      <c r="B182" s="17" t="n"/>
-      <c r="C182" s="17" t="n"/>
-      <c r="D182" s="17" t="n"/>
-      <c r="E182" s="17" t="n"/>
-      <c r="F182" s="17" t="n"/>
-    </row>
-    <row r="183" ht="14" customHeight="1">
-      <c r="A183" s="18" t="inlineStr">
+      <c r="B202" s="34" t="n"/>
+      <c r="C202" s="34" t="n"/>
+      <c r="D202" s="34" t="n"/>
+      <c r="E202" s="34" t="n"/>
+      <c r="F202" s="34" t="n"/>
+    </row>
+    <row r="203" ht="14" customHeight="1">
+      <c r="A203" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B183" s="19" t="n"/>
-      <c r="C183" s="19" t="n"/>
-      <c r="D183" s="19" t="n"/>
-      <c r="E183" s="19" t="n"/>
-      <c r="F183" s="19" t="n"/>
-    </row>
-    <row r="184" ht="384" customHeight="1">
-      <c r="A184" s="20" t="inlineStr">
+      <c r="B203" s="36" t="n"/>
+      <c r="C203" s="36" t="n"/>
+      <c r="D203" s="36" t="n"/>
+      <c r="E203" s="36" t="n"/>
+      <c r="F203" s="36" t="n"/>
+    </row>
+    <row r="204" ht="384" customHeight="1">
+      <c r="A204" s="37" t="inlineStr">
         <is>
           <t>뱀독 볼륨에센스(젤)은
 바르는 보톡스인 씨네이크펩타이드 최대함량인 4%와
@@ -6333,8 +6657,8 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="208" customHeight="1">
-      <c r="A185" s="20" t="inlineStr">
+    <row r="205" ht="208" customHeight="1">
+      <c r="A205" s="37" t="inlineStr">
         <is>
           <t>살모사의 뱀독에서 추출한 단백질은
 유방암 세포의 성장을 70%나 억제하는 것으로 밝혀지기도 했습니다.
@@ -6352,20 +6676,20 @@
         </is>
       </c>
     </row>
-    <row r="186" ht="14" customHeight="1">
-      <c r="A186" s="18" t="inlineStr">
+    <row r="206" ht="14" customHeight="1">
+      <c r="A206" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B186" s="19" t="n"/>
-      <c r="C186" s="19" t="n"/>
-      <c r="D186" s="19" t="n"/>
-      <c r="E186" s="19" t="n"/>
-      <c r="F186" s="19" t="n"/>
-    </row>
-    <row r="187" ht="80" customHeight="1">
-      <c r="A187" s="20" t="inlineStr">
+      <c r="B206" s="36" t="n"/>
+      <c r="C206" s="36" t="n"/>
+      <c r="D206" s="36" t="n"/>
+      <c r="E206" s="36" t="n"/>
+      <c r="F206" s="36" t="n"/>
+    </row>
+    <row r="207" ht="80" customHeight="1">
+      <c r="A207" s="37" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.동백오일과 올리브리퀴드를 먼저 섞어주세요.
@@ -6374,137 +6698,137 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="6" customHeight="1"/>
-    <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="7" t="inlineStr">
+    <row r="208" ht="6" customHeight="1"/>
+    <row r="209" ht="22" customHeight="1">
+      <c r="A209" s="24" t="inlineStr">
         <is>
           <t>아임레알 제주화산송이팩    [(트러블, 모공이 넓은 피부) / 1회분량]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B189" s="8" t="n"/>
-      <c r="C189" s="8" t="n"/>
-      <c r="D189" s="8" t="n"/>
-      <c r="E189" s="8" t="n"/>
-      <c r="F189" s="8" t="n"/>
-    </row>
-    <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="9" t="inlineStr">
+      <c r="B209" s="25" t="n"/>
+      <c r="C209" s="25" t="n"/>
+      <c r="D209" s="25" t="n"/>
+      <c r="E209" s="25" t="n"/>
+      <c r="F209" s="25" t="n"/>
+    </row>
+    <row r="210" ht="15" customHeight="1">
+      <c r="A210" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B190" s="9" t="inlineStr">
+      <c r="B210" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C190" s="9" t="inlineStr">
+      <c r="C210" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D190" s="9" t="inlineStr">
+      <c r="D210" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E190" s="9" t="inlineStr">
+      <c r="E210" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F190" s="9" t="inlineStr">
+      <c r="F210" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="80" customHeight="1">
-      <c r="A191" s="21" t="inlineStr">
+    <row r="211" ht="80" customHeight="1">
+      <c r="A211" s="38" t="inlineStr">
         <is>
           <t>제주 화산송이분말</t>
         </is>
       </c>
-      <c r="B191" s="21" t="inlineStr">
+      <c r="B211" s="38" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C191" s="22" t="inlineStr">
+      <c r="C211" s="39" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D191" s="28" t="inlineStr">
+      <c r="D211" s="44" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E191" s="21" t="inlineStr">
+      <c r="E211" s="38" t="inlineStr">
         <is>
           <t>섭씨 2000도의 화산작용이 만든 기능성 미네럴, 제주 화산석 송이 · (먹는 '송이(버섯)' 아니죠^^) · 화산송이 7 : 카오링클레이3</t>
         </is>
       </c>
-      <c r="F191" s="21" t="inlineStr"/>
-    </row>
-    <row r="192" ht="64" customHeight="1">
-      <c r="A192" s="21" t="inlineStr">
+      <c r="F211" s="38" t="inlineStr"/>
+    </row>
+    <row r="212" ht="64" customHeight="1">
+      <c r="A212" s="38" t="inlineStr">
         <is>
           <t>위치헤이즐워터 / (편백워터)</t>
         </is>
       </c>
-      <c r="B192" s="21" t="inlineStr">
+      <c r="B212" s="38" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C192" s="22" t="inlineStr">
+      <c r="C212" s="39" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D192" s="23" t="inlineStr">
+      <c r="D212" s="40" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E192" s="21" t="inlineStr">
+      <c r="E212" s="38" t="inlineStr">
         <is>
           <t>제주화산송이 양의 반이하의 양, 정제수도 가능, 위치헤즐은 수렴, 트러블, 모공 넓은 피부적합</t>
         </is>
       </c>
-      <c r="F192" s="21" t="inlineStr">
+      <c r="F212" s="38" t="inlineStr">
         <is>
           <t>정수기 물, 수돗물^^, 녹차우린 물. 어성초우린 물</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="14" customHeight="1">
-      <c r="A193" s="16" t="inlineStr">
+    <row r="213" ht="14" customHeight="1">
+      <c r="A213" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 23 · 색소 77</t>
         </is>
       </c>
-      <c r="B193" s="17" t="n"/>
-      <c r="C193" s="17" t="n"/>
-      <c r="D193" s="17" t="n"/>
-      <c r="E193" s="17" t="n"/>
-      <c r="F193" s="17" t="n"/>
-    </row>
-    <row r="194" ht="14" customHeight="1">
-      <c r="A194" s="18" t="inlineStr">
+      <c r="B213" s="34" t="n"/>
+      <c r="C213" s="34" t="n"/>
+      <c r="D213" s="34" t="n"/>
+      <c r="E213" s="34" t="n"/>
+      <c r="F213" s="34" t="n"/>
+    </row>
+    <row r="214" ht="14" customHeight="1">
+      <c r="A214" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B194" s="19" t="n"/>
-      <c r="C194" s="19" t="n"/>
-      <c r="D194" s="19" t="n"/>
-      <c r="E194" s="19" t="n"/>
-      <c r="F194" s="19" t="n"/>
-    </row>
-    <row r="195" ht="368" customHeight="1">
-      <c r="A195" s="25" t="inlineStr">
+      <c r="B214" s="36" t="n"/>
+      <c r="C214" s="36" t="n"/>
+      <c r="D214" s="36" t="n"/>
+      <c r="E214" s="36" t="n"/>
+      <c r="F214" s="36" t="n"/>
+    </row>
+    <row r="215" ht="368" customHeight="1">
+      <c r="A215" s="42" t="inlineStr">
         <is>
           <t>제주화산송이,
 먹는 송이가 아니죠^^
@@ -6529,26 +6853,26 @@
 초간단 레알 화산송이팩으로 피부 피지와 노폐물을 관리해보세요.</t>
         </is>
       </c>
-      <c r="B195" s="26" t="n"/>
-      <c r="C195" s="26" t="n"/>
-      <c r="D195" s="26" t="n"/>
-      <c r="E195" s="26" t="n"/>
-      <c r="F195" s="26" t="n"/>
-    </row>
-    <row r="196" ht="14" customHeight="1">
-      <c r="A196" s="18" t="inlineStr">
+      <c r="B215" s="23" t="n"/>
+      <c r="C215" s="23" t="n"/>
+      <c r="D215" s="23" t="n"/>
+      <c r="E215" s="23" t="n"/>
+      <c r="F215" s="23" t="n"/>
+    </row>
+    <row r="216" ht="14" customHeight="1">
+      <c r="A216" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B196" s="19" t="n"/>
-      <c r="C196" s="19" t="n"/>
-      <c r="D196" s="19" t="n"/>
-      <c r="E196" s="19" t="n"/>
-      <c r="F196" s="19" t="n"/>
-    </row>
-    <row r="197" ht="288" customHeight="1">
-      <c r="A197" s="25" t="inlineStr">
+      <c r="B216" s="36" t="n"/>
+      <c r="C216" s="36" t="n"/>
+      <c r="D216" s="36" t="n"/>
+      <c r="E216" s="36" t="n"/>
+      <c r="F216" s="36" t="n"/>
+    </row>
+    <row r="217" ht="288" customHeight="1">
+      <c r="A217" s="42" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1. 제주화산송이를 두스푼(약10g)계량하시고
@@ -6568,367 +6892,367 @@
 8.팩을 갤때 사용하셨던 플로럴워터로 피부결을 정돈하세요.</t>
         </is>
       </c>
-      <c r="B197" s="26" t="n"/>
-      <c r="C197" s="26" t="n"/>
-      <c r="D197" s="26" t="n"/>
-      <c r="E197" s="26" t="n"/>
-      <c r="F197" s="26" t="n"/>
-    </row>
-    <row r="198" ht="6" customHeight="1"/>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="7" t="inlineStr">
+      <c r="B217" s="23" t="n"/>
+      <c r="C217" s="23" t="n"/>
+      <c r="D217" s="23" t="n"/>
+      <c r="E217" s="23" t="n"/>
+      <c r="F217" s="23" t="n"/>
+    </row>
+    <row r="218" ht="6" customHeight="1"/>
+    <row r="219" ht="22" customHeight="1">
+      <c r="A219" s="24" t="inlineStr">
         <is>
           <t>TX 토닝 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B199" s="8" t="n"/>
-      <c r="C199" s="8" t="n"/>
-      <c r="D199" s="8" t="n"/>
-      <c r="E199" s="8" t="n"/>
-      <c r="F199" s="8" t="n"/>
-    </row>
-    <row r="200" ht="15" customHeight="1">
-      <c r="A200" s="9" t="inlineStr">
+      <c r="B219" s="25" t="n"/>
+      <c r="C219" s="25" t="n"/>
+      <c r="D219" s="25" t="n"/>
+      <c r="E219" s="25" t="n"/>
+      <c r="F219" s="25" t="n"/>
+    </row>
+    <row r="220" ht="15" customHeight="1">
+      <c r="A220" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B200" s="9" t="inlineStr">
+      <c r="B220" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C200" s="9" t="inlineStr">
+      <c r="C220" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D200" s="9" t="inlineStr">
+      <c r="D220" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E200" s="9" t="inlineStr">
+      <c r="E220" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F200" s="9" t="inlineStr">
+      <c r="F220" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="32" customHeight="1">
-      <c r="A201" s="10" t="inlineStr">
+    <row r="221" ht="32" customHeight="1">
+      <c r="A221" s="27" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B201" s="10" t="inlineStr">
+      <c r="B221" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C201" s="11" t="inlineStr">
+      <c r="C221" s="28" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D201" s="12" t="inlineStr">
+      <c r="D221" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E201" s="10" t="inlineStr">
+      <c r="E221" s="27" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="F201" s="10" t="inlineStr">
+      <c r="F221" s="27" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="48" customHeight="1">
-      <c r="A202" s="10" t="inlineStr">
+    <row r="222" ht="48" customHeight="1">
+      <c r="A222" s="27" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B202" s="10" t="inlineStr">
+      <c r="B222" s="27" t="inlineStr">
         <is>
           <t>22g</t>
         </is>
       </c>
-      <c r="C202" s="11" t="inlineStr">
+      <c r="C222" s="28" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="D202" s="23" t="inlineStr">
+      <c r="D222" s="40" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E202" s="10" t="inlineStr">
+      <c r="E222" s="27" t="inlineStr">
         <is>
           <t>불가리아 장미수</t>
         </is>
       </c>
-      <c r="F202" s="10" t="inlineStr">
+      <c r="F222" s="27" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="16" customHeight="1">
-      <c r="A203" s="10" t="inlineStr">
+    <row r="223" ht="16" customHeight="1">
+      <c r="A223" s="27" t="inlineStr">
         <is>
           <t>슈퍼시카4</t>
         </is>
       </c>
-      <c r="B203" s="10" t="inlineStr">
+      <c r="B223" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C203" s="11" t="inlineStr">
+      <c r="C223" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D203" s="12" t="inlineStr">
+      <c r="D223" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E203" s="10" t="inlineStr">
+      <c r="E223" s="27" t="inlineStr">
         <is>
           <t>병풀의 핵심성분 4가지 복합물</t>
         </is>
       </c>
-      <c r="F203" s="10" t="inlineStr">
+      <c r="F223" s="27" t="inlineStr">
         <is>
           <t>병풀추출물</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="32" customHeight="1">
-      <c r="A204" s="10" t="inlineStr">
+    <row r="224" ht="32" customHeight="1">
+      <c r="A224" s="27" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B204" s="10" t="inlineStr">
+      <c r="B224" s="27" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C204" s="11" t="inlineStr">
+      <c r="C224" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D204" s="12" t="inlineStr">
+      <c r="D224" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E204" s="10" t="inlineStr">
+      <c r="E224" s="27" t="inlineStr">
         <is>
           <t>비타민B3, 식약처 기능성 고시원료</t>
         </is>
       </c>
-      <c r="F204" s="10" t="inlineStr">
+      <c r="F224" s="27" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="48" customHeight="1">
-      <c r="A205" s="10" t="inlineStr">
+    <row r="225" ht="48" customHeight="1">
+      <c r="A225" s="27" t="inlineStr">
         <is>
           <t>프로바이오틱스3</t>
         </is>
       </c>
-      <c r="B205" s="10" t="inlineStr">
+      <c r="B225" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C205" s="11" t="inlineStr">
+      <c r="C225" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D205" s="12" t="inlineStr">
+      <c r="D225" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E205" s="10" t="inlineStr">
+      <c r="E225" s="27" t="inlineStr">
         <is>
           <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
-      <c r="F205" s="10" t="inlineStr">
+      <c r="F225" s="27" t="inlineStr">
         <is>
           <t>사카로, 비피다, 갈락토, 콤부차발효여과물..</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="16" customHeight="1">
-      <c r="A206" s="10" t="inlineStr">
+    <row r="226" ht="16" customHeight="1">
+      <c r="A226" s="27" t="inlineStr">
         <is>
           <t>덱스판테놀</t>
         </is>
       </c>
-      <c r="B206" s="10" t="inlineStr">
+      <c r="B226" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C206" s="11" t="inlineStr">
+      <c r="C226" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D206" s="12" t="inlineStr">
+      <c r="D226" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E206" s="10" t="inlineStr">
+      <c r="E226" s="27" t="inlineStr">
         <is>
           <t>비타민B5, 보습 재생</t>
         </is>
       </c>
-      <c r="F206" s="10" t="inlineStr">
+      <c r="F226" s="27" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="64" customHeight="1">
-      <c r="A207" s="10" t="inlineStr">
+    <row r="227" ht="64" customHeight="1">
+      <c r="A227" s="27" t="inlineStr">
         <is>
           <t>트라넥삼산 (펩타이드)</t>
         </is>
       </c>
-      <c r="B207" s="10" t="inlineStr">
+      <c r="B227" s="27" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C207" s="11" t="inlineStr">
+      <c r="C227" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D207" s="12" t="inlineStr">
+      <c r="D227" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E207" s="10" t="inlineStr">
+      <c r="E227" s="27" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="F207" s="10" t="inlineStr">
+      <c r="F227" s="27" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="16" customHeight="1">
-      <c r="A208" s="10" t="inlineStr">
+    <row r="228" ht="16" customHeight="1">
+      <c r="A228" s="27" t="inlineStr">
         <is>
           <t>글루타치온</t>
         </is>
       </c>
-      <c r="B208" s="10" t="inlineStr">
+      <c r="B228" s="27" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C208" s="11" t="inlineStr">
+      <c r="C228" s="28" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D208" s="12" t="inlineStr">
+      <c r="D228" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E208" s="10" t="inlineStr">
+      <c r="E228" s="27" t="inlineStr">
         <is>
           <t>미백효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="F208" s="10" t="inlineStr"/>
-    </row>
-    <row r="209" ht="64" customHeight="1">
-      <c r="A209" s="10" t="inlineStr">
+      <c r="F228" s="27" t="inlineStr"/>
+    </row>
+    <row r="229" ht="64" customHeight="1">
+      <c r="A229" s="27" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B209" s="10" t="inlineStr">
+      <c r="B229" s="27" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C209" s="11" t="inlineStr">
+      <c r="C229" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D209" s="24" t="inlineStr">
+      <c r="D229" s="41" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E209" s="10" t="inlineStr">
+      <c r="E229" s="27" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="F209" s="10" t="inlineStr">
+      <c r="F229" s="27" t="inlineStr">
         <is>
           <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="14" customHeight="1">
-      <c r="A210" s="16" t="inlineStr">
+    <row r="230" ht="14" customHeight="1">
+      <c r="A230" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 22 · 활성 76 · 방부 2</t>
         </is>
       </c>
-      <c r="B210" s="17" t="n"/>
-      <c r="C210" s="17" t="n"/>
-      <c r="D210" s="17" t="n"/>
-      <c r="E210" s="17" t="n"/>
-      <c r="F210" s="17" t="n"/>
-    </row>
-    <row r="211" ht="14" customHeight="1">
-      <c r="A211" s="18" t="inlineStr">
+      <c r="B230" s="34" t="n"/>
+      <c r="C230" s="34" t="n"/>
+      <c r="D230" s="34" t="n"/>
+      <c r="E230" s="34" t="n"/>
+      <c r="F230" s="34" t="n"/>
+    </row>
+    <row r="231" ht="14" customHeight="1">
+      <c r="A231" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B211" s="19" t="n"/>
-      <c r="C211" s="19" t="n"/>
-      <c r="D211" s="19" t="n"/>
-      <c r="E211" s="19" t="n"/>
-      <c r="F211" s="19" t="n"/>
-    </row>
-    <row r="212" ht="384" customHeight="1">
-      <c r="A212" s="20" t="inlineStr">
+      <c r="B231" s="36" t="n"/>
+      <c r="C231" s="36" t="n"/>
+      <c r="D231" s="36" t="n"/>
+      <c r="E231" s="36" t="n"/>
+      <c r="F231" s="36" t="n"/>
+    </row>
+    <row r="232" ht="384" customHeight="1">
+      <c r="A232" s="37" t="inlineStr">
         <is>
           <t>기미, 잡티 초기 진압에 TX 토닝 젤 (100g)
 난이도 : 하
@@ -6957,8 +7281,8 @@
         </is>
       </c>
     </row>
-    <row r="213" ht="80" customHeight="1">
-      <c r="A213" s="20" t="inlineStr">
+    <row r="233" ht="80" customHeight="1">
+      <c r="A233" s="37" t="inlineStr">
         <is>
           <t>현대약품 계열사 특허 성분)
 트라넥삼산과 나이아신아마이드를
@@ -6968,20 +7292,20 @@
         </is>
       </c>
     </row>
-    <row r="214" ht="14" customHeight="1">
-      <c r="A214" s="18" t="inlineStr">
+    <row r="234" ht="14" customHeight="1">
+      <c r="A234" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B214" s="19" t="n"/>
-      <c r="C214" s="19" t="n"/>
-      <c r="D214" s="19" t="n"/>
-      <c r="E214" s="19" t="n"/>
-      <c r="F214" s="19" t="n"/>
-    </row>
-    <row r="215" ht="64" customHeight="1">
-      <c r="A215" s="20" t="inlineStr">
+      <c r="B234" s="36" t="n"/>
+      <c r="C234" s="36" t="n"/>
+      <c r="D234" s="36" t="n"/>
+      <c r="E234" s="36" t="n"/>
+      <c r="F234" s="36" t="n"/>
+    </row>
+    <row r="235" ht="64" customHeight="1">
+      <c r="A235" s="37" t="inlineStr">
         <is>
           <t>TX 토닝 젤 토너 만들기
 1. 모든 재료를 계량합니다.
@@ -6990,122 +7314,142 @@
         </is>
       </c>
     </row>
-    <row r="216" ht="6" customHeight="1"/>
+    <row r="236" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="96">
-    <mergeCell ref="A183:F183"/>
-    <mergeCell ref="A75:F75"/>
+  <mergeCells count="116">
+    <mergeCell ref="A205:F205"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="A133:F133"/>
     <mergeCell ref="A189:F189"/>
+    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="B11:F11"/>
     <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A97:F97"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A152:F152"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A144:F144"/>
+    <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A134:F134"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A161:F161"/>
+    <mergeCell ref="A202:F202"/>
     <mergeCell ref="A186:F186"/>
-    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A212:F212"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A108:F108"/>
     <mergeCell ref="A214:F214"/>
-    <mergeCell ref="A101:F101"/>
-    <mergeCell ref="A195:F195"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A163:F163"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A204:F204"/>
     <mergeCell ref="A213:F213"/>
     <mergeCell ref="A151:F151"/>
-    <mergeCell ref="A126:F126"/>
-    <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A206:F206"/>
+    <mergeCell ref="B8:F8"/>
     <mergeCell ref="A215:F215"/>
-    <mergeCell ref="A125:F125"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A112:F112"/>
-    <mergeCell ref="A199:F199"/>
-    <mergeCell ref="A127:F127"/>
-    <mergeCell ref="A167:F167"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A230:F230"/>
+    <mergeCell ref="B10:F10"/>
     <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A182:F182"/>
+    <mergeCell ref="A232:F232"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A216:F216"/>
     <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A153:F153"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A139:F139"/>
-    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A177:F177"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A145:F145"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A116:F116"/>
-    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A203:F203"/>
     <mergeCell ref="A131:F131"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A140:F140"/>
     <mergeCell ref="A171:F171"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A231:F231"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A173:F173"/>
     <mergeCell ref="A111:F111"/>
-    <mergeCell ref="A143:F143"/>
-    <mergeCell ref="A157:F157"/>
-    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A207:F207"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A103:F103"/>
-    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A193:F193"/>
-    <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A185:F185"/>
-    <mergeCell ref="A194:F194"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A233:F233"/>
+    <mergeCell ref="A120:F120"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A235:F235"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A219:F219"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="A234:F234"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A96:F96"/>
     <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A184:F184"/>
-    <mergeCell ref="A211:F211"/>
-    <mergeCell ref="A138:F138"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="A110:F110"/>
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A209:F209"/>
+    <mergeCell ref="A170:F170"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A130:F130"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A123:F123"/>
+    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A146:F146"/>
+    <mergeCell ref="A119:F119"/>
     <mergeCell ref="A187:F187"/>
-    <mergeCell ref="A196:F196"/>
+    <mergeCell ref="A69:F69"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A171" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>

--- a/카드_아키타입/02_젤.xlsx
+++ b/카드_아키타입/02_젤.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +70,13 @@
       <color rgb="0055606E"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="005B3A7A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -178,6 +183,16 @@
         <fgColor rgb="00EEF3F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EEFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAF8FD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -210,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -305,6 +320,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -610,7 +632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="23279100"/>
+    <pos x="7848600" y="24028400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -630,7 +652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="23279100"/>
+    <pos x="9696450" y="24028400"/>
     <ext cx="1809750" cy="857250"/>
     <pic>
       <nvPicPr>
@@ -650,7 +672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="23279100"/>
+    <pos x="11544300" y="24028400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -670,7 +692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="23279100"/>
+    <pos x="13392150" y="24028400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -690,7 +712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="25126950"/>
+    <pos x="7848600" y="25876250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -710,7 +732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="26974800"/>
+    <pos x="7848600" y="27724100"/>
     <ext cx="5143500" cy="3857625"/>
     <pic>
       <nvPicPr>
@@ -730,7 +752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="30946725"/>
+    <pos x="7848600" y="31724600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -750,7 +772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="30946725"/>
+    <pos x="9696450" y="31724600"/>
     <ext cx="1809750" cy="1485900"/>
     <pic>
       <nvPicPr>
@@ -770,7 +792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="30946725"/>
+    <pos x="11544300" y="31724600"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -790,7 +812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="30946725"/>
+    <pos x="13392150" y="31724600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -810,7 +832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="32794575"/>
+    <pos x="7848600" y="33572450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -830,7 +852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="32794575"/>
+    <pos x="9696450" y="33572450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -850,7 +872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="32794575"/>
+    <pos x="11544300" y="33572450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -870,7 +892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="32794575"/>
+    <pos x="13392150" y="33572450"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -890,7 +912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="34642425"/>
+    <pos x="7848600" y="35420300"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -910,7 +932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="40560625"/>
+    <pos x="7848600" y="42468800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -930,7 +952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="40560625"/>
+    <pos x="9696450" y="42468800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -950,7 +972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="40560625"/>
+    <pos x="11544300" y="42468800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -970,7 +992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="40560625"/>
+    <pos x="13392150" y="42468800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -990,7 +1012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="42408475"/>
+    <pos x="7848600" y="44316650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1010,7 +1032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="46720125"/>
+    <pos x="7848600" y="49568100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1030,7 +1052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="46720125"/>
+    <pos x="9696450" y="49568100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1050,7 +1072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="46720125"/>
+    <pos x="11544300" y="49568100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1070,7 +1092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="48567975"/>
+    <pos x="7848600" y="51415950"/>
     <ext cx="3857625" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1090,7 +1112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="57146825"/>
+    <pos x="7848600" y="60934600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1110,7 +1132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="57146825"/>
+    <pos x="9696450" y="60934600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1130,7 +1152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="57146825"/>
+    <pos x="11544300" y="60934600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1150,7 +1172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="57146825"/>
+    <pos x="13392150" y="60934600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1170,7 +1192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="63306325"/>
+    <pos x="7848600" y="68033900"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1190,7 +1212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="63306325"/>
+    <pos x="9696450" y="68033900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1210,7 +1232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="63306325"/>
+    <pos x="11544300" y="68033900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1230,7 +1252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="63306325"/>
+    <pos x="13392150" y="68033900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1250,7 +1272,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="65154175"/>
+    <pos x="7848600" y="69881750"/>
     <ext cx="5143500" cy="2143125"/>
     <pic>
       <nvPicPr>
@@ -1270,7 +1292,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="71091425"/>
+    <pos x="7848600" y="76758800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1290,7 +1312,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="71091425"/>
+    <pos x="9696450" y="76758800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1310,7 +1332,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="71091425"/>
+    <pos x="11544300" y="76758800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1330,7 +1352,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="71091425"/>
+    <pos x="13392150" y="76758800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1350,7 +1372,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="72939275"/>
+    <pos x="7848600" y="78606650"/>
     <ext cx="5143500" cy="2143125"/>
     <pic>
       <nvPicPr>
@@ -1370,7 +1392,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="77860525"/>
+    <pos x="7848600" y="84467700"/>
     <ext cx="5143500" cy="3857625"/>
     <pic>
       <nvPicPr>
@@ -1390,7 +1412,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="81756249"/>
+    <pos x="7848600" y="88363425"/>
     <ext cx="5143500" cy="4019550"/>
     <pic>
       <nvPicPr>
@@ -1410,7 +1432,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="85890099"/>
+    <pos x="7848600" y="92497275"/>
     <ext cx="3200400" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1430,7 +1452,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="92684600"/>
+    <pos x="7848600" y="99291775"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1450,7 +1472,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="92684600"/>
+    <pos x="9696450" y="99291775"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1470,7 +1492,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="92684600"/>
+    <pos x="11544300" y="99291775"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1490,7 +1512,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="92684600"/>
+    <pos x="13392150" y="99291775"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1510,7 +1532,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="94532450"/>
+    <pos x="7848600" y="101139625"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1530,7 +1552,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="94532450"/>
+    <pos x="9696450" y="101139625"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1550,7 +1572,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="94532450"/>
+    <pos x="11544300" y="101139625"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1570,7 +1592,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="94532450"/>
+    <pos x="13392150" y="101139625"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1590,7 +1612,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="96380300"/>
+    <pos x="7848600" y="102987475"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1610,7 +1632,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="96380300"/>
+    <pos x="9696450" y="102987475"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1630,7 +1652,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="96380300"/>
+    <pos x="11544300" y="102987475"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1650,7 +1672,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="96380300"/>
+    <pos x="13392150" y="102987475"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1670,7 +1692,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="98228150"/>
+    <pos x="7848600" y="104835325"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1690,7 +1712,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="98228150"/>
+    <pos x="9696450" y="104835325"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1710,7 +1732,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="98228150"/>
+    <pos x="11544300" y="104835325"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1730,7 +1752,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="98228150"/>
+    <pos x="13392150" y="104835325"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1750,7 +1772,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="100076000"/>
+    <pos x="7848600" y="106683175"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1770,7 +1792,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="105257600"/>
+    <pos x="7848600" y="111864775"/>
     <ext cx="5143500" cy="1390650"/>
     <pic>
       <nvPicPr>
@@ -1790,7 +1812,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="106686350"/>
+    <pos x="7848600" y="113293525"/>
     <ext cx="2695575" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1810,7 +1832,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="111944150"/>
+    <pos x="7848600" y="118551325"/>
     <ext cx="3200400" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1830,7 +1852,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="118941850"/>
+    <pos x="7848600" y="125549025"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1850,7 +1872,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="118941850"/>
+    <pos x="9696450" y="125549025"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1870,7 +1892,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="118941850"/>
+    <pos x="11544300" y="125549025"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1890,7 +1912,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="118941850"/>
+    <pos x="13392150" y="125549025"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1910,7 +1932,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="120789700"/>
+    <pos x="7848600" y="127396875"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1930,7 +1952,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="120789700"/>
+    <pos x="9696450" y="127396875"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1950,7 +1972,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="122637550"/>
+    <pos x="7848600" y="129244725"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -1970,7 +1992,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="135870950"/>
+    <pos x="7848600" y="143798925"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1990,7 +2012,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="135870950"/>
+    <pos x="9696450" y="143798925"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2010,7 +2032,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="135870950"/>
+    <pos x="11544300" y="143798925"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2030,7 +2052,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="135870950"/>
+    <pos x="13392150" y="143798925"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2050,7 +2072,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="137718800"/>
+    <pos x="7848600" y="145646775"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2070,7 +2092,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="137718800"/>
+    <pos x="9696450" y="145646775"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2090,7 +2112,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="137718800"/>
+    <pos x="11544300" y="145646775"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2110,7 +2132,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="137718800"/>
+    <pos x="13392150" y="145646775"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2130,7 +2152,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="139566650"/>
+    <pos x="7848600" y="147494625"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2150,7 +2172,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="139566650"/>
+    <pos x="9696450" y="147494625"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2170,7 +2192,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="147110450"/>
+    <pos x="7848600" y="155571825"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2190,7 +2212,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="147110450"/>
+    <pos x="9696450" y="155571825"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2210,7 +2232,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="147110450"/>
+    <pos x="11544300" y="155571825"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2230,7 +2252,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="148958300"/>
+    <pos x="7848600" y="157419675"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2541,7 +2563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3123,301 +3145,322 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="6" customHeight="1"/>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
+    <row r="38" ht="14" customHeight="1">
+      <c r="A38" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B38" s="39" t="n"/>
+      <c r="C38" s="39" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="39" t="n"/>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="40" t="inlineStr">
+        <is>
+          <t>· 기능: 활성 합 64%(아로마베이스95 64%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 보습 4% · 점증·pH 31% · 향 1% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="6" customHeight="1"/>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>허니 촉촉 바디젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="25" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="25" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="B41" s="25" t="n"/>
+      <c r="C41" s="25" t="n"/>
+      <c r="D41" s="25" t="n"/>
+      <c r="E41" s="25" t="n"/>
+      <c r="F41" s="25" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F40" s="26" t="inlineStr">
+      <c r="F42" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="80" customHeight="1">
-      <c r="A41" s="38" t="inlineStr">
+    <row r="43" ht="80" customHeight="1">
+      <c r="A43" s="41" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B41" s="38" t="inlineStr">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>68g</t>
         </is>
       </c>
-      <c r="C41" s="39" t="inlineStr">
+      <c r="C43" s="42" t="inlineStr">
         <is>
           <t>68%</t>
         </is>
       </c>
-      <c r="D41" s="29" t="inlineStr">
+      <c r="D43" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E41" s="38" t="inlineStr">
+      <c r="E43" s="41" t="inlineStr">
         <is>
           <t>수분, 자체 점증.</t>
         </is>
       </c>
-      <c r="F41" s="38" t="inlineStr">
+      <c r="F43" s="41" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="32" customHeight="1">
-      <c r="A42" s="38" t="inlineStr">
+    <row r="44" ht="32" customHeight="1">
+      <c r="A44" s="41" t="inlineStr">
         <is>
           <t>워터 코포아수</t>
         </is>
       </c>
-      <c r="B42" s="38" t="inlineStr">
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C42" s="39" t="inlineStr">
+      <c r="C44" s="42" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D42" s="40" t="inlineStr">
+      <c r="D44" s="43" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E42" s="38" t="inlineStr">
+      <c r="E44" s="41" t="inlineStr">
         <is>
           <t>천연 레시틴으로 코포아수 버터를 리포좀화.</t>
         </is>
       </c>
-      <c r="F42" s="38" t="inlineStr">
+      <c r="F44" s="41" t="inlineStr">
         <is>
           <t>워터 아르간</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="38" t="inlineStr">
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="41" t="inlineStr">
         <is>
           <t>세라마이드 (수용성)</t>
         </is>
       </c>
-      <c r="B43" s="38" t="inlineStr">
+      <c r="B45" s="41" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C43" s="39" t="inlineStr">
+      <c r="C45" s="42" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D43" s="29" t="inlineStr">
+      <c r="D45" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E43" s="38" t="inlineStr">
+      <c r="E45" s="41" t="inlineStr">
         <is>
           <t>세라마이드 리포좀화</t>
         </is>
       </c>
-      <c r="F43" s="38" t="inlineStr">
+      <c r="F45" s="41" t="inlineStr">
         <is>
           <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="38" t="inlineStr">
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="41" t="inlineStr">
         <is>
           <t>꿀 추출물</t>
         </is>
       </c>
-      <c r="B44" s="38" t="inlineStr">
+      <c r="B46" s="41" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C44" s="39" t="inlineStr">
+      <c r="C46" s="42" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D44" s="29" t="inlineStr">
+      <c r="D46" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E44" s="38" t="inlineStr">
+      <c r="E46" s="41" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="F44" s="38" t="inlineStr">
+      <c r="F46" s="41" t="inlineStr">
         <is>
           <t>원하는 · 추출물</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="64" customHeight="1">
-      <c r="A45" s="38" t="inlineStr">
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="41" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B45" s="38" t="inlineStr">
+      <c r="B47" s="41" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C45" s="39" t="inlineStr">
+      <c r="C47" s="42" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D45" s="41" t="inlineStr">
+      <c r="D47" s="44" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E45" s="38" t="inlineStr">
+      <c r="E47" s="41" t="inlineStr">
         <is>
           <t>균번식 억제제</t>
         </is>
       </c>
-      <c r="F45" s="38" t="inlineStr">
+      <c r="F47" s="41" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g · (알로에베라겔의 양을 67g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="38" t="inlineStr">
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="41" t="inlineStr">
         <is>
           <t>스윗 오렌지에센셜오일</t>
         </is>
       </c>
-      <c r="B46" s="38" t="inlineStr">
+      <c r="B48" s="41" t="inlineStr">
         <is>
           <t>10방울</t>
         </is>
       </c>
-      <c r="C46" s="39" t="inlineStr">
+      <c r="C48" s="42" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D46" s="32" t="inlineStr">
+      <c r="D48" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E46" s="38" t="inlineStr">
+      <c r="E48" s="41" t="inlineStr">
         <is>
           <t>오렌지 껍질 오일</t>
         </is>
       </c>
-      <c r="F46" s="38" t="inlineStr">
+      <c r="F48" s="41" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="38" t="inlineStr">
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="41" t="inlineStr">
         <is>
           <t>네롤리에센셜오일</t>
         </is>
       </c>
-      <c r="B47" s="38" t="inlineStr">
+      <c r="B49" s="41" t="inlineStr">
         <is>
           <t>3방울</t>
         </is>
       </c>
-      <c r="C47" s="39" t="inlineStr">
+      <c r="C49" s="42" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D47" s="32" t="inlineStr">
+      <c r="D49" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E47" s="38" t="inlineStr">
+      <c r="E49" s="41" t="inlineStr">
         <is>
           <t>오렌지꽃오일 · 민감, 모든 피부</t>
         </is>
       </c>
-      <c r="F47" s="38" t="inlineStr">
+      <c r="F49" s="41" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="33" t="inlineStr">
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 10 · 활성 88 · 향 1 · 방부 1</t>
         </is>
       </c>
-      <c r="B48" s="34" t="n"/>
-      <c r="C48" s="34" t="n"/>
-      <c r="D48" s="34" t="n"/>
-      <c r="E48" s="34" t="n"/>
-      <c r="F48" s="34" t="n"/>
-    </row>
-    <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="35" t="inlineStr">
+      <c r="B50" s="34" t="n"/>
+      <c r="C50" s="34" t="n"/>
+      <c r="D50" s="34" t="n"/>
+      <c r="E50" s="34" t="n"/>
+      <c r="F50" s="34" t="n"/>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B49" s="36" t="n"/>
-      <c r="C49" s="36" t="n"/>
-      <c r="D49" s="36" t="n"/>
-      <c r="E49" s="36" t="n"/>
-      <c r="F49" s="36" t="n"/>
-    </row>
-    <row r="50" ht="96" customHeight="1">
-      <c r="A50" s="42" t="inlineStr">
+      <c r="B51" s="36" t="n"/>
+      <c r="C51" s="36" t="n"/>
+      <c r="D51" s="36" t="n"/>
+      <c r="E51" s="36" t="n"/>
+      <c r="F51" s="36" t="n"/>
+    </row>
+    <row r="52" ht="96" customHeight="1">
+      <c r="A52" s="45" t="inlineStr">
         <is>
           <t>클레오파트라, 네로의 아내 포파이아 등 전설적인 미인들이 꿀과
 우유로 목욕을 했다는 것은 이미 알려진 사실인데요 그만큼 꿀은 거친
@@ -3427,369 +3470,383 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B50" s="23" t="n"/>
-      <c r="C50" s="23" t="n"/>
-      <c r="D50" s="23" t="n"/>
-      <c r="E50" s="23" t="n"/>
-      <c r="F50" s="23" t="n"/>
-    </row>
-    <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="35" t="inlineStr">
-        <is>
-          <t>— 만들기 —</t>
-        </is>
-      </c>
-      <c r="B51" s="36" t="n"/>
-      <c r="C51" s="36" t="n"/>
-      <c r="D51" s="36" t="n"/>
-      <c r="E51" s="36" t="n"/>
-      <c r="F51" s="36" t="n"/>
-    </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="42" t="inlineStr">
-        <is>
-          <t>1. 모든 재료를 계량한 후
-2. 골고루 섞어주세요.
-3. 용기에 넣으면 완성.</t>
-        </is>
-      </c>
       <c r="B52" s="23" t="n"/>
       <c r="C52" s="23" t="n"/>
       <c r="D52" s="23" t="n"/>
       <c r="E52" s="23" t="n"/>
       <c r="F52" s="23" t="n"/>
     </row>
-    <row r="53" ht="86.74999999999997" customHeight="1">
-      <c r="A53" s="23" t="n"/>
-      <c r="B53" s="23" t="n"/>
-      <c r="C53" s="23" t="n"/>
-      <c r="D53" s="23" t="n"/>
-      <c r="E53" s="23" t="n"/>
-      <c r="F53" s="23" t="n"/>
-    </row>
-    <row r="54" ht="6" customHeight="1"/>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="24" t="inlineStr">
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="35" t="inlineStr">
+        <is>
+          <t>— 만들기 —</t>
+        </is>
+      </c>
+      <c r="B53" s="36" t="n"/>
+      <c r="C53" s="36" t="n"/>
+      <c r="D53" s="36" t="n"/>
+      <c r="E53" s="36" t="n"/>
+      <c r="F53" s="36" t="n"/>
+    </row>
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="45" t="inlineStr">
+        <is>
+          <t>1. 모든 재료를 계량한 후
+2. 골고루 섞어주세요.
+3. 용기에 넣으면 완성.</t>
+        </is>
+      </c>
+      <c r="B54" s="23" t="n"/>
+      <c r="C54" s="23" t="n"/>
+      <c r="D54" s="23" t="n"/>
+      <c r="E54" s="23" t="n"/>
+      <c r="F54" s="23" t="n"/>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B55" s="39" t="n"/>
+      <c r="C55" s="39" t="n"/>
+      <c r="D55" s="39" t="n"/>
+      <c r="E55" s="39" t="n"/>
+      <c r="F55" s="39" t="n"/>
+    </row>
+    <row r="56" ht="75" customHeight="1">
+      <c r="A56" s="40" t="inlineStr">
+        <is>
+          <t>· 베이스: 수상 10%(워터 코포아수 10%)가 제형의 뼈대·수분 공급.
+· 기능: 활성 합 88%(알로에베라겔 68%, 세라마이드 (수용성) 10%, 꿀 추출물 10%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 방부 1% · 향 1% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="6" customHeight="1"/>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
         <is>
           <t>트러블 SSG~필링젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B55" s="25" t="n"/>
-      <c r="C55" s="25" t="n"/>
-      <c r="D55" s="25" t="n"/>
-      <c r="E55" s="25" t="n"/>
-      <c r="F55" s="25" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="26" t="inlineStr">
+      <c r="B58" s="25" t="n"/>
+      <c r="C58" s="25" t="n"/>
+      <c r="D58" s="25" t="n"/>
+      <c r="E58" s="25" t="n"/>
+      <c r="F58" s="25" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B56" s="26" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C56" s="26" t="inlineStr">
+      <c r="C59" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D56" s="26" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E56" s="26" t="inlineStr">
+      <c r="E59" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F56" s="26" t="inlineStr">
+      <c r="F59" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="27" t="inlineStr">
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>내추럴 / 셀룰로오즈</t>
         </is>
       </c>
-      <c r="B57" s="27" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C57" s="28" t="inlineStr">
+      <c r="C60" s="28" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D57" s="30" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E57" s="27" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>프랑스산 목화 섬유질로 · 만든 천연 필링제.</t>
         </is>
       </c>
-      <c r="F57" s="27" t="inlineStr"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="27" t="inlineStr">
-        <is>
-          <t>티트리워터</t>
-        </is>
-      </c>
-      <c r="B58" s="27" t="inlineStr">
-        <is>
-          <t>37g</t>
-        </is>
-      </c>
-      <c r="C58" s="28" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="D58" s="40" t="inlineStr">
-        <is>
-          <t>수상</t>
-        </is>
-      </c>
-      <c r="E58" s="27" t="inlineStr">
-        <is>
-          <t>티트리 수증기 · 증류법으로 추출</t>
-        </is>
-      </c>
-      <c r="F58" s="27" t="inlineStr">
-        <is>
-          <t>로즈마리 · 편백워터</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="64" customHeight="1">
-      <c r="A59" s="27" t="inlineStr">
-        <is>
-          <t>알로에베라겔</t>
-        </is>
-      </c>
-      <c r="B59" s="27" t="inlineStr">
-        <is>
-          <t>40g</t>
-        </is>
-      </c>
-      <c r="C59" s="28" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="D59" s="29" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="E59" s="27" t="inlineStr">
-        <is>
-          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. · 남은 재료 활용 팁 : 젤타입스킨으로 사용가능 · 헤어에센스로 사용가능.</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="inlineStr">
-        <is>
-          <t>카보폴프리젤</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="48" customHeight="1">
-      <c r="A60" s="27" t="inlineStr">
-        <is>
-          <t>알란토인분말</t>
-        </is>
-      </c>
-      <c r="B60" s="27" t="inlineStr">
-        <is>
-          <t>0.2g</t>
-        </is>
-      </c>
-      <c r="C60" s="28" t="inlineStr">
-        <is>
-          <t>&lt;1%</t>
-        </is>
-      </c>
-      <c r="D60" s="29" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="E60" s="27" t="inlineStr">
-        <is>
-          <t>진정, 계량스푼 작은 쪽 깎아서 4개면 0.2g</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="inlineStr">
-        <is>
-          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
-        </is>
-      </c>
+      <c r="F60" s="27" t="inlineStr"/>
     </row>
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="27" t="inlineStr">
         <is>
-          <t>마치현추출물</t>
+          <t>티트리워터</t>
         </is>
       </c>
       <c r="B61" s="27" t="inlineStr">
         <is>
-          <t>5g</t>
+          <t>37g</t>
         </is>
       </c>
       <c r="C61" s="28" t="inlineStr">
         <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="D61" s="29" t="inlineStr">
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="D61" s="43" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>티트리 수증기 · 증류법으로 추출</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="inlineStr">
+        <is>
+          <t>로즈마리 · 편백워터</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="64" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>알로에베라겔</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>40g</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="D62" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E61" s="27" t="inlineStr">
-        <is>
-          <t>쇠비름, 진정 · 트러블 관리</t>
-        </is>
-      </c>
-      <c r="F61" s="27" t="inlineStr">
-        <is>
-          <t>어성초 · 병풀 추출물 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="48" customHeight="1">
-      <c r="A62" s="27" t="inlineStr">
-        <is>
-          <t>글리세린</t>
-        </is>
-      </c>
-      <c r="B62" s="27" t="inlineStr">
-        <is>
-          <t>3.8g</t>
-        </is>
-      </c>
-      <c r="C62" s="28" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D62" s="31" t="inlineStr">
-        <is>
-          <t>보습</t>
-        </is>
-      </c>
       <c r="E62" s="27" t="inlineStr">
         <is>
-          <t>보습</t>
+          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. · 남은 재료 활용 팁 : 젤타입스킨으로 사용가능 · 헤어에센스로 사용가능.</t>
         </is>
       </c>
       <c r="F62" s="27" t="inlineStr">
         <is>
-          <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="64" customHeight="1">
+          <t>카보폴프리젤</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="48" customHeight="1">
       <c r="A63" s="27" t="inlineStr">
         <is>
-          <t>천연한방보존제</t>
+          <t>알란토인분말</t>
         </is>
       </c>
       <c r="B63" s="27" t="inlineStr">
         <is>
-          <t>1g</t>
+          <t>0.2g</t>
         </is>
       </c>
       <c r="C63" s="28" t="inlineStr">
         <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="D63" s="41" t="inlineStr">
-        <is>
-          <t>방부</t>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D63" s="29" t="inlineStr">
+        <is>
+          <t>활성</t>
         </is>
       </c>
       <c r="E63" s="27" t="inlineStr">
         <is>
-          <t>균번식 억제</t>
+          <t>진정, 계량스푼 작은 쪽 깎아서 4개면 0.2g</t>
         </is>
       </c>
       <c r="F63" s="27" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g · (티트리워터의 양을 36g으로 줄여주세요.)</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="27" t="inlineStr">
         <is>
+          <t>마치현추출물</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>5g</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D64" s="29" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>쇠비름, 진정 · 트러블 관리</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="inlineStr">
+        <is>
+          <t>어성초 · 병풀 추출물 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="48" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>글리세린</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>3.8g</t>
+        </is>
+      </c>
+      <c r="C65" s="28" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D65" s="31" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E65" s="27" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="F65" s="27" t="inlineStr">
+        <is>
+          <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="64" customHeight="1">
+      <c r="A66" s="27" t="inlineStr">
+        <is>
+          <t>천연한방보존제</t>
+        </is>
+      </c>
+      <c r="B66" s="27" t="inlineStr">
+        <is>
+          <t>1g</t>
+        </is>
+      </c>
+      <c r="C66" s="28" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D66" s="44" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="E66" s="27" t="inlineStr">
+        <is>
+          <t>균번식 억제</t>
+        </is>
+      </c>
+      <c r="F66" s="27" t="inlineStr">
+        <is>
+          <t>1,2-헥산디올2g · (티트리워터의 양을 36g으로 줄여주세요.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="32" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
           <t>레몬EO</t>
         </is>
       </c>
-      <c r="B64" s="27" t="inlineStr">
+      <c r="B67" s="27" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C64" s="28" t="inlineStr">
+      <c r="C67" s="28" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D64" s="32" t="inlineStr">
+      <c r="D67" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E64" s="27" t="inlineStr">
+      <c r="E67" s="27" t="inlineStr">
         <is>
           <t>레몬껍질오일,상큼, 아로마테라피</t>
         </is>
       </c>
-      <c r="F64" s="27" t="inlineStr">
+      <c r="F67" s="27" t="inlineStr">
         <is>
           <t>무향 또는 · 원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="33" t="inlineStr">
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 38 · 보습 4 · 활성 46 · 향 0 · 방부 1 · 점증/pH 10</t>
         </is>
       </c>
-      <c r="B65" s="34" t="n"/>
-      <c r="C65" s="34" t="n"/>
-      <c r="D65" s="34" t="n"/>
-      <c r="E65" s="34" t="n"/>
-      <c r="F65" s="34" t="n"/>
-    </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="35" t="inlineStr">
+      <c r="B68" s="34" t="n"/>
+      <c r="C68" s="34" t="n"/>
+      <c r="D68" s="34" t="n"/>
+      <c r="E68" s="34" t="n"/>
+      <c r="F68" s="34" t="n"/>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B66" s="36" t="n"/>
-      <c r="C66" s="36" t="n"/>
-      <c r="D66" s="36" t="n"/>
-      <c r="E66" s="36" t="n"/>
-      <c r="F66" s="36" t="n"/>
-    </row>
-    <row r="67" ht="224" customHeight="1">
-      <c r="A67" s="37" t="inlineStr">
+      <c r="B69" s="36" t="n"/>
+      <c r="C69" s="36" t="n"/>
+      <c r="D69" s="36" t="n"/>
+      <c r="E69" s="36" t="n"/>
+      <c r="F69" s="36" t="n"/>
+    </row>
+    <row r="70" ht="224" customHeight="1">
+      <c r="A70" s="37" t="inlineStr">
         <is>
           <t>누구에게나 '때'는 있습니다.
 이 '때'관리만 잘 해줘도
@@ -3808,20 +3865,20 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="14" customHeight="1">
-      <c r="A68" s="35" t="inlineStr">
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B68" s="36" t="n"/>
-      <c r="C68" s="36" t="n"/>
-      <c r="D68" s="36" t="n"/>
-      <c r="E68" s="36" t="n"/>
-      <c r="F68" s="36" t="n"/>
-    </row>
-    <row r="69" ht="96" customHeight="1">
-      <c r="A69" s="37" t="inlineStr">
+      <c r="B71" s="36" t="n"/>
+      <c r="C71" s="36" t="n"/>
+      <c r="D71" s="36" t="n"/>
+      <c r="E71" s="36" t="n"/>
+      <c r="F71" s="36" t="n"/>
+    </row>
+    <row r="72" ht="96" customHeight="1">
+      <c r="A72" s="37" t="inlineStr">
         <is>
           <t>1. 알란토인분말 0.2g은 계량스푼 작은 쪽에 깍아서 4개로 해주세요.
 2. 비커에 넣고 내추럴 셀룰로오즈을 비롯 모든 재료를
@@ -3832,233 +3889,255 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="6" customHeight="1"/>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="24" t="inlineStr">
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B73" s="39" t="n"/>
+      <c r="C73" s="39" t="n"/>
+      <c r="D73" s="39" t="n"/>
+      <c r="E73" s="39" t="n"/>
+      <c r="F73" s="39" t="n"/>
+    </row>
+    <row r="74" ht="75" customHeight="1">
+      <c r="A74" s="40" t="inlineStr">
+        <is>
+          <t>· 베이스: 수상 38%(티트리워터 38%)가 제형의 뼈대·수분 공급.
+· 기능: 활성 합 46%(알로에베라겔 41%, 마치현추출물 5%, 알란토인분말 0%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 보습 4% · 방부 1% · 점증·pH 10% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="6" customHeight="1"/>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
         <is>
           <t>이데베논 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B71" s="25" t="n"/>
-      <c r="C71" s="25" t="n"/>
-      <c r="D71" s="25" t="n"/>
-      <c r="E71" s="25" t="n"/>
-      <c r="F71" s="25" t="n"/>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="26" t="inlineStr">
+      <c r="B76" s="25" t="n"/>
+      <c r="C76" s="25" t="n"/>
+      <c r="D76" s="25" t="n"/>
+      <c r="E76" s="25" t="n"/>
+      <c r="F76" s="25" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B72" s="26" t="inlineStr">
+      <c r="B77" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C72" s="26" t="inlineStr">
+      <c r="C77" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D72" s="26" t="inlineStr">
+      <c r="D77" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E72" s="26" t="inlineStr">
+      <c r="E77" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F72" s="26" t="inlineStr">
+      <c r="F77" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="48" customHeight="1">
-      <c r="A73" s="38" t="inlineStr">
+    <row r="78" ht="48" customHeight="1">
+      <c r="A78" s="41" t="inlineStr">
         <is>
           <t>로즈 플라워젤</t>
         </is>
       </c>
-      <c r="B73" s="38" t="inlineStr">
+      <c r="B78" s="41" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="C73" s="39" t="inlineStr">
+      <c r="C78" s="42" t="inlineStr">
         <is>
           <t>87%</t>
         </is>
       </c>
-      <c r="D73" s="29" t="inlineStr">
+      <c r="D78" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E73" s="38" t="inlineStr">
+      <c r="E78" s="41" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 젤타입으로. · 에코보습제, 알란토인 함유</t>
         </is>
       </c>
-      <c r="F73" s="38" t="inlineStr">
+      <c r="F78" s="41" t="inlineStr">
         <is>
           <t>허브누리 · 알로에베라겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="48" customHeight="1">
-      <c r="A74" s="38" t="inlineStr">
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="41" t="inlineStr">
         <is>
           <t>이데베논</t>
         </is>
       </c>
-      <c r="B74" s="38" t="inlineStr">
+      <c r="B79" s="41" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C74" s="39" t="inlineStr">
+      <c r="C79" s="42" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D74" s="29" t="inlineStr">
+      <c r="D79" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E74" s="38" t="inlineStr">
+      <c r="E79" s="41" t="inlineStr">
         <is>
           <t>코엔자임의 10배 · 항산화효과 · 레시피 처방시 500ppm 함유크림 완성.</t>
         </is>
       </c>
-      <c r="F74" s="38" t="inlineStr"/>
-    </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="38" t="inlineStr">
+      <c r="F79" s="41" t="inlineStr"/>
+    </row>
+    <row r="80" ht="32" customHeight="1">
+      <c r="A80" s="41" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
-      <c r="B75" s="38" t="inlineStr">
+      <c r="B80" s="41" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C75" s="39" t="inlineStr">
+      <c r="C80" s="42" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D75" s="29" t="inlineStr">
+      <c r="D80" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E75" s="38" t="inlineStr">
+      <c r="E80" s="41" t="inlineStr">
         <is>
           <t>비타민 펩타이드, 화이트닝</t>
         </is>
       </c>
-      <c r="F75" s="38" t="inlineStr">
+      <c r="F80" s="41" t="inlineStr">
         <is>
           <t>4GF · 씨네이크펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="64" customHeight="1">
-      <c r="A76" s="38" t="inlineStr">
+    <row r="81" ht="64" customHeight="1">
+      <c r="A81" s="41" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B76" s="38" t="inlineStr">
+      <c r="B81" s="41" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C76" s="39" t="inlineStr">
+      <c r="C81" s="42" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D76" s="41" t="inlineStr">
+      <c r="D81" s="44" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E76" s="38" t="inlineStr">
+      <c r="E81" s="41" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="F76" s="38" t="inlineStr">
+      <c r="F81" s="41" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g · (로즈플라워 겔의 양을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="38" t="inlineStr">
+    <row r="82" ht="32" customHeight="1">
+      <c r="A82" s="41" t="inlineStr">
         <is>
           <t>다중히아루론산</t>
         </is>
       </c>
-      <c r="B77" s="38" t="inlineStr">
+      <c r="B82" s="41" t="inlineStr">
         <is>
           <t>0~5g</t>
         </is>
       </c>
-      <c r="C77" s="39" t="inlineStr">
+      <c r="C82" s="42" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D77" s="29" t="inlineStr">
+      <c r="D82" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E77" s="38" t="inlineStr">
+      <c r="E82" s="41" t="inlineStr">
         <is>
           <t>고분자, 중분자, 저분자로 이루어짐. · 피부 각층별 수분공급</t>
         </is>
       </c>
-      <c r="F77" s="38" t="inlineStr">
+      <c r="F82" s="41" t="inlineStr">
         <is>
           <t>판테놀</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="33" t="inlineStr">
+    <row r="83" ht="14" customHeight="1">
+      <c r="A83" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 99 · 방부 1</t>
         </is>
       </c>
-      <c r="B78" s="34" t="n"/>
-      <c r="C78" s="34" t="n"/>
-      <c r="D78" s="34" t="n"/>
-      <c r="E78" s="34" t="n"/>
-      <c r="F78" s="34" t="n"/>
-    </row>
-    <row r="79" ht="14" customHeight="1">
-      <c r="A79" s="35" t="inlineStr">
+      <c r="B83" s="34" t="n"/>
+      <c r="C83" s="34" t="n"/>
+      <c r="D83" s="34" t="n"/>
+      <c r="E83" s="34" t="n"/>
+      <c r="F83" s="34" t="n"/>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B79" s="36" t="n"/>
-      <c r="C79" s="36" t="n"/>
-      <c r="D79" s="36" t="n"/>
-      <c r="E79" s="36" t="n"/>
-      <c r="F79" s="36" t="n"/>
-    </row>
-    <row r="80" ht="112" customHeight="1">
-      <c r="A80" s="42" t="inlineStr">
+      <c r="B84" s="36" t="n"/>
+      <c r="C84" s="36" t="n"/>
+      <c r="D84" s="36" t="n"/>
+      <c r="E84" s="36" t="n"/>
+      <c r="F84" s="36" t="n"/>
+    </row>
+    <row r="85" ht="112" customHeight="1">
+      <c r="A85" s="45" t="inlineStr">
         <is>
           <t>황금톡스라 불리는 ,이데베논.
 코엔자임Q10의 10배 항산화효과를 가지고 있습니다.
@@ -4069,26 +4148,26 @@
 또 급이 다른 이데베논의 항산화효과로 시간을 되돌리세요.</t>
         </is>
       </c>
-      <c r="B80" s="23" t="n"/>
-      <c r="C80" s="23" t="n"/>
-      <c r="D80" s="23" t="n"/>
-      <c r="E80" s="23" t="n"/>
-      <c r="F80" s="23" t="n"/>
-    </row>
-    <row r="81" ht="14" customHeight="1">
-      <c r="A81" s="35" t="inlineStr">
+      <c r="B85" s="23" t="n"/>
+      <c r="C85" s="23" t="n"/>
+      <c r="D85" s="23" t="n"/>
+      <c r="E85" s="23" t="n"/>
+      <c r="F85" s="23" t="n"/>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B81" s="36" t="n"/>
-      <c r="C81" s="36" t="n"/>
-      <c r="D81" s="36" t="n"/>
-      <c r="E81" s="36" t="n"/>
-      <c r="F81" s="36" t="n"/>
-    </row>
-    <row r="82" ht="64" customHeight="1">
-      <c r="A82" s="42" t="inlineStr">
+      <c r="B86" s="36" t="n"/>
+      <c r="C86" s="36" t="n"/>
+      <c r="D86" s="36" t="n"/>
+      <c r="E86" s="36" t="n"/>
+      <c r="F86" s="36" t="n"/>
+    </row>
+    <row r="87" ht="64" customHeight="1">
+      <c r="A87" s="45" t="inlineStr">
         <is>
           <t>만들기 과정
 1.로즈플라워겔을 계량하고
@@ -4096,243 +4175,264 @@
 3.고른 점도가 나오면 용기에 담아주세요.</t>
         </is>
       </c>
-      <c r="B82" s="23" t="n"/>
-      <c r="C82" s="23" t="n"/>
-      <c r="D82" s="23" t="n"/>
-      <c r="E82" s="23" t="n"/>
-      <c r="F82" s="23" t="n"/>
-    </row>
-    <row r="83" ht="6" customHeight="1"/>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="24" t="inlineStr">
+      <c r="B87" s="23" t="n"/>
+      <c r="C87" s="23" t="n"/>
+      <c r="D87" s="23" t="n"/>
+      <c r="E87" s="23" t="n"/>
+      <c r="F87" s="23" t="n"/>
+    </row>
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B88" s="39" t="n"/>
+      <c r="C88" s="39" t="n"/>
+      <c r="D88" s="39" t="n"/>
+      <c r="E88" s="39" t="n"/>
+      <c r="F88" s="39" t="n"/>
+    </row>
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="40" t="inlineStr">
+        <is>
+          <t>· 기능: 활성 합 99%(로즈 플라워젤 87%, 이데베논 5%, 화이트펩타이드 5%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 방부 1% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="6" customHeight="1"/>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="24" t="inlineStr">
         <is>
           <t>TX 멜라 토닝 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B84" s="25" t="n"/>
-      <c r="C84" s="25" t="n"/>
-      <c r="D84" s="25" t="n"/>
-      <c r="E84" s="25" t="n"/>
-      <c r="F84" s="25" t="n"/>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="26" t="inlineStr">
+      <c r="B91" s="25" t="n"/>
+      <c r="C91" s="25" t="n"/>
+      <c r="D91" s="25" t="n"/>
+      <c r="E91" s="25" t="n"/>
+      <c r="F91" s="25" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B85" s="26" t="inlineStr">
+      <c r="B92" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C85" s="26" t="inlineStr">
+      <c r="C92" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D85" s="26" t="inlineStr">
+      <c r="D92" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E85" s="26" t="inlineStr">
+      <c r="E92" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F85" s="26" t="inlineStr">
+      <c r="F92" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="48" customHeight="1">
-      <c r="A86" s="27" t="inlineStr">
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="27" t="inlineStr">
         <is>
           <t>로즈 플라워겔</t>
         </is>
       </c>
-      <c r="B86" s="27" t="inlineStr">
+      <c r="B93" s="27" t="inlineStr">
         <is>
           <t>89g</t>
         </is>
       </c>
-      <c r="C86" s="28" t="inlineStr">
+      <c r="C93" s="28" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
       </c>
-      <c r="D86" s="29" t="inlineStr">
+      <c r="D93" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E86" s="27" t="inlineStr">
+      <c r="E93" s="27" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수를 듬뿍 담은젤 · 에코보습제, 알란토인 함유</t>
         </is>
       </c>
-      <c r="F86" s="27" t="inlineStr">
+      <c r="F93" s="27" t="inlineStr">
         <is>
           <t>알로에베라겔 · 네롤리플라워젤</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="64" customHeight="1">
-      <c r="A87" s="27" t="inlineStr">
+    <row r="94" ht="64" customHeight="1">
+      <c r="A94" s="27" t="inlineStr">
         <is>
           <t>트라넥삼산 / (펩타이드)</t>
         </is>
       </c>
-      <c r="B87" s="27" t="inlineStr">
+      <c r="B94" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C87" s="28" t="inlineStr">
+      <c r="C94" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D87" s="29" t="inlineStr">
+      <c r="D94" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E87" s="27" t="inlineStr">
+      <c r="E94" s="27" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 · 펩타이드 말단에 합성으로 · 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="F87" s="27" t="inlineStr">
+      <c r="F94" s="27" t="inlineStr">
         <is>
           <t>화이트 펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="48" customHeight="1">
-      <c r="A88" s="27" t="inlineStr">
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
         <is>
           <t>4GF</t>
         </is>
       </c>
-      <c r="B88" s="27" t="inlineStr">
+      <c r="B95" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C88" s="28" t="inlineStr">
+      <c r="C95" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D88" s="29" t="inlineStr">
+      <c r="D95" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E88" s="27" t="inlineStr">
+      <c r="E95" s="27" t="inlineStr">
         <is>
           <t>EGF, FGF, IGF, TGF · 복합 펩타이드</t>
         </is>
       </c>
-      <c r="F88" s="27" t="inlineStr">
+      <c r="F95" s="27" t="inlineStr">
         <is>
           <t>아세틸헥사 · 씨네이크펩타이드, 화이트펩타이드 등</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="64" customHeight="1">
-      <c r="A89" s="27" t="inlineStr">
+    <row r="96" ht="64" customHeight="1">
+      <c r="A96" s="27" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B89" s="27" t="inlineStr">
+      <c r="B96" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C89" s="28" t="inlineStr">
+      <c r="C96" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D89" s="41" t="inlineStr">
+      <c r="D96" s="44" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E89" s="27" t="inlineStr">
+      <c r="E96" s="27" t="inlineStr">
         <is>
           <t>균번식 억제, 식물복합</t>
         </is>
       </c>
-      <c r="F89" s="27" t="inlineStr">
+      <c r="F96" s="27" t="inlineStr">
         <is>
           <t>1.2헥산디올2g · (로즈플라워겔을 88g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="48" customHeight="1">
-      <c r="A90" s="27" t="inlineStr">
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="27" t="inlineStr">
         <is>
           <t>브라이트닝 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B90" s="27" t="inlineStr">
+      <c r="B97" s="27" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C90" s="28" t="inlineStr">
+      <c r="C97" s="28" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D90" s="32" t="inlineStr">
+      <c r="D97" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E90" s="27" t="inlineStr">
+      <c r="E97" s="27" t="inlineStr">
         <is>
           <t>네롤리, 일랑일랑, 버가못FCF · 프랑킨센스 EO 블렌딩오일, 생략 가능</t>
         </is>
       </c>
-      <c r="F90" s="27" t="inlineStr">
+      <c r="F97" s="27" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="14" customHeight="1">
-      <c r="A91" s="33" t="inlineStr">
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 99 · 향 0 · 방부 1</t>
         </is>
       </c>
-      <c r="B91" s="34" t="n"/>
-      <c r="C91" s="34" t="n"/>
-      <c r="D91" s="34" t="n"/>
-      <c r="E91" s="34" t="n"/>
-      <c r="F91" s="34" t="n"/>
-    </row>
-    <row r="92" ht="14" customHeight="1">
-      <c r="A92" s="35" t="inlineStr">
+      <c r="B98" s="34" t="n"/>
+      <c r="C98" s="34" t="n"/>
+      <c r="D98" s="34" t="n"/>
+      <c r="E98" s="34" t="n"/>
+      <c r="F98" s="34" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B92" s="36" t="n"/>
-      <c r="C92" s="36" t="n"/>
-      <c r="D92" s="36" t="n"/>
-      <c r="E92" s="36" t="n"/>
-      <c r="F92" s="36" t="n"/>
-    </row>
-    <row r="93" ht="384" customHeight="1">
-      <c r="A93" s="37" t="inlineStr">
+      <c r="B99" s="36" t="n"/>
+      <c r="C99" s="36" t="n"/>
+      <c r="D99" s="36" t="n"/>
+      <c r="E99" s="36" t="n"/>
+      <c r="F99" s="36" t="n"/>
+    </row>
+    <row r="100" ht="384" customHeight="1">
+      <c r="A100" s="37" t="inlineStr">
         <is>
           <t>트레넥삼산(Tranexamic acid, TX)은 원래 지혈제로 사용되고 있습니다.
 산후 , 외상, 월경, 코피 등 과다 출혈에 사용되는 항플라즈민제로 의약 성분입니다.
@@ -4361,27 +4461,27 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="37" t="inlineStr">
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="37" t="inlineStr">
         <is>
           <t>도움을 줍니다.</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="14" customHeight="1">
-      <c r="A95" s="35" t="inlineStr">
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B95" s="36" t="n"/>
-      <c r="C95" s="36" t="n"/>
-      <c r="D95" s="36" t="n"/>
-      <c r="E95" s="36" t="n"/>
-      <c r="F95" s="36" t="n"/>
-    </row>
-    <row r="96" ht="64" customHeight="1">
-      <c r="A96" s="37" t="inlineStr">
+      <c r="B102" s="36" t="n"/>
+      <c r="C102" s="36" t="n"/>
+      <c r="D102" s="36" t="n"/>
+      <c r="E102" s="36" t="n"/>
+      <c r="F102" s="36" t="n"/>
+    </row>
+    <row r="103" ht="64" customHeight="1">
+      <c r="A103" s="37" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량하고
@@ -4390,237 +4490,258 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="6" customHeight="1"/>
-    <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="24" t="inlineStr">
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B104" s="39" t="n"/>
+      <c r="C104" s="39" t="n"/>
+      <c r="D104" s="39" t="n"/>
+      <c r="E104" s="39" t="n"/>
+      <c r="F104" s="39" t="n"/>
+    </row>
+    <row r="105" ht="60" customHeight="1">
+      <c r="A105" s="40" t="inlineStr">
+        <is>
+          <t>· 기능: 활성 합 99%(로즈 플라워겔 89%, 트라넥삼산 / (펩타이드) 5%, 4GF 5%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 방부 1% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="6" customHeight="1"/>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="24" t="inlineStr">
         <is>
           <t>콜라겐 드림 수면팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B98" s="25" t="n"/>
-      <c r="C98" s="25" t="n"/>
-      <c r="D98" s="25" t="n"/>
-      <c r="E98" s="25" t="n"/>
-      <c r="F98" s="25" t="n"/>
-    </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="26" t="inlineStr">
+      <c r="B107" s="25" t="n"/>
+      <c r="C107" s="25" t="n"/>
+      <c r="D107" s="25" t="n"/>
+      <c r="E107" s="25" t="n"/>
+      <c r="F107" s="25" t="n"/>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B99" s="26" t="inlineStr">
+      <c r="B108" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C99" s="26" t="inlineStr">
+      <c r="C108" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D99" s="26" t="inlineStr">
+      <c r="D108" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E99" s="26" t="inlineStr">
+      <c r="E108" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F99" s="26" t="inlineStr">
+      <c r="F108" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="48" customHeight="1">
-      <c r="A100" s="38" t="inlineStr">
+    <row r="109" ht="48" customHeight="1">
+      <c r="A109" s="41" t="inlineStr">
         <is>
           <t>워터 호호바</t>
         </is>
       </c>
-      <c r="B100" s="38" t="inlineStr">
+      <c r="B109" s="41" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C100" s="39" t="inlineStr">
+      <c r="C109" s="42" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D100" s="40" t="inlineStr">
+      <c r="D109" s="43" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E100" s="38" t="inlineStr">
+      <c r="E109" s="41" t="inlineStr">
         <is>
           <t>호호바오일에 천연레시틴을 · 이용하여 리포좀화 · 수상에 쉽게 분산</t>
         </is>
       </c>
-      <c r="F100" s="38" t="inlineStr">
+      <c r="F109" s="41" t="inlineStr">
         <is>
           <t>슈퍼 곡물 · 단백질추출물</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="48" customHeight="1">
-      <c r="A101" s="38" t="inlineStr">
+    <row r="110" ht="48" customHeight="1">
+      <c r="A110" s="41" t="inlineStr">
         <is>
           <t>콜라겐 펩타이드</t>
         </is>
       </c>
-      <c r="B101" s="38" t="inlineStr">
+      <c r="B110" s="41" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C101" s="39" t="inlineStr">
+      <c r="C110" s="42" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D101" s="29" t="inlineStr">
+      <c r="D110" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E101" s="38" t="inlineStr">
+      <c r="E110" s="41" t="inlineStr">
         <is>
           <t>인체 흡수가 용이한 · 저분자화 순수 단백질 사용 · 18종의 아미노산으로 구성</t>
         </is>
       </c>
-      <c r="F101" s="38" t="inlineStr">
+      <c r="F110" s="41" t="inlineStr">
         <is>
           <t>아카시아 · 마린콜라겐</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="32" customHeight="1">
-      <c r="A102" s="38" t="inlineStr">
+    <row r="111" ht="32" customHeight="1">
+      <c r="A111" s="41" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
-      <c r="B102" s="38" t="inlineStr">
+      <c r="B111" s="41" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C102" s="39" t="inlineStr">
+      <c r="C111" s="42" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D102" s="29" t="inlineStr">
+      <c r="D111" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E102" s="38" t="inlineStr">
+      <c r="E111" s="41" t="inlineStr">
         <is>
           <t>비타민 펩타이드, 화이트닝</t>
         </is>
       </c>
-      <c r="F102" s="38" t="inlineStr">
+      <c r="F111" s="41" t="inlineStr">
         <is>
           <t>트라넥 · 삼산펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="32" customHeight="1">
-      <c r="A103" s="38" t="inlineStr">
+    <row r="112" ht="32" customHeight="1">
+      <c r="A112" s="41" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B103" s="38" t="inlineStr">
+      <c r="B112" s="41" t="inlineStr">
         <is>
           <t>85g</t>
         </is>
       </c>
-      <c r="C103" s="39" t="inlineStr">
+      <c r="C112" s="42" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="D103" s="29" t="inlineStr">
+      <c r="D112" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E103" s="38" t="inlineStr">
+      <c r="E112" s="41" t="inlineStr">
         <is>
           <t>불가리아 다마스크 · 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="F103" s="38" t="inlineStr">
+      <c r="F112" s="41" t="inlineStr">
         <is>
           <t>네롤리플라워겔 · 알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="64" customHeight="1">
-      <c r="A104" s="38" t="inlineStr">
+    <row r="113" ht="64" customHeight="1">
+      <c r="A113" s="41" t="inlineStr">
         <is>
           <t>1,2 헥산디올</t>
         </is>
       </c>
-      <c r="B104" s="38" t="inlineStr">
+      <c r="B113" s="41" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C104" s="39" t="inlineStr">
+      <c r="C113" s="42" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D104" s="31" t="inlineStr">
+      <c r="D113" s="31" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E104" s="38" t="inlineStr">
+      <c r="E113" s="41" t="inlineStr">
         <is>
           <t>보습제, 자유수 억제, 균번식억제</t>
         </is>
       </c>
-      <c r="F104" s="38" t="inlineStr">
+      <c r="F113" s="41" t="inlineStr">
         <is>
           <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="14" customHeight="1">
-      <c r="A105" s="33" t="inlineStr">
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 3 · 보습 2 · 활성 95</t>
         </is>
       </c>
-      <c r="B105" s="34" t="n"/>
-      <c r="C105" s="34" t="n"/>
-      <c r="D105" s="34" t="n"/>
-      <c r="E105" s="34" t="n"/>
-      <c r="F105" s="34" t="n"/>
-    </row>
-    <row r="106" ht="14" customHeight="1">
-      <c r="A106" s="35" t="inlineStr">
+      <c r="B114" s="34" t="n"/>
+      <c r="C114" s="34" t="n"/>
+      <c r="D114" s="34" t="n"/>
+      <c r="E114" s="34" t="n"/>
+      <c r="F114" s="34" t="n"/>
+    </row>
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B106" s="36" t="n"/>
-      <c r="C106" s="36" t="n"/>
-      <c r="D106" s="36" t="n"/>
-      <c r="E106" s="36" t="n"/>
-      <c r="F106" s="36" t="n"/>
-    </row>
-    <row r="107" ht="112" customHeight="1">
-      <c r="A107" s="42" t="inlineStr">
+      <c r="B115" s="36" t="n"/>
+      <c r="C115" s="36" t="n"/>
+      <c r="D115" s="36" t="n"/>
+      <c r="E115" s="36" t="n"/>
+      <c r="F115" s="36" t="n"/>
+    </row>
+    <row r="116" ht="112" customHeight="1">
+      <c r="A116" s="45" t="inlineStr">
         <is>
           <t>25세 이후 콜라겐 합성이 줄어들므로
 피부가 탄력을 잃고 주름이 생기기 시작하며 활기를 잃게 됩니다.
@@ -4631,26 +4752,26 @@
 보습은 물론 탄력관리에 좋고 생기있는 피부를 가꿔줍니다.</t>
         </is>
       </c>
-      <c r="B107" s="23" t="n"/>
-      <c r="C107" s="23" t="n"/>
-      <c r="D107" s="23" t="n"/>
-      <c r="E107" s="23" t="n"/>
-      <c r="F107" s="23" t="n"/>
-    </row>
-    <row r="108" ht="14" customHeight="1">
-      <c r="A108" s="35" t="inlineStr">
+      <c r="B116" s="23" t="n"/>
+      <c r="C116" s="23" t="n"/>
+      <c r="D116" s="23" t="n"/>
+      <c r="E116" s="23" t="n"/>
+      <c r="F116" s="23" t="n"/>
+    </row>
+    <row r="117" ht="14" customHeight="1">
+      <c r="A117" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B108" s="36" t="n"/>
-      <c r="C108" s="36" t="n"/>
-      <c r="D108" s="36" t="n"/>
-      <c r="E108" s="36" t="n"/>
-      <c r="F108" s="36" t="n"/>
-    </row>
-    <row r="109" ht="64" customHeight="1">
-      <c r="A109" s="42" t="inlineStr">
+      <c r="B117" s="36" t="n"/>
+      <c r="C117" s="36" t="n"/>
+      <c r="D117" s="36" t="n"/>
+      <c r="E117" s="36" t="n"/>
+      <c r="F117" s="36" t="n"/>
+    </row>
+    <row r="118" ht="64" customHeight="1">
+      <c r="A118" s="45" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 모든 재료를 계량합니다.
@@ -4658,207 +4779,228 @@
 3. 점도가 고르게 되면 용기에 옮겨 담으면 완성.</t>
         </is>
       </c>
-      <c r="B109" s="23" t="n"/>
-      <c r="C109" s="23" t="n"/>
-      <c r="D109" s="23" t="n"/>
-      <c r="E109" s="23" t="n"/>
-      <c r="F109" s="23" t="n"/>
-    </row>
-    <row r="110" ht="6" customHeight="1"/>
-    <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="24" t="inlineStr">
+      <c r="B118" s="23" t="n"/>
+      <c r="C118" s="23" t="n"/>
+      <c r="D118" s="23" t="n"/>
+      <c r="E118" s="23" t="n"/>
+      <c r="F118" s="23" t="n"/>
+    </row>
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B119" s="39" t="n"/>
+      <c r="C119" s="39" t="n"/>
+      <c r="D119" s="39" t="n"/>
+      <c r="E119" s="39" t="n"/>
+      <c r="F119" s="39" t="n"/>
+    </row>
+    <row r="120" ht="60" customHeight="1">
+      <c r="A120" s="40" t="inlineStr">
+        <is>
+          <t>· 기능: 활성 합 95%(로즈플라워겔 85%, 콜라겐 펩타이드 5%, 화이트펩타이드 5%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 보습 2% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="6" customHeight="1"/>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="24" t="inlineStr">
         <is>
           <t>셀프백신 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B111" s="25" t="n"/>
-      <c r="C111" s="25" t="n"/>
-      <c r="D111" s="25" t="n"/>
-      <c r="E111" s="25" t="n"/>
-      <c r="F111" s="25" t="n"/>
-    </row>
-    <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="26" t="inlineStr">
+      <c r="B122" s="25" t="n"/>
+      <c r="C122" s="25" t="n"/>
+      <c r="D122" s="25" t="n"/>
+      <c r="E122" s="25" t="n"/>
+      <c r="F122" s="25" t="n"/>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B112" s="26" t="inlineStr">
+      <c r="B123" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C112" s="26" t="inlineStr">
+      <c r="C123" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D112" s="26" t="inlineStr">
+      <c r="D123" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E112" s="26" t="inlineStr">
+      <c r="E123" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F112" s="26" t="inlineStr">
+      <c r="F123" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="27" t="inlineStr">
+    <row r="124" ht="16" customHeight="1">
+      <c r="A124" s="27" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B113" s="27" t="inlineStr">
+      <c r="B124" s="27" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C113" s="28" t="inlineStr">
+      <c r="C124" s="28" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D113" s="29" t="inlineStr">
+      <c r="D124" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E113" s="27" t="inlineStr">
+      <c r="E124" s="27" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="F113" s="27" t="inlineStr">
+      <c r="F124" s="27" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="48" customHeight="1">
-      <c r="A114" s="27" t="inlineStr">
+    <row r="125" ht="48" customHeight="1">
+      <c r="A125" s="27" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B114" s="27" t="inlineStr">
+      <c r="B125" s="27" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C114" s="28" t="inlineStr">
+      <c r="C125" s="28" t="inlineStr">
         <is>
           <t>30%</t>
         </is>
       </c>
-      <c r="D114" s="30" t="inlineStr">
+      <c r="D125" s="30" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E114" s="27" t="inlineStr">
+      <c r="E125" s="27" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 · 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="F114" s="27" t="inlineStr"/>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="27" t="inlineStr">
+      <c r="F125" s="27" t="inlineStr"/>
+    </row>
+    <row r="126" ht="16" customHeight="1">
+      <c r="A126" s="27" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B115" s="27" t="inlineStr">
+      <c r="B126" s="27" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C115" s="28" t="inlineStr">
+      <c r="C126" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D115" s="29" t="inlineStr">
+      <c r="D126" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E115" s="27" t="inlineStr">
+      <c r="E126" s="27" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="F115" s="27" t="inlineStr">
+      <c r="F126" s="27" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="48" customHeight="1">
-      <c r="A116" s="27" t="inlineStr">
+    <row r="127" ht="48" customHeight="1">
+      <c r="A127" s="27" t="inlineStr">
         <is>
           <t>니아울리에센셜오일</t>
         </is>
       </c>
-      <c r="B116" s="27" t="inlineStr">
+      <c r="B127" s="27" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C116" s="28" t="inlineStr">
+      <c r="C127" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D116" s="32" t="inlineStr">
+      <c r="D127" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E116" s="27" t="inlineStr">
+      <c r="E127" s="27" t="inlineStr">
         <is>
           <t>광엽 티트리라 불림. 향과 성분이 · 유칼립투스와 티트리의 부드러운 버전</t>
         </is>
       </c>
-      <c r="F116" s="27" t="inlineStr">
+      <c r="F127" s="27" t="inlineStr">
         <is>
           <t>유칼립튜스, 티트리 등</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="14" customHeight="1">
-      <c r="A117" s="33" t="inlineStr">
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 69 · 향 1 · 점증/pH 30</t>
         </is>
       </c>
-      <c r="B117" s="34" t="n"/>
-      <c r="C117" s="34" t="n"/>
-      <c r="D117" s="34" t="n"/>
-      <c r="E117" s="34" t="n"/>
-      <c r="F117" s="34" t="n"/>
-    </row>
-    <row r="118" ht="14" customHeight="1">
-      <c r="A118" s="35" t="inlineStr">
+      <c r="B128" s="34" t="n"/>
+      <c r="C128" s="34" t="n"/>
+      <c r="D128" s="34" t="n"/>
+      <c r="E128" s="34" t="n"/>
+      <c r="F128" s="34" t="n"/>
+    </row>
+    <row r="129" ht="14" customHeight="1">
+      <c r="A129" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B118" s="36" t="n"/>
-      <c r="C118" s="36" t="n"/>
-      <c r="D118" s="36" t="n"/>
-      <c r="E118" s="36" t="n"/>
-      <c r="F118" s="36" t="n"/>
-    </row>
-    <row r="119" ht="320" customHeight="1">
-      <c r="A119" s="37" t="inlineStr">
+      <c r="B129" s="36" t="n"/>
+      <c r="C129" s="36" t="n"/>
+      <c r="D129" s="36" t="n"/>
+      <c r="E129" s="36" t="n"/>
+      <c r="F129" s="36" t="n"/>
+    </row>
+    <row r="130" ht="320" customHeight="1">
+      <c r="A130" s="37" t="inlineStr">
         <is>
           <t>무제 문서
 코로나19 예방을 위해 전문가들이
@@ -4883,20 +5025,20 @@
         </is>
       </c>
     </row>
-    <row r="120" ht="14" customHeight="1">
-      <c r="A120" s="35" t="inlineStr">
+    <row r="131" ht="14" customHeight="1">
+      <c r="A131" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B120" s="36" t="n"/>
-      <c r="C120" s="36" t="n"/>
-      <c r="D120" s="36" t="n"/>
-      <c r="E120" s="36" t="n"/>
-      <c r="F120" s="36" t="n"/>
-    </row>
-    <row r="121" ht="80" customHeight="1">
-      <c r="A121" s="37" t="inlineStr">
+      <c r="B131" s="36" t="n"/>
+      <c r="C131" s="36" t="n"/>
+      <c r="D131" s="36" t="n"/>
+      <c r="E131" s="36" t="n"/>
+      <c r="F131" s="36" t="n"/>
+    </row>
+    <row r="132" ht="80" customHeight="1">
+      <c r="A132" s="37" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -4906,233 +5048,254 @@
         </is>
       </c>
     </row>
-    <row r="122" ht="6" customHeight="1"/>
-    <row r="123" ht="22" customHeight="1">
-      <c r="A123" s="24" t="inlineStr">
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B133" s="39" t="n"/>
+      <c r="C133" s="39" t="n"/>
+      <c r="D133" s="39" t="n"/>
+      <c r="E133" s="39" t="n"/>
+      <c r="F133" s="39" t="n"/>
+    </row>
+    <row r="134" ht="60" customHeight="1">
+      <c r="A134" s="40" t="inlineStr">
+        <is>
+          <t>· 기능: 활성 합 69%(아로마베이스 95 66%, (다중) 히아루론산 3%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 점증·pH 30% · 향 1% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="6" customHeight="1"/>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="24" t="inlineStr">
         <is>
           <t>상큼 손소독제(젤)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B123" s="25" t="n"/>
-      <c r="C123" s="25" t="n"/>
-      <c r="D123" s="25" t="n"/>
-      <c r="E123" s="25" t="n"/>
-      <c r="F123" s="25" t="n"/>
-    </row>
-    <row r="124" ht="15" customHeight="1">
-      <c r="A124" s="26" t="inlineStr">
+      <c r="B136" s="25" t="n"/>
+      <c r="C136" s="25" t="n"/>
+      <c r="D136" s="25" t="n"/>
+      <c r="E136" s="25" t="n"/>
+      <c r="F136" s="25" t="n"/>
+    </row>
+    <row r="137" ht="15" customHeight="1">
+      <c r="A137" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B124" s="26" t="inlineStr">
+      <c r="B137" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C124" s="26" t="inlineStr">
+      <c r="C137" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D124" s="26" t="inlineStr">
+      <c r="D137" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E124" s="26" t="inlineStr">
+      <c r="E137" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F124" s="26" t="inlineStr">
+      <c r="F137" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="16" customHeight="1">
-      <c r="A125" s="38" t="inlineStr">
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="41" t="inlineStr">
         <is>
           <t>아로마베이스 95</t>
         </is>
       </c>
-      <c r="B125" s="38" t="inlineStr">
+      <c r="B138" s="41" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C125" s="39" t="inlineStr">
+      <c r="C138" s="42" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D125" s="29" t="inlineStr">
+      <c r="D138" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E125" s="38" t="inlineStr">
+      <c r="E138" s="41" t="inlineStr">
         <is>
           <t>95% 곡물 발효 알코올</t>
         </is>
       </c>
-      <c r="F125" s="38" t="inlineStr">
+      <c r="F138" s="41" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="48" customHeight="1">
-      <c r="A126" s="38" t="inlineStr">
+    <row r="139" ht="48" customHeight="1">
+      <c r="A139" s="41" t="inlineStr">
         <is>
           <t>카보머 프리젤</t>
         </is>
       </c>
-      <c r="B126" s="38" t="inlineStr">
+      <c r="B139" s="41" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C126" s="39" t="inlineStr">
+      <c r="C139" s="42" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D126" s="30" t="inlineStr">
+      <c r="D139" s="30" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E126" s="38" t="inlineStr">
+      <c r="E139" s="41" t="inlineStr">
         <is>
           <t>손쉬운 이용을 위해 · 미리 카보머를 젤타입으로 만들어놓은 것.</t>
         </is>
       </c>
-      <c r="F126" s="38" t="inlineStr"/>
-    </row>
-    <row r="127" ht="32" customHeight="1">
-      <c r="A127" s="38" t="inlineStr">
+      <c r="F139" s="41" t="inlineStr"/>
+    </row>
+    <row r="140" ht="32" customHeight="1">
+      <c r="A140" s="41" t="inlineStr">
         <is>
           <t>알란토인(액상)</t>
         </is>
       </c>
-      <c r="B127" s="38" t="inlineStr">
+      <c r="B140" s="41" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C127" s="39" t="inlineStr">
+      <c r="C140" s="42" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D127" s="29" t="inlineStr">
+      <c r="D140" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E127" s="38" t="inlineStr">
+      <c r="E140" s="41" t="inlineStr">
         <is>
           <t>진정</t>
         </is>
       </c>
-      <c r="F127" s="38" t="inlineStr">
+      <c r="F140" s="41" t="inlineStr">
         <is>
           <t>프로폴리스추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="38" t="inlineStr">
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="41" t="inlineStr">
         <is>
           <t>(다중) 히아루론산</t>
         </is>
       </c>
-      <c r="B128" s="38" t="inlineStr">
+      <c r="B141" s="41" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C128" s="39" t="inlineStr">
+      <c r="C141" s="42" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D128" s="29" t="inlineStr">
+      <c r="D141" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E128" s="38" t="inlineStr">
+      <c r="E141" s="41" t="inlineStr">
         <is>
           <t>보습, 글리세린보다 덜 끈적함</t>
         </is>
       </c>
-      <c r="F128" s="38" t="inlineStr">
+      <c r="F141" s="41" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="48" customHeight="1">
-      <c r="A129" s="38" t="inlineStr">
+    <row r="142" ht="48" customHeight="1">
+      <c r="A142" s="41" t="inlineStr">
         <is>
           <t>레몬쥬스EO</t>
         </is>
       </c>
-      <c r="B129" s="38" t="inlineStr">
+      <c r="B142" s="41" t="inlineStr">
         <is>
           <t>20~25방울</t>
         </is>
       </c>
-      <c r="C129" s="39" t="inlineStr">
+      <c r="C142" s="42" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D129" s="32" t="inlineStr">
+      <c r="D142" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E129" s="38" t="inlineStr">
+      <c r="E142" s="41" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드에센셜오일 · 블랜딩오일</t>
         </is>
       </c>
-      <c r="F129" s="38" t="inlineStr">
+      <c r="F142" s="41" t="inlineStr">
         <is>
           <t>레몬, 만다린, 그레이프푸룻, 라임, 오렌지에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="14" customHeight="1">
-      <c r="A130" s="33" t="inlineStr">
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  활성 74 · 향 1 · 점증/pH 25</t>
         </is>
       </c>
-      <c r="B130" s="34" t="n"/>
-      <c r="C130" s="34" t="n"/>
-      <c r="D130" s="34" t="n"/>
-      <c r="E130" s="34" t="n"/>
-      <c r="F130" s="34" t="n"/>
-    </row>
-    <row r="131" ht="14" customHeight="1">
-      <c r="A131" s="35" t="inlineStr">
+      <c r="B143" s="34" t="n"/>
+      <c r="C143" s="34" t="n"/>
+      <c r="D143" s="34" t="n"/>
+      <c r="E143" s="34" t="n"/>
+      <c r="F143" s="34" t="n"/>
+    </row>
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B131" s="36" t="n"/>
-      <c r="C131" s="36" t="n"/>
-      <c r="D131" s="36" t="n"/>
-      <c r="E131" s="36" t="n"/>
-      <c r="F131" s="36" t="n"/>
-    </row>
-    <row r="132" ht="208" customHeight="1">
-      <c r="A132" s="42" t="inlineStr">
+      <c r="B144" s="36" t="n"/>
+      <c r="C144" s="36" t="n"/>
+      <c r="D144" s="36" t="n"/>
+      <c r="E144" s="36" t="n"/>
+      <c r="F144" s="36" t="n"/>
+    </row>
+    <row r="145" ht="208" customHeight="1">
+      <c r="A145" s="45" t="inlineStr">
         <is>
           <t>무제 문서
 그 어느 때보다 손 청결이 중요한 때입니다.
@@ -5149,26 +5312,26 @@
 '상큼 손소독제 만들기'를 안내해드립니다.</t>
         </is>
       </c>
-      <c r="B132" s="23" t="n"/>
-      <c r="C132" s="23" t="n"/>
-      <c r="D132" s="23" t="n"/>
-      <c r="E132" s="23" t="n"/>
-      <c r="F132" s="23" t="n"/>
-    </row>
-    <row r="133" ht="14" customHeight="1">
-      <c r="A133" s="35" t="inlineStr">
+      <c r="B145" s="23" t="n"/>
+      <c r="C145" s="23" t="n"/>
+      <c r="D145" s="23" t="n"/>
+      <c r="E145" s="23" t="n"/>
+      <c r="F145" s="23" t="n"/>
+    </row>
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B133" s="36" t="n"/>
-      <c r="C133" s="36" t="n"/>
-      <c r="D133" s="36" t="n"/>
-      <c r="E133" s="36" t="n"/>
-      <c r="F133" s="36" t="n"/>
-    </row>
-    <row r="134" ht="80" customHeight="1">
-      <c r="A134" s="42" t="inlineStr">
+      <c r="B146" s="36" t="n"/>
+      <c r="C146" s="36" t="n"/>
+      <c r="D146" s="36" t="n"/>
+      <c r="E146" s="36" t="n"/>
+      <c r="F146" s="36" t="n"/>
+    </row>
+    <row r="147" ht="80" customHeight="1">
+      <c r="A147" s="45" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 아로마베이스 95, 카보머 프리젤, 히아루론산, 에센셜오일을 계량합니다.
@@ -5177,295 +5340,316 @@
 언제나 어디서나 사용하세요.</t>
         </is>
       </c>
-      <c r="B134" s="23" t="n"/>
-      <c r="C134" s="23" t="n"/>
-      <c r="D134" s="23" t="n"/>
-      <c r="E134" s="23" t="n"/>
-      <c r="F134" s="23" t="n"/>
-    </row>
-    <row r="135" ht="6" customHeight="1"/>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="24" t="inlineStr">
+      <c r="B147" s="23" t="n"/>
+      <c r="C147" s="23" t="n"/>
+      <c r="D147" s="23" t="n"/>
+      <c r="E147" s="23" t="n"/>
+      <c r="F147" s="23" t="n"/>
+    </row>
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B148" s="39" t="n"/>
+      <c r="C148" s="39" t="n"/>
+      <c r="D148" s="39" t="n"/>
+      <c r="E148" s="39" t="n"/>
+      <c r="F148" s="39" t="n"/>
+    </row>
+    <row r="149" ht="60" customHeight="1">
+      <c r="A149" s="40" t="inlineStr">
+        <is>
+          <t>· 기능: 활성 합 74%(아로마베이스 95 66%, 알란토인(액상) 5%, (다중) 히아루론산 3%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 점증·pH 25% · 향 1% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="6" customHeight="1"/>
+    <row r="151" ht="22" customHeight="1">
+      <c r="A151" s="24" t="inlineStr">
         <is>
           <t>트러블 잠잠 스팟젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B136" s="25" t="n"/>
-      <c r="C136" s="25" t="n"/>
-      <c r="D136" s="25" t="n"/>
-      <c r="E136" s="25" t="n"/>
-      <c r="F136" s="25" t="n"/>
-    </row>
-    <row r="137" ht="15" customHeight="1">
-      <c r="A137" s="26" t="inlineStr">
+      <c r="B151" s="25" t="n"/>
+      <c r="C151" s="25" t="n"/>
+      <c r="D151" s="25" t="n"/>
+      <c r="E151" s="25" t="n"/>
+      <c r="F151" s="25" t="n"/>
+    </row>
+    <row r="152" ht="15" customHeight="1">
+      <c r="A152" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B137" s="26" t="inlineStr">
+      <c r="B152" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C137" s="26" t="inlineStr">
+      <c r="C152" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D137" s="26" t="inlineStr">
+      <c r="D152" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E137" s="26" t="inlineStr">
+      <c r="E152" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F137" s="26" t="inlineStr">
+      <c r="F152" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="27" t="inlineStr">
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="27" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B138" s="27" t="inlineStr">
+      <c r="B153" s="27" t="inlineStr">
         <is>
           <t>20방울</t>
         </is>
       </c>
-      <c r="C138" s="28" t="inlineStr">
+      <c r="C153" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D138" s="32" t="inlineStr">
+      <c r="D153" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E138" s="27" t="inlineStr">
+      <c r="E153" s="27" t="inlineStr">
         <is>
           <t>항균</t>
         </is>
       </c>
-      <c r="F138" s="27" t="inlineStr">
+      <c r="F153" s="27" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="32" customHeight="1">
-      <c r="A139" s="27" t="inlineStr">
+    <row r="154" ht="32" customHeight="1">
+      <c r="A154" s="27" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B139" s="27" t="inlineStr">
+      <c r="B154" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C139" s="28" t="inlineStr">
+      <c r="C154" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D139" s="43" t="inlineStr">
+      <c r="D154" s="46" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E139" s="27" t="inlineStr">
+      <c r="E154" s="27" t="inlineStr">
         <is>
           <t>가용화제. · 물과요일이 분리되지않도록 하는 역할</t>
         </is>
       </c>
-      <c r="F139" s="27" t="inlineStr">
+      <c r="F154" s="27" t="inlineStr">
         <is>
           <t>솔루벌라이저</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="27" t="inlineStr">
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="27" t="inlineStr">
         <is>
           <t>라벤더워터</t>
         </is>
       </c>
-      <c r="B140" s="27" t="inlineStr">
+      <c r="B155" s="27" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C140" s="28" t="inlineStr">
+      <c r="C155" s="28" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D140" s="40" t="inlineStr">
+      <c r="D155" s="43" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E140" s="27" t="inlineStr">
+      <c r="E155" s="27" t="inlineStr">
         <is>
           <t>진정,재생</t>
         </is>
       </c>
-      <c r="F140" s="27" t="inlineStr">
+      <c r="F155" s="27" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="32" customHeight="1">
-      <c r="A141" s="27" t="inlineStr">
+    <row r="156" ht="32" customHeight="1">
+      <c r="A156" s="27" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔</t>
         </is>
       </c>
-      <c r="B141" s="27" t="inlineStr">
+      <c r="B156" s="27" t="inlineStr">
         <is>
           <t>25g</t>
         </is>
       </c>
-      <c r="C141" s="28" t="inlineStr">
+      <c r="C156" s="28" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D141" s="29" t="inlineStr">
+      <c r="D156" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E141" s="27" t="inlineStr">
+      <c r="E156" s="27" t="inlineStr">
         <is>
           <t>겔타입, 수분공급</t>
         </is>
       </c>
-      <c r="F141" s="27" t="inlineStr">
+      <c r="F156" s="27" t="inlineStr">
         <is>
           <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="27" t="inlineStr">
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="27" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
-      <c r="B142" s="27" t="inlineStr">
+      <c r="B157" s="27" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C142" s="28" t="inlineStr">
+      <c r="C157" s="28" t="inlineStr">
         <is>
           <t>16%</t>
         </is>
       </c>
-      <c r="D142" s="29" t="inlineStr">
+      <c r="D157" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E142" s="27" t="inlineStr">
+      <c r="E157" s="27" t="inlineStr">
         <is>
           <t>항균,진정</t>
         </is>
       </c>
-      <c r="F142" s="27" t="inlineStr">
+      <c r="F157" s="27" t="inlineStr">
         <is>
           <t>카렌듈라추출물</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="16" customHeight="1">
-      <c r="A143" s="27" t="inlineStr">
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="27" t="inlineStr">
         <is>
           <t>한방보존제</t>
         </is>
       </c>
-      <c r="B143" s="27" t="inlineStr">
+      <c r="B158" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C143" s="28" t="inlineStr">
+      <c r="C158" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D143" s="41" t="inlineStr">
+      <c r="D158" s="44" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E143" s="27" t="inlineStr">
+      <c r="E158" s="27" t="inlineStr">
         <is>
           <t>복합한방추출물, 균번식억제</t>
         </is>
       </c>
-      <c r="F143" s="27" t="inlineStr">
+      <c r="F158" s="27" t="inlineStr">
         <is>
           <t>수용성보존제</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="14" customHeight="1">
-      <c r="A144" s="33" t="inlineStr">
+    <row r="159" ht="14" customHeight="1">
+      <c r="A159" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 28 · 유화 2 · 활성 66 · 향 2 · 방부 2</t>
         </is>
       </c>
-      <c r="B144" s="34" t="n"/>
-      <c r="C144" s="34" t="n"/>
-      <c r="D144" s="34" t="n"/>
-      <c r="E144" s="34" t="n"/>
-      <c r="F144" s="34" t="n"/>
-    </row>
-    <row r="145" ht="14" customHeight="1">
-      <c r="A145" s="35" t="inlineStr">
+      <c r="B159" s="34" t="n"/>
+      <c r="C159" s="34" t="n"/>
+      <c r="D159" s="34" t="n"/>
+      <c r="E159" s="34" t="n"/>
+      <c r="F159" s="34" t="n"/>
+    </row>
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B145" s="36" t="n"/>
-      <c r="C145" s="36" t="n"/>
-      <c r="D145" s="36" t="n"/>
-      <c r="E145" s="36" t="n"/>
-      <c r="F145" s="36" t="n"/>
-    </row>
-    <row r="146" ht="64" customHeight="1">
-      <c r="A146" s="37" t="inlineStr">
+      <c r="B160" s="36" t="n"/>
+      <c r="C160" s="36" t="n"/>
+      <c r="D160" s="36" t="n"/>
+      <c r="E160" s="36" t="n"/>
+      <c r="F160" s="36" t="n"/>
+    </row>
+    <row r="161" ht="64" customHeight="1">
+      <c r="A161" s="37" t="inlineStr">
         <is>
           <t>[ 사용법 ]
 티트리에센셜오일은 국소부위에 원액을 발라도 되는 에센셜오일입니다. 스팟젤은 티트리에센셜오일을 전체의 2%를 정도로 희석한 순한 젤타입에센스입니다. 소량을 여드름이 난 부분에 발라주세요.</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="14" customHeight="1">
-      <c r="A147" s="35" t="inlineStr">
+    <row r="162" ht="14" customHeight="1">
+      <c r="A162" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B147" s="36" t="n"/>
-      <c r="C147" s="36" t="n"/>
-      <c r="D147" s="36" t="n"/>
-      <c r="E147" s="36" t="n"/>
-      <c r="F147" s="36" t="n"/>
-    </row>
-    <row r="148" ht="112" customHeight="1">
-      <c r="A148" s="37" t="inlineStr">
+      <c r="B162" s="36" t="n"/>
+      <c r="C162" s="36" t="n"/>
+      <c r="D162" s="36" t="n"/>
+      <c r="E162" s="36" t="n"/>
+      <c r="F162" s="36" t="n"/>
+    </row>
+    <row r="163" ht="112" customHeight="1">
+      <c r="A163" s="37" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 티트리, 올리브리퀴드를 계량합니다.
@@ -5477,206 +5661,228 @@
         </is>
       </c>
     </row>
-    <row r="149" ht="243.2499999999993" customHeight="1"/>
-    <row r="150" ht="6" customHeight="1"/>
-    <row r="151" ht="22" customHeight="1">
-      <c r="A151" s="24" t="inlineStr">
+    <row r="164" ht="14" customHeight="1">
+      <c r="A164" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B164" s="39" t="n"/>
+      <c r="C164" s="39" t="n"/>
+      <c r="D164" s="39" t="n"/>
+      <c r="E164" s="39" t="n"/>
+      <c r="F164" s="39" t="n"/>
+    </row>
+    <row r="165" ht="75" customHeight="1">
+      <c r="A165" s="40" t="inlineStr">
+        <is>
+          <t>· 베이스: 수상 28%(라벤더워터 28%)가 제형의 뼈대·수분 공급.
+· 기능: 활성 합 66%(허브누리 / 알로에베라겔 50%, 어성초추출물 16%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 방부 2% · 향 2% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="154.25" customHeight="1"/>
+    <row r="167" ht="6" customHeight="1"/>
+    <row r="168" ht="22" customHeight="1">
+      <c r="A168" s="24" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 바디팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B151" s="25" t="n"/>
-      <c r="C151" s="25" t="n"/>
-      <c r="D151" s="25" t="n"/>
-      <c r="E151" s="25" t="n"/>
-      <c r="F151" s="25" t="n"/>
-    </row>
-    <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="26" t="inlineStr">
+      <c r="B168" s="25" t="n"/>
+      <c r="C168" s="25" t="n"/>
+      <c r="D168" s="25" t="n"/>
+      <c r="E168" s="25" t="n"/>
+      <c r="F168" s="25" t="n"/>
+    </row>
+    <row r="169" ht="15" customHeight="1">
+      <c r="A169" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B152" s="26" t="inlineStr">
+      <c r="B169" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C152" s="26" t="inlineStr">
+      <c r="C169" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D152" s="26" t="inlineStr">
+      <c r="D169" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E152" s="26" t="inlineStr">
+      <c r="E169" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F152" s="26" t="inlineStr">
+      <c r="F169" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="32" customHeight="1">
-      <c r="A153" s="38" t="inlineStr">
+    <row r="170" ht="32" customHeight="1">
+      <c r="A170" s="41" t="inlineStr">
         <is>
           <t>그린 클레이</t>
         </is>
       </c>
-      <c r="B153" s="38" t="inlineStr">
+      <c r="B170" s="41" t="inlineStr">
         <is>
           <t>54.35%</t>
         </is>
       </c>
-      <c r="C153" s="39" t="inlineStr"/>
-      <c r="D153" s="44" t="inlineStr">
+      <c r="C170" s="42" t="inlineStr"/>
+      <c r="D170" s="47" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E153" s="38" t="inlineStr">
+      <c r="E170" s="41" t="inlineStr">
         <is>
           <t>녹색 점토, 피지·노폐물 흡착</t>
         </is>
       </c>
-      <c r="F153" s="38" t="inlineStr">
+      <c r="F170" s="41" t="inlineStr">
         <is>
           <t>핑크클레이, 카올린</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="64" customHeight="1">
-      <c r="A154" s="38" t="inlineStr">
+    <row r="171" ht="64" customHeight="1">
+      <c r="A171" s="41" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B154" s="38" t="inlineStr">
+      <c r="B171" s="41" t="inlineStr">
         <is>
           <t>43.48%</t>
         </is>
       </c>
-      <c r="C154" s="39" t="inlineStr"/>
-      <c r="D154" s="40" t="inlineStr">
+      <c r="C171" s="42" t="inlineStr"/>
+      <c r="D171" s="43" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E154" s="38" t="inlineStr">
+      <c r="E171" s="41" t="inlineStr">
         <is>
           <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
-      <c r="F154" s="38" t="inlineStr">
+      <c r="F171" s="41" t="inlineStr">
         <is>
           <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="32" customHeight="1">
-      <c r="A155" s="38" t="inlineStr">
+    <row r="172" ht="32" customHeight="1">
+      <c r="A172" s="41" t="inlineStr">
         <is>
           <t>그레이프프룻EO</t>
         </is>
       </c>
-      <c r="B155" s="38" t="inlineStr">
+      <c r="B172" s="41" t="inlineStr">
         <is>
           <t>1.09%</t>
         </is>
       </c>
-      <c r="C155" s="39" t="inlineStr"/>
-      <c r="D155" s="32" t="inlineStr">
+      <c r="C172" s="42" t="inlineStr"/>
+      <c r="D172" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E155" s="38" t="inlineStr">
+      <c r="E172" s="41" t="inlineStr">
         <is>
           <t>자몽 에센셜오일, 상쾌·수렴</t>
         </is>
       </c>
-      <c r="F155" s="38" t="inlineStr">
+      <c r="F172" s="41" t="inlineStr">
         <is>
           <t>오렌지, 레몬에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="64" customHeight="1">
-      <c r="A156" s="38" t="inlineStr">
+    <row r="173" ht="64" customHeight="1">
+      <c r="A173" s="41" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B156" s="38" t="inlineStr">
+      <c r="B173" s="41" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C156" s="39" t="inlineStr"/>
-      <c r="D156" s="32" t="inlineStr">
+      <c r="C173" s="42" t="inlineStr"/>
+      <c r="D173" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E156" s="38" t="inlineStr">
+      <c r="E173" s="41" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="F156" s="38" t="inlineStr">
+      <c r="F173" s="41" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="32" customHeight="1">
-      <c r="A157" s="38" t="inlineStr">
+    <row r="174" ht="32" customHeight="1">
+      <c r="A174" s="41" t="inlineStr">
         <is>
           <t>싸이프러스</t>
         </is>
       </c>
-      <c r="B157" s="38" t="inlineStr">
+      <c r="B174" s="41" t="inlineStr">
         <is>
           <t>0.54%</t>
         </is>
       </c>
-      <c r="C157" s="39" t="inlineStr"/>
-      <c r="D157" s="32" t="inlineStr">
+      <c r="C174" s="42" t="inlineStr"/>
+      <c r="D174" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E157" s="38" t="inlineStr">
+      <c r="E174" s="41" t="inlineStr">
         <is>
           <t>상록 침엽수로 · 스팀 증류법 추출, 숲향</t>
         </is>
       </c>
-      <c r="F157" s="38" t="inlineStr">
+      <c r="F174" s="41" t="inlineStr">
         <is>
           <t>편백</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="14" customHeight="1">
-      <c r="A158" s="35" t="inlineStr">
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B158" s="36" t="n"/>
-      <c r="C158" s="36" t="n"/>
-      <c r="D158" s="36" t="n"/>
-      <c r="E158" s="36" t="n"/>
-      <c r="F158" s="36" t="n"/>
-    </row>
-    <row r="159" ht="192" customHeight="1">
-      <c r="A159" s="42" t="inlineStr">
+      <c r="B175" s="36" t="n"/>
+      <c r="C175" s="36" t="n"/>
+      <c r="D175" s="36" t="n"/>
+      <c r="E175" s="36" t="n"/>
+      <c r="F175" s="36" t="n"/>
+    </row>
+    <row r="176" ht="192" customHeight="1">
+      <c r="A176" s="45" t="inlineStr">
         <is>
           <t>그린클레이 - 프랑스 아질레지방에서 채취하는 클레이(흙). 미세한 클레이가 피부 깊숙이 침투 모공속 노폐물 배출, 흡착, 풍부한 미네랄 성분 해독 효과를 줍니다. 셀룰라이트관리, 여드름지성 피부에 사용.
 그레이프프룻(자몽껍질오일), 제라늄, 싸이프러스, 쥬니퍼베리, 레몬, 펜넬에센셜오일이 다이어트에 효과적인 오일이다. 림프자극, 독소배출, 호르몬균형, 해독 등의 효과를 준다.
@@ -5687,237 +5893,237 @@
 4. 이런 오일로 비누, 마사지오일, 젤, 로션/크림류 제품을 만들어 병행하면 좋다.</t>
         </is>
       </c>
-      <c r="B159" s="23" t="n"/>
-      <c r="C159" s="23" t="n"/>
-      <c r="D159" s="23" t="n"/>
-      <c r="E159" s="23" t="n"/>
-      <c r="F159" s="23" t="n"/>
-    </row>
-    <row r="160" ht="14" customHeight="1">
-      <c r="A160" s="35" t="inlineStr">
+      <c r="B176" s="23" t="n"/>
+      <c r="C176" s="23" t="n"/>
+      <c r="D176" s="23" t="n"/>
+      <c r="E176" s="23" t="n"/>
+      <c r="F176" s="23" t="n"/>
+    </row>
+    <row r="177" ht="14" customHeight="1">
+      <c r="A177" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B160" s="36" t="n"/>
-      <c r="C160" s="36" t="n"/>
-      <c r="D160" s="36" t="n"/>
-      <c r="E160" s="36" t="n"/>
-      <c r="F160" s="36" t="n"/>
-    </row>
-    <row r="161" ht="48" customHeight="1">
-      <c r="A161" s="42" t="inlineStr">
+      <c r="B177" s="36" t="n"/>
+      <c r="C177" s="36" t="n"/>
+      <c r="D177" s="36" t="n"/>
+      <c r="E177" s="36" t="n"/>
+      <c r="F177" s="36" t="n"/>
+    </row>
+    <row r="178" ht="48" customHeight="1">
+      <c r="A178" s="45" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 그린클레이, 물, 에센셜오일을 다 넣고
 2. 잘 섞어줍니다.</t>
         </is>
       </c>
-      <c r="B161" s="23" t="n"/>
-      <c r="C161" s="23" t="n"/>
-      <c r="D161" s="23" t="n"/>
-      <c r="E161" s="23" t="n"/>
-      <c r="F161" s="23" t="n"/>
-    </row>
-    <row r="162" ht="6" customHeight="1"/>
-    <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="24" t="inlineStr">
+      <c r="B178" s="23" t="n"/>
+      <c r="C178" s="23" t="n"/>
+      <c r="D178" s="23" t="n"/>
+      <c r="E178" s="23" t="n"/>
+      <c r="F178" s="23" t="n"/>
+    </row>
+    <row r="179" ht="6" customHeight="1"/>
+    <row r="180" ht="22" customHeight="1">
+      <c r="A180" s="24" t="inlineStr">
         <is>
           <t>레몬 손소독제(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B163" s="25" t="n"/>
-      <c r="C163" s="25" t="n"/>
-      <c r="D163" s="25" t="n"/>
-      <c r="E163" s="25" t="n"/>
-      <c r="F163" s="25" t="n"/>
-    </row>
-    <row r="164" ht="15" customHeight="1">
-      <c r="A164" s="26" t="inlineStr">
+      <c r="B180" s="25" t="n"/>
+      <c r="C180" s="25" t="n"/>
+      <c r="D180" s="25" t="n"/>
+      <c r="E180" s="25" t="n"/>
+      <c r="F180" s="25" t="n"/>
+    </row>
+    <row r="181" ht="15" customHeight="1">
+      <c r="A181" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B164" s="26" t="inlineStr">
+      <c r="B181" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C164" s="26" t="inlineStr">
+      <c r="C181" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D164" s="26" t="inlineStr">
+      <c r="D181" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E164" s="26" t="inlineStr">
+      <c r="E181" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F164" s="26" t="inlineStr">
+      <c r="F181" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="64" customHeight="1">
-      <c r="A165" s="27" t="inlineStr">
+    <row r="182" ht="64" customHeight="1">
+      <c r="A182" s="27" t="inlineStr">
         <is>
           <t>정제수</t>
         </is>
       </c>
-      <c r="B165" s="27" t="inlineStr">
+      <c r="B182" s="27" t="inlineStr">
         <is>
           <t>28g</t>
         </is>
       </c>
-      <c r="C165" s="28" t="inlineStr">
+      <c r="C182" s="28" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D165" s="40" t="inlineStr">
+      <c r="D182" s="43" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E165" s="27" t="inlineStr">
+      <c r="E182" s="27" t="inlineStr">
         <is>
           <t>5중 필터링 정제된 물.</t>
         </is>
       </c>
-      <c r="F165" s="27" t="inlineStr">
+      <c r="F182" s="27" t="inlineStr">
         <is>
           <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="48" customHeight="1">
-      <c r="A166" s="27" t="inlineStr">
+    <row r="183" ht="48" customHeight="1">
+      <c r="A183" s="27" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B166" s="27" t="inlineStr">
+      <c r="B183" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C166" s="28" t="inlineStr">
+      <c r="C183" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D166" s="31" t="inlineStr">
+      <c r="D183" s="31" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E166" s="27" t="inlineStr">
+      <c r="E183" s="27" t="inlineStr">
         <is>
           <t>보습제, 향이 오랫동안 머물 수 · 있도록 고착제 역할을 함.</t>
         </is>
       </c>
-      <c r="F166" s="27" t="inlineStr">
+      <c r="F183" s="27" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="32" customHeight="1">
-      <c r="A167" s="27" t="inlineStr">
+    <row r="184" ht="32" customHeight="1">
+      <c r="A184" s="27" t="inlineStr">
         <is>
           <t>아로마베이스95</t>
         </is>
       </c>
-      <c r="B167" s="27" t="inlineStr">
+      <c r="B184" s="27" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C167" s="28" t="inlineStr">
+      <c r="C184" s="28" t="inlineStr">
         <is>
           <t>66%</t>
         </is>
       </c>
-      <c r="D167" s="32" t="inlineStr">
+      <c r="D184" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E167" s="27" t="inlineStr">
+      <c r="E184" s="27" t="inlineStr">
         <is>
           <t>에센셜오일 분산, 방향용으로 사용시 · 공기정화, 소독효과</t>
         </is>
       </c>
-      <c r="F167" s="27" t="inlineStr">
+      <c r="F184" s="27" t="inlineStr">
         <is>
           <t>에탄올</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="48" customHeight="1">
-      <c r="A168" s="27" t="inlineStr">
+    <row r="185" ht="48" customHeight="1">
+      <c r="A185" s="27" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B168" s="27" t="inlineStr">
+      <c r="B185" s="27" t="inlineStr">
         <is>
           <t>15~20방울</t>
         </is>
       </c>
-      <c r="C168" s="28" t="inlineStr">
+      <c r="C185" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D168" s="32" t="inlineStr">
+      <c r="D185" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E168" s="27" t="inlineStr">
+      <c r="E185" s="27" t="inlineStr">
         <is>
           <t>레몬껍질에서 추출한 100%천연오일. · 상큼한 향.</t>
         </is>
       </c>
-      <c r="F168" s="27" t="inlineStr">
+      <c r="F185" s="27" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 편백 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="14" customHeight="1">
-      <c r="A169" s="33" t="inlineStr">
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 28 · 보습 5 · 향 67</t>
         </is>
       </c>
-      <c r="B169" s="34" t="n"/>
-      <c r="C169" s="34" t="n"/>
-      <c r="D169" s="34" t="n"/>
-      <c r="E169" s="34" t="n"/>
-      <c r="F169" s="34" t="n"/>
-    </row>
-    <row r="170" ht="14" customHeight="1">
-      <c r="A170" s="35" t="inlineStr">
+      <c r="B186" s="34" t="n"/>
+      <c r="C186" s="34" t="n"/>
+      <c r="D186" s="34" t="n"/>
+      <c r="E186" s="34" t="n"/>
+      <c r="F186" s="34" t="n"/>
+    </row>
+    <row r="187" ht="14" customHeight="1">
+      <c r="A187" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B170" s="36" t="n"/>
-      <c r="C170" s="36" t="n"/>
-      <c r="D170" s="36" t="n"/>
-      <c r="E170" s="36" t="n"/>
-      <c r="F170" s="36" t="n"/>
-    </row>
-    <row r="171" ht="304" customHeight="1">
-      <c r="A171" s="37" t="inlineStr">
+      <c r="B187" s="36" t="n"/>
+      <c r="C187" s="36" t="n"/>
+      <c r="D187" s="36" t="n"/>
+      <c r="E187" s="36" t="n"/>
+      <c r="F187" s="36" t="n"/>
+    </row>
+    <row r="188" ht="304" customHeight="1">
+      <c r="A188" s="37" t="inlineStr">
         <is>
           <t>2009년 젤타입 손소독제 만들기를 위해
 하이셀을 이용해 만든 젤타입 손소독제입니다.
@@ -5941,20 +6147,20 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="14" customHeight="1">
-      <c r="A172" s="35" t="inlineStr">
+    <row r="189" ht="14" customHeight="1">
+      <c r="A189" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B172" s="36" t="n"/>
-      <c r="C172" s="36" t="n"/>
-      <c r="D172" s="36" t="n"/>
-      <c r="E172" s="36" t="n"/>
-      <c r="F172" s="36" t="n"/>
-    </row>
-    <row r="173" ht="288" customHeight="1">
-      <c r="A173" s="37" t="inlineStr">
+      <c r="B189" s="36" t="n"/>
+      <c r="C189" s="36" t="n"/>
+      <c r="D189" s="36" t="n"/>
+      <c r="E189" s="36" t="n"/>
+      <c r="F189" s="36" t="n"/>
+    </row>
+    <row r="190" ht="288" customHeight="1">
+      <c r="A190" s="37" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 [하이셀 계량하기]
@@ -5977,259 +6183,279 @@
         </is>
       </c>
     </row>
-    <row r="174" ht="409" customHeight="1"/>
-    <row r="175" ht="238.4999999999999" customHeight="1"/>
-    <row r="176" ht="6" customHeight="1"/>
-    <row r="177" ht="22" customHeight="1">
-      <c r="A177" s="24" t="inlineStr">
+    <row r="191" ht="14" customHeight="1">
+      <c r="A191" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B191" s="39" t="n"/>
+      <c r="C191" s="39" t="n"/>
+      <c r="D191" s="39" t="n"/>
+      <c r="E191" s="39" t="n"/>
+      <c r="F191" s="39" t="n"/>
+    </row>
+    <row r="192" ht="30" customHeight="1">
+      <c r="A192" s="40" t="inlineStr">
+        <is>
+          <t>· 베이스: 수상 28%(정제수 28%)가 제형의 뼈대·수분 공급.
+· 마무리: 보습 5% · 향 67% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="409" customHeight="1"/>
+    <row r="194" ht="194.5" customHeight="1"/>
+    <row r="195" ht="6" customHeight="1"/>
+    <row r="196" ht="22" customHeight="1">
+      <c r="A196" s="24" t="inlineStr">
         <is>
           <t>안티 셀룰라이트 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B177" s="25" t="n"/>
-      <c r="C177" s="25" t="n"/>
-      <c r="D177" s="25" t="n"/>
-      <c r="E177" s="25" t="n"/>
-      <c r="F177" s="25" t="n"/>
-    </row>
-    <row r="178" ht="15" customHeight="1">
-      <c r="A178" s="26" t="inlineStr">
+      <c r="B196" s="25" t="n"/>
+      <c r="C196" s="25" t="n"/>
+      <c r="D196" s="25" t="n"/>
+      <c r="E196" s="25" t="n"/>
+      <c r="F196" s="25" t="n"/>
+    </row>
+    <row r="197" ht="15" customHeight="1">
+      <c r="A197" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B178" s="26" t="inlineStr">
+      <c r="B197" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C178" s="26" t="inlineStr">
+      <c r="C197" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D178" s="26" t="inlineStr">
+      <c r="D197" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E178" s="26" t="inlineStr">
+      <c r="E197" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F178" s="26" t="inlineStr">
+      <c r="F197" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="48" customHeight="1">
-      <c r="A179" s="38" t="inlineStr">
+    <row r="198" ht="48" customHeight="1">
+      <c r="A198" s="41" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B179" s="38" t="inlineStr">
+      <c r="B198" s="41" t="inlineStr">
         <is>
           <t>92.17%</t>
         </is>
       </c>
-      <c r="C179" s="39" t="inlineStr"/>
-      <c r="D179" s="40" t="inlineStr">
+      <c r="C198" s="42" t="inlineStr"/>
+      <c r="D198" s="43" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E179" s="38" t="inlineStr">
+      <c r="E198" s="41" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="F179" s="38" t="inlineStr">
+      <c r="F198" s="41" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="38" t="inlineStr">
+    <row r="199" ht="16" customHeight="1">
+      <c r="A199" s="41" t="inlineStr">
         <is>
           <t>하이셀</t>
         </is>
       </c>
-      <c r="B180" s="38" t="inlineStr">
+      <c r="B199" s="41" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C180" s="39" t="inlineStr"/>
-      <c r="D180" s="30" t="inlineStr">
+      <c r="C199" s="42" t="inlineStr"/>
+      <c r="D199" s="30" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E180" s="38" t="inlineStr">
+      <c r="E199" s="41" t="inlineStr">
         <is>
           <t>점증제총량의 1%이하</t>
         </is>
       </c>
-      <c r="F180" s="38" t="inlineStr"/>
-    </row>
-    <row r="181" ht="64" customHeight="1">
-      <c r="A181" s="38" t="inlineStr">
+      <c r="F199" s="41" t="inlineStr"/>
+    </row>
+    <row r="200" ht="64" customHeight="1">
+      <c r="A200" s="41" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B181" s="38" t="inlineStr">
+      <c r="B200" s="41" t="inlineStr">
         <is>
           <t>4.61%</t>
         </is>
       </c>
-      <c r="C181" s="39" t="inlineStr"/>
-      <c r="D181" s="31" t="inlineStr">
+      <c r="C200" s="42" t="inlineStr"/>
+      <c r="D200" s="31" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E181" s="38" t="inlineStr">
+      <c r="E200" s="41" t="inlineStr">
         <is>
           <t>보습, 피부타입에따라 줄이거나 늘려서 첨가 · ※3g이상 들어가면 스프레이보다는 펌핑용기에 담아사용하세요.</t>
         </is>
       </c>
-      <c r="F181" s="38" t="inlineStr">
+      <c r="F200" s="41" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="32" customHeight="1">
-      <c r="A182" s="38" t="inlineStr">
+    <row r="201" ht="32" customHeight="1">
+      <c r="A201" s="41" t="inlineStr">
         <is>
           <t>그레이프프룻EO</t>
         </is>
       </c>
-      <c r="B182" s="38" t="inlineStr">
+      <c r="B201" s="41" t="inlineStr">
         <is>
           <t>0.92%</t>
         </is>
       </c>
-      <c r="C182" s="39" t="inlineStr"/>
-      <c r="D182" s="32" t="inlineStr">
+      <c r="C201" s="42" t="inlineStr"/>
+      <c r="D201" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E182" s="38" t="inlineStr">
+      <c r="E201" s="41" t="inlineStr">
         <is>
           <t>자몽 에센셜오일, 상쾌·수렴</t>
         </is>
       </c>
-      <c r="F182" s="38" t="inlineStr">
+      <c r="F201" s="41" t="inlineStr">
         <is>
           <t>오렌지, 레몬에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="32" customHeight="1">
-      <c r="A183" s="38" t="inlineStr">
+    <row r="202" ht="32" customHeight="1">
+      <c r="A202" s="41" t="inlineStr">
         <is>
           <t>페퍼민트오일</t>
         </is>
       </c>
-      <c r="B183" s="38" t="inlineStr">
+      <c r="B202" s="41" t="inlineStr">
         <is>
           <t>0.23%</t>
         </is>
       </c>
-      <c r="C183" s="39" t="inlineStr"/>
-      <c r="D183" s="45" t="inlineStr">
+      <c r="C202" s="42" t="inlineStr"/>
+      <c r="D202" s="48" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E183" s="38" t="inlineStr">
+      <c r="E202" s="41" t="inlineStr">
         <is>
           <t>허브의 고농축오일 · 시원, 커피와 시너지효과</t>
         </is>
       </c>
-      <c r="F183" s="38" t="inlineStr">
+      <c r="F202" s="41" t="inlineStr">
         <is>
           <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="32" customHeight="1">
-      <c r="A184" s="38" t="inlineStr">
+    <row r="203" ht="32" customHeight="1">
+      <c r="A203" s="41" t="inlineStr">
         <is>
           <t>주니퍼베리EO</t>
         </is>
       </c>
-      <c r="B184" s="38" t="inlineStr">
+      <c r="B203" s="41" t="inlineStr">
         <is>
           <t>0.69%</t>
         </is>
       </c>
-      <c r="C184" s="39" t="inlineStr"/>
-      <c r="D184" s="32" t="inlineStr">
+      <c r="C203" s="42" t="inlineStr"/>
+      <c r="D203" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E184" s="38" t="inlineStr">
+      <c r="E203" s="41" t="inlineStr">
         <is>
           <t>주니퍼베리 에센셜오일, 수렴·정화</t>
         </is>
       </c>
-      <c r="F184" s="38" t="inlineStr">
+      <c r="F203" s="41" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="64" customHeight="1">
-      <c r="A185" s="38" t="inlineStr">
+    <row r="204" ht="64" customHeight="1">
+      <c r="A204" s="41" t="inlineStr">
         <is>
           <t>로즈제라늄EO</t>
         </is>
       </c>
-      <c r="B185" s="38" t="inlineStr">
+      <c r="B204" s="41" t="inlineStr">
         <is>
           <t>0.46%</t>
         </is>
       </c>
-      <c r="C185" s="39" t="inlineStr"/>
-      <c r="D185" s="32" t="inlineStr">
+      <c r="C204" s="42" t="inlineStr"/>
+      <c r="D204" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E185" s="38" t="inlineStr">
+      <c r="E204" s="41" t="inlineStr">
         <is>
           <t>균형의 오일, 피지조절, 장미향이 나는 제라늄 꽃.잎을 수증기증류법으로 추출. *일랑일랑오일에서 변경(15.5.9)</t>
         </is>
       </c>
-      <c r="F185" s="38" t="inlineStr">
+      <c r="F204" s="41" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈우드 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="14" customHeight="1">
-      <c r="A186" s="35" t="inlineStr">
+    <row r="205" ht="14" customHeight="1">
+      <c r="A205" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B186" s="36" t="n"/>
-      <c r="C186" s="36" t="n"/>
-      <c r="D186" s="36" t="n"/>
-      <c r="E186" s="36" t="n"/>
-      <c r="F186" s="36" t="n"/>
-    </row>
-    <row r="187" ht="96" customHeight="1">
-      <c r="A187" s="42" t="inlineStr">
+      <c r="B205" s="36" t="n"/>
+      <c r="C205" s="36" t="n"/>
+      <c r="D205" s="36" t="n"/>
+      <c r="E205" s="36" t="n"/>
+      <c r="F205" s="36" t="n"/>
+    </row>
+    <row r="206" ht="96" customHeight="1">
+      <c r="A206" s="45" t="inlineStr">
         <is>
           <t>*끈적임없이 흡수되는 다이어트젤
 다이어트에 좋은 에센셜오일 6종: 그레이프프룻, 팬넬, 쥬니퍼베리, 싸이프러스, 레몬, 제라늄
@@ -6239,26 +6465,26 @@
 제라늄 - 호로몬 균형, 피지균형</t>
         </is>
       </c>
-      <c r="B187" s="23" t="n"/>
-      <c r="C187" s="23" t="n"/>
-      <c r="D187" s="23" t="n"/>
-      <c r="E187" s="23" t="n"/>
-      <c r="F187" s="23" t="n"/>
-    </row>
-    <row r="188" ht="14" customHeight="1">
-      <c r="A188" s="35" t="inlineStr">
+      <c r="B206" s="23" t="n"/>
+      <c r="C206" s="23" t="n"/>
+      <c r="D206" s="23" t="n"/>
+      <c r="E206" s="23" t="n"/>
+      <c r="F206" s="23" t="n"/>
+    </row>
+    <row r="207" ht="14" customHeight="1">
+      <c r="A207" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B188" s="36" t="n"/>
-      <c r="C188" s="36" t="n"/>
-      <c r="D188" s="36" t="n"/>
-      <c r="E188" s="36" t="n"/>
-      <c r="F188" s="36" t="n"/>
-    </row>
-    <row r="189" ht="96" customHeight="1">
-      <c r="A189" s="42" t="inlineStr">
+      <c r="B207" s="36" t="n"/>
+      <c r="C207" s="36" t="n"/>
+      <c r="D207" s="36" t="n"/>
+      <c r="E207" s="36" t="n"/>
+      <c r="F207" s="36" t="n"/>
+    </row>
+    <row r="208" ht="96" customHeight="1">
+      <c r="A208" s="45" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 로즈워터를 계량한다.
@@ -6268,367 +6494,367 @@
 6~7. 손으로 저어서 마무리해주면 끝!</t>
         </is>
       </c>
-      <c r="B189" s="23" t="n"/>
-      <c r="C189" s="23" t="n"/>
-      <c r="D189" s="23" t="n"/>
-      <c r="E189" s="23" t="n"/>
-      <c r="F189" s="23" t="n"/>
-    </row>
-    <row r="190" ht="6" customHeight="1"/>
-    <row r="191" ht="22" customHeight="1">
-      <c r="A191" s="24" t="inlineStr">
+      <c r="B208" s="23" t="n"/>
+      <c r="C208" s="23" t="n"/>
+      <c r="D208" s="23" t="n"/>
+      <c r="E208" s="23" t="n"/>
+      <c r="F208" s="23" t="n"/>
+    </row>
+    <row r="209" ht="6" customHeight="1"/>
+    <row r="210" ht="22" customHeight="1">
+      <c r="A210" s="24" t="inlineStr">
         <is>
           <t>뱀독 볼륨 에센스(젤)    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B191" s="25" t="n"/>
-      <c r="C191" s="25" t="n"/>
-      <c r="D191" s="25" t="n"/>
-      <c r="E191" s="25" t="n"/>
-      <c r="F191" s="25" t="n"/>
-    </row>
-    <row r="192" ht="15" customHeight="1">
-      <c r="A192" s="26" t="inlineStr">
+      <c r="B210" s="25" t="n"/>
+      <c r="C210" s="25" t="n"/>
+      <c r="D210" s="25" t="n"/>
+      <c r="E210" s="25" t="n"/>
+      <c r="F210" s="25" t="n"/>
+    </row>
+    <row r="211" ht="15" customHeight="1">
+      <c r="A211" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B192" s="26" t="inlineStr">
+      <c r="B211" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C192" s="26" t="inlineStr">
+      <c r="C211" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D192" s="26" t="inlineStr">
+      <c r="D211" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E192" s="26" t="inlineStr">
+      <c r="E211" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F192" s="26" t="inlineStr">
+      <c r="F211" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="48" customHeight="1">
-      <c r="A193" s="27" t="inlineStr">
+    <row r="212" ht="48" customHeight="1">
+      <c r="A212" s="27" t="inlineStr">
         <is>
           <t>(제주산) / 비정제동백오일</t>
         </is>
       </c>
-      <c r="B193" s="27" t="inlineStr">
+      <c r="B212" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C193" s="28" t="inlineStr">
+      <c r="C212" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D193" s="45" t="inlineStr">
+      <c r="D212" s="48" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E193" s="27" t="inlineStr">
+      <c r="E212" s="27" t="inlineStr">
         <is>
           <t>올레인산 풍부 고보습 · 청정 섬 국내 제주산 야생동백씨 압착.</t>
         </is>
       </c>
-      <c r="F193" s="27" t="inlineStr">
+      <c r="F212" s="27" t="inlineStr">
         <is>
           <t>아르간, 로즈힙, 마카다미아넛오일 등</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="32" customHeight="1">
-      <c r="A194" s="27" t="inlineStr">
+    <row r="213" ht="32" customHeight="1">
+      <c r="A213" s="27" t="inlineStr">
         <is>
           <t>올리브리퀴드</t>
         </is>
       </c>
-      <c r="B194" s="27" t="inlineStr">
+      <c r="B213" s="27" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C194" s="28" t="inlineStr">
+      <c r="C213" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D194" s="43" t="inlineStr">
+      <c r="D213" s="46" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E194" s="27" t="inlineStr">
+      <c r="E213" s="27" t="inlineStr">
         <is>
           <t>가용화제, 물에 오일이 분산되도록 도와줌</t>
         </is>
       </c>
-      <c r="F194" s="27" t="inlineStr">
+      <c r="F213" s="27" t="inlineStr">
         <is>
           <t>솔루벌라이저(Polysorbate 80)동량</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="64" customHeight="1">
-      <c r="A195" s="27" t="inlineStr">
+    <row r="214" ht="64" customHeight="1">
+      <c r="A214" s="27" t="inlineStr">
         <is>
           <t>오가닉7솔루션</t>
         </is>
       </c>
-      <c r="B195" s="27" t="inlineStr">
+      <c r="B214" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C195" s="28" t="inlineStr">
+      <c r="C214" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D195" s="29" t="inlineStr">
+      <c r="D214" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E195" s="27" t="inlineStr">
+      <c r="E214" s="27" t="inlineStr">
         <is>
           <t>비타민류가 다량 함유되어있는 · 유기농 야채(당근, 토마토,브로컬리,현미, 양배추,샐러리, 현미)를 저온 추출.</t>
         </is>
       </c>
-      <c r="F195" s="27" t="inlineStr">
+      <c r="F214" s="27" t="inlineStr">
         <is>
           <t>콜라겐, 석류,토마토</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="144" customHeight="1">
-      <c r="A196" s="27" t="inlineStr">
+    <row r="215" ht="144" customHeight="1">
+      <c r="A215" s="27" t="inlineStr">
         <is>
           <t>씨네이크(뱀독) / 펩타이드</t>
         </is>
       </c>
-      <c r="B196" s="27" t="inlineStr">
+      <c r="B215" s="27" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C196" s="28" t="inlineStr">
+      <c r="C215" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D196" s="29" t="inlineStr">
+      <c r="D215" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E196" s="27" t="inlineStr">
+      <c r="E215" s="27" t="inlineStr">
         <is>
           <t>독사에게 물리면 피부,근육이 마비되는 점을 착안해 만든 단백질. 독사의 독을 모방하여 만든 펩타이드. 2~4% 사용. · 임상시 아세틸헥사펩타이드보다 효과적. · 2006년 스위스 테크놀로지 어워드 바이오부분 수상, 유럽특허를 획득. · '바르는 보톡스' 등으로 인기</t>
         </is>
       </c>
-      <c r="F196" s="27" t="inlineStr"/>
-    </row>
-    <row r="197" ht="32" customHeight="1">
-      <c r="A197" s="27" t="inlineStr">
+      <c r="F215" s="27" t="inlineStr"/>
+    </row>
+    <row r="216" ht="32" customHeight="1">
+      <c r="A216" s="27" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B197" s="27" t="inlineStr">
+      <c r="B216" s="27" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C197" s="28" t="inlineStr">
+      <c r="C216" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D197" s="29" t="inlineStr">
+      <c r="D216" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E197" s="27" t="inlineStr">
+      <c r="E216" s="27" t="inlineStr">
         <is>
           <t>녹황색채소에 들어있는 비타민B3. · 식약처 인증 미백원료</t>
         </is>
       </c>
-      <c r="F197" s="27" t="inlineStr">
+      <c r="F216" s="27" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="198" ht="80" customHeight="1">
-      <c r="A198" s="27" t="inlineStr">
+    <row r="217" ht="80" customHeight="1">
+      <c r="A217" s="27" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B198" s="27" t="inlineStr">
+      <c r="B217" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C198" s="28" t="inlineStr">
+      <c r="C217" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D198" s="41" t="inlineStr">
+      <c r="D217" s="44" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E198" s="27" t="inlineStr">
+      <c r="E217" s="27" t="inlineStr">
         <is>
           <t>미생물 번식 억제제.</t>
         </is>
       </c>
-      <c r="F198" s="27" t="inlineStr">
+      <c r="F217" s="27" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="32" customHeight="1">
-      <c r="A199" s="27" t="inlineStr">
+    <row r="218" ht="32" customHeight="1">
+      <c r="A218" s="27" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
-      <c r="B199" s="27" t="inlineStr">
+      <c r="B218" s="27" t="inlineStr">
         <is>
           <t>0~6g</t>
         </is>
       </c>
-      <c r="C199" s="28" t="inlineStr">
+      <c r="C218" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D199" s="29" t="inlineStr">
+      <c r="D218" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E199" s="27" t="inlineStr">
+      <c r="E218" s="27" t="inlineStr">
         <is>
           <t>보습제. 원하시면 넣어주세요.</t>
         </is>
       </c>
-      <c r="F199" s="27" t="inlineStr">
+      <c r="F218" s="27" t="inlineStr">
         <is>
           <t>리피듀어 · 식물성글리세린</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="64" customHeight="1">
-      <c r="A200" s="27" t="inlineStr">
+    <row r="219" ht="64" customHeight="1">
+      <c r="A219" s="27" t="inlineStr">
         <is>
           <t>로즈우드에센셜오일</t>
         </is>
       </c>
-      <c r="B200" s="27" t="inlineStr">
+      <c r="B219" s="27" t="inlineStr">
         <is>
           <t>4~8방울</t>
         </is>
       </c>
-      <c r="C200" s="28" t="inlineStr">
+      <c r="C219" s="28" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D200" s="32" t="inlineStr">
+      <c r="D219" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E200" s="27" t="inlineStr">
+      <c r="E219" s="27" t="inlineStr">
         <is>
           <t>아로마테라피 · 장미향이 나는 제라늄, 모든 피부</t>
         </is>
       </c>
-      <c r="F200" s="27" t="inlineStr">
+      <c r="F219" s="27" t="inlineStr">
         <is>
           <t>로즈3%, 로즈엡솔루트, 로즈제라늄 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="80" customHeight="1">
-      <c r="A201" s="27" t="inlineStr">
+    <row r="220" ht="80" customHeight="1">
+      <c r="A220" s="27" t="inlineStr">
         <is>
           <t>알로에모이스트</t>
         </is>
       </c>
-      <c r="B201" s="27" t="inlineStr">
+      <c r="B220" s="27" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C201" s="28" t="inlineStr">
+      <c r="C220" s="28" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D201" s="29" t="inlineStr">
+      <c r="D220" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E201" s="27" t="inlineStr">
+      <c r="E220" s="27" t="inlineStr">
         <is>
           <t>자체점증, 가용화안정, 수분공급 , 진정</t>
         </is>
       </c>
-      <c r="F201" s="27" t="inlineStr">
+      <c r="F220" s="27" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="14" customHeight="1">
-      <c r="A202" s="33" t="inlineStr">
+    <row r="221" ht="14" customHeight="1">
+      <c r="A221" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 4 · 유화 3 · 활성 92 · 향 0 · 방부 1</t>
         </is>
       </c>
-      <c r="B202" s="34" t="n"/>
-      <c r="C202" s="34" t="n"/>
-      <c r="D202" s="34" t="n"/>
-      <c r="E202" s="34" t="n"/>
-      <c r="F202" s="34" t="n"/>
-    </row>
-    <row r="203" ht="14" customHeight="1">
-      <c r="A203" s="35" t="inlineStr">
+      <c r="B221" s="34" t="n"/>
+      <c r="C221" s="34" t="n"/>
+      <c r="D221" s="34" t="n"/>
+      <c r="E221" s="34" t="n"/>
+      <c r="F221" s="34" t="n"/>
+    </row>
+    <row r="222" ht="14" customHeight="1">
+      <c r="A222" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B203" s="36" t="n"/>
-      <c r="C203" s="36" t="n"/>
-      <c r="D203" s="36" t="n"/>
-      <c r="E203" s="36" t="n"/>
-      <c r="F203" s="36" t="n"/>
-    </row>
-    <row r="204" ht="384" customHeight="1">
-      <c r="A204" s="37" t="inlineStr">
+      <c r="B222" s="36" t="n"/>
+      <c r="C222" s="36" t="n"/>
+      <c r="D222" s="36" t="n"/>
+      <c r="E222" s="36" t="n"/>
+      <c r="F222" s="36" t="n"/>
+    </row>
+    <row r="223" ht="384" customHeight="1">
+      <c r="A223" s="37" t="inlineStr">
         <is>
           <t>뱀독 볼륨에센스(젤)은
 바르는 보톡스인 씨네이크펩타이드 최대함량인 4%와
@@ -6657,8 +6883,8 @@
         </is>
       </c>
     </row>
-    <row r="205" ht="208" customHeight="1">
-      <c r="A205" s="37" t="inlineStr">
+    <row r="224" ht="208" customHeight="1">
+      <c r="A224" s="37" t="inlineStr">
         <is>
           <t>살모사의 뱀독에서 추출한 단백질은
 유방암 세포의 성장을 70%나 억제하는 것으로 밝혀지기도 했습니다.
@@ -6676,20 +6902,20 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="14" customHeight="1">
-      <c r="A206" s="35" t="inlineStr">
+    <row r="225" ht="14" customHeight="1">
+      <c r="A225" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B206" s="36" t="n"/>
-      <c r="C206" s="36" t="n"/>
-      <c r="D206" s="36" t="n"/>
-      <c r="E206" s="36" t="n"/>
-      <c r="F206" s="36" t="n"/>
-    </row>
-    <row r="207" ht="80" customHeight="1">
-      <c r="A207" s="37" t="inlineStr">
+      <c r="B225" s="36" t="n"/>
+      <c r="C225" s="36" t="n"/>
+      <c r="D225" s="36" t="n"/>
+      <c r="E225" s="36" t="n"/>
+      <c r="F225" s="36" t="n"/>
+    </row>
+    <row r="226" ht="80" customHeight="1">
+      <c r="A226" s="37" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.동백오일과 올리브리퀴드를 먼저 섞어주세요.
@@ -6698,137 +6924,160 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="6" customHeight="1"/>
-    <row r="209" ht="22" customHeight="1">
-      <c r="A209" s="24" t="inlineStr">
+    <row r="227" ht="14" customHeight="1">
+      <c r="A227" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B227" s="39" t="n"/>
+      <c r="C227" s="39" t="n"/>
+      <c r="D227" s="39" t="n"/>
+      <c r="E227" s="39" t="n"/>
+      <c r="F227" s="39" t="n"/>
+    </row>
+    <row r="228" ht="90" customHeight="1">
+      <c r="A228" s="40" t="inlineStr">
+        <is>
+          <t>· 베이스: 유상 중심, 주 오일 (제주산) / 비정제동백오일(4%)로 보습막·발림 설계.
+· 기능: 활성 합 92%(알로에모이스트 77%, 오가닉7솔루션 5%, 씨네이크(뱀독) / 펩타이드 4%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 방부 1% 로 안정·사용감 보완.
+· 포인트: 유상 대비 유화제가 넉넉 → 분리 적고 안정 중시(묵직할 수).
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="6" customHeight="1"/>
+    <row r="230" ht="22" customHeight="1">
+      <c r="A230" s="24" t="inlineStr">
         <is>
           <t>아임레알 제주화산송이팩    [(트러블, 모공이 넓은 피부) / 1회분량]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B209" s="25" t="n"/>
-      <c r="C209" s="25" t="n"/>
-      <c r="D209" s="25" t="n"/>
-      <c r="E209" s="25" t="n"/>
-      <c r="F209" s="25" t="n"/>
-    </row>
-    <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="26" t="inlineStr">
+      <c r="B230" s="25" t="n"/>
+      <c r="C230" s="25" t="n"/>
+      <c r="D230" s="25" t="n"/>
+      <c r="E230" s="25" t="n"/>
+      <c r="F230" s="25" t="n"/>
+    </row>
+    <row r="231" ht="15" customHeight="1">
+      <c r="A231" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B210" s="26" t="inlineStr">
+      <c r="B231" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C210" s="26" t="inlineStr">
+      <c r="C231" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D210" s="26" t="inlineStr">
+      <c r="D231" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E210" s="26" t="inlineStr">
+      <c r="E231" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F210" s="26" t="inlineStr">
+      <c r="F231" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="211" ht="80" customHeight="1">
-      <c r="A211" s="38" t="inlineStr">
+    <row r="232" ht="80" customHeight="1">
+      <c r="A232" s="41" t="inlineStr">
         <is>
           <t>제주 화산송이분말</t>
         </is>
       </c>
-      <c r="B211" s="38" t="inlineStr">
+      <c r="B232" s="41" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C211" s="39" t="inlineStr">
+      <c r="C232" s="42" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
       </c>
-      <c r="D211" s="44" t="inlineStr">
+      <c r="D232" s="47" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E211" s="38" t="inlineStr">
+      <c r="E232" s="41" t="inlineStr">
         <is>
           <t>섭씨 2000도의 화산작용이 만든 기능성 미네럴, 제주 화산석 송이 · (먹는 '송이(버섯)' 아니죠^^) · 화산송이 7 : 카오링클레이3</t>
         </is>
       </c>
-      <c r="F211" s="38" t="inlineStr"/>
-    </row>
-    <row r="212" ht="64" customHeight="1">
-      <c r="A212" s="38" t="inlineStr">
+      <c r="F232" s="41" t="inlineStr"/>
+    </row>
+    <row r="233" ht="64" customHeight="1">
+      <c r="A233" s="41" t="inlineStr">
         <is>
           <t>위치헤이즐워터 / (편백워터)</t>
         </is>
       </c>
-      <c r="B212" s="38" t="inlineStr">
+      <c r="B233" s="41" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C212" s="39" t="inlineStr">
+      <c r="C233" s="42" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D212" s="40" t="inlineStr">
+      <c r="D233" s="43" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E212" s="38" t="inlineStr">
+      <c r="E233" s="41" t="inlineStr">
         <is>
           <t>제주화산송이 양의 반이하의 양, 정제수도 가능, 위치헤즐은 수렴, 트러블, 모공 넓은 피부적합</t>
         </is>
       </c>
-      <c r="F212" s="38" t="inlineStr">
+      <c r="F233" s="41" t="inlineStr">
         <is>
           <t>정수기 물, 수돗물^^, 녹차우린 물. 어성초우린 물</t>
         </is>
       </c>
     </row>
-    <row r="213" ht="14" customHeight="1">
-      <c r="A213" s="33" t="inlineStr">
+    <row r="234" ht="14" customHeight="1">
+      <c r="A234" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 23 · 색소 77</t>
         </is>
       </c>
-      <c r="B213" s="34" t="n"/>
-      <c r="C213" s="34" t="n"/>
-      <c r="D213" s="34" t="n"/>
-      <c r="E213" s="34" t="n"/>
-      <c r="F213" s="34" t="n"/>
-    </row>
-    <row r="214" ht="14" customHeight="1">
-      <c r="A214" s="35" t="inlineStr">
+      <c r="B234" s="34" t="n"/>
+      <c r="C234" s="34" t="n"/>
+      <c r="D234" s="34" t="n"/>
+      <c r="E234" s="34" t="n"/>
+      <c r="F234" s="34" t="n"/>
+    </row>
+    <row r="235" ht="14" customHeight="1">
+      <c r="A235" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B214" s="36" t="n"/>
-      <c r="C214" s="36" t="n"/>
-      <c r="D214" s="36" t="n"/>
-      <c r="E214" s="36" t="n"/>
-      <c r="F214" s="36" t="n"/>
-    </row>
-    <row r="215" ht="368" customHeight="1">
-      <c r="A215" s="42" t="inlineStr">
+      <c r="B235" s="36" t="n"/>
+      <c r="C235" s="36" t="n"/>
+      <c r="D235" s="36" t="n"/>
+      <c r="E235" s="36" t="n"/>
+      <c r="F235" s="36" t="n"/>
+    </row>
+    <row r="236" ht="368" customHeight="1">
+      <c r="A236" s="45" t="inlineStr">
         <is>
           <t>제주화산송이,
 먹는 송이가 아니죠^^
@@ -6853,26 +7102,26 @@
 초간단 레알 화산송이팩으로 피부 피지와 노폐물을 관리해보세요.</t>
         </is>
       </c>
-      <c r="B215" s="23" t="n"/>
-      <c r="C215" s="23" t="n"/>
-      <c r="D215" s="23" t="n"/>
-      <c r="E215" s="23" t="n"/>
-      <c r="F215" s="23" t="n"/>
-    </row>
-    <row r="216" ht="14" customHeight="1">
-      <c r="A216" s="35" t="inlineStr">
+      <c r="B236" s="23" t="n"/>
+      <c r="C236" s="23" t="n"/>
+      <c r="D236" s="23" t="n"/>
+      <c r="E236" s="23" t="n"/>
+      <c r="F236" s="23" t="n"/>
+    </row>
+    <row r="237" ht="14" customHeight="1">
+      <c r="A237" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B216" s="36" t="n"/>
-      <c r="C216" s="36" t="n"/>
-      <c r="D216" s="36" t="n"/>
-      <c r="E216" s="36" t="n"/>
-      <c r="F216" s="36" t="n"/>
-    </row>
-    <row r="217" ht="288" customHeight="1">
-      <c r="A217" s="42" t="inlineStr">
+      <c r="B237" s="36" t="n"/>
+      <c r="C237" s="36" t="n"/>
+      <c r="D237" s="36" t="n"/>
+      <c r="E237" s="36" t="n"/>
+      <c r="F237" s="36" t="n"/>
+    </row>
+    <row r="238" ht="288" customHeight="1">
+      <c r="A238" s="45" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1. 제주화산송이를 두스푼(약10g)계량하시고
@@ -6892,367 +7141,386 @@
 8.팩을 갤때 사용하셨던 플로럴워터로 피부결을 정돈하세요.</t>
         </is>
       </c>
-      <c r="B217" s="23" t="n"/>
-      <c r="C217" s="23" t="n"/>
-      <c r="D217" s="23" t="n"/>
-      <c r="E217" s="23" t="n"/>
-      <c r="F217" s="23" t="n"/>
-    </row>
-    <row r="218" ht="6" customHeight="1"/>
-    <row r="219" ht="22" customHeight="1">
-      <c r="A219" s="24" t="inlineStr">
+      <c r="B238" s="23" t="n"/>
+      <c r="C238" s="23" t="n"/>
+      <c r="D238" s="23" t="n"/>
+      <c r="E238" s="23" t="n"/>
+      <c r="F238" s="23" t="n"/>
+    </row>
+    <row r="239" ht="14" customHeight="1">
+      <c r="A239" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B239" s="39" t="n"/>
+      <c r="C239" s="39" t="n"/>
+      <c r="D239" s="39" t="n"/>
+      <c r="E239" s="39" t="n"/>
+      <c r="F239" s="39" t="n"/>
+    </row>
+    <row r="240" ht="28" customHeight="1">
+      <c r="A240" s="40" t="inlineStr">
+        <is>
+          <t>· 베이스: 수상 23%(위치헤이즐워터 / (편백워터) 23%)가 제형의 뼈대·수분 공급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="6" customHeight="1"/>
+    <row r="242" ht="22" customHeight="1">
+      <c r="A242" s="24" t="inlineStr">
         <is>
           <t>TX 토닝 젤    ↗ 원본</t>
         </is>
       </c>
-      <c r="B219" s="25" t="n"/>
-      <c r="C219" s="25" t="n"/>
-      <c r="D219" s="25" t="n"/>
-      <c r="E219" s="25" t="n"/>
-      <c r="F219" s="25" t="n"/>
-    </row>
-    <row r="220" ht="15" customHeight="1">
-      <c r="A220" s="26" t="inlineStr">
+      <c r="B242" s="25" t="n"/>
+      <c r="C242" s="25" t="n"/>
+      <c r="D242" s="25" t="n"/>
+      <c r="E242" s="25" t="n"/>
+      <c r="F242" s="25" t="n"/>
+    </row>
+    <row r="243" ht="15" customHeight="1">
+      <c r="A243" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B220" s="26" t="inlineStr">
+      <c r="B243" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C220" s="26" t="inlineStr">
+      <c r="C243" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D220" s="26" t="inlineStr">
+      <c r="D243" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E220" s="26" t="inlineStr">
+      <c r="E243" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F220" s="26" t="inlineStr">
+      <c r="F243" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="32" customHeight="1">
-      <c r="A221" s="27" t="inlineStr">
+    <row r="244" ht="32" customHeight="1">
+      <c r="A244" s="27" t="inlineStr">
         <is>
           <t>로즈플라워겔</t>
         </is>
       </c>
-      <c r="B221" s="27" t="inlineStr">
+      <c r="B244" s="27" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C221" s="28" t="inlineStr">
+      <c r="C244" s="28" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
       </c>
-      <c r="D221" s="29" t="inlineStr">
+      <c r="D244" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E221" s="27" t="inlineStr">
+      <c r="E244" s="27" t="inlineStr">
         <is>
           <t>불가리아 다마스크 장미수 함유 · 점증, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="F221" s="27" t="inlineStr">
+      <c r="F244" s="27" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="48" customHeight="1">
-      <c r="A222" s="27" t="inlineStr">
+    <row r="245" ht="48" customHeight="1">
+      <c r="A245" s="27" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B222" s="27" t="inlineStr">
+      <c r="B245" s="27" t="inlineStr">
         <is>
           <t>22g</t>
         </is>
       </c>
-      <c r="C222" s="28" t="inlineStr">
+      <c r="C245" s="28" t="inlineStr">
         <is>
           <t>22%</t>
         </is>
       </c>
-      <c r="D222" s="40" t="inlineStr">
+      <c r="D245" s="43" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E222" s="27" t="inlineStr">
+      <c r="E245" s="27" t="inlineStr">
         <is>
           <t>불가리아 장미수</t>
         </is>
       </c>
-      <c r="F222" s="27" t="inlineStr">
+      <c r="F245" s="27" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="16" customHeight="1">
-      <c r="A223" s="27" t="inlineStr">
+    <row r="246" ht="16" customHeight="1">
+      <c r="A246" s="27" t="inlineStr">
         <is>
           <t>슈퍼시카4</t>
         </is>
       </c>
-      <c r="B223" s="27" t="inlineStr">
+      <c r="B246" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C223" s="28" t="inlineStr">
+      <c r="C246" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D223" s="29" t="inlineStr">
+      <c r="D246" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E223" s="27" t="inlineStr">
+      <c r="E246" s="27" t="inlineStr">
         <is>
           <t>병풀의 핵심성분 4가지 복합물</t>
         </is>
       </c>
-      <c r="F223" s="27" t="inlineStr">
+      <c r="F246" s="27" t="inlineStr">
         <is>
           <t>병풀추출물</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="32" customHeight="1">
-      <c r="A224" s="27" t="inlineStr">
+    <row r="247" ht="32" customHeight="1">
+      <c r="A247" s="27" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B224" s="27" t="inlineStr">
+      <c r="B247" s="27" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C224" s="28" t="inlineStr">
+      <c r="C247" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D224" s="29" t="inlineStr">
+      <c r="D247" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E224" s="27" t="inlineStr">
+      <c r="E247" s="27" t="inlineStr">
         <is>
           <t>비타민B3, 식약처 기능성 고시원료</t>
         </is>
       </c>
-      <c r="F224" s="27" t="inlineStr">
+      <c r="F247" s="27" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="48" customHeight="1">
-      <c r="A225" s="27" t="inlineStr">
+    <row r="248" ht="48" customHeight="1">
+      <c r="A248" s="27" t="inlineStr">
         <is>
           <t>프로바이오틱스3</t>
         </is>
       </c>
-      <c r="B225" s="27" t="inlineStr">
+      <c r="B248" s="27" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C225" s="28" t="inlineStr">
+      <c r="C248" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D225" s="29" t="inlineStr">
+      <c r="D248" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E225" s="27" t="inlineStr">
+      <c r="E248" s="27" t="inlineStr">
         <is>
           <t>락토바실러스 람노서스, 비피다발효용해물, 락토코쿠스발효용해물 · 3가지 유산균 복합 성분</t>
         </is>
       </c>
-      <c r="F225" s="27" t="inlineStr">
+      <c r="F248" s="27" t="inlineStr">
         <is>
           <t>사카로, 비피다, 갈락토, 콤부차발효여과물..</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="16" customHeight="1">
-      <c r="A226" s="27" t="inlineStr">
+    <row r="249" ht="16" customHeight="1">
+      <c r="A249" s="27" t="inlineStr">
         <is>
           <t>덱스판테놀</t>
         </is>
       </c>
-      <c r="B226" s="27" t="inlineStr">
+      <c r="B249" s="27" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C226" s="28" t="inlineStr">
+      <c r="C249" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D226" s="29" t="inlineStr">
+      <c r="D249" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E226" s="27" t="inlineStr">
+      <c r="E249" s="27" t="inlineStr">
         <is>
           <t>비타민B5, 보습 재생</t>
         </is>
       </c>
-      <c r="F226" s="27" t="inlineStr">
+      <c r="F249" s="27" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="227" ht="64" customHeight="1">
-      <c r="A227" s="27" t="inlineStr">
+    <row r="250" ht="64" customHeight="1">
+      <c r="A250" s="27" t="inlineStr">
         <is>
           <t>트라넥삼산 (펩타이드)</t>
         </is>
       </c>
-      <c r="B227" s="27" t="inlineStr">
+      <c r="B250" s="27" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C227" s="28" t="inlineStr">
+      <c r="C250" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D227" s="29" t="inlineStr">
+      <c r="D250" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E227" s="27" t="inlineStr">
+      <c r="E250" s="27" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="F227" s="27" t="inlineStr">
+      <c r="F250" s="27" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="228" ht="16" customHeight="1">
-      <c r="A228" s="27" t="inlineStr">
+    <row r="251" ht="16" customHeight="1">
+      <c r="A251" s="27" t="inlineStr">
         <is>
           <t>글루타치온</t>
         </is>
       </c>
-      <c r="B228" s="27" t="inlineStr">
+      <c r="B251" s="27" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C228" s="28" t="inlineStr">
+      <c r="C251" s="28" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D228" s="29" t="inlineStr">
+      <c r="D251" s="29" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E228" s="27" t="inlineStr">
+      <c r="E251" s="27" t="inlineStr">
         <is>
           <t>미백효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="F228" s="27" t="inlineStr"/>
-    </row>
-    <row r="229" ht="64" customHeight="1">
-      <c r="A229" s="27" t="inlineStr">
+      <c r="F251" s="27" t="inlineStr"/>
+    </row>
+    <row r="252" ht="64" customHeight="1">
+      <c r="A252" s="27" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B229" s="27" t="inlineStr">
+      <c r="B252" s="27" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C229" s="28" t="inlineStr">
+      <c r="C252" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D229" s="41" t="inlineStr">
+      <c r="D252" s="44" t="inlineStr">
         <is>
           <t>방부</t>
         </is>
       </c>
-      <c r="E229" s="27" t="inlineStr">
+      <c r="E252" s="27" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="F229" s="27" t="inlineStr">
+      <c r="F252" s="27" t="inlineStr">
         <is>
           <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="230" ht="14" customHeight="1">
-      <c r="A230" s="33" t="inlineStr">
+    <row r="253" ht="14" customHeight="1">
+      <c r="A253" s="33" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 22 · 활성 76 · 방부 2</t>
         </is>
       </c>
-      <c r="B230" s="34" t="n"/>
-      <c r="C230" s="34" t="n"/>
-      <c r="D230" s="34" t="n"/>
-      <c r="E230" s="34" t="n"/>
-      <c r="F230" s="34" t="n"/>
-    </row>
-    <row r="231" ht="14" customHeight="1">
-      <c r="A231" s="35" t="inlineStr">
+      <c r="B253" s="34" t="n"/>
+      <c r="C253" s="34" t="n"/>
+      <c r="D253" s="34" t="n"/>
+      <c r="E253" s="34" t="n"/>
+      <c r="F253" s="34" t="n"/>
+    </row>
+    <row r="254" ht="14" customHeight="1">
+      <c r="A254" s="35" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B231" s="36" t="n"/>
-      <c r="C231" s="36" t="n"/>
-      <c r="D231" s="36" t="n"/>
-      <c r="E231" s="36" t="n"/>
-      <c r="F231" s="36" t="n"/>
-    </row>
-    <row r="232" ht="384" customHeight="1">
-      <c r="A232" s="37" t="inlineStr">
+      <c r="B254" s="36" t="n"/>
+      <c r="C254" s="36" t="n"/>
+      <c r="D254" s="36" t="n"/>
+      <c r="E254" s="36" t="n"/>
+      <c r="F254" s="36" t="n"/>
+    </row>
+    <row r="255" ht="384" customHeight="1">
+      <c r="A255" s="37" t="inlineStr">
         <is>
           <t>기미, 잡티 초기 진압에 TX 토닝 젤 (100g)
 난이도 : 하
@@ -7281,8 +7549,8 @@
         </is>
       </c>
     </row>
-    <row r="233" ht="80" customHeight="1">
-      <c r="A233" s="37" t="inlineStr">
+    <row r="256" ht="80" customHeight="1">
+      <c r="A256" s="37" t="inlineStr">
         <is>
           <t>현대약품 계열사 특허 성분)
 트라넥삼산과 나이아신아마이드를
@@ -7292,20 +7560,20 @@
         </is>
       </c>
     </row>
-    <row r="234" ht="14" customHeight="1">
-      <c r="A234" s="35" t="inlineStr">
+    <row r="257" ht="14" customHeight="1">
+      <c r="A257" s="35" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B234" s="36" t="n"/>
-      <c r="C234" s="36" t="n"/>
-      <c r="D234" s="36" t="n"/>
-      <c r="E234" s="36" t="n"/>
-      <c r="F234" s="36" t="n"/>
-    </row>
-    <row r="235" ht="64" customHeight="1">
-      <c r="A235" s="37" t="inlineStr">
+      <c r="B257" s="36" t="n"/>
+      <c r="C257" s="36" t="n"/>
+      <c r="D257" s="36" t="n"/>
+      <c r="E257" s="36" t="n"/>
+      <c r="F257" s="36" t="n"/>
+    </row>
+    <row r="258" ht="64" customHeight="1">
+      <c r="A258" s="37" t="inlineStr">
         <is>
           <t>TX 토닝 젤 토너 만들기
 1. 모든 재료를 계량합니다.
@@ -7314,142 +7582,190 @@
         </is>
       </c>
     </row>
-    <row r="236" ht="6" customHeight="1"/>
+    <row r="259" ht="14" customHeight="1">
+      <c r="A259" s="38" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B259" s="39" t="n"/>
+      <c r="C259" s="39" t="n"/>
+      <c r="D259" s="39" t="n"/>
+      <c r="E259" s="39" t="n"/>
+      <c r="F259" s="39" t="n"/>
+    </row>
+    <row r="260" ht="75" customHeight="1">
+      <c r="A260" s="40" t="inlineStr">
+        <is>
+          <t>· 베이스: 수상 22%(로즈워터 22%)가 제형의 뼈대·수분 공급.
+· 기능: 활성 합 76%(로즈플라워겔 50%, 글루타치온 10%, 슈퍼시카4 5%) → 이 제품이 노리는 효능 컨셉.
+· 마무리: 방부 2% 로 안정·사용감 보완.
+· 포인트: 활성 합이 높음 → 기능성(앰플·세럼급)에 집중한 처방.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="116">
+  <mergeCells count="142">
     <mergeCell ref="A205:F205"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A84:F84"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="A66:F66"/>
     <mergeCell ref="A118:F118"/>
     <mergeCell ref="A133:F133"/>
     <mergeCell ref="A189:F189"/>
-    <mergeCell ref="A158:F158"/>
+    <mergeCell ref="A238:F238"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A239:F239"/>
     <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A175:F175"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="A144:F144"/>
     <mergeCell ref="A159:F159"/>
+    <mergeCell ref="A224:F224"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A134:F134"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A161:F161"/>
-    <mergeCell ref="A202:F202"/>
+    <mergeCell ref="A258:F258"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A186:F186"/>
+    <mergeCell ref="A257:F257"/>
     <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A73:F73"/>
     <mergeCell ref="A51:F51"/>
     <mergeCell ref="A107:F107"/>
-    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A226:F226"/>
+    <mergeCell ref="A260:F260"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="A172:F172"/>
-    <mergeCell ref="A108:F108"/>
-    <mergeCell ref="A214:F214"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A228:F228"/>
+    <mergeCell ref="A237:F237"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A221:F221"/>
+    <mergeCell ref="A236:F236"/>
+    <mergeCell ref="A149:F149"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A163:F163"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A223:F223"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A204:F204"/>
-    <mergeCell ref="A213:F213"/>
+    <mergeCell ref="A85:F85"/>
     <mergeCell ref="A151:F151"/>
     <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A259:F259"/>
+    <mergeCell ref="A254:F254"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A206:F206"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="A215:F215"/>
+    <mergeCell ref="A240:F240"/>
+    <mergeCell ref="A122:F122"/>
     <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A190:F190"/>
     <mergeCell ref="A230:F230"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A232:F232"/>
+    <mergeCell ref="A176:F176"/>
+    <mergeCell ref="A114:F114"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A216:F216"/>
     <mergeCell ref="A98:F98"/>
     <mergeCell ref="A191:F191"/>
-    <mergeCell ref="A169:F169"/>
-    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A225:F225"/>
+    <mergeCell ref="A178:F178"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A162:F162"/>
+    <mergeCell ref="A227:F227"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="A177:F177"/>
-    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="A208:F208"/>
+    <mergeCell ref="A164:F164"/>
     <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A74:F74"/>
     <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="A145:F145"/>
     <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A210:F210"/>
     <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A203:F203"/>
+    <mergeCell ref="A129:F129"/>
+    <mergeCell ref="A242:F242"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A116:F116"/>
     <mergeCell ref="A131:F131"/>
-    <mergeCell ref="A171:F171"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A231:F231"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A253:F253"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A165:F165"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A115:F115"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A102:F102"/>
     <mergeCell ref="A117:F117"/>
-    <mergeCell ref="A173:F173"/>
-    <mergeCell ref="A111:F111"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A207:F207"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A256:F256"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A255:F255"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A233:F233"/>
+    <mergeCell ref="A89:F89"/>
     <mergeCell ref="A120:F120"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A192:F192"/>
+    <mergeCell ref="A104:F104"/>
     <mergeCell ref="A235:F235"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A219:F219"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A106:F106"/>
     <mergeCell ref="A234:F234"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="A96:F96"/>
     <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
-    <mergeCell ref="A209:F209"/>
-    <mergeCell ref="A170:F170"/>
     <mergeCell ref="A52:F52"/>
-    <mergeCell ref="A67:F67"/>
     <mergeCell ref="A130:F130"/>
     <mergeCell ref="A148:F148"/>
-    <mergeCell ref="A123:F123"/>
+    <mergeCell ref="A222:F222"/>
     <mergeCell ref="A132:F132"/>
     <mergeCell ref="A146:F146"/>
     <mergeCell ref="A119:F119"/>
     <mergeCell ref="A187:F187"/>
     <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A196:F196"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A209" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A219" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A151" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A196" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A230" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A242" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
